--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44210,6 +44210,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1907">
+      <c r="A1907" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1907" t="n">
+        <v>2057</v>
+      </c>
+      <c r="C1907" t="n">
+        <v>48</v>
+      </c>
+      <c r="D1907" t="n">
+        <v>47.0999984741211</v>
+      </c>
+      <c r="E1907" t="n">
+        <v>47.7000007629395</v>
+      </c>
+      <c r="F1907" t="n">
+        <v>47.7999992370605</v>
+      </c>
+      <c r="G1907" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44233,6 +44233,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1908">
+      <c r="A1908" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1908" t="n">
+        <v>6978</v>
+      </c>
+      <c r="C1908" t="n">
+        <v>47.0999984741211</v>
+      </c>
+      <c r="D1908" t="n">
+        <v>46.2000007629395</v>
+      </c>
+      <c r="E1908" t="n">
+        <v>47.0999984741211</v>
+      </c>
+      <c r="F1908" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1908" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44256,6 +44256,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1909">
+      <c r="A1909" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1909" t="n">
+        <v>2215</v>
+      </c>
+      <c r="C1909" t="n">
+        <v>46.7999992370605</v>
+      </c>
+      <c r="D1909" t="n">
+        <v>46</v>
+      </c>
+      <c r="E1909" t="n">
+        <v>46.4000015258789</v>
+      </c>
+      <c r="F1909" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G1909" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44279,6 +44279,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1910">
+      <c r="A1910" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1910" t="n">
+        <v>11155</v>
+      </c>
+      <c r="C1910" t="n">
+        <v>48.2999992370605</v>
+      </c>
+      <c r="D1910" t="n">
+        <v>46.5999984741211</v>
+      </c>
+      <c r="E1910" t="n">
+        <v>46.5999984741211</v>
+      </c>
+      <c r="F1910" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1910" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44120,22 +44120,22 @@
     </row>
     <row r="1903">
       <c r="A1903" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1903" t="n">
-        <v>9195</v>
+        <v>4001</v>
       </c>
       <c r="C1903" t="n">
-        <v>50</v>
+        <v>49.9000015258789</v>
       </c>
       <c r="D1903" t="n">
-        <v>48.7999992370605</v>
+        <v>48.9000015258789</v>
       </c>
       <c r="E1903" t="n">
-        <v>50</v>
+        <v>49.2999992370605</v>
       </c>
       <c r="F1903" t="n">
-        <v>50</v>
+        <v>49.7999992370605</v>
       </c>
       <c r="G1903" t="s">
         <v>7</v>
@@ -44143,22 +44143,22 @@
     </row>
     <row r="1904">
       <c r="A1904" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1904" t="n">
-        <v>6721</v>
+        <v>9195</v>
       </c>
       <c r="C1904" t="n">
-        <v>49.9000015258789</v>
+        <v>50</v>
       </c>
       <c r="D1904" t="n">
-        <v>48.5</v>
+        <v>48.7999992370605</v>
       </c>
       <c r="E1904" t="n">
-        <v>49.7999992370605</v>
+        <v>50</v>
       </c>
       <c r="F1904" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="G1904" t="s">
         <v>7</v>
@@ -44166,22 +44166,22 @@
     </row>
     <row r="1905">
       <c r="A1905" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1905" t="n">
-        <v>2102</v>
+        <v>6721</v>
       </c>
       <c r="C1905" t="n">
         <v>49.9000015258789</v>
       </c>
       <c r="D1905" t="n">
-        <v>47.9000015258789</v>
+        <v>48.5</v>
       </c>
       <c r="E1905" t="n">
+        <v>49.7999992370605</v>
+      </c>
+      <c r="F1905" t="n">
         <v>48.5</v>
-      </c>
-      <c r="F1905" t="n">
-        <v>49.2000007629395</v>
       </c>
       <c r="G1905" t="s">
         <v>7</v>
@@ -44189,22 +44189,22 @@
     </row>
     <row r="1906">
       <c r="A1906" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1906" t="n">
-        <v>2796</v>
+        <v>2102</v>
       </c>
       <c r="C1906" t="n">
-        <v>48.5</v>
+        <v>49.9000015258789</v>
       </c>
       <c r="D1906" t="n">
-        <v>47.7999992370605</v>
+        <v>47.9000015258789</v>
       </c>
       <c r="E1906" t="n">
         <v>48.5</v>
       </c>
       <c r="F1906" t="n">
-        <v>48.2000007629395</v>
+        <v>49.2000007629395</v>
       </c>
       <c r="G1906" t="s">
         <v>7</v>
@@ -44212,22 +44212,22 @@
     </row>
     <row r="1907">
       <c r="A1907" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1907" t="n">
-        <v>2057</v>
+        <v>2796</v>
       </c>
       <c r="C1907" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="D1907" t="n">
-        <v>47.0999984741211</v>
+        <v>47.7999992370605</v>
       </c>
       <c r="E1907" t="n">
-        <v>47.7000007629395</v>
+        <v>48.5</v>
       </c>
       <c r="F1907" t="n">
-        <v>47.7999992370605</v>
+        <v>48.2000007629395</v>
       </c>
       <c r="G1907" t="s">
         <v>7</v>
@@ -44235,22 +44235,22 @@
     </row>
     <row r="1908">
       <c r="A1908" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1908" t="n">
-        <v>6978</v>
+        <v>2057</v>
       </c>
       <c r="C1908" t="n">
+        <v>48</v>
+      </c>
+      <c r="D1908" t="n">
         <v>47.0999984741211</v>
       </c>
-      <c r="D1908" t="n">
-        <v>46.2000007629395</v>
-      </c>
       <c r="E1908" t="n">
-        <v>47.0999984741211</v>
+        <v>47.7000007629395</v>
       </c>
       <c r="F1908" t="n">
-        <v>47</v>
+        <v>47.7999992370605</v>
       </c>
       <c r="G1908" t="s">
         <v>7</v>
@@ -44258,22 +44258,22 @@
     </row>
     <row r="1909">
       <c r="A1909" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1909" t="n">
-        <v>2215</v>
+        <v>6978</v>
       </c>
       <c r="C1909" t="n">
-        <v>46.7999992370605</v>
+        <v>47.0999984741211</v>
       </c>
       <c r="D1909" t="n">
-        <v>46</v>
+        <v>46.2000007629395</v>
       </c>
       <c r="E1909" t="n">
-        <v>46.4000015258789</v>
+        <v>47.0999984741211</v>
       </c>
       <c r="F1909" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="G1909" t="s">
         <v>7</v>
@@ -44281,24 +44281,47 @@
     </row>
     <row r="1910">
       <c r="A1910" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1910" t="n">
-        <v>11155</v>
+        <v>2215</v>
       </c>
       <c r="C1910" t="n">
-        <v>48.2999992370605</v>
+        <v>46.7999992370605</v>
       </c>
       <c r="D1910" t="n">
-        <v>46.5999984741211</v>
+        <v>46</v>
       </c>
       <c r="E1910" t="n">
-        <v>46.5999984741211</v>
+        <v>46.4000015258789</v>
       </c>
       <c r="F1910" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G1910" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1911" t="n">
+        <v>3858</v>
+      </c>
+      <c r="C1911" t="n">
+        <v>47.5999984741211</v>
+      </c>
+      <c r="D1911" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="E1911" t="n">
+        <v>47.5999984741211</v>
+      </c>
+      <c r="F1911" t="n">
         <v>47</v>
       </c>
-      <c r="G1910" t="s">
+      <c r="G1911" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.28757858276367</v>
+        <v>9.28757762908936</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293647766113</v>
+        <v>9.88293552398682</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.76386547088623</v>
+        <v>9.76386642456055</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G6" t="n">
-        <v>9.78767871856689</v>
+        <v>9.78767967224121</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>9.67654705047607</v>
+        <v>9.67654609680176</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>9.60510349273682</v>
+        <v>9.60510444641113</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>9.23995208740234</v>
+        <v>9.23995113372803</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>9.39871406555176</v>
+        <v>9.39871311187744</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52572345733643</v>
+        <v>9.52572250366211</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44634246826172</v>
+        <v>9.4463415145874</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.91468715667725</v>
+        <v>9.91468906402588</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3195333480835</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>10.3195333480835</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2877807617188</v>
+        <v>10.2877788543701</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.3195333480835</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G21" t="n">
-        <v>10.208399772644</v>
+        <v>10.2083978652954</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>10.208399772644</v>
+        <v>10.2083978652954</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>10.3195333480835</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3989143371582</v>
+        <v>10.3989152908325</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>10.1925220489502</v>
+        <v>10.1925230026245</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>13.5</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7164392471313</v>
+        <v>10.716438293457</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7005615234375</v>
+        <v>10.7005605697632</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>10.5100479125977</v>
+        <v>10.5100469589233</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588312149048</v>
+        <v>11.0588321685791</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419792175293</v>
+        <v>11.1419811248779</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G38" t="n">
-        <v>11.1087198257446</v>
+        <v>11.1087188720703</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G40" t="n">
-        <v>10.7761240005493</v>
+        <v>10.776123046875</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>10.6264562606812</v>
+        <v>10.6264553070068</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G43" t="n">
-        <v>10.6763458251953</v>
+        <v>10.676344871521</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>10.6763458251953</v>
+        <v>10.676344871521</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>13</v>
       </c>
       <c r="G45" t="n">
-        <v>10.8093852996826</v>
+        <v>10.809383392334</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G46" t="n">
-        <v>10.609827041626</v>
+        <v>10.6098260879517</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G47" t="n">
-        <v>10.34375</v>
+        <v>10.3437490463257</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G50" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G54" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G55" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G56" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>10.2772283554077</v>
+        <v>10.277229309082</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G59" t="n">
-        <v>10.3271188735962</v>
+        <v>10.3271198272705</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485530853271</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.47899723052979</v>
+        <v>9.4789981842041</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G70" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G73" t="n">
-        <v>9.92800331115723</v>
+        <v>9.92800426483154</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>9.72844505310059</v>
+        <v>9.72844409942627</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>9.72844505310059</v>
+        <v>9.72844409942627</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G77" t="n">
-        <v>9.99452209472656</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G78" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G80" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G81" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>9.49562931060791</v>
+        <v>9.49562835693359</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G87" t="n">
-        <v>9.49562931060791</v>
+        <v>9.49562835693359</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>9.71181583404541</v>
+        <v>9.71181488037109</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>9.72844505310059</v>
+        <v>9.72844409942627</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>9.72844505310059</v>
+        <v>9.72844409942627</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.1441926956177</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G97" t="n">
-        <v>9.92800331115723</v>
+        <v>9.92800426483154</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G98" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G99" t="n">
-        <v>10.1275625228882</v>
+        <v>10.1275606155396</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12</v>
       </c>
       <c r="G101" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G107" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G108" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529609680176</v>
+        <v>9.64529514312744</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529609680176</v>
+        <v>9.64529514312744</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148262023926</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12</v>
       </c>
       <c r="G113" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12</v>
       </c>
       <c r="G114" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G116" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485530853271</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12</v>
       </c>
       <c r="G117" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G118" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G119" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G120" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>10.1441926956177</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G122" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12</v>
       </c>
       <c r="G123" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G125" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>9.99452209472656</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G128" t="n">
-        <v>10.2772283554077</v>
+        <v>10.277229309082</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>10.3936395645142</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G130" t="n">
-        <v>10.2772283554077</v>
+        <v>10.277229309082</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G133" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>10.1441926956177</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>10.1441926956177</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12</v>
       </c>
       <c r="G138" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G140" t="n">
-        <v>9.92800331115723</v>
+        <v>9.92800426483154</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148262023926</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148262023926</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G153" t="n">
-        <v>10.1275625228882</v>
+        <v>10.1275606155396</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G155" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G156" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G157" t="n">
-        <v>9.92800331115723</v>
+        <v>9.92800426483154</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G161" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3936395645142</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G170" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G171" t="n">
-        <v>10.2439699172974</v>
+        <v>10.243968963623</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>10.1441926956177</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G175" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126174926758</v>
+        <v>9.96126365661621</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12</v>
       </c>
       <c r="G178" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12</v>
       </c>
       <c r="G179" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G181" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G183" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G184" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12</v>
       </c>
       <c r="G186" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G188" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G190" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G191" t="n">
-        <v>9.99452209472656</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G192" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>9.99452209472656</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>9.99452209472656</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G195" t="n">
-        <v>9.99452209472656</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G196" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G198" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G201" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G205" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485530853271</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G209" t="n">
-        <v>10.2439699172974</v>
+        <v>10.243968963623</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>12</v>
       </c>
       <c r="G211" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="G213" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G215" t="n">
-        <v>9.99452209472656</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.1441926956177</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G217" t="n">
-        <v>10.34375</v>
+        <v>10.3437490463257</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2107105255127</v>
+        <v>10.2107095718384</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>12</v>
       </c>
       <c r="G221" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="G222" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>10.1940793991089</v>
+        <v>10.1940803527832</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12</v>
       </c>
       <c r="G226" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G228" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603782653809</v>
+        <v>10.3603792190552</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G234" t="n">
-        <v>9.99452209472656</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G235" t="n">
-        <v>9.99452209472656</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2606019973755</v>
+        <v>10.2606000900269</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G241" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G242" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>9.72844505310059</v>
+        <v>9.72844409942627</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G245" t="n">
-        <v>9.52888679504395</v>
+        <v>9.52888774871826</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.17966175079346</v>
+        <v>9.17966079711914</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41247844696045</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41247844696045</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.11314296722412</v>
+        <v>9.11314105987549</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G254" t="n">
-        <v>8.13198280334473</v>
+        <v>8.13198375701904</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>8.48120784759521</v>
+        <v>8.48120880126953</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.14861297607422</v>
+        <v>8.14861106872559</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.14861297607422</v>
+        <v>8.14861106872559</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568441390991</v>
+        <v>7.96568536758423</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10</v>
       </c>
       <c r="G262" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="G264" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.48120784759521</v>
+        <v>8.48120880126953</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>8.48120784759521</v>
+        <v>8.48120880126953</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640235900879</v>
+        <v>9.14640140533447</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640235900879</v>
+        <v>9.14640140533447</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>8.98010349273682</v>
+        <v>8.98010444641113</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>8.98010349273682</v>
+        <v>8.98010444641113</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>9.06325149536133</v>
+        <v>9.06325244903564</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211292266846</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G298" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10</v>
       </c>
       <c r="G305" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10</v>
       </c>
       <c r="G307" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10</v>
       </c>
       <c r="G308" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10</v>
       </c>
       <c r="G310" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G316" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10</v>
       </c>
       <c r="G319" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>10</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G360" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.75</v>
       </c>
       <c r="G370" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.75</v>
       </c>
       <c r="G373" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.75</v>
       </c>
       <c r="G374" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.204176902771</v>
+        <v>8.20417785644531</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="G383" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10</v>
       </c>
       <c r="G386" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>10</v>
       </c>
       <c r="G399" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>10</v>
       </c>
       <c r="G408" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>10</v>
       </c>
       <c r="G409" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848499298096</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211292266846</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211292266846</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211292266846</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>11.5</v>
       </c>
       <c r="G438" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G439" t="n">
-        <v>9.7934684753418</v>
+        <v>9.79346752166748</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>11.5</v>
       </c>
       <c r="G442" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>10.4807291030884</v>
+        <v>10.4807281494141</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>11.5</v>
       </c>
       <c r="G464" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>10.4807291030884</v>
+        <v>10.4807281494141</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>10.4807291030884</v>
+        <v>10.4807281494141</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.5</v>
       </c>
       <c r="G485" t="n">
-        <v>10.7384519577026</v>
+        <v>10.738450050354</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>10.7384519577026</v>
+        <v>10.738450050354</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.9102668762207</v>
+        <v>10.9102649688721</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.9102668762207</v>
+        <v>10.9102649688721</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>10.9102668762207</v>
+        <v>10.9102649688721</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>11.3398036956787</v>
+        <v>11.339804649353</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>11.5116205215454</v>
+        <v>11.5116195678711</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G498" t="n">
-        <v>11.3398036956787</v>
+        <v>11.339804649353</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.4257116317749</v>
+        <v>11.4257106781006</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>11.8552503585815</v>
+        <v>11.8552494049072</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>11.9411582946777</v>
+        <v>11.9411573410034</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>12.1129732131958</v>
+        <v>12.1129751205444</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>12.62841796875</v>
+        <v>12.6284189224243</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>15</v>
       </c>
       <c r="G506" t="n">
-        <v>12.8861408233643</v>
+        <v>12.8861417770386</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>12.7143268585205</v>
+        <v>12.7143259048462</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G508" t="n">
-        <v>12.7143268585205</v>
+        <v>12.7143259048462</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720478057861</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720478057861</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720478057861</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.8311252593994</v>
+        <v>13.8311243057251</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>16</v>
       </c>
       <c r="G517" t="n">
-        <v>13.7452182769775</v>
+        <v>13.7452173233032</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>16.5</v>
       </c>
       <c r="G519" t="n">
-        <v>14.1747550964355</v>
+        <v>14.1747541427612</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>16.5</v>
       </c>
       <c r="G522" t="n">
-        <v>14.1747550964355</v>
+        <v>14.1747541427612</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>13.8311252593994</v>
+        <v>13.8311243057251</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>14.0029401779175</v>
+        <v>14.0029392242432</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>14.3465709686279</v>
+        <v>14.3465719223022</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042947769165</v>
+        <v>14.6042919158936</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>18</v>
       </c>
       <c r="G529" t="n">
-        <v>15.4633722305298</v>
+        <v>15.4633674621582</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>15.2915525436401</v>
+        <v>15.2915544509888</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>18</v>
       </c>
       <c r="G531" t="n">
-        <v>15.4633722305298</v>
+        <v>15.4633674621582</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056474685669</v>
+        <v>15.2056493759155</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>18</v>
       </c>
       <c r="G534" t="n">
-        <v>15.4633722305298</v>
+        <v>15.4633674621582</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="n">
-        <v>15.4633722305298</v>
+        <v>15.4633674621582</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.5492782592773</v>
+        <v>15.5492792129517</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>15.7259721755981</v>
+        <v>15.7259731292725</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376256942749</v>
+        <v>15.6376276016235</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>15.7259721755981</v>
+        <v>15.7259731292725</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>17</v>
       </c>
       <c r="G540" t="n">
-        <v>15.0191898345947</v>
+        <v>15.0191869735718</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>15.7259721755981</v>
+        <v>15.7259731292725</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>16.0793685913086</v>
+        <v>16.07936668396</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>18</v>
       </c>
       <c r="G546" t="n">
-        <v>15.9026718139648</v>
+        <v>15.9026679992676</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>18.5</v>
       </c>
       <c r="G547" t="n">
-        <v>16.344409942627</v>
+        <v>16.3444080352783</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>16.4327583312988</v>
+        <v>16.4327602386475</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>16.1677150726318</v>
+        <v>16.1677131652832</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>18.5</v>
       </c>
       <c r="G550" t="n">
-        <v>16.344409942627</v>
+        <v>16.3444080352783</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>16.2560634613037</v>
+        <v>16.2560615539551</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>16.2560634613037</v>
+        <v>16.2560615539551</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>16.2560634613037</v>
+        <v>16.2560615539551</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.5</v>
       </c>
       <c r="G554" t="n">
-        <v>16.344409942627</v>
+        <v>16.3444080352783</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>16.2560634613037</v>
+        <v>16.2560615539551</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>16.4327583312988</v>
+        <v>16.4327602386475</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>18.5</v>
       </c>
       <c r="G557" t="n">
-        <v>16.344409942627</v>
+        <v>16.3444080352783</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>18.1997222900391</v>
+        <v>18.1997241973877</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>19.0832042694092</v>
+        <v>19.0832061767578</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>22</v>
       </c>
       <c r="G565" t="n">
-        <v>19.4365997314453</v>
+        <v>19.436595916748</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>21</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>17.4929332733154</v>
+        <v>17.4929351806641</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>20</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6696319580078</v>
+        <v>17.6696300506592</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278938293457</v>
+        <v>17.2278900146484</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>19</v>
       </c>
       <c r="G576" t="n">
-        <v>16.7861518859863</v>
+        <v>16.7861499786377</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.1395454406738</v>
+        <v>17.1395435333252</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>17.1395454406738</v>
+        <v>17.1395435333252</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>17.051197052002</v>
+        <v>17.0511951446533</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>19</v>
       </c>
       <c r="G581" t="n">
-        <v>16.7861518859863</v>
+        <v>16.7861499786377</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>17.051197052002</v>
+        <v>17.0511951446533</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>17.4929332733154</v>
+        <v>17.4929351806641</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>17.6696319580078</v>
+        <v>17.6696300506592</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>17.4045886993408</v>
+        <v>17.4045906066895</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>21</v>
       </c>
       <c r="G586" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>21</v>
       </c>
       <c r="G589" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>21</v>
       </c>
       <c r="G590" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>21</v>
       </c>
       <c r="G592" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>18.9065074920654</v>
+        <v>18.9065055847168</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>22</v>
       </c>
       <c r="G601" t="n">
-        <v>19.4365997314453</v>
+        <v>19.436595916748</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>20.143383026123</v>
+        <v>20.1433811187744</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>23</v>
       </c>
       <c r="G603" t="n">
-        <v>20.3200798034668</v>
+        <v>20.3200778961182</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>21.7336502075195</v>
+        <v>21.7336483001709</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>21.7336502075195</v>
+        <v>21.7336483001709</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G616" t="n">
-        <v>24.560791015625</v>
+        <v>24.5607891082764</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472206115723</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>24.560791015625</v>
+        <v>24.5607891082764</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>27.9180202484131</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>28.4481105804443</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>35</v>
       </c>
       <c r="G633" t="n">
-        <v>30.9218578338623</v>
+        <v>30.921854019165</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082874298096</v>
+        <v>29.5082893371582</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>27.9180202484131</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>28.4481105804443</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>27.9180202484131</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>27.9180202484131</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>27.5646286010742</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>27.5646286010742</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811447143555</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33</v>
       </c>
       <c r="G663" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548919677734</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G664" t="n">
-        <v>29.6849842071533</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>34</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0383796691895</v>
+        <v>30.0383739471436</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>29.6849842071533</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>28.978199005127</v>
+        <v>28.9781970977783</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G672" t="n">
-        <v>29.6849842071533</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>28.978199005127</v>
+        <v>28.9781970977783</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>33</v>
       </c>
       <c r="G674" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548919677734</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33</v>
       </c>
       <c r="G677" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548919677734</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>28.6248054504395</v>
+        <v>28.6248073577881</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>27.9180202484131</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>28.6248054504395</v>
+        <v>28.6248073577881</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>28.4481105804443</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>28.8015022277832</v>
+        <v>28.8015003204346</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>31</v>
       </c>
       <c r="G689" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>25.7976665496826</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811447143555</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G699" t="n">
-        <v>28.6248054504395</v>
+        <v>28.6248073577881</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>27.5646286010742</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>31</v>
       </c>
       <c r="G703" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>31</v>
       </c>
       <c r="G715" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>31</v>
       </c>
       <c r="G716" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>24.560791015625</v>
+        <v>24.5607891082764</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>24.560791015625</v>
+        <v>24.5607891082764</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>24.560791015625</v>
+        <v>24.5607891082764</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>28</v>
       </c>
       <c r="G741" t="n">
-        <v>24.7374877929688</v>
+        <v>24.7374839782715</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>29</v>
       </c>
       <c r="G743" t="n">
-        <v>25.6209697723389</v>
+        <v>25.6209678649902</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>25.7976665496826</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>24.560791015625</v>
+        <v>24.5607891082764</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>22.6171321868896</v>
+        <v>22.617130279541</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>22.6171321868896</v>
+        <v>22.617130279541</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>25</v>
       </c>
       <c r="G755" t="n">
-        <v>22.0870418548584</v>
+        <v>22.0870399475098</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>21.7336502075195</v>
+        <v>21.7336483001709</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>21.5569534301758</v>
+        <v>21.5569515228271</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>24</v>
       </c>
       <c r="G758" t="n">
-        <v>21.2035598754883</v>
+        <v>21.2035579681396</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>25</v>
       </c>
       <c r="G760" t="n">
-        <v>22.0870418548584</v>
+        <v>22.0870399475098</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>24.560791015625</v>
+        <v>24.5607891082764</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>28</v>
       </c>
       <c r="G764" t="n">
-        <v>24.7374877929688</v>
+        <v>24.7374839782715</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>28</v>
       </c>
       <c r="G765" t="n">
-        <v>24.7374877929688</v>
+        <v>24.7374839782715</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811447143555</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>27.5646286010742</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811447143555</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>25.7976665496826</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>29</v>
       </c>
       <c r="G780" t="n">
-        <v>25.6209697723389</v>
+        <v>25.6209678649902</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>25.532621383667</v>
+        <v>25.5326194763184</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G784" t="n">
-        <v>23.9423542022705</v>
+        <v>23.9423522949219</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>24.6491394042969</v>
+        <v>24.6491374969482</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G787" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472206115723</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>22.7054786682129</v>
+        <v>22.7054805755615</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>28</v>
       </c>
       <c r="G805" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>23.7404136657715</v>
+        <v>23.7404155731201</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>24.100118637085</v>
+        <v>24.1001167297363</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>23.7404136657715</v>
+        <v>23.7404155731201</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>26</v>
       </c>
       <c r="G829" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>26</v>
       </c>
       <c r="G832" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>26</v>
       </c>
       <c r="G833" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>26</v>
       </c>
       <c r="G834" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G855" t="n">
-        <v>20.413158416748</v>
+        <v>20.4131603240967</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>22</v>
       </c>
       <c r="G856" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>22</v>
       </c>
       <c r="G857" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>19.5139026641846</v>
+        <v>19.5139007568359</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>19.693754196167</v>
+        <v>19.6937522888184</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>21.5</v>
       </c>
       <c r="G864" t="n">
-        <v>19.3340492248535</v>
+        <v>19.3340511322021</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.3915271759033</v>
+        <v>22.3915252685547</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>20.5030860900879</v>
+        <v>20.5030841827393</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>23</v>
       </c>
       <c r="G878" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>20.5030860900879</v>
+        <v>20.5030841827393</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>22</v>
       </c>
       <c r="G882" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>22</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>22</v>
       </c>
       <c r="G886" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>22</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>22</v>
       </c>
       <c r="G888" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>22</v>
       </c>
       <c r="G889" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>23</v>
       </c>
       <c r="G890" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>23.5</v>
       </c>
       <c r="G891" t="n">
-        <v>21.1325645446777</v>
+        <v>21.132568359375</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G892" t="n">
-        <v>21.8519725799561</v>
+        <v>21.8519706726074</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>26</v>
       </c>
       <c r="G894" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>26</v>
       </c>
       <c r="G895" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>26</v>
       </c>
       <c r="G897" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.3915271759033</v>
+        <v>22.3915252685547</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.3915271759033</v>
+        <v>22.3915252685547</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>26</v>
       </c>
       <c r="G931" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>28.5</v>
       </c>
       <c r="G947" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288585662842</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>30.5</v>
       </c>
       <c r="G956" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>30.5</v>
       </c>
       <c r="G961" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>28.5</v>
       </c>
       <c r="G971" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288585662842</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>28</v>
       </c>
       <c r="G982" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>24.819522857666</v>
+        <v>24.8195247650146</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>24.9993762969971</v>
+        <v>24.9993743896484</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>24.9993762969971</v>
+        <v>24.9993743896484</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>28</v>
       </c>
       <c r="G990" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>24.9993762969971</v>
+        <v>24.9993743896484</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>28</v>
       </c>
       <c r="G996" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>28.5</v>
       </c>
       <c r="G999" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288585662842</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>28</v>
       </c>
       <c r="G1000" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>28</v>
       </c>
       <c r="G1005" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>24.819522857666</v>
+        <v>24.8195247650146</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>24.9993762969971</v>
+        <v>24.9993743896484</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>27.5172996520996</v>
+        <v>27.517297744751</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>34</v>
       </c>
       <c r="G1022" t="n">
-        <v>30.5747776031494</v>
+        <v>30.5747756958008</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>28.2367038726807</v>
+        <v>28.2367057800293</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>29.4057426452637</v>
+        <v>29.405740737915</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>28.956111907959</v>
+        <v>28.9561138153076</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1038" t="n">
-        <v>30.8445510864258</v>
+        <v>30.8445529937744</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.8337364196777</v>
+        <v>31.833740234375</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>30.9344806671143</v>
+        <v>30.9344825744629</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150707244873</v>
+        <v>30.2150688171387</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1057" t="n">
-        <v>29.5855922698975</v>
+        <v>29.5855941772461</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1058" t="n">
-        <v>29.4057426452637</v>
+        <v>29.405740737915</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1067" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1068" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>27.9832134246826</v>
+        <v>27.9832153320312</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1102" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>30.1003665924072</v>
+        <v>30.1003646850586</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1118" t="n">
-        <v>30.1003665924072</v>
+        <v>30.1003646850586</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1146" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1154" t="n">
-        <v>28.1673145294189</v>
+        <v>28.1673126220703</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1159" t="n">
-        <v>27.3388633728027</v>
+        <v>27.3388652801514</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.8786163330078</v>
+        <v>26.8786144256592</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>28.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>28.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.1045608520508</v>
+        <v>23.1045627593994</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966114044189</v>
+        <v>23.1966133117676</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>28.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1199" t="n">
-        <v>25.2217140197754</v>
+        <v>25.2217121124268</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>26.1422119140625</v>
+        <v>26.1422138214111</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>28.5</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1213" t="n">
-        <v>27.3388633728027</v>
+        <v>27.3388652801514</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>26.8786163330078</v>
+        <v>26.8786144256592</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>28.5</v>
       </c>
       <c r="G1220" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.3388633728027</v>
+        <v>27.3388652801514</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>29.5</v>
       </c>
       <c r="G1226" t="n">
-        <v>27.1547660827637</v>
+        <v>27.154764175415</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>28</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.7740154266357</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>28.5</v>
       </c>
       <c r="G1231" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>28</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.7740154266357</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2217140197754</v>
+        <v>25.2217121124268</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>25.1296615600586</v>
+        <v>25.1296634674072</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>24.0250625610352</v>
+        <v>24.0250606536865</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1273" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1274" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>30.5606136322021</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>30.5606136322021</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>31.1129131317139</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1287" t="n">
-        <v>31.1129131317139</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1290" t="n">
-        <v>31.1129131317139</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526622772217</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526622772217</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.1129131317139</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>31.1129131317139</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>30.5606136322021</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>31.1129131317139</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>30.5606136322021</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526622772217</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>30.1003665924072</v>
+        <v>30.1003646850586</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -50110,6 +50110,32 @@
         <v>46.7999992370605</v>
       </c>
       <c r="H1913" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1914" t="n">
+        <v>14508</v>
+      </c>
+      <c r="C1914" t="n">
+        <v>49.2000007629395</v>
+      </c>
+      <c r="D1914" t="n">
+        <v>46.0999984741211</v>
+      </c>
+      <c r="E1914" t="n">
+        <v>46.0999984741211</v>
+      </c>
+      <c r="F1914" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="G1914" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H1914" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.28757762908936</v>
+        <v>9.28757858276367</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293552398682</v>
+        <v>9.88293647766113</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.76386642456055</v>
+        <v>9.76386547088623</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>9.60510444641113</v>
+        <v>9.60510349273682</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>9.23995113372803</v>
+        <v>9.23995208740234</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2877788543701</v>
+        <v>10.2877807617188</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G21" t="n">
-        <v>10.2083978652954</v>
+        <v>10.2083988189697</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2719039916992</v>
+        <v>10.2719030380249</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>10.2083978652954</v>
+        <v>10.2083988189697</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5259227752686</v>
+        <v>10.5259237289429</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3989152908325</v>
+        <v>10.3989143371582</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G28" t="n">
-        <v>10.2560272216797</v>
+        <v>10.256028175354</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>10.5100469589233</v>
+        <v>10.510046005249</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G38" t="n">
-        <v>11.1087188720703</v>
+        <v>11.1087207794189</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G40" t="n">
-        <v>10.776123046875</v>
+        <v>10.7761249542236</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>10.6264553070068</v>
+        <v>10.6264562606812</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>13</v>
       </c>
       <c r="G45" t="n">
-        <v>10.809383392334</v>
+        <v>10.8093843460083</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G50" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G56" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.4789981842041</v>
+        <v>9.47899723052979</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474487304688</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474487304688</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G73" t="n">
-        <v>9.92800426483154</v>
+        <v>9.92800331115723</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>9.72844409942627</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>9.72844409942627</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G77" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474487304688</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>9.77833557128906</v>
+        <v>9.77833461761475</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>9.67855739593506</v>
+        <v>9.67855834960938</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G85" t="n">
-        <v>9.67855739593506</v>
+        <v>9.67855834960938</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>9.49562835693359</v>
+        <v>9.49562740325928</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G87" t="n">
-        <v>9.49562835693359</v>
+        <v>9.49562740325928</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.5</v>
       </c>
       <c r="G88" t="n">
-        <v>9.56214618682861</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>9.71181488037109</v>
+        <v>9.71181583404541</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.56214618682861</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>9.72844409942627</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>9.72844409942627</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474487304688</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474487304688</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G97" t="n">
-        <v>9.92800426483154</v>
+        <v>9.92800331115723</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G99" t="n">
-        <v>10.1275606155396</v>
+        <v>10.1275615692139</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.77833557128906</v>
+        <v>9.77833461761475</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>9.77833557128906</v>
+        <v>9.77833461761475</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G107" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G108" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529514312744</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529514312744</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148262023926</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G119" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G122" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G125" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474487304688</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>10.3936386108398</v>
+        <v>10.3936376571655</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G131" t="n">
-        <v>10.4435291290283</v>
+        <v>10.443528175354</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>10.4601573944092</v>
+        <v>10.4601583480835</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G133" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0277814865112</v>
+        <v>10.0277824401855</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G140" t="n">
-        <v>9.92800426483154</v>
+        <v>9.92800331115723</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148262023926</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148262023926</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G147" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G153" t="n">
-        <v>10.1275606155396</v>
+        <v>10.1275615692139</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G157" t="n">
-        <v>9.92800426483154</v>
+        <v>9.92800331115723</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474487304688</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474487304688</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G164" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3936386108398</v>
+        <v>10.3936376571655</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G173" t="n">
-        <v>10.0277814865112</v>
+        <v>10.0277824401855</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G175" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126365661621</v>
+        <v>9.96126270294189</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G181" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474487304688</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G190" t="n">
-        <v>10.2938594818115</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G191" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G192" t="n">
-        <v>10.2938594818115</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G195" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G196" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G198" t="n">
-        <v>10.2938594818115</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G200" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G215" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2107095718384</v>
+        <v>10.2107105255127</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603792190552</v>
+        <v>10.3603782653809</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G231" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G234" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G235" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G236" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G241" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G242" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>9.72844409942627</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>9.41247844696045</v>
+        <v>9.41247940063477</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>9.41247844696045</v>
+        <v>9.41247940063477</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>11.5</v>
       </c>
       <c r="G249" t="n">
-        <v>9.56214618682861</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.11314105987549</v>
+        <v>9.11314296722412</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>8.44794940948486</v>
+        <v>8.44794845581055</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G254" t="n">
-        <v>8.13198375701904</v>
+        <v>8.13198280334473</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G256" t="n">
-        <v>7.42521572113037</v>
+        <v>7.42521524429321</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.14861106872559</v>
+        <v>8.1486120223999</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.14861106872559</v>
+        <v>8.1486120223999</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>8.03220272064209</v>
+        <v>8.03220367431641</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>8.03220272064209</v>
+        <v>8.03220367431641</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G271" t="n">
-        <v>8.3980598449707</v>
+        <v>8.39805889129639</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640045166016</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640045166016</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>8.98010444641113</v>
+        <v>8.98010349273682</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>8.98010444641113</v>
+        <v>8.98010349273682</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>9.36392879486084</v>
+        <v>9.36392974853516</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>9.1062068939209</v>
+        <v>9.10620594024658</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10</v>
       </c>
       <c r="G305" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10</v>
       </c>
       <c r="G307" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10</v>
       </c>
       <c r="G308" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10</v>
       </c>
       <c r="G310" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G311" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10</v>
       </c>
       <c r="G319" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G321" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G322" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G323" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G352" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G353" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>10</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G360" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.75</v>
       </c>
       <c r="G370" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.75</v>
       </c>
       <c r="G373" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.75</v>
       </c>
       <c r="G374" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.20417785644531</v>
+        <v>8.204176902771</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="G383" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10</v>
       </c>
       <c r="G386" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>10</v>
       </c>
       <c r="G399" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>10</v>
       </c>
       <c r="G408" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>10</v>
       </c>
       <c r="G409" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>8.54780673980713</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>8.93439102172852</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>9.1062068939209</v>
+        <v>9.10620594024658</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>9.36392879486084</v>
+        <v>9.36392974853516</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.70755958557129</v>
+        <v>9.70756053924561</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>12</v>
       </c>
       <c r="G445" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12</v>
       </c>
       <c r="G446" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>12</v>
       </c>
       <c r="G447" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807291030884</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>12</v>
       </c>
       <c r="G449" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>10.3948221206665</v>
+        <v>10.3948211669922</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12</v>
       </c>
       <c r="G452" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G457" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>9.70755958557129</v>
+        <v>9.70756053924561</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G460" t="n">
-        <v>9.70755958557129</v>
+        <v>9.70756053924561</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>9.6216516494751</v>
+        <v>9.62165260314941</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G466" t="n">
-        <v>9.70755958557129</v>
+        <v>9.70756053924561</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807291030884</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>10.5666360855103</v>
+        <v>10.5666370391846</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>10.5666360855103</v>
+        <v>10.5666370391846</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>12</v>
       </c>
       <c r="G472" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G473" t="n">
-        <v>10.3948221206665</v>
+        <v>10.3948211669922</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12</v>
       </c>
       <c r="G474" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G477" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0511894226074</v>
+        <v>10.0511903762817</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0511894226074</v>
+        <v>10.0511903762817</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807291030884</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G484" t="n">
-        <v>10.6525430679321</v>
+        <v>10.6525440216064</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.5</v>
       </c>
       <c r="G485" t="n">
-        <v>10.738450050354</v>
+        <v>10.7384510040283</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>10.738450050354</v>
+        <v>10.7384510040283</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.9102649688721</v>
+        <v>10.9102659225464</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.9102649688721</v>
+        <v>10.9102659225464</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>10.9102649688721</v>
+        <v>10.9102659225464</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243579864502</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243579864502</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243579864502</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.4257106781006</v>
+        <v>11.4257125854492</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>11.8552494049072</v>
+        <v>11.8552513122559</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>12.1129751205444</v>
+        <v>12.1129741668701</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>12.9720478057861</v>
+        <v>12.9720497131348</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>12.9720478057861</v>
+        <v>12.9720497131348</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9720478057861</v>
+        <v>12.9720497131348</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.8311243057251</v>
+        <v>13.8311252593994</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>13.487494468689</v>
+        <v>13.4874954223633</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>16.5</v>
       </c>
       <c r="G519" t="n">
-        <v>14.1747541427612</v>
+        <v>14.1747560501099</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>14.2606630325317</v>
+        <v>14.2606639862061</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>16.5</v>
       </c>
       <c r="G522" t="n">
-        <v>14.1747541427612</v>
+        <v>14.1747560501099</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>13.8311243057251</v>
+        <v>13.8311252593994</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>14.2606630325317</v>
+        <v>14.2606639862061</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>14.3465719223022</v>
+        <v>14.3465709686279</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042919158936</v>
+        <v>14.6042928695679</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>18</v>
       </c>
       <c r="G529" t="n">
-        <v>15.4633674621582</v>
+        <v>15.4633712768555</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>18</v>
       </c>
       <c r="G531" t="n">
-        <v>15.4633674621582</v>
+        <v>15.4633712768555</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056493759155</v>
+        <v>15.2056465148926</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>15.1197385787964</v>
+        <v>15.1197414398193</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>18</v>
       </c>
       <c r="G534" t="n">
-        <v>15.4633674621582</v>
+        <v>15.4633712768555</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="n">
-        <v>15.4633674621582</v>
+        <v>15.4633712768555</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.5492792129517</v>
+        <v>15.5492782592773</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>15.7259731292725</v>
+        <v>15.7259740829468</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376276016235</v>
+        <v>15.6376247406006</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>15.7259731292725</v>
+        <v>15.7259740829468</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>17</v>
       </c>
       <c r="G540" t="n">
-        <v>15.0191869735718</v>
+        <v>15.0191879272461</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G541" t="n">
-        <v>15.1958856582642</v>
+        <v>15.1958847045898</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>15.7259731292725</v>
+        <v>15.7259740829468</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.5492763519287</v>
+        <v>15.5492792129517</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>15.81432056427</v>
+        <v>15.8143224716187</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>16.07936668396</v>
+        <v>16.0793647766113</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>18</v>
       </c>
       <c r="G546" t="n">
-        <v>15.9026679992676</v>
+        <v>15.9026718139648</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>18.5</v>
       </c>
       <c r="G547" t="n">
-        <v>16.3444080352783</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>16.1677131652832</v>
+        <v>16.1677150726318</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>18.5</v>
       </c>
       <c r="G550" t="n">
-        <v>16.3444080352783</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.5</v>
       </c>
       <c r="G554" t="n">
-        <v>16.3444080352783</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>18.5</v>
       </c>
       <c r="G557" t="n">
-        <v>16.3444080352783</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>16.9628505706787</v>
+        <v>16.9628486633301</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>19.9666843414307</v>
+        <v>19.9666862487793</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>19.9666843414307</v>
+        <v>19.9666862487793</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G567" t="n">
-        <v>18.7298126220703</v>
+        <v>18.7298107147217</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>17.4929351806641</v>
+        <v>17.4929370880127</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>18.3764171600342</v>
+        <v>18.3764190673828</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>18.3764171600342</v>
+        <v>18.3764190673828</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>20</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6696300506592</v>
+        <v>17.6696338653564</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278900146484</v>
+        <v>17.2278919219971</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>19</v>
       </c>
       <c r="G576" t="n">
-        <v>16.7861499786377</v>
+        <v>16.7861518859863</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>19</v>
       </c>
       <c r="G581" t="n">
-        <v>16.7861499786377</v>
+        <v>16.7861518859863</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>17.4929351806641</v>
+        <v>17.4929370880127</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>17.6696300506592</v>
+        <v>17.6696338653564</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>18.7298126220703</v>
+        <v>18.7298107147217</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>18.3764171600342</v>
+        <v>18.3764190673828</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>18.3764171600342</v>
+        <v>18.3764190673828</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>18.7298126220703</v>
+        <v>18.7298107147217</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938289642334</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>20.673469543457</v>
+        <v>20.6734714508057</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>19.2598991394043</v>
+        <v>19.2599010467529</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G599" t="n">
-        <v>19.2598991394043</v>
+        <v>19.2599010467529</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>19.2598991394043</v>
+        <v>19.2599010467529</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>22.2637386322021</v>
+        <v>22.2637367248535</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938289642334</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938289642334</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>23.5006103515625</v>
+        <v>23.5006141662598</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="G617" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540019989014</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>23.1472206115723</v>
+        <v>23.1472187042236</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="G622" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540019989014</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180221557617</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>28.4481086730957</v>
+        <v>28.4481105804443</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>29.8616790771484</v>
+        <v>29.8616809844971</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>35</v>
       </c>
       <c r="G633" t="n">
-        <v>30.921854019165</v>
+        <v>30.9218597412109</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0985527038574</v>
+        <v>31.0985584259033</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.5684642791748</v>
+        <v>30.5684661865234</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>30.5684642791748</v>
+        <v>30.5684661865234</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G638" t="n">
-        <v>30.3917713165283</v>
+        <v>30.3917694091797</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082893371582</v>
+        <v>29.5082874298096</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180221557617</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>28.4481086730957</v>
+        <v>28.4481105804443</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180221557617</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180221557617</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>25.2675743103027</v>
+        <v>25.267578125</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112331390381</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>27.0345363616943</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112331390381</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112331390381</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>27.0345363616943</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>26.6811447143555</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33</v>
       </c>
       <c r="G663" t="n">
-        <v>29.1548919677734</v>
+        <v>29.1548957824707</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G665" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>34</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0383739471436</v>
+        <v>30.0383758544922</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>29.8616790771484</v>
+        <v>29.8616809844971</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>33</v>
       </c>
       <c r="G674" t="n">
-        <v>29.1548919677734</v>
+        <v>29.1548957824707</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>29.8616790771484</v>
+        <v>29.8616809844971</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33</v>
       </c>
       <c r="G677" t="n">
-        <v>29.1548919677734</v>
+        <v>29.1548957824707</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180221557617</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>28.4481086730957</v>
+        <v>28.4481105804443</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>25.2675743103027</v>
+        <v>25.267578125</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>26.6811447143555</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.0345363616943</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112331390381</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>27.0345363616943</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G717" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112331390381</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112331390381</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>24.9141864776611</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840961456299</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>24.9141864776611</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840961456299</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840961456299</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>25.2675743103027</v>
+        <v>25.267578125</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>27</v>
       </c>
       <c r="G749" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540019989014</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>22.617130279541</v>
+        <v>22.6171321868896</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>22.617130279541</v>
+        <v>22.6171321868896</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>25</v>
       </c>
       <c r="G755" t="n">
-        <v>22.0870399475098</v>
+        <v>22.0870418548584</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>21.5569515228271</v>
+        <v>21.5569534301758</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>24</v>
       </c>
       <c r="G758" t="n">
-        <v>21.2035579681396</v>
+        <v>21.2035598754883</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>20.8501644134521</v>
+        <v>20.8501682281494</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>25</v>
       </c>
       <c r="G760" t="n">
-        <v>22.0870399475098</v>
+        <v>22.0870418548584</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540019989014</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>24.9141864776611</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840961456299</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>26.6811447143555</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>27.0345363616943</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>27.0345363616943</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G775" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112331390381</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>26.6811447143555</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>26.3277530670166</v>
+        <v>26.327751159668</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840961456299</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840961456299</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G784" t="n">
-        <v>23.9423522949219</v>
+        <v>23.9423542022705</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>24.6491374969482</v>
+        <v>24.6491394042969</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>27</v>
       </c>
       <c r="G786" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540019989014</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G787" t="n">
-        <v>23.1472206115723</v>
+        <v>23.1472187042236</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>23.5006103515625</v>
+        <v>23.5006141662598</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>23.5006103515625</v>
+        <v>23.5006141662598</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>23.5006103515625</v>
+        <v>23.5006141662598</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>22.7054805755615</v>
+        <v>22.7054786682129</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840961456299</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>28.5</v>
       </c>
       <c r="G796" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>28.5</v>
       </c>
       <c r="G797" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>25.8986339569092</v>
+        <v>25.8986320495605</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>24.1900424957275</v>
+        <v>24.1900444030762</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>27</v>
       </c>
       <c r="G808" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>27</v>
       </c>
       <c r="G810" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>27</v>
       </c>
       <c r="G811" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>23.7404155731201</v>
+        <v>23.7404136657715</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>23.7404155731201</v>
+        <v>23.7404136657715</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>26.5</v>
       </c>
       <c r="G823" t="n">
-        <v>23.8303394317627</v>
+        <v>23.8303413391113</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>25.5</v>
       </c>
       <c r="G839" t="n">
-        <v>22.9310817718506</v>
+        <v>22.9310836791992</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>25.5</v>
       </c>
       <c r="G840" t="n">
-        <v>22.9310817718506</v>
+        <v>22.9310836791992</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>24.5</v>
       </c>
       <c r="G843" t="n">
-        <v>22.0318241119385</v>
+        <v>22.0318260192871</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>21.3124160766602</v>
+        <v>21.3124198913574</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>25</v>
       </c>
       <c r="G849" t="n">
-        <v>22.4814529418945</v>
+        <v>22.4814548492432</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>24.5</v>
       </c>
       <c r="G850" t="n">
-        <v>22.0318241119385</v>
+        <v>22.0318260192871</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>21.40234375</v>
+        <v>21.4023418426514</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038284301758</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>19.4239749908447</v>
+        <v>19.4239768981934</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038284301758</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>21.5</v>
       </c>
       <c r="G864" t="n">
-        <v>19.3340511322021</v>
+        <v>19.3340492248535</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038284301758</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>25</v>
       </c>
       <c r="G869" t="n">
-        <v>22.4814529418945</v>
+        <v>22.4814548492432</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.3915252685547</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>22.3015995025635</v>
+        <v>22.3016014099121</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>25.5</v>
       </c>
       <c r="G873" t="n">
-        <v>22.9310817718506</v>
+        <v>22.9310836791992</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G883" t="n">
-        <v>19.4239749908447</v>
+        <v>19.4239768981934</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>19.1541957855225</v>
+        <v>19.1541976928711</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>23.5</v>
       </c>
       <c r="G891" t="n">
-        <v>21.132568359375</v>
+        <v>21.1325645446777</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>27</v>
       </c>
       <c r="G893" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>25.5</v>
       </c>
       <c r="G899" t="n">
-        <v>22.9310817718506</v>
+        <v>22.9310836791992</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>24.5</v>
       </c>
       <c r="G905" t="n">
-        <v>22.0318241119385</v>
+        <v>22.0318260192871</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.3915252685547</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>25.5</v>
       </c>
       <c r="G909" t="n">
-        <v>22.9310817718506</v>
+        <v>22.9310836791992</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>22.3015995025635</v>
+        <v>22.3016014099121</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>24.5</v>
       </c>
       <c r="G913" t="n">
-        <v>22.0318241119385</v>
+        <v>22.0318260192871</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.3915252685547</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>25</v>
       </c>
       <c r="G917" t="n">
-        <v>22.4814529418945</v>
+        <v>22.4814548492432</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>29</v>
       </c>
       <c r="G937" t="n">
-        <v>26.0784854888916</v>
+        <v>26.0784873962402</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>29.5</v>
       </c>
       <c r="G938" t="n">
-        <v>26.5281143188477</v>
+        <v>26.5281162261963</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>29.5</v>
       </c>
       <c r="G939" t="n">
-        <v>26.5281143188477</v>
+        <v>26.5281162261963</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G940" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187843322754</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187843322754</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>29</v>
       </c>
       <c r="G945" t="n">
-        <v>26.0784854888916</v>
+        <v>26.0784873962402</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187843322754</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>28.5</v>
       </c>
       <c r="G947" t="n">
-        <v>25.6288585662842</v>
+        <v>25.6288566589355</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>29.5</v>
       </c>
       <c r="G953" t="n">
-        <v>26.5281143188477</v>
+        <v>26.5281162261963</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>26.7978916168213</v>
+        <v>26.7978897094727</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>30.5</v>
       </c>
       <c r="G956" t="n">
-        <v>27.4273738861084</v>
+        <v>27.4273719787598</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G959" t="n">
-        <v>29.3158149719238</v>
+        <v>29.3158130645752</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>30.5</v>
       </c>
       <c r="G961" t="n">
-        <v>27.4273738861084</v>
+        <v>27.4273719787598</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>26.7079677581787</v>
+        <v>26.7079658508301</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>26.7079677581787</v>
+        <v>26.7079658508301</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>29.5</v>
       </c>
       <c r="G966" t="n">
-        <v>26.5281143188477</v>
+        <v>26.5281162261963</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>29.5</v>
       </c>
       <c r="G967" t="n">
-        <v>26.5281143188477</v>
+        <v>26.5281162261963</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187843322754</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>25.8986339569092</v>
+        <v>25.8986320495605</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>28.5</v>
       </c>
       <c r="G971" t="n">
-        <v>25.6288585662842</v>
+        <v>25.6288566589355</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>29</v>
       </c>
       <c r="G972" t="n">
-        <v>26.0784854888916</v>
+        <v>26.0784873962402</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>29</v>
       </c>
       <c r="G973" t="n">
-        <v>26.0784854888916</v>
+        <v>26.0784873962402</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>26.1684131622314</v>
+        <v>26.1684112548828</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>24.9094524383545</v>
+        <v>24.9094505310059</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>24.9094524383545</v>
+        <v>24.9094505310059</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>25.2691535949707</v>
+        <v>25.2691555023193</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>25.8986339569092</v>
+        <v>25.8986320495605</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187843322754</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>28.5</v>
       </c>
       <c r="G999" t="n">
-        <v>25.6288585662842</v>
+        <v>25.6288566589355</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187843322754</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>25.8986339569092</v>
+        <v>25.8986320495605</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>26.4381866455078</v>
+        <v>26.4381885528564</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>30</v>
       </c>
       <c r="G1016" t="n">
-        <v>26.9777431488037</v>
+        <v>26.9777450561523</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>27.517297744751</v>
+        <v>27.5172996520996</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>31</v>
       </c>
       <c r="G1023" t="n">
-        <v>27.8770027160645</v>
+        <v>27.8770008087158</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>29.0460376739502</v>
+        <v>29.0460357666016</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1030" t="n">
-        <v>29.7654418945312</v>
+        <v>29.7654438018799</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251487731934</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1032" t="n">
-        <v>30.0352230072021</v>
+        <v>30.0352191925049</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>32.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>29.2258892059326</v>
+        <v>29.225887298584</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>32</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.7762603759766</v>
+        <v>28.7762584686279</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1038" t="n">
-        <v>30.8445529937744</v>
+        <v>30.8445510864258</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1039" t="n">
-        <v>30.3949241638184</v>
+        <v>30.394926071167</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639572143555</v>
+        <v>31.5639591217041</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.833740234375</v>
+        <v>31.8337383270264</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042560577393</v>
+        <v>31.2042579650879</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251487731934</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>32</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7762603759766</v>
+        <v>28.7762584686279</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1048" t="n">
-        <v>29.7654418945312</v>
+        <v>29.7654438018799</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>30.9344825744629</v>
+        <v>30.9344787597656</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>30.3949241638184</v>
+        <v>30.394926071167</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251487731934</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150688171387</v>
+        <v>30.2150707244873</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1055" t="n">
-        <v>29.9452934265137</v>
+        <v>29.9452953338623</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1057" t="n">
-        <v>29.5855941772461</v>
+        <v>29.5855922698975</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1060" t="n">
-        <v>28.5064830780029</v>
+        <v>28.5064849853516</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>32</v>
       </c>
       <c r="G1061" t="n">
-        <v>28.7762603759766</v>
+        <v>28.7762584686279</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>32.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>29.2258892059326</v>
+        <v>29.225887298584</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>30.0083141326904</v>
+        <v>30.0083122253418</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1067" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1068" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>32.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>29.1798648834229</v>
+        <v>29.1798667907715</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>29.1798648834229</v>
+        <v>29.1798667907715</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>27.9832153320312</v>
+        <v>27.9832134246826</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>32.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>29.1798648834229</v>
+        <v>29.1798667907715</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>28.6275634765625</v>
+        <v>28.6275653839111</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1107" t="n">
-        <v>28.4434642791748</v>
+        <v>28.4434661865234</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>28.6275634765625</v>
+        <v>28.6275653839111</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1112" t="n">
-        <v>28.4434642791748</v>
+        <v>28.4434661865234</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>30.0083141326904</v>
+        <v>30.0083122253418</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1127" t="n">
-        <v>30.0083141326904</v>
+        <v>30.0083122253418</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>32.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>32.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>32.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>29.1798648834229</v>
+        <v>29.1798667907715</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1146" t="n">
-        <v>28.6275634765625</v>
+        <v>28.6275653839111</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1154" t="n">
-        <v>28.1673126220703</v>
+        <v>28.1673145294189</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>27.2468147277832</v>
+        <v>27.2468128204346</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>30</v>
       </c>
       <c r="G1161" t="n">
-        <v>27.6150131225586</v>
+        <v>27.6150150299072</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1162" t="n">
-        <v>27.2468147277832</v>
+        <v>27.2468128204346</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>27.5</v>
       </c>
       <c r="G1169" t="n">
-        <v>25.3137626647949</v>
+        <v>25.3137607574463</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>24.301212310791</v>
+        <v>24.3012104034424</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>25.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>23.4727611541748</v>
+        <v>23.4727630615234</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966133117676</v>
+        <v>23.1966114044189</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>25</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0125102996826</v>
+        <v>23.0125122070312</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>26.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>25.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.4727611541748</v>
+        <v>23.4727630615234</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1199" t="n">
-        <v>25.2217121124268</v>
+        <v>25.2217140197754</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>26.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>24.301212310791</v>
+        <v>24.3012104034424</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>26.1422138214111</v>
+        <v>26.1422119140625</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.4309139251709</v>
+        <v>27.4309120178223</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.786563873291</v>
+        <v>26.7865619659424</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>26.786563873291</v>
+        <v>26.7865619659424</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>29</v>
       </c>
       <c r="G1223" t="n">
-        <v>26.6945133209229</v>
+        <v>26.6945152282715</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>26.9706630706787</v>
+        <v>26.9706649780273</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.2468147277832</v>
+        <v>27.2468128204346</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>28</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.7740135192871</v>
+        <v>25.7740116119385</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>28</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.7740135192871</v>
+        <v>25.7740116119385</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2217121124268</v>
+        <v>25.2217140197754</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>27.5</v>
       </c>
       <c r="G1240" t="n">
-        <v>25.3137626647949</v>
+        <v>25.3137607574463</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>25.1296634674072</v>
+        <v>25.1296615600586</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>24.0250606536865</v>
+        <v>24.0250625610352</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>26.9706630706787</v>
+        <v>26.9706649780273</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1268" t="n">
-        <v>29.1798648834229</v>
+        <v>29.1798667907715</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>28.6275634765625</v>
+        <v>28.6275653839111</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>32.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>31.1129150390625</v>
+        <v>31.1129169464111</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1287" t="n">
-        <v>31.1129150390625</v>
+        <v>31.1129169464111</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.020866394043</v>
+        <v>31.0208644866943</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1289" t="n">
-        <v>30.468563079834</v>
+        <v>30.4685649871826</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1290" t="n">
-        <v>31.1129150390625</v>
+        <v>31.1129169464111</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.7447166442871</v>
+        <v>30.7447147369385</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.468563079834</v>
+        <v>30.4685649871826</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>30.468563079834</v>
+        <v>30.4685649871826</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1294" t="n">
-        <v>30.468563079834</v>
+        <v>30.4685649871826</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.6526622772217</v>
+        <v>30.6526641845703</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>30.6526622772217</v>
+        <v>30.6526641845703</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.836763381958</v>
+        <v>30.8367671966553</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.1129150390625</v>
+        <v>31.1129169464111</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>31.1129150390625</v>
+        <v>31.1129169464111</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>31.1129150390625</v>
+        <v>31.1129169464111</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>30.6526622772217</v>
+        <v>30.6526641845703</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1312" t="n">
-        <v>29.1798648834229</v>
+        <v>29.1798667907715</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>32.5</v>
       </c>
       <c r="G1314" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.095422744751</v>
+        <v>29.0954246520996</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851448059082</v>
+        <v>33.7851486206055</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095996856689</v>
+        <v>31.0095977783203</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.8413314819336</v>
+        <v>25.841329574585</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>27</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.8413314819336</v>
+        <v>25.841329574585</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>26.5112934112549</v>
+        <v>26.5112915039062</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.6499137878418</v>
+        <v>25.6499118804932</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>25.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.4057006835938</v>
+        <v>24.4057025909424</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7456207275391</v>
+        <v>25.7456226348877</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>29</v>
       </c>
       <c r="G1554" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>29</v>
       </c>
       <c r="G1555" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1570" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -50136,6 +50136,32 @@
         <v>47.5</v>
       </c>
       <c r="H1914" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1915" t="n">
+        <v>2805</v>
+      </c>
+      <c r="C1915" t="n">
+        <v>48.9000015258789</v>
+      </c>
+      <c r="D1915" t="n">
+        <v>47.2000007629395</v>
+      </c>
+      <c r="E1915" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1915" t="n">
+        <v>46.9000015258789</v>
+      </c>
+      <c r="G1915" t="n">
+        <v>46.9000015258789</v>
+      </c>
+      <c r="H1915" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>9.58128929138184</v>
+        <v>9.58129024505615</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>9.60510349273682</v>
+        <v>9.60510444641113</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>9.23995208740234</v>
+        <v>9.23994922637939</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52572250366211</v>
+        <v>9.52572345733643</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>9.4463415145874</v>
+        <v>9.44634056091309</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4147901535034</v>
+        <v>10.4147891998291</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3989143371582</v>
+        <v>10.3989133834839</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>10.5576763153076</v>
+        <v>10.5576772689819</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>10.5576763153076</v>
+        <v>10.5576772689819</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>10.4147901535034</v>
+        <v>10.4147891998291</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7005605697632</v>
+        <v>10.7005615234375</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>10.510046005249</v>
+        <v>10.5100469589233</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588321685791</v>
+        <v>11.0588312149048</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G40" t="n">
-        <v>10.7761249542236</v>
+        <v>10.7761259078979</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>10.6264562606812</v>
+        <v>10.6264572143555</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G43" t="n">
-        <v>10.676344871521</v>
+        <v>10.6763458251953</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>10.676344871521</v>
+        <v>10.6763458251953</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G46" t="n">
-        <v>10.6098260879517</v>
+        <v>10.609827041626</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G55" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G56" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>10.277229309082</v>
+        <v>10.2772312164307</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G77" t="n">
-        <v>9.99452304840088</v>
+        <v>9.99452209472656</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G81" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>9.77833461761475</v>
+        <v>9.77833652496338</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>9.67855834960938</v>
+        <v>9.67855644226074</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G85" t="n">
-        <v>9.67855834960938</v>
+        <v>9.67855644226074</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>9.49562740325928</v>
+        <v>9.49562835693359</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G87" t="n">
-        <v>9.49562740325928</v>
+        <v>9.49562835693359</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G90" t="n">
-        <v>9.69518566131592</v>
+        <v>9.6951847076416</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.1441917419434</v>
+        <v>10.144190788269</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.77833461761475</v>
+        <v>9.77833652496338</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>9.77833461761475</v>
+        <v>9.77833652496338</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G107" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G108" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529609680176</v>
+        <v>9.64529514312744</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529609680176</v>
+        <v>9.64529514312744</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148357391357</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G119" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>10.1441917419434</v>
+        <v>10.144190788269</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G122" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G125" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>9.99452304840088</v>
+        <v>9.99452209472656</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G128" t="n">
-        <v>10.277229309082</v>
+        <v>10.2772312164307</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G130" t="n">
-        <v>10.277229309082</v>
+        <v>10.2772312164307</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>10.4601583480835</v>
+        <v>10.4601573944092</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G133" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>10.1441917419434</v>
+        <v>10.144190788269</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0277824401855</v>
+        <v>10.0277833938599</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>10.1441917419434</v>
+        <v>10.144190788269</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>9.82822418212891</v>
+        <v>9.82822513580322</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148357391357</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148357391357</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G161" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G170" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G173" t="n">
-        <v>10.0277824401855</v>
+        <v>10.0277833938599</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>10.1441917419434</v>
+        <v>10.144190788269</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G175" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126270294189</v>
+        <v>9.96126174926758</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G181" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G183" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G184" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G190" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G191" t="n">
-        <v>9.99452304840088</v>
+        <v>9.99452209472656</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G192" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>9.99452304840088</v>
+        <v>9.99452209472656</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>9.99452304840088</v>
+        <v>9.99452209472656</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G195" t="n">
-        <v>9.99452304840088</v>
+        <v>9.99452209472656</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G196" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G198" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G201" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>10.0776710510254</v>
+        <v>10.077672958374</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G215" t="n">
-        <v>9.99452304840088</v>
+        <v>9.99452209472656</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.1441917419434</v>
+        <v>10.144190788269</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2107105255127</v>
+        <v>10.2107095718384</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603782653809</v>
+        <v>10.3603792190552</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G234" t="n">
-        <v>9.99452304840088</v>
+        <v>9.99452209472656</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G235" t="n">
-        <v>9.99452304840088</v>
+        <v>9.99452209472656</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G241" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G242" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G245" t="n">
-        <v>9.52888774871826</v>
+        <v>9.52888870239258</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41247844696045</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41247844696045</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.11314296722412</v>
+        <v>9.1131420135498</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G256" t="n">
-        <v>7.42521524429321</v>
+        <v>7.42521619796753</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568536758423</v>
+        <v>7.96568441390991</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>8.03220367431641</v>
+        <v>8.03220462799072</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>8.03220367431641</v>
+        <v>8.03220462799072</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10</v>
       </c>
       <c r="G262" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491088867188</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491088867188</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="G264" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491088867188</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491088867188</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39805889129639</v>
+        <v>8.3980598449707</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640045166016</v>
+        <v>9.14640140533447</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640045166016</v>
+        <v>9.14640140533447</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>9.06325244903564</v>
+        <v>9.06325340270996</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.19211292266846</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>9.10620594024658</v>
+        <v>9.1062068939209</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>8.33303737640381</v>
+        <v>8.33303833007812</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.33303737640381</v>
+        <v>8.33303833007812</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>8.33303737640381</v>
+        <v>8.33303833007812</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G328" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G363" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.75</v>
       </c>
       <c r="G370" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.75</v>
       </c>
       <c r="G373" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.75</v>
       </c>
       <c r="G374" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.204176902771</v>
+        <v>8.20417594909668</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G405" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G425" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G426" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.19211292266846</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>9.10620594024658</v>
+        <v>9.1062068939209</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19211292266846</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>9.19211292266846</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>9.27802276611328</v>
+        <v>9.27802181243896</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G434" t="n">
-        <v>9.27802276611328</v>
+        <v>9.27802181243896</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>9.27802276611328</v>
+        <v>9.27802181243896</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G436" t="n">
-        <v>9.27802276611328</v>
+        <v>9.27802181243896</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>9.27802276611328</v>
+        <v>9.27802181243896</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528148651123</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>12</v>
       </c>
       <c r="G445" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12</v>
       </c>
       <c r="G446" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>12</v>
       </c>
       <c r="G447" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>10.4807291030884</v>
+        <v>10.4807281494141</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>12</v>
       </c>
       <c r="G449" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12</v>
       </c>
       <c r="G452" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528148651123</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528148651123</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>10.4807291030884</v>
+        <v>10.4807281494141</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>12</v>
       </c>
       <c r="G472" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12</v>
       </c>
       <c r="G474" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528148651123</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>10.4807291030884</v>
+        <v>10.4807281494141</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G484" t="n">
-        <v>10.6525440216064</v>
+        <v>10.6525430679321</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.5</v>
       </c>
       <c r="G485" t="n">
-        <v>10.7384510040283</v>
+        <v>10.738450050354</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>10.7384510040283</v>
+        <v>10.738450050354</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>10.8243579864502</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.8243579864502</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>10.8243579864502</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>13</v>
       </c>
       <c r="G493" t="n">
-        <v>11.1679887771606</v>
+        <v>11.167989730835</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>13</v>
       </c>
       <c r="G494" t="n">
-        <v>11.1679887771606</v>
+        <v>11.167989730835</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>13</v>
       </c>
       <c r="G495" t="n">
-        <v>11.1679887771606</v>
+        <v>11.167989730835</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>11.339804649353</v>
+        <v>11.3398056030273</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G498" t="n">
-        <v>11.339804649353</v>
+        <v>11.3398056030273</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.4257125854492</v>
+        <v>11.4257116317749</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>12.1129741668701</v>
+        <v>12.1129732131958</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>12.6284189224243</v>
+        <v>12.62841796875</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>15</v>
       </c>
       <c r="G506" t="n">
-        <v>12.8861417770386</v>
+        <v>12.8861408233643</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>12.7143259048462</v>
+        <v>12.7143268585205</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G508" t="n">
-        <v>12.7143259048462</v>
+        <v>12.7143268585205</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>13.0579557418823</v>
+        <v>13.057957649231</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>13.0579557418823</v>
+        <v>13.057957649231</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720487594604</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720487594604</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720487594604</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G514" t="n">
-        <v>13.0579557418823</v>
+        <v>13.057957649231</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.8311252593994</v>
+        <v>13.8311262130737</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>13.9170331954956</v>
+        <v>13.9170322418213</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>16.5</v>
       </c>
       <c r="G519" t="n">
-        <v>14.1747560501099</v>
+        <v>14.1747550964355</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324779510498</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>16.5</v>
       </c>
       <c r="G522" t="n">
-        <v>14.1747560501099</v>
+        <v>14.1747550964355</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>13.8311252593994</v>
+        <v>13.8311262130737</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>14.0029392242432</v>
+        <v>14.0029401779175</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>14.3465709686279</v>
+        <v>14.3465719223022</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324779510498</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042928695679</v>
+        <v>14.6042938232422</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>18</v>
       </c>
       <c r="G529" t="n">
-        <v>15.4633712768555</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>18</v>
       </c>
       <c r="G531" t="n">
-        <v>15.4633712768555</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056465148926</v>
+        <v>15.2056493759155</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>15.1197414398193</v>
+        <v>15.1197395324707</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>18</v>
       </c>
       <c r="G534" t="n">
-        <v>15.4633712768555</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="n">
-        <v>15.4633712768555</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.5492782592773</v>
+        <v>15.549277305603</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376247406006</v>
+        <v>15.6376276016235</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>17</v>
       </c>
       <c r="G540" t="n">
-        <v>15.0191879272461</v>
+        <v>15.0191888809204</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G541" t="n">
-        <v>15.1958847045898</v>
+        <v>15.1958856582642</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.5492792129517</v>
+        <v>15.549277305603</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>15.8143224716187</v>
+        <v>15.8143186569214</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>16.0793647766113</v>
+        <v>16.07936668396</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>18</v>
       </c>
       <c r="G546" t="n">
-        <v>15.9026718139648</v>
+        <v>15.9026699066162</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230236053467</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G561" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230236053467</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>19.0832061767578</v>
+        <v>19.0832042694092</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>21</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5531139373779</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G567" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230236053467</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>18.3764190673828</v>
+        <v>18.3764171600342</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>18.3764190673828</v>
+        <v>18.3764171600342</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230236053467</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278919219971</v>
+        <v>17.2278938293457</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.1395435333252</v>
+        <v>17.1395454406738</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>17.1395435333252</v>
+        <v>17.1395454406738</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>17.3162422180176</v>
+        <v>17.3162403106689</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>21</v>
       </c>
       <c r="G586" t="n">
-        <v>18.5531139373779</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>18.3764190673828</v>
+        <v>18.3764171600342</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>21</v>
       </c>
       <c r="G589" t="n">
-        <v>18.5531139373779</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>21</v>
       </c>
       <c r="G590" t="n">
-        <v>18.5531139373779</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>18.3764190673828</v>
+        <v>18.3764171600342</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>21</v>
       </c>
       <c r="G592" t="n">
-        <v>18.5531139373779</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>18.9065055847168</v>
+        <v>18.9065074920654</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>22.7938289642334</v>
+        <v>22.7938270568848</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G606" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>22.2637367248535</v>
+        <v>22.2637405395508</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>22.7938289642334</v>
+        <v>22.7938270568848</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>22.7938289642334</v>
+        <v>22.7938270568848</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>24.2073993682861</v>
+        <v>24.2073974609375</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="G617" t="n">
-        <v>23.8540019989014</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>23.3239154815674</v>
+        <v>23.323917388916</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>26</v>
       </c>
       <c r="G620" t="n">
-        <v>22.9705219268799</v>
+        <v>22.9705238342285</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>23.3239154815674</v>
+        <v>23.323917388916</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="G622" t="n">
-        <v>23.8540019989014</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>28.4481105804443</v>
+        <v>28.448112487793</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>30.7451610565186</v>
+        <v>30.7451629638672</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>35</v>
       </c>
       <c r="G633" t="n">
-        <v>30.9218597412109</v>
+        <v>30.9218559265137</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0985584259033</v>
+        <v>31.0985546112061</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.5684661865234</v>
+        <v>30.5684642791748</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>30.5684661865234</v>
+        <v>30.5684642791748</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>30.7451610565186</v>
+        <v>30.7451629638672</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G638" t="n">
-        <v>30.3917694091797</v>
+        <v>30.3917713165283</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082874298096</v>
+        <v>29.5082893371582</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>28.4481105804443</v>
+        <v>28.448112487793</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>25.267578125</v>
+        <v>25.2675762176514</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>24.2073993682861</v>
+        <v>24.2073974609375</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>27.5646286010742</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>27.5646286010742</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578453063965</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578453063965</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33</v>
       </c>
       <c r="G663" t="n">
-        <v>29.1548957824707</v>
+        <v>29.1548938751221</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G664" t="n">
-        <v>29.6849822998047</v>
+        <v>29.6849803924561</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>34</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0383758544922</v>
+        <v>30.0383777618408</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>29.6849822998047</v>
+        <v>29.6849803924561</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>28.9781970977783</v>
+        <v>28.978199005127</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G672" t="n">
-        <v>29.6849822998047</v>
+        <v>29.6849803924561</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>28.9781970977783</v>
+        <v>28.978199005127</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>33</v>
       </c>
       <c r="G674" t="n">
-        <v>29.1548957824707</v>
+        <v>29.1548938751221</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33</v>
       </c>
       <c r="G677" t="n">
-        <v>29.1548957824707</v>
+        <v>29.1548938751221</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>28.6248073577881</v>
+        <v>28.6248054504395</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>28.6248073577881</v>
+        <v>28.6248054504395</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>28.4481105804443</v>
+        <v>28.448112487793</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>28.8015003204346</v>
+        <v>28.8015022277832</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>31</v>
       </c>
       <c r="G689" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>25.267578125</v>
+        <v>25.2675762176514</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G699" t="n">
-        <v>28.6248073577881</v>
+        <v>28.6248054504395</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>27.5646286010742</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>31</v>
       </c>
       <c r="G703" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578453063965</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G707" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578453063965</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>30</v>
       </c>
       <c r="G708" t="n">
-        <v>26.5044498443604</v>
+        <v>26.5044479370117</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>31</v>
       </c>
       <c r="G715" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>31</v>
       </c>
       <c r="G716" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G717" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578453063965</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>30</v>
       </c>
       <c r="G720" t="n">
-        <v>26.5044498443604</v>
+        <v>26.5044479370117</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>30</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5044498443604</v>
+        <v>26.5044479370117</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141826629639</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141826629639</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>28</v>
       </c>
       <c r="G741" t="n">
-        <v>24.7374839782715</v>
+        <v>24.7374877929688</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>25.267578125</v>
+        <v>25.2675762176514</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>24.2073993682861</v>
+        <v>24.2073974609375</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>27</v>
       </c>
       <c r="G749" t="n">
-        <v>23.8540019989014</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>23.3239154815674</v>
+        <v>23.323917388916</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>22.6171321868896</v>
+        <v>22.617130279541</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>22.6171321868896</v>
+        <v>22.617130279541</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>25</v>
       </c>
       <c r="G755" t="n">
-        <v>22.0870418548584</v>
+        <v>22.0870399475098</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>21.5569534301758</v>
+        <v>21.5569515228271</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>24</v>
       </c>
       <c r="G758" t="n">
-        <v>21.2035598754883</v>
+        <v>21.2035617828369</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>25</v>
       </c>
       <c r="G760" t="n">
-        <v>22.0870418548584</v>
+        <v>22.0870399475098</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>23.8540019989014</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141826629639</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>28</v>
       </c>
       <c r="G764" t="n">
-        <v>24.7374839782715</v>
+        <v>24.7374877929688</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>28</v>
       </c>
       <c r="G765" t="n">
-        <v>24.7374839782715</v>
+        <v>24.7374877929688</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>30</v>
       </c>
       <c r="G771" t="n">
-        <v>26.5044498443604</v>
+        <v>26.5044479370117</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>27.0345401763916</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>27.5646286010742</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G775" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>26.327751159668</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>25.5326194763184</v>
+        <v>25.532621383667</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>27</v>
       </c>
       <c r="G786" t="n">
-        <v>23.8540019989014</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>26</v>
       </c>
       <c r="G792" t="n">
-        <v>22.9705219268799</v>
+        <v>22.9705238342285</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>26</v>
       </c>
       <c r="G793" t="n">
-        <v>22.9705219268799</v>
+        <v>22.9705238342285</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>26</v>
       </c>
       <c r="G794" t="n">
-        <v>22.9705219268799</v>
+        <v>22.9705238342285</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>25.4490032196045</v>
+        <v>25.4490051269531</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>23.9202651977539</v>
+        <v>23.9202671051025</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>28</v>
       </c>
       <c r="G805" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>27.5</v>
       </c>
       <c r="G809" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>24.1001167297363</v>
+        <v>24.100118637085</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>27.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>27.5</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>27.5</v>
       </c>
       <c r="G820" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>27.5</v>
       </c>
       <c r="G821" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>26.5</v>
       </c>
       <c r="G823" t="n">
-        <v>23.8303413391113</v>
+        <v>23.8303394317627</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G825" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>25.5</v>
       </c>
       <c r="G839" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>25.5</v>
       </c>
       <c r="G840" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>22.661304473877</v>
+        <v>22.6613063812256</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>24.5</v>
       </c>
       <c r="G843" t="n">
-        <v>22.0318260192871</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>21.3124198913574</v>
+        <v>21.3124179840088</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>25</v>
       </c>
       <c r="G849" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814510345459</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>24.5</v>
       </c>
       <c r="G850" t="n">
-        <v>22.0318260192871</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G855" t="n">
-        <v>20.4131603240967</v>
+        <v>20.4131622314453</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>19.6038284301758</v>
+        <v>19.6038265228271</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>19.4239768981934</v>
+        <v>19.4239749908447</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>19.6038284301758</v>
+        <v>19.6038265228271</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>21.5</v>
       </c>
       <c r="G864" t="n">
-        <v>19.3340492248535</v>
+        <v>19.3340511322021</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>19.6038284301758</v>
+        <v>19.6038265228271</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>20.5930118560791</v>
+        <v>20.5930099487305</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>25</v>
       </c>
       <c r="G869" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814510345459</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.3915271759033</v>
+        <v>22.3915252685547</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>25.5</v>
       </c>
       <c r="G873" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>23</v>
       </c>
       <c r="G878" t="n">
-        <v>20.6829357147217</v>
+        <v>20.6829376220703</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>20.5930118560791</v>
+        <v>20.5930099487305</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G883" t="n">
-        <v>19.4239768981934</v>
+        <v>19.4239749908447</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>23</v>
       </c>
       <c r="G890" t="n">
-        <v>20.6829357147217</v>
+        <v>20.6829376220703</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>23.5</v>
       </c>
       <c r="G891" t="n">
-        <v>21.1325645446777</v>
+        <v>21.1325664520264</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>25.5</v>
       </c>
       <c r="G899" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>22.5713787078857</v>
+        <v>22.5713806152344</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>24.5</v>
       </c>
       <c r="G905" t="n">
-        <v>22.0318260192871</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.3915271759033</v>
+        <v>22.3915252685547</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>25.5</v>
       </c>
       <c r="G909" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>24.5</v>
       </c>
       <c r="G913" t="n">
-        <v>22.0318260192871</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.3915271759033</v>
+        <v>22.3915252685547</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>25</v>
       </c>
       <c r="G917" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814510345459</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>22.5713787078857</v>
+        <v>22.5713806152344</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G932" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.9885578155518</v>
+        <v>25.988561630249</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>29</v>
       </c>
       <c r="G937" t="n">
-        <v>26.0784873962402</v>
+        <v>26.0784854888916</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>29.5</v>
       </c>
       <c r="G938" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>29.5</v>
       </c>
       <c r="G939" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G940" t="n">
-        <v>25.7187843322754</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>25.7187843322754</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>29</v>
       </c>
       <c r="G945" t="n">
-        <v>26.0784873962402</v>
+        <v>26.0784854888916</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>25.7187843322754</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.9885578155518</v>
+        <v>25.988561630249</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>29.5</v>
       </c>
       <c r="G953" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>26.7978897094727</v>
+        <v>26.7978916168213</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.9885578155518</v>
+        <v>25.988561630249</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>26.7079658508301</v>
+        <v>26.7079677581787</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>26.7079658508301</v>
+        <v>26.7079677581787</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>27.1575965881348</v>
+        <v>27.1575946807861</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>29.5</v>
       </c>
       <c r="G966" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>29.5</v>
       </c>
       <c r="G967" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>25.7187843322754</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>29</v>
       </c>
       <c r="G972" t="n">
-        <v>26.0784873962402</v>
+        <v>26.0784854888916</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>29</v>
       </c>
       <c r="G973" t="n">
-        <v>26.0784873962402</v>
+        <v>26.0784854888916</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.9885578155518</v>
+        <v>25.988561630249</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>28</v>
       </c>
       <c r="G982" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>24.9094505310059</v>
+        <v>24.9094524383545</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>24.9094505310059</v>
+        <v>24.9094524383545</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>27.5</v>
       </c>
       <c r="G989" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>28</v>
       </c>
       <c r="G990" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>25.2691555023193</v>
+        <v>25.2691535949707</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>28</v>
       </c>
       <c r="G996" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>25.7187843322754</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>28</v>
       </c>
       <c r="G1000" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>28</v>
       </c>
       <c r="G1005" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>27.5</v>
       </c>
       <c r="G1007" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>25.7187843322754</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>26.4381885528564</v>
+        <v>26.4381866455078</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>30</v>
       </c>
       <c r="G1016" t="n">
-        <v>26.9777450561523</v>
+        <v>26.9777431488037</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>27.1575965881348</v>
+        <v>27.1575946807861</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1019" t="n">
-        <v>28.0568542480469</v>
+        <v>28.0568523406982</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>27.5172996520996</v>
+        <v>27.517297744751</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>31</v>
       </c>
       <c r="G1023" t="n">
-        <v>27.8770008087158</v>
+        <v>27.8770046234131</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>28.1467781066895</v>
+        <v>28.1467800140381</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1030" t="n">
-        <v>29.7654438018799</v>
+        <v>29.7654418945312</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251487731934</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1032" t="n">
-        <v>30.0352191925049</v>
+        <v>30.0352230072021</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>32.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>29.225887298584</v>
+        <v>29.2258892059326</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>32</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.7762584686279</v>
+        <v>28.7762603759766</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1038" t="n">
-        <v>30.8445510864258</v>
+        <v>30.8445529937744</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1039" t="n">
-        <v>30.394926071167</v>
+        <v>30.3949241638184</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639591217041</v>
+        <v>31.5639572143555</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.8337383270264</v>
+        <v>31.833740234375</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2941818237305</v>
+        <v>31.2941837310791</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>31.2941818237305</v>
+        <v>31.2941837310791</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042579650879</v>
+        <v>31.2042560577393</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251487731934</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>32</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7762584686279</v>
+        <v>28.7762603759766</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1048" t="n">
-        <v>29.7654438018799</v>
+        <v>29.7654418945312</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3049983978271</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>30.9344787597656</v>
+        <v>30.9344825744629</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>30.394926071167</v>
+        <v>30.3949241638184</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251487731934</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150707244873</v>
+        <v>30.2150688171387</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3049983978271</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1055" t="n">
-        <v>29.9452953338623</v>
+        <v>29.945291519165</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1057" t="n">
-        <v>29.5855922698975</v>
+        <v>29.5855941772461</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1060" t="n">
-        <v>28.5064849853516</v>
+        <v>28.5064830780029</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>32</v>
       </c>
       <c r="G1061" t="n">
-        <v>28.7762584686279</v>
+        <v>28.7762603759766</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>32.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>29.225887298584</v>
+        <v>29.2258892059326</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>30.0083122253418</v>
+        <v>30.0083141326904</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1067" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1068" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>32.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>27.9832134246826</v>
+        <v>27.9832153320312</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>32.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1107" t="n">
-        <v>28.4434661865234</v>
+        <v>28.4434642791748</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1112" t="n">
-        <v>28.4434661865234</v>
+        <v>28.4434642791748</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>30.0083122253418</v>
+        <v>30.0083141326904</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1127" t="n">
-        <v>30.0083122253418</v>
+        <v>30.0083141326904</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>32.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>32.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>32.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1146" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1154" t="n">
-        <v>28.1673145294189</v>
+        <v>28.1673126220703</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>27.2468128204346</v>
+        <v>27.2468147277832</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>30</v>
       </c>
       <c r="G1161" t="n">
-        <v>27.6150150299072</v>
+        <v>27.6150131225586</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1162" t="n">
-        <v>27.2468128204346</v>
+        <v>27.2468147277832</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>27.5</v>
       </c>
       <c r="G1169" t="n">
-        <v>25.3137607574463</v>
+        <v>25.3137626647949</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>24.9455623626709</v>
+        <v>24.9455642700195</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>24.3012104034424</v>
+        <v>24.301212310791</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>25.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>23.4727630615234</v>
+        <v>23.4727611541748</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966114044189</v>
+        <v>23.1966133117676</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>25</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0125122070312</v>
+        <v>23.0125102996826</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>26.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>24.3932628631592</v>
+        <v>24.3932609558105</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>25.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.4727630615234</v>
+        <v>23.4727611541748</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1199" t="n">
-        <v>25.2217140197754</v>
+        <v>25.2217121124268</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.9455623626709</v>
+        <v>24.9455642700195</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>26.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3932628631592</v>
+        <v>24.3932609558105</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>24.3012104034424</v>
+        <v>24.301212310791</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>26.1422119140625</v>
+        <v>26.1422138214111</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.4309120178223</v>
+        <v>27.4309139251709</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.7865619659424</v>
+        <v>26.786563873291</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>26.7865619659424</v>
+        <v>26.786563873291</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>29</v>
       </c>
       <c r="G1223" t="n">
-        <v>26.6945152282715</v>
+        <v>26.6945133209229</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>26.9706649780273</v>
+        <v>26.9706630706787</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.2468128204346</v>
+        <v>27.2468147277832</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>28</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.7740116119385</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>28</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.7740116119385</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2217140197754</v>
+        <v>25.2217121124268</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>27.5</v>
       </c>
       <c r="G1240" t="n">
-        <v>25.3137607574463</v>
+        <v>25.3137626647949</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>25.1296615600586</v>
+        <v>25.1296634674072</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>24.0250625610352</v>
+        <v>24.0250606536865</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>26.9706649780273</v>
+        <v>26.9706630706787</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1268" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>32.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1287" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.0208644866943</v>
+        <v>31.020866394043</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1289" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1290" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.7447147369385</v>
+        <v>30.7447166442871</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1294" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526622772217</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526622772217</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.8367671966553</v>
+        <v>30.836763381958</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526622772217</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1312" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>32.5</v>
       </c>
       <c r="G1314" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.0954246520996</v>
+        <v>29.095422744751</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851486206055</v>
+        <v>33.7851448059082</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095977783203</v>
+        <v>31.0095996856689</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>27</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>26.5112915039062</v>
+        <v>26.5112934112549</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.6499118804932</v>
+        <v>25.6499137878418</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>25.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.4057025909424</v>
+        <v>24.4057006835938</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7456226348877</v>
+        <v>25.7456207275391</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>29</v>
       </c>
       <c r="G1554" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>29</v>
       </c>
       <c r="G1555" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1570" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -50150,7 +50150,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="D1915" t="n">
-        <v>47.2000007629395</v>
+        <v>46.9000015258789</v>
       </c>
       <c r="E1915" t="n">
         <v>48</v>
@@ -50162,6 +50162,32 @@
         <v>46.9000015258789</v>
       </c>
       <c r="H1915" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1916" t="n">
+        <v>1136</v>
+      </c>
+      <c r="C1916" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="D1916" t="n">
+        <v>46.4000015258789</v>
+      </c>
+      <c r="E1916" t="n">
+        <v>46.9000015258789</v>
+      </c>
+      <c r="F1916" t="n">
+        <v>46.2000007629395</v>
+      </c>
+      <c r="G1916" t="n">
+        <v>46.2000007629395</v>
+      </c>
+      <c r="H1916" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>9.58129024505615</v>
+        <v>9.58128929138184</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.76386547088623</v>
+        <v>9.76386737823486</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>9.67654609680176</v>
+        <v>9.67654514312744</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>9.60510444641113</v>
+        <v>9.6051025390625</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>9.23994922637939</v>
+        <v>9.23995208740234</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>9.39871311187744</v>
+        <v>9.39871406555176</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52572345733643</v>
+        <v>9.52572250366211</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44634056091309</v>
+        <v>9.4463415145874</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>10.1607713699341</v>
+        <v>10.1607704162598</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2877807617188</v>
+        <v>10.2877788543701</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2719030380249</v>
+        <v>10.2719049453735</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>10.1607713699341</v>
+        <v>10.1607704162598</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5259237289429</v>
+        <v>10.5259227752686</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3989133834839</v>
+        <v>10.3989152908325</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G28" t="n">
-        <v>10.256028175354</v>
+        <v>10.2560272216797</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>10.5576772689819</v>
+        <v>10.5576763153076</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>10.5576772689819</v>
+        <v>10.5576763153076</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588312149048</v>
+        <v>11.0588321685791</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419811248779</v>
+        <v>11.1419801712036</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G38" t="n">
-        <v>11.1087207794189</v>
+        <v>11.1087198257446</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G40" t="n">
-        <v>10.7761259078979</v>
+        <v>10.776123046875</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>10.6264572143555</v>
+        <v>10.6264553070068</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>13</v>
       </c>
       <c r="G45" t="n">
-        <v>10.8093843460083</v>
+        <v>10.809383392334</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G46" t="n">
-        <v>10.609827041626</v>
+        <v>10.6098260879517</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G47" t="n">
-        <v>10.3437490463257</v>
+        <v>10.3437480926514</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G55" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>10.2772312164307</v>
+        <v>10.2772302627563</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>9.84485530853271</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G67" t="n">
-        <v>9.44573783874512</v>
+        <v>9.44573879241943</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.47899723052979</v>
+        <v>9.4789981842041</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G70" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G77" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G80" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G81" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833461761475</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.5</v>
       </c>
       <c r="G88" t="n">
-        <v>9.56214714050293</v>
+        <v>9.56214618682861</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.56214714050293</v>
+        <v>9.56214618682861</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441926956177</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12</v>
       </c>
       <c r="G101" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G103" t="n">
-        <v>9.74507522583008</v>
+        <v>9.74507617950439</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G104" t="n">
-        <v>9.74507522583008</v>
+        <v>9.74507617950439</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833461761475</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833461761475</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G107" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G108" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G109" t="n">
-        <v>9.61203670501709</v>
+        <v>9.61203765869141</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529514312744</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529514312744</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148262023926</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12</v>
       </c>
       <c r="G113" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12</v>
       </c>
       <c r="G114" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G116" t="n">
-        <v>9.84485530853271</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12</v>
       </c>
       <c r="G117" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G118" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G120" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441926956177</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G122" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12</v>
       </c>
       <c r="G123" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G128" t="n">
-        <v>10.2772312164307</v>
+        <v>10.2772302627563</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>10.3936376571655</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G130" t="n">
-        <v>10.2772312164307</v>
+        <v>10.2772302627563</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G131" t="n">
-        <v>10.443528175354</v>
+        <v>10.4435291290283</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G133" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441926956177</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0277833938599</v>
+        <v>10.0277814865112</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G136" t="n">
-        <v>10.044412612915</v>
+        <v>10.0444116592407</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441926956177</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12</v>
       </c>
       <c r="G138" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>9.82822513580322</v>
+        <v>9.82822418212891</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148262023926</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148262023926</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G155" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G156" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G161" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G164" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3936376571655</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G170" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G173" t="n">
-        <v>10.0277833938599</v>
+        <v>10.0277814865112</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441926956177</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126174926758</v>
+        <v>9.96126270294189</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12</v>
       </c>
       <c r="G178" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12</v>
       </c>
       <c r="G179" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G181" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G183" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G184" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G185" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12</v>
       </c>
       <c r="G186" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G188" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G190" t="n">
-        <v>10.2938594818115</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G191" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G192" t="n">
-        <v>10.2938594818115</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G195" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G196" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G198" t="n">
-        <v>10.2938594818115</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G201" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G203" t="n">
-        <v>10.044412612915</v>
+        <v>10.0444116592407</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>10.044412612915</v>
+        <v>10.0444116592407</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G205" t="n">
-        <v>9.84485530853271</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>12</v>
       </c>
       <c r="G211" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="G213" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G215" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441926956177</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G217" t="n">
-        <v>10.3437490463257</v>
+        <v>10.3437480926514</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2107095718384</v>
+        <v>10.2107105255127</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>12</v>
       </c>
       <c r="G221" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="G222" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>10.1940803527832</v>
+        <v>10.1940813064575</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12</v>
       </c>
       <c r="G226" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G228" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603792190552</v>
+        <v>10.3603782653809</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G234" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G235" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G241" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G242" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.17966079711914</v>
+        <v>9.17966270446777</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>11.5</v>
       </c>
       <c r="G249" t="n">
-        <v>9.56214714050293</v>
+        <v>9.56214618682861</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.1131420135498</v>
+        <v>9.11314105987549</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>8.66413688659668</v>
+        <v>8.664137840271</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>8.64750671386719</v>
+        <v>8.64750576019287</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>8.44794845581055</v>
+        <v>8.44794940948486</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G254" t="n">
-        <v>8.13198280334473</v>
+        <v>8.13198375701904</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568441390991</v>
+        <v>7.96568536758423</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>8.03220462799072</v>
+        <v>8.03220272064209</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>8.03220462799072</v>
+        <v>8.03220272064209</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10</v>
       </c>
       <c r="G262" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="G264" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>8.64750671386719</v>
+        <v>8.64750576019287</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G271" t="n">
-        <v>8.3980598449707</v>
+        <v>8.39806079864502</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.64750671386719</v>
+        <v>8.64750576019287</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>8.64750671386719</v>
+        <v>8.64750576019287</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>8.64750671386719</v>
+        <v>8.64750576019287</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.64750671386719</v>
+        <v>8.64750576019287</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.64750671386719</v>
+        <v>8.64750576019287</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640235900879</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640235900879</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>8.98010349273682</v>
+        <v>8.98010444641113</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>8.98010349273682</v>
+        <v>8.98010444641113</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36392879486084</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.5</v>
       </c>
       <c r="G293" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G298" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10</v>
       </c>
       <c r="G305" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10</v>
       </c>
       <c r="G307" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10</v>
       </c>
       <c r="G308" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10</v>
       </c>
       <c r="G310" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G311" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.5</v>
       </c>
       <c r="G313" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.5</v>
       </c>
       <c r="G314" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.5</v>
       </c>
       <c r="G315" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G316" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10</v>
       </c>
       <c r="G319" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G321" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G322" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G323" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G352" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G353" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>10</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G360" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.75</v>
       </c>
       <c r="G370" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.75</v>
       </c>
       <c r="G373" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.75</v>
       </c>
       <c r="G374" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.20417594909668</v>
+        <v>8.20417785644531</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485229492188</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="G383" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10</v>
       </c>
       <c r="G386" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>10</v>
       </c>
       <c r="G399" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>10</v>
       </c>
       <c r="G408" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>10</v>
       </c>
       <c r="G409" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36392879486084</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>9.96528148651123</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.70756053924561</v>
+        <v>9.70755958557129</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>12</v>
       </c>
       <c r="G445" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12</v>
       </c>
       <c r="G446" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>12</v>
       </c>
       <c r="G447" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807271957397</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>12</v>
       </c>
       <c r="G449" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12</v>
       </c>
       <c r="G452" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G457" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>9.70756053924561</v>
+        <v>9.70755958557129</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G460" t="n">
-        <v>9.70756053924561</v>
+        <v>9.70755958557129</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>9.62165260314941</v>
+        <v>9.6216516494751</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.96528148651123</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.96528148651123</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G466" t="n">
-        <v>9.70756053924561</v>
+        <v>9.70755958557129</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807271957397</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>10.5666370391846</v>
+        <v>10.5666360855103</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>10.5666370391846</v>
+        <v>10.5666360855103</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>12</v>
       </c>
       <c r="G472" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12</v>
       </c>
       <c r="G474" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>9.96528148651123</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G477" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807271957397</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="n">
-        <v>10.3089141845703</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.5</v>
       </c>
       <c r="G485" t="n">
-        <v>10.738450050354</v>
+        <v>10.7384510040283</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>10.738450050354</v>
+        <v>10.7384510040283</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.9102659225464</v>
+        <v>10.9102668762207</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.9102659225464</v>
+        <v>10.9102668762207</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>10.9102659225464</v>
+        <v>10.9102668762207</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>13</v>
       </c>
       <c r="G493" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679887771606</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>13</v>
       </c>
       <c r="G494" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679887771606</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>13</v>
       </c>
       <c r="G495" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679887771606</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>11.3398056030273</v>
+        <v>11.339804649353</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>11.5116195678711</v>
+        <v>11.5116205215454</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G498" t="n">
-        <v>11.3398056030273</v>
+        <v>11.339804649353</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>11.8552513122559</v>
+        <v>11.8552503585815</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>12.62841796875</v>
+        <v>12.6284189224243</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>15</v>
       </c>
       <c r="G506" t="n">
-        <v>12.8861408233643</v>
+        <v>12.8861417770386</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>12.7143268585205</v>
+        <v>12.7143259048462</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G508" t="n">
-        <v>12.7143268585205</v>
+        <v>12.7143259048462</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>13.057957649231</v>
+        <v>13.0579566955566</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>13.057957649231</v>
+        <v>13.0579566955566</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G514" t="n">
-        <v>13.057957649231</v>
+        <v>13.0579566955566</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.8311262130737</v>
+        <v>13.8311243057251</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>13.9170322418213</v>
+        <v>13.9170331954956</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>13.4874954223633</v>
+        <v>13.487494468689</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>16.5</v>
       </c>
       <c r="G519" t="n">
-        <v>14.1747550964355</v>
+        <v>14.1747541427612</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324769973755</v>
+        <v>14.4324760437012</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>16.5</v>
       </c>
       <c r="G522" t="n">
-        <v>14.1747550964355</v>
+        <v>14.1747541427612</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>13.8311262130737</v>
+        <v>13.8311243057251</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>14.0029401779175</v>
+        <v>14.0029392242432</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324769973755</v>
+        <v>14.4324760437012</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042938232422</v>
+        <v>14.6042919158936</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>15.2915544509888</v>
+        <v>15.2915534973145</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056493759155</v>
+        <v>15.2056474685669</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>15.1197395324707</v>
+        <v>15.119740486145</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>15.7259740829468</v>
+        <v>15.7259731292725</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376276016235</v>
+        <v>15.6376266479492</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>15.7259740829468</v>
+        <v>15.7259731292725</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>17</v>
       </c>
       <c r="G540" t="n">
-        <v>15.0191888809204</v>
+        <v>15.0191869735718</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>15.7259740829468</v>
+        <v>15.7259731292725</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>15.8143186569214</v>
+        <v>15.81432056427</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>18</v>
       </c>
       <c r="G546" t="n">
-        <v>15.9026699066162</v>
+        <v>15.9026679992676</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>18.1997241973877</v>
+        <v>18.1997222900391</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G561" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>19.9666862487793</v>
+        <v>19.9666843414307</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>19.9666862487793</v>
+        <v>19.9666843414307</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>21</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>17.4929370880127</v>
+        <v>17.4929351806641</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>20</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6696338653564</v>
+        <v>17.6696319580078</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278938293457</v>
+        <v>17.2278919219971</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>19</v>
       </c>
       <c r="G576" t="n">
-        <v>16.7861518859863</v>
+        <v>16.7861499786377</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.1395454406738</v>
+        <v>17.1395435333252</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>17.1395454406738</v>
+        <v>17.1395435333252</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>19</v>
       </c>
       <c r="G581" t="n">
-        <v>16.7861518859863</v>
+        <v>16.7861499786377</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>17.4929370880127</v>
+        <v>17.4929351806641</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>17.6696338653564</v>
+        <v>17.6696319580078</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>21</v>
       </c>
       <c r="G586" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>21</v>
       </c>
       <c r="G589" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>21</v>
       </c>
       <c r="G590" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>21</v>
       </c>
       <c r="G592" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531139373779</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>18.9065074920654</v>
+        <v>18.9065055847168</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938251495361</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>20.6734714508057</v>
+        <v>20.673469543457</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>21.0268611907959</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>19.2599010467529</v>
+        <v>19.2598972320557</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G599" t="n">
-        <v>19.2599010467529</v>
+        <v>19.2598972320557</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>19.2599010467529</v>
+        <v>19.2598972320557</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>21.0268611907959</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>21.0268611907959</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G606" t="n">
-        <v>21.0268611907959</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>21.0268611907959</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>21.7336502075195</v>
+        <v>21.7336483001709</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>21.7336502075195</v>
+        <v>21.7336483001709</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>22.2637405395508</v>
+        <v>22.2637367248535</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938251495361</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938251495361</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="G617" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>23.323917388916</v>
+        <v>23.3239154815674</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>26</v>
       </c>
       <c r="G620" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>23.323917388916</v>
+        <v>23.3239154815674</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="G622" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>30.7451629638672</v>
+        <v>30.7451610565186</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>35</v>
       </c>
       <c r="G633" t="n">
-        <v>30.9218559265137</v>
+        <v>30.921854019165</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>30.7451629638672</v>
+        <v>30.7451610565186</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082893371582</v>
+        <v>29.5082874298096</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>27.0345363616943</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>27.0345363616943</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>26.8578453063965</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>26.8578453063965</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33</v>
       </c>
       <c r="G663" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548919677734</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G664" t="n">
-        <v>29.6849803924561</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>34</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0383777618408</v>
+        <v>30.0383739471436</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>29.6849803924561</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>28.978199005127</v>
+        <v>28.9781970977783</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G672" t="n">
-        <v>29.6849803924561</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>28.978199005127</v>
+        <v>28.9781970977783</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>33</v>
       </c>
       <c r="G674" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548919677734</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33</v>
       </c>
       <c r="G677" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548919677734</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>28.6248054504395</v>
+        <v>28.6248073577881</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>28.6248054504395</v>
+        <v>28.6248073577881</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>28.8015022277832</v>
+        <v>28.8015003204346</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>31</v>
       </c>
       <c r="G689" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>25.7976665496826</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G699" t="n">
-        <v>28.6248054504395</v>
+        <v>28.6248073577881</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>31</v>
       </c>
       <c r="G703" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>26.8578453063965</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.0345363616943</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G707" t="n">
-        <v>26.8578453063965</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>30</v>
       </c>
       <c r="G708" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>27.0345363616943</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>31</v>
       </c>
       <c r="G715" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>31</v>
       </c>
       <c r="G716" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G717" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>26.8578453063965</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>30</v>
       </c>
       <c r="G720" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>30</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>24.9141826629639</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>24.9141826629639</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>28</v>
       </c>
       <c r="G741" t="n">
-        <v>24.7374877929688</v>
+        <v>24.7374858856201</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>29</v>
       </c>
       <c r="G743" t="n">
-        <v>25.6209678649902</v>
+        <v>25.6209697723389</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>25.7976665496826</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>27</v>
       </c>
       <c r="G749" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>23.323917388916</v>
+        <v>23.3239154815674</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>21.7336502075195</v>
+        <v>21.7336483001709</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>21.5569515228271</v>
+        <v>21.5569496154785</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>24</v>
       </c>
       <c r="G758" t="n">
-        <v>21.2035617828369</v>
+        <v>21.2035579681396</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>20.8501682281494</v>
+        <v>20.8501644134521</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>24.9141826629639</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>28</v>
       </c>
       <c r="G764" t="n">
-        <v>24.7374877929688</v>
+        <v>24.7374858856201</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>28</v>
       </c>
       <c r="G765" t="n">
-        <v>24.7374877929688</v>
+        <v>24.7374858856201</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>27.0345363616943</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>30</v>
       </c>
       <c r="G771" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>27.0345363616943</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G775" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>26.3277549743652</v>
+        <v>26.3277530670166</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>25.7976665496826</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>29</v>
       </c>
       <c r="G780" t="n">
-        <v>25.6209678649902</v>
+        <v>25.6209697723389</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>25.532621383667</v>
+        <v>25.5326194763184</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G784" t="n">
-        <v>23.9423542022705</v>
+        <v>23.9423522949219</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>24.6491394042969</v>
+        <v>24.6491374969482</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>27</v>
       </c>
       <c r="G786" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>26</v>
       </c>
       <c r="G792" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>26</v>
       </c>
       <c r="G793" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>26</v>
       </c>
       <c r="G794" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>28.5</v>
       </c>
       <c r="G796" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>28.5</v>
       </c>
       <c r="G797" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G798" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>25.4490051269531</v>
+        <v>25.4490032196045</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>24.1900444030762</v>
+        <v>24.1900424957275</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>28</v>
       </c>
       <c r="G805" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>27</v>
       </c>
       <c r="G808" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>27.5</v>
       </c>
       <c r="G809" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>27</v>
       </c>
       <c r="G810" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>27</v>
       </c>
       <c r="G811" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>24.100118637085</v>
+        <v>24.1001167297363</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>27.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>27.5</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>27.5</v>
       </c>
       <c r="G820" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>27.5</v>
       </c>
       <c r="G821" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>26.5</v>
       </c>
       <c r="G823" t="n">
-        <v>23.8303394317627</v>
+        <v>23.8303413391113</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G825" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>25.5</v>
       </c>
       <c r="G839" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>25.5</v>
       </c>
       <c r="G840" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>22.6613063812256</v>
+        <v>22.661304473877</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>22.1217498779297</v>
+        <v>22.1217517852783</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>25</v>
       </c>
       <c r="G849" t="n">
-        <v>22.4814510345459</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>21.4023418426514</v>
+        <v>21.40234375</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G855" t="n">
-        <v>20.4131622314453</v>
+        <v>20.4131603240967</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>19.5139007568359</v>
+        <v>19.5139026641846</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>20.5930099487305</v>
+        <v>20.5930118560791</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>25</v>
       </c>
       <c r="G869" t="n">
-        <v>22.4814510345459</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.3915252685547</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>22.3016014099121</v>
+        <v>22.3015995025635</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>25.5</v>
       </c>
       <c r="G873" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>21.4922695159912</v>
+        <v>21.4922676086426</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>23</v>
       </c>
       <c r="G878" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>20.5930099487305</v>
+        <v>20.5930118560791</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>19.1541976928711</v>
+        <v>19.1541957855225</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>23</v>
       </c>
       <c r="G890" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>27</v>
       </c>
       <c r="G893" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>23.110933303833</v>
+        <v>23.1109352111816</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>25.5</v>
       </c>
       <c r="G899" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>22.5713806152344</v>
+        <v>22.5713787078857</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>21.9418983459473</v>
+        <v>21.9418964385986</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>22.1217498779297</v>
+        <v>22.1217517852783</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.3915252685547</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>25.5</v>
       </c>
       <c r="G909" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>22.3016014099121</v>
+        <v>22.3015995025635</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.3915252685547</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>21.9418983459473</v>
+        <v>21.9418964385986</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>25</v>
       </c>
       <c r="G917" t="n">
-        <v>22.4814510345459</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>23.110933303833</v>
+        <v>23.1109352111816</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>23.110933303833</v>
+        <v>23.1109352111816</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>22.5713806152344</v>
+        <v>22.5713787078857</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G932" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G934" t="n">
-        <v>25.0893020629883</v>
+        <v>25.0893001556396</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G935" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.988561630249</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>25.0893020629883</v>
+        <v>25.0893001556396</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>28.5</v>
       </c>
       <c r="G947" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288585662842</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.988561630249</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>26.7978916168213</v>
+        <v>26.7978935241699</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.988561630249</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>30.5</v>
       </c>
       <c r="G956" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>28.4165573120117</v>
+        <v>28.4165592193604</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>30.5</v>
       </c>
       <c r="G961" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>27.1575946807861</v>
+        <v>27.1575984954834</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>28.5</v>
       </c>
       <c r="G971" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288585662842</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.988561630249</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>26.1684112548828</v>
+        <v>26.1684131622314</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G981" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>28</v>
       </c>
       <c r="G982" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>24.8195247650146</v>
+        <v>24.819522857666</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>24.9993743896484</v>
+        <v>24.9993762969971</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>24.9993743896484</v>
+        <v>24.9993762969971</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>27.5</v>
       </c>
       <c r="G989" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>28</v>
       </c>
       <c r="G990" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>24.9993743896484</v>
+        <v>24.9993762969971</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>25.0893020629883</v>
+        <v>25.0893001556396</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>28</v>
       </c>
       <c r="G996" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>28.5</v>
       </c>
       <c r="G999" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288585662842</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>28</v>
       </c>
       <c r="G1000" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>25.808708190918</v>
+        <v>25.8087062835693</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>25.808708190918</v>
+        <v>25.8087062835693</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1003" t="n">
-        <v>25.808708190918</v>
+        <v>25.8087062835693</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>28</v>
       </c>
       <c r="G1005" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>27.5</v>
       </c>
       <c r="G1007" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>24.8195247650146</v>
+        <v>24.819522857666</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>24.9993743896484</v>
+        <v>24.9993762969971</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>26.4381866455078</v>
+        <v>26.4381885528564</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>27.1575946807861</v>
+        <v>27.1575984954834</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1019" t="n">
-        <v>28.0568523406982</v>
+        <v>28.0568542480469</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>27.517297744751</v>
+        <v>27.5172996520996</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>31</v>
       </c>
       <c r="G1023" t="n">
-        <v>27.8770046234131</v>
+        <v>27.8770027160645</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>28.2367057800293</v>
+        <v>28.2367038726807</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>29.0460357666016</v>
+        <v>29.0460376739502</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1032" t="n">
-        <v>30.0352230072021</v>
+        <v>30.0352210998535</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>28.9561138153076</v>
+        <v>28.956111907959</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1038" t="n">
-        <v>30.8445529937744</v>
+        <v>30.844554901123</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1039" t="n">
-        <v>30.3949241638184</v>
+        <v>30.3949222564697</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639572143555</v>
+        <v>31.5639610290527</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.833740234375</v>
+        <v>31.8337364196777</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2941837310791</v>
+        <v>31.2941799163818</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>31.2941837310791</v>
+        <v>31.2941799163818</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042560577393</v>
+        <v>31.2042541503906</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>30.9344825744629</v>
+        <v>30.9344844818115</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>30.3949241638184</v>
+        <v>30.3949222564697</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150688171387</v>
+        <v>30.2150707244873</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1055" t="n">
-        <v>29.945291519165</v>
+        <v>29.9452934265137</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -50176,7 +50176,7 @@
         <v>47.5</v>
       </c>
       <c r="D1916" t="n">
-        <v>46.4000015258789</v>
+        <v>46.2000007629395</v>
       </c>
       <c r="E1916" t="n">
         <v>46.9000015258789</v>
@@ -50188,6 +50188,32 @@
         <v>46.2000007629395</v>
       </c>
       <c r="H1916" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1917" t="n">
+        <v>1662</v>
+      </c>
+      <c r="C1917" t="n">
+        <v>46.7999992370605</v>
+      </c>
+      <c r="D1917" t="n">
+        <v>46</v>
+      </c>
+      <c r="E1917" t="n">
+        <v>46.7000007629395</v>
+      </c>
+      <c r="F1917" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G1917" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H1917" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.28757953643799</v>
+        <v>9.2875804901123</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>9.58128833770752</v>
+        <v>9.58128929138184</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293743133545</v>
+        <v>9.88293647766113</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.76386547088623</v>
+        <v>9.76386642456055</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G6" t="n">
-        <v>9.78767967224121</v>
+        <v>9.78768062591553</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>9.67654705047607</v>
+        <v>9.67654609680176</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>9.39871406555176</v>
+        <v>9.39871215820312</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52572154998779</v>
+        <v>9.52572250366211</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44633960723877</v>
+        <v>9.44634056091309</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.75</v>
       </c>
       <c r="G13" t="n">
-        <v>9.32726955413818</v>
+        <v>9.32727146148682</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.9146900177002</v>
+        <v>9.91468811035156</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G21" t="n">
-        <v>10.2083978652954</v>
+        <v>10.208399772644</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2719030380249</v>
+        <v>10.2719049453735</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>10.2083978652954</v>
+        <v>10.208399772644</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5259237289429</v>
+        <v>10.5259246826172</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3989124298096</v>
+        <v>10.3989143371582</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G28" t="n">
-        <v>10.2560272216797</v>
+        <v>10.256028175354</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>10.5576763153076</v>
+        <v>10.5576753616333</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>10.5576763153076</v>
+        <v>10.5576753616333</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7005605697632</v>
+        <v>10.7005615234375</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>10.510046005249</v>
+        <v>10.5100469589233</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588312149048</v>
+        <v>11.0588321685791</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419801712036</v>
+        <v>11.1419792175293</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G39" t="n">
-        <v>10.842643737793</v>
+        <v>10.8426427841187</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>10.6264553070068</v>
+        <v>10.6264562606812</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G50" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G54" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G59" t="n">
-        <v>10.3271207809448</v>
+        <v>10.3271188735962</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>9.84485530853271</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G67" t="n">
-        <v>9.44573879241943</v>
+        <v>9.44573783874512</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G77" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G78" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>9.77833461761475</v>
+        <v>9.77833557128906</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>9.67855739593506</v>
+        <v>9.67855644226074</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G85" t="n">
-        <v>9.67855739593506</v>
+        <v>9.67855644226074</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>9.49562740325928</v>
+        <v>9.49562835693359</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G87" t="n">
-        <v>9.49562740325928</v>
+        <v>9.49562835693359</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.5</v>
       </c>
       <c r="G88" t="n">
-        <v>9.56214809417725</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.56214809417725</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G98" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12</v>
       </c>
       <c r="G101" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G103" t="n">
-        <v>9.74507427215576</v>
+        <v>9.74507522583008</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G104" t="n">
-        <v>9.74507427215576</v>
+        <v>9.74507522583008</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.77833461761475</v>
+        <v>9.77833557128906</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>9.77833461761475</v>
+        <v>9.77833557128906</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G109" t="n">
-        <v>9.61203765869141</v>
+        <v>9.61203670501709</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12</v>
       </c>
       <c r="G113" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12</v>
       </c>
       <c r="G114" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G116" t="n">
-        <v>9.84485530853271</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12</v>
       </c>
       <c r="G117" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12</v>
       </c>
       <c r="G123" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>10.3936395645142</v>
+        <v>10.3936376571655</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>10.4601583480835</v>
+        <v>10.4601573944092</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G133" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0277824401855</v>
+        <v>10.0277833938599</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12</v>
       </c>
       <c r="G138" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>9.82822608947754</v>
+        <v>9.82822513580322</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G147" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3936395645142</v>
+        <v>10.3936376571655</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G173" t="n">
-        <v>10.0277824401855</v>
+        <v>10.0277833938599</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126365661621</v>
+        <v>9.96126270294189</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12</v>
       </c>
       <c r="G178" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12</v>
       </c>
       <c r="G179" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G181" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12</v>
       </c>
       <c r="G186" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G191" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G195" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G196" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G200" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G205" t="n">
-        <v>9.84485530853271</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>12</v>
       </c>
       <c r="G211" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="G213" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G215" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>12</v>
       </c>
       <c r="G221" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="G222" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12</v>
       </c>
       <c r="G226" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603792190552</v>
+        <v>10.3603782653809</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G231" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G234" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G235" t="n">
-        <v>9.99452209472656</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G236" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2606000900269</v>
+        <v>10.2605991363525</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.17966079711914</v>
+        <v>9.17966175079346</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41247844696045</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41247844696045</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>11.5</v>
       </c>
       <c r="G249" t="n">
-        <v>9.56214809417725</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.1131420135498</v>
+        <v>9.11314296722412</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>8.66413688659668</v>
+        <v>8.66413879394531</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>8.44794940948486</v>
+        <v>8.44794845581055</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G256" t="n">
-        <v>7.42521572113037</v>
+        <v>7.42521667480469</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568441390991</v>
+        <v>7.9656834602356</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>8.03220367431641</v>
+        <v>8.03220462799072</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>8.03220367431641</v>
+        <v>8.03220462799072</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G271" t="n">
-        <v>8.3980598449707</v>
+        <v>8.39805889129639</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>8.9801025390625</v>
+        <v>8.98010349273682</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>8.9801025390625</v>
+        <v>8.98010349273682</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36393070220947</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211483001709</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.5</v>
       </c>
       <c r="G293" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G298" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10</v>
       </c>
       <c r="G305" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10</v>
       </c>
       <c r="G307" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10</v>
       </c>
       <c r="G308" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10</v>
       </c>
       <c r="G310" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G311" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.5</v>
       </c>
       <c r="G313" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.5</v>
       </c>
       <c r="G314" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.5</v>
       </c>
       <c r="G315" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G316" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10</v>
       </c>
       <c r="G319" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G321" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G322" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G323" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G328" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G352" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G353" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>10</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G363" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.20417785644531</v>
+        <v>8.204176902771</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>8.50485324859619</v>
+        <v>8.50485420227051</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="G383" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10</v>
       </c>
       <c r="G386" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>10</v>
       </c>
       <c r="G399" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G405" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>10</v>
       </c>
       <c r="G408" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>10</v>
       </c>
       <c r="G409" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G425" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G426" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257705688477</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211483001709</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36393070220947</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211483001709</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211483001709</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>11.5</v>
       </c>
       <c r="G438" t="n">
-        <v>9.87937450408936</v>
+        <v>9.87937545776367</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>11.5</v>
       </c>
       <c r="G442" t="n">
-        <v>9.87937450408936</v>
+        <v>9.87937545776367</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G457" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>9.6216516494751</v>
+        <v>9.62165260314941</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>11.5</v>
       </c>
       <c r="G464" t="n">
-        <v>9.87937450408936</v>
+        <v>9.87937545776367</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G477" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0511903762817</v>
+        <v>10.0511894226074</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0511903762817</v>
+        <v>10.0511894226074</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.5</v>
       </c>
       <c r="G485" t="n">
-        <v>10.7384519577026</v>
+        <v>10.7384510040283</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>10.7384519577026</v>
+        <v>10.7384510040283</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.9102668762207</v>
+        <v>10.9102659225464</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.9102668762207</v>
+        <v>10.9102659225464</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>10.9102668762207</v>
+        <v>10.9102659225464</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>11.339804649353</v>
+        <v>11.3398036956787</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G498" t="n">
-        <v>11.339804649353</v>
+        <v>11.3398036956787</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>11.9411582946777</v>
+        <v>11.9411563873291</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>12.198881149292</v>
+        <v>12.1988801956177</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>12.1129741668701</v>
+        <v>12.1129732131958</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>12.7143278121948</v>
+        <v>12.7143259048462</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G508" t="n">
-        <v>12.7143278121948</v>
+        <v>12.7143259048462</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>13.0579566955566</v>
+        <v>13.0579557418823</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>13.0579566955566</v>
+        <v>13.0579557418823</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>12.9720487594604</v>
+        <v>12.9720497131348</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>12.9720487594604</v>
+        <v>12.9720497131348</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9720487594604</v>
+        <v>12.9720497131348</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G514" t="n">
-        <v>13.0579566955566</v>
+        <v>13.0579557418823</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>13.9170322418213</v>
+        <v>13.9170331954956</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>16.5</v>
       </c>
       <c r="G519" t="n">
-        <v>14.1747541427612</v>
+        <v>14.1747560501099</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>14.2606639862061</v>
+        <v>14.2606630325317</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324779510498</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>16.5</v>
       </c>
       <c r="G522" t="n">
-        <v>14.1747541427612</v>
+        <v>14.1747560501099</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>14.2606639862061</v>
+        <v>14.2606630325317</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>14.3465709686279</v>
+        <v>14.3465719223022</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324779510498</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042928695679</v>
+        <v>14.6042938232422</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>18</v>
       </c>
       <c r="G529" t="n">
-        <v>15.4633703231812</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>18</v>
       </c>
       <c r="G531" t="n">
-        <v>15.4633703231812</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056493759155</v>
+        <v>15.2056474685669</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>15.119740486145</v>
+        <v>15.1197385787964</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>18</v>
       </c>
       <c r="G534" t="n">
-        <v>15.4633703231812</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="n">
-        <v>15.4633703231812</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.5492792129517</v>
+        <v>15.5492782592773</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376266479492</v>
+        <v>15.6376276016235</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G541" t="n">
-        <v>15.1958856582642</v>
+        <v>15.1958847045898</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.5492792129517</v>
+        <v>15.549277305603</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>15.81432056427</v>
+        <v>15.8143215179443</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>16.0793685913086</v>
+        <v>16.07936668396</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>16.1677150726318</v>
+        <v>16.1677169799805</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>16.9628467559814</v>
+        <v>16.9628486633301</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230274200439</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>18.1997241973877</v>
+        <v>18.1997222900391</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G561" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230274200439</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>19.0832061767578</v>
+        <v>19.0832042694092</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>22</v>
       </c>
       <c r="G565" t="n">
-        <v>19.4365978240967</v>
+        <v>19.436595916748</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230274200439</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>17.4929370880127</v>
+        <v>17.4929389953613</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230274200439</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278919219971</v>
+        <v>17.2278938293457</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>19</v>
       </c>
       <c r="G576" t="n">
-        <v>16.7861499786377</v>
+        <v>16.7861518859863</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>17.051197052002</v>
+        <v>17.0511951446533</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>17.3162422180176</v>
+        <v>17.3162403106689</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>19</v>
       </c>
       <c r="G581" t="n">
-        <v>16.7861499786377</v>
+        <v>16.7861518859863</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>17.051197052002</v>
+        <v>17.0511951446533</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>17.4929370880127</v>
+        <v>17.4929389953613</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>17.4045886993408</v>
+        <v>17.4045906066895</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>18.9065055847168</v>
+        <v>18.9065074920654</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>20.6734714508057</v>
+        <v>20.673469543457</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>19.2599010467529</v>
+        <v>19.2599029541016</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G599" t="n">
-        <v>19.2599010467529</v>
+        <v>19.2599029541016</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>19.2599010467529</v>
+        <v>19.2599029541016</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>22</v>
       </c>
       <c r="G601" t="n">
-        <v>19.4365978240967</v>
+        <v>19.436595916748</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>23</v>
       </c>
       <c r="G603" t="n">
-        <v>20.3200759887695</v>
+        <v>20.3200798034668</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G606" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>23.6773071289062</v>
+        <v>23.6773090362549</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G616" t="n">
-        <v>24.5607891082764</v>
+        <v>24.5607872009277</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="G617" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540077209473</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472206115723</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="G622" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540077209473</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>24.5607891082764</v>
+        <v>24.5607872009277</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0985584259033</v>
+        <v>31.0985546112061</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.5684623718262</v>
+        <v>30.5684642791748</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>30.5684623718262</v>
+        <v>30.5684642791748</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G638" t="n">
-        <v>30.3917713165283</v>
+        <v>30.3917694091797</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082874298096</v>
+        <v>29.5082893371582</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>25.2675743103027</v>
+        <v>25.267578125</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33</v>
       </c>
       <c r="G663" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548957824707</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G665" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>28.9781970977783</v>
+        <v>28.978199005127</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>28.9781970977783</v>
+        <v>28.978199005127</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>33</v>
       </c>
       <c r="G674" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548957824707</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33</v>
       </c>
       <c r="G677" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548957824707</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>31</v>
       </c>
       <c r="G689" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>25.2675743103027</v>
+        <v>25.267578125</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>25.9743633270264</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>31</v>
       </c>
       <c r="G703" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G707" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>30</v>
       </c>
       <c r="G708" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>25.9743633270264</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>31</v>
       </c>
       <c r="G715" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>31</v>
       </c>
       <c r="G716" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>30</v>
       </c>
       <c r="G720" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>30</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>25.9743633270264</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G729" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>25.9743633270264</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>24.5607891082764</v>
+        <v>24.5607872009277</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>24.5607891082764</v>
+        <v>24.5607872009277</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>24.9141864776611</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>24.5607891082764</v>
+        <v>24.5607872009277</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>24.9141864776611</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>28</v>
       </c>
       <c r="G741" t="n">
-        <v>24.7374839782715</v>
+        <v>24.7374877929688</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>29</v>
       </c>
       <c r="G743" t="n">
-        <v>25.6209678649902</v>
+        <v>25.6209659576416</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>25.2675743103027</v>
+        <v>25.267578125</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>24.5607891082764</v>
+        <v>24.5607872009277</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>27</v>
       </c>
       <c r="G749" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540077209473</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>23.6773071289062</v>
+        <v>23.6773090362549</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>23.6773071289062</v>
+        <v>23.6773090362549</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>20.8501663208008</v>
+        <v>20.8501682281494</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540077209473</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>24.9141864776611</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>24.5607891082764</v>
+        <v>24.5607872009277</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>28</v>
       </c>
       <c r="G764" t="n">
-        <v>24.7374839782715</v>
+        <v>24.7374877929688</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>28</v>
       </c>
       <c r="G765" t="n">
-        <v>24.7374839782715</v>
+        <v>24.7374877929688</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>25.9743633270264</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>30</v>
       </c>
       <c r="G771" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>26.3277530670166</v>
+        <v>26.3277549743652</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>29</v>
       </c>
       <c r="G780" t="n">
-        <v>25.6209678649902</v>
+        <v>25.6209659576416</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G784" t="n">
-        <v>23.9423542022705</v>
+        <v>23.9423522949219</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>24.6491374969482</v>
+        <v>24.6491394042969</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>27</v>
       </c>
       <c r="G786" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540077209473</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G787" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472206115723</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>22.7054805755615</v>
+        <v>22.7054786682129</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G798" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>25.4490032196045</v>
+        <v>25.4490051269531</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>24.1900444030762</v>
+        <v>24.1900424957275</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>28</v>
       </c>
       <c r="G805" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>27</v>
       </c>
       <c r="G808" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>27.5</v>
       </c>
       <c r="G809" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>27</v>
       </c>
       <c r="G810" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>27</v>
       </c>
       <c r="G811" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>23.7404155731201</v>
+        <v>23.7404117584229</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>24.1001167297363</v>
+        <v>24.100118637085</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>27.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>27.5</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>27.5</v>
       </c>
       <c r="G820" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>27.5</v>
       </c>
       <c r="G821" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>23.7404155731201</v>
+        <v>23.7404117584229</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G825" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>24.3698959350586</v>
+        <v>24.36989402771</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>24.3698959350586</v>
+        <v>24.36989402771</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>25.5</v>
       </c>
       <c r="G839" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>25.5</v>
       </c>
       <c r="G840" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>21.6721229553223</v>
+        <v>21.6721210479736</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>20.9527149200439</v>
+        <v>20.9527130126953</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>20.9527149200439</v>
+        <v>20.9527130126953</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G855" t="n">
-        <v>20.4131622314453</v>
+        <v>20.4131603240967</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>22</v>
       </c>
       <c r="G856" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>22</v>
       </c>
       <c r="G857" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>19.5139007568359</v>
+        <v>19.5139026641846</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038284301758</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>19.4239768981934</v>
+        <v>19.4239749908447</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>19.693754196167</v>
+        <v>19.6937503814697</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038284301758</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038284301758</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G868" t="n">
-        <v>21.6721229553223</v>
+        <v>21.6721210479736</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>25.5</v>
       </c>
       <c r="G873" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>21.4922676086426</v>
+        <v>21.4922695159912</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>23</v>
       </c>
       <c r="G878" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829395294189</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>22</v>
       </c>
       <c r="G882" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G883" t="n">
-        <v>19.4239768981934</v>
+        <v>19.4239749908447</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>19.1541976928711</v>
+        <v>19.1541957855225</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>22</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>22</v>
       </c>
       <c r="G886" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>22</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>22</v>
       </c>
       <c r="G888" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>22</v>
       </c>
       <c r="G889" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>23</v>
       </c>
       <c r="G890" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829395294189</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>23.5</v>
       </c>
       <c r="G891" t="n">
-        <v>21.1325645446777</v>
+        <v>21.1325664520264</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>27</v>
       </c>
       <c r="G893" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>23.1109352111816</v>
+        <v>23.110933303833</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>25.5</v>
       </c>
       <c r="G899" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>22.5713806152344</v>
+        <v>22.5713787078857</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>21.9418983459473</v>
+        <v>21.9419002532959</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>25.5</v>
       </c>
       <c r="G909" t="n">
-        <v>22.9310836791992</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>21.9418983459473</v>
+        <v>21.9419002532959</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>23.1109352111816</v>
+        <v>23.110933303833</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>23.1109352111816</v>
+        <v>23.110933303833</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>22.5713806152344</v>
+        <v>22.5713787078857</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G932" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G935" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.9885578155518</v>
+        <v>25.988561630249</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>29</v>
       </c>
       <c r="G937" t="n">
-        <v>26.0784854888916</v>
+        <v>26.078483581543</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>29</v>
       </c>
       <c r="G945" t="n">
-        <v>26.0784854888916</v>
+        <v>26.078483581543</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>28.5</v>
       </c>
       <c r="G947" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288547515869</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.9885578155518</v>
+        <v>25.988561630249</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>26.7978897094727</v>
+        <v>26.7978916168213</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.9885578155518</v>
+        <v>25.988561630249</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>28.4165573120117</v>
+        <v>28.4165554046631</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G959" t="n">
-        <v>29.3158149719238</v>
+        <v>29.3158130645752</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G960" t="n">
-        <v>29.1359634399414</v>
+        <v>29.13596534729</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>28.5</v>
       </c>
       <c r="G971" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288547515869</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>29</v>
       </c>
       <c r="G972" t="n">
-        <v>26.0784854888916</v>
+        <v>26.078483581543</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>29</v>
       </c>
       <c r="G973" t="n">
-        <v>26.0784854888916</v>
+        <v>26.078483581543</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.9885578155518</v>
+        <v>25.988561630249</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G981" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>28</v>
       </c>
       <c r="G982" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>24.9993762969971</v>
+        <v>24.9993724822998</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>24.9993762969971</v>
+        <v>24.9993724822998</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>27.5</v>
       </c>
       <c r="G989" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>28</v>
       </c>
       <c r="G990" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>24.9993762969971</v>
+        <v>24.9993724822998</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>28</v>
       </c>
       <c r="G996" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>28.5</v>
       </c>
       <c r="G999" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288547515869</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>28</v>
       </c>
       <c r="G1000" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>28</v>
       </c>
       <c r="G1005" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>27.5</v>
       </c>
       <c r="G1007" t="n">
-        <v>24.7295970916748</v>
+        <v>24.7295989990234</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>24.9993762969971</v>
+        <v>24.9993724822998</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>26.8878192901611</v>
+        <v>26.8878173828125</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>31.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>28.3266296386719</v>
+        <v>28.3266315460205</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>34</v>
       </c>
       <c r="G1022" t="n">
-        <v>30.5747737884521</v>
+        <v>30.5747756958008</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>28.1467800140381</v>
+        <v>28.1467781066895</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>29.405740737915</v>
+        <v>29.4057426452637</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>29.0460376739502</v>
+        <v>29.0460357666016</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1030" t="n">
-        <v>29.7654438018799</v>
+        <v>29.7654418945312</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251487731934</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1032" t="n">
-        <v>30.0352191925049</v>
+        <v>30.0352230072021</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1035" t="n">
-        <v>29.1359634399414</v>
+        <v>29.13596534729</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1037" t="n">
-        <v>29.1359634399414</v>
+        <v>29.13596534729</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639553070068</v>
+        <v>31.5639610290527</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.8337383270264</v>
+        <v>31.833740234375</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2941818237305</v>
+        <v>31.2941837310791</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>31.2941818237305</v>
+        <v>31.2941837310791</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042579650879</v>
+        <v>31.2042560577393</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251487731934</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1048" t="n">
-        <v>29.7654438018799</v>
+        <v>29.7654418945312</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3049964904785</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251487731934</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150726318359</v>
+        <v>30.2150707244873</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3049964904785</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1055" t="n">
-        <v>29.9452934265137</v>
+        <v>29.9452953338623</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1058" t="n">
-        <v>29.405740737915</v>
+        <v>29.4057426452637</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>33</v>
       </c>
       <c r="G1064" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765163421631</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>33</v>
       </c>
       <c r="G1065" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765163421631</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>30.0083122253418</v>
+        <v>30.0083141326904</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>31.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>31.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>31.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1089" t="n">
-        <v>28.8116645812988</v>
+        <v>28.8116626739502</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>31.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>31.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>27.9832134246826</v>
+        <v>27.983211517334</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1102" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1118" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>33</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765163421631</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>30.0083122253418</v>
+        <v>30.0083141326904</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>33</v>
       </c>
       <c r="G1126" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765163421631</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1127" t="n">
-        <v>30.0083122253418</v>
+        <v>30.0083141326904</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1140" t="n">
-        <v>28.8116645812988</v>
+        <v>28.8116626739502</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1146" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>27.2468128204346</v>
+        <v>27.2468147277832</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1159" t="n">
-        <v>27.3388652801514</v>
+        <v>27.3388633728027</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1162" t="n">
-        <v>27.2468128204346</v>
+        <v>27.2468147277832</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>28.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>28.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>27.5</v>
       </c>
       <c r="G1169" t="n">
-        <v>25.3137607574463</v>
+        <v>25.3137626647949</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>25.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>23.4727630615234</v>
+        <v>23.4727611541748</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.1045627593994</v>
+        <v>23.1045608520508</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>25.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.4727630615234</v>
+        <v>23.4727611541748</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>28.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1198" t="n">
-        <v>25.5899124145508</v>
+        <v>25.5899105072021</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>27</v>
       </c>
       <c r="G1201" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>27</v>
       </c>
       <c r="G1208" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1210" t="n">
-        <v>26.5104122161865</v>
+        <v>26.5104141235352</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>28.5</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5104122161865</v>
+        <v>26.5104141235352</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1213" t="n">
-        <v>27.3388652801514</v>
+        <v>27.3388633728027</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.4309120178223</v>
+        <v>27.4309139251709</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.7865619659424</v>
+        <v>26.786563873291</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>26.7865619659424</v>
+        <v>26.786563873291</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>28.5</v>
       </c>
       <c r="G1220" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>29</v>
       </c>
       <c r="G1223" t="n">
-        <v>26.6945152282715</v>
+        <v>26.6945114135742</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>26.9706649780273</v>
+        <v>26.9706630706787</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.3388652801514</v>
+        <v>27.3388633728027</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>29.5</v>
       </c>
       <c r="G1226" t="n">
-        <v>27.154764175415</v>
+        <v>27.1547660827637</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.2468128204346</v>
+        <v>27.2468147277832</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>28</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.7740116119385</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>28.5</v>
       </c>
       <c r="G1231" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>28</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.7740116119385</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>27.5</v>
       </c>
       <c r="G1240" t="n">
-        <v>25.3137607574463</v>
+        <v>25.3137626647949</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>27</v>
       </c>
       <c r="G1242" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>27</v>
       </c>
       <c r="G1251" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>27</v>
       </c>
       <c r="G1252" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>27</v>
       </c>
       <c r="G1261" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>26.9706649780273</v>
+        <v>26.9706630706787</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1268" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1271" t="n">
-        <v>28.8116645812988</v>
+        <v>28.8116626739502</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1273" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>31.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606136322021</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606136322021</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>33</v>
       </c>
       <c r="G1285" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765163421631</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1287" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.0208644866943</v>
+        <v>31.020866394043</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1289" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1290" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.7447147369385</v>
+        <v>30.7447166442871</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1294" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>33</v>
       </c>
       <c r="G1295" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765163421631</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526660919189</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>33</v>
       </c>
       <c r="G1297" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765163421631</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526660919189</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.8367671966553</v>
+        <v>30.836763381958</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606136322021</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>31.1129169464111</v>
+        <v>31.1129150390625</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606136322021</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526660919189</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>33</v>
       </c>
       <c r="G1308" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765163421631</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1312" t="n">
-        <v>29.1798667907715</v>
+        <v>29.1798648834229</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.0954246520996</v>
+        <v>29.095422744751</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851486206055</v>
+        <v>33.7851448059082</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095977783203</v>
+        <v>31.0095996856689</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>27</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>26.5112915039062</v>
+        <v>26.5112934112549</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.6499118804932</v>
+        <v>25.6499137878418</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>25.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.4057025909424</v>
+        <v>24.4057006835938</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7456226348877</v>
+        <v>25.7456207275391</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>29</v>
       </c>
       <c r="G1554" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>29</v>
       </c>
       <c r="G1555" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1570" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -50266,6 +50266,32 @@
         <v>45.2000007629395</v>
       </c>
       <c r="H1919" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1920" t="n">
+        <v>3567</v>
+      </c>
+      <c r="C1920" t="n">
+        <v>46</v>
+      </c>
+      <c r="D1920" t="n">
+        <v>45.2999992370605</v>
+      </c>
+      <c r="E1920" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1920" t="n">
+        <v>45.7999992370605</v>
+      </c>
+      <c r="G1920" t="n">
+        <v>45.7999992370605</v>
+      </c>
+      <c r="H1920" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44589,13 +44589,36 @@
         <v>44.7999992370605</v>
       </c>
       <c r="D1923" t="n">
-        <v>43.4000015258789</v>
+        <v>43.2000007629395</v>
       </c>
       <c r="E1923" t="n">
         <v>44.7000007629395</v>
       </c>
-      <c r="F1923"/>
+      <c r="F1923" t="n">
+        <v>43.2000007629395</v>
+      </c>
       <c r="G1923" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1924" t="n">
+        <v>8489</v>
+      </c>
+      <c r="C1924" t="n">
+        <v>44.7000007629395</v>
+      </c>
+      <c r="D1924" t="n">
+        <v>42.5999984741211</v>
+      </c>
+      <c r="E1924" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1924"/>
+      <c r="G1924" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44617,8 +44617,31 @@
       <c r="E1924" t="n">
         <v>43</v>
       </c>
-      <c r="F1924"/>
+      <c r="F1924" t="n">
+        <v>44</v>
+      </c>
       <c r="G1924" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1925" t="n">
+        <v>19486</v>
+      </c>
+      <c r="C1925" t="n">
+        <v>45.4000015258789</v>
+      </c>
+      <c r="D1925" t="n">
+        <v>43.5999984741211</v>
+      </c>
+      <c r="E1925" t="n">
+        <v>44.5999984741211</v>
+      </c>
+      <c r="F1925"/>
+      <c r="G1925" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44635,13 +44635,36 @@
         <v>45.4000015258789</v>
       </c>
       <c r="D1925" t="n">
-        <v>43.5999984741211</v>
+        <v>43.2000007629395</v>
       </c>
       <c r="E1925" t="n">
         <v>44.5999984741211</v>
       </c>
-      <c r="F1925"/>
+      <c r="F1925" t="n">
+        <v>43.2000007629395</v>
+      </c>
       <c r="G1925" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1926" t="n">
+        <v>3978</v>
+      </c>
+      <c r="C1926" t="n">
+        <v>44.4000015258789</v>
+      </c>
+      <c r="D1926" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E1926" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F1926"/>
+      <c r="G1926" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44663,8 +44663,31 @@
       <c r="E1926" t="n">
         <v>43.5</v>
       </c>
-      <c r="F1926"/>
+      <c r="F1926" t="n">
+        <v>43.5999984741211</v>
+      </c>
       <c r="G1926" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1927" t="n">
+        <v>6197</v>
+      </c>
+      <c r="C1927" t="n">
+        <v>46.2000007629395</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>43.9000015258789</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>44.2000007629395</v>
+      </c>
+      <c r="F1927"/>
+      <c r="G1927" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -44693,6 +44693,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1928">
+      <c r="A1928" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1928" t="n">
+        <v>9498</v>
+      </c>
+      <c r="C1928" t="n">
+        <v>46.7000007629395</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>43.7000007629395</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>46.7000007629395</v>
+      </c>
+      <c r="F1928" t="n">
+        <v>43.7000007629395</v>
+      </c>
+      <c r="G1928" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.28757953643799</v>
+        <v>9.28757762908936</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>9.58128833770752</v>
+        <v>9.58129024505615</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293743133545</v>
+        <v>9.88293647766113</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.76386642456055</v>
+        <v>9.76386547088623</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>9.67654705047607</v>
+        <v>9.67654609680176</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>9.60510349273682</v>
+        <v>9.6051025390625</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>9.39871215820312</v>
+        <v>9.39871311187744</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52572154998779</v>
+        <v>9.52572250366211</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.75</v>
       </c>
       <c r="G13" t="n">
-        <v>9.3272705078125</v>
+        <v>9.32726955413818</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.9146900177002</v>
+        <v>9.91468811035156</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2719030380249</v>
+        <v>10.2719039916992</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5259237289429</v>
+        <v>10.5259246826172</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>10.1925220489502</v>
+        <v>10.1925230026245</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>13.5</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7164373397827</v>
+        <v>10.716438293457</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7005615234375</v>
+        <v>10.7005624771118</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>10.5100479125977</v>
+        <v>10.5100469589233</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588321685791</v>
+        <v>11.0588302612305</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419811248779</v>
+        <v>11.1419792175293</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G38" t="n">
-        <v>11.1087198257446</v>
+        <v>11.1087207794189</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G39" t="n">
-        <v>10.8426446914673</v>
+        <v>10.8426427841187</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>10.6264562606812</v>
+        <v>10.6264553070068</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G43" t="n">
-        <v>10.6763458251953</v>
+        <v>10.6763467788696</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>10.6763458251953</v>
+        <v>10.6763467788696</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G47" t="n">
-        <v>10.34375</v>
+        <v>10.3437490463257</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G50" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G54" t="n">
-        <v>9.9446325302124</v>
+        <v>9.94463348388672</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G56" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>10.2772274017334</v>
+        <v>10.2772302627563</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485530853271</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.4789981842041</v>
+        <v>9.47899723052979</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G70" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G77" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G78" t="n">
-        <v>9.9446325302124</v>
+        <v>9.94463348388672</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G80" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>9.77833461761475</v>
+        <v>9.77833652496338</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>9.49562740325928</v>
+        <v>9.49562931060791</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G87" t="n">
-        <v>9.49562740325928</v>
+        <v>9.49562931060791</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.5</v>
       </c>
       <c r="G88" t="n">
-        <v>9.56214809417725</v>
+        <v>9.56214618682861</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.56214809417725</v>
+        <v>9.56214618682861</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G98" t="n">
-        <v>9.9446325302124</v>
+        <v>9.94463348388672</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12</v>
       </c>
       <c r="G101" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G103" t="n">
-        <v>9.74507427215576</v>
+        <v>9.74507522583008</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G104" t="n">
-        <v>9.74507427215576</v>
+        <v>9.74507522583008</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.77833461761475</v>
+        <v>9.77833652496338</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>9.77833461761475</v>
+        <v>9.77833652496338</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G109" t="n">
-        <v>9.61203765869141</v>
+        <v>9.61203670501709</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529609680176</v>
+        <v>9.64529705047607</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529609680176</v>
+        <v>9.64529705047607</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12</v>
       </c>
       <c r="G113" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12</v>
       </c>
       <c r="G114" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G116" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485530853271</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12</v>
       </c>
       <c r="G117" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G119" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12</v>
       </c>
       <c r="G123" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G125" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G128" t="n">
-        <v>10.2772274017334</v>
+        <v>10.2772302627563</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>10.3936386108398</v>
+        <v>10.3936376571655</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G130" t="n">
-        <v>10.2772274017334</v>
+        <v>10.2772302627563</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G133" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12</v>
       </c>
       <c r="G138" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>9.82822608947754</v>
+        <v>9.82822418212891</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G147" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>9.9446325302124</v>
+        <v>9.94463348388672</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3936386108398</v>
+        <v>10.3936376571655</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G171" t="n">
-        <v>10.2439699172974</v>
+        <v>10.2439708709717</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G175" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126365661621</v>
+        <v>9.96126174926758</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12</v>
       </c>
       <c r="G178" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12</v>
       </c>
       <c r="G179" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G181" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109323501587</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12</v>
       </c>
       <c r="G186" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>9.89474487304688</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G190" t="n">
-        <v>10.2938585281372</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G191" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G192" t="n">
-        <v>10.2938585281372</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G195" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G196" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G198" t="n">
-        <v>10.2938585281372</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G200" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G205" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485530853271</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G209" t="n">
-        <v>10.2439699172974</v>
+        <v>10.2439708709717</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>12</v>
       </c>
       <c r="G211" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="G213" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G215" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G217" t="n">
-        <v>10.34375</v>
+        <v>10.3437490463257</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2107095718384</v>
+        <v>10.2107105255127</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>12</v>
       </c>
       <c r="G221" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="G222" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>10.1940803527832</v>
+        <v>10.1940813064575</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12</v>
       </c>
       <c r="G226" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603792190552</v>
+        <v>10.3603801727295</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="n">
-        <v>9.9778938293457</v>
+        <v>9.97789096832275</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G231" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G234" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G235" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G236" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2606000900269</v>
+        <v>10.2606010437012</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G245" t="n">
-        <v>9.52888870239258</v>
+        <v>9.52888774871826</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.17966175079346</v>
+        <v>9.17966079711914</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41248035430908</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41248035430908</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>11.5</v>
       </c>
       <c r="G249" t="n">
-        <v>9.56214809417725</v>
+        <v>9.56214618682861</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.11314392089844</v>
+        <v>9.11314105987549</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>8.664137840271</v>
+        <v>8.66413688659668</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>8.48120880126953</v>
+        <v>8.48120784759521</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>8.03220367431641</v>
+        <v>8.03220272064209</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>8.03220367431641</v>
+        <v>8.03220272064209</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10</v>
       </c>
       <c r="G262" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="G264" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>8.27333545684814</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.27333545684814</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>8.27333545684814</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.48120880126953</v>
+        <v>8.48120784759521</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39806079864502</v>
+        <v>8.39805889129639</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>8.48120880126953</v>
+        <v>8.48120784759521</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>8.27333545684814</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640235900879</v>
+        <v>9.14640140533447</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640235900879</v>
+        <v>9.14640140533447</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>8.98010349273682</v>
+        <v>8.98010444641113</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>8.98010349273682</v>
+        <v>8.98010444641113</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36392879486084</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211292266846</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.5</v>
       </c>
       <c r="G293" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G298" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10</v>
       </c>
       <c r="G305" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10</v>
       </c>
       <c r="G307" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10</v>
       </c>
       <c r="G308" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10</v>
       </c>
       <c r="G310" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.5</v>
       </c>
       <c r="G313" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>10.5</v>
       </c>
       <c r="G314" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.5</v>
       </c>
       <c r="G315" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G316" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10</v>
       </c>
       <c r="G319" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>8.33303928375244</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.33303928375244</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>8.33303928375244</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>10</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.75</v>
       </c>
       <c r="G370" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.75</v>
       </c>
       <c r="G373" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.75</v>
       </c>
       <c r="G374" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599086761475</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.204176902771</v>
+        <v>8.20417785644531</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="G383" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10</v>
       </c>
       <c r="G386" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>10</v>
       </c>
       <c r="G399" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>10</v>
       </c>
       <c r="G408" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>10</v>
       </c>
       <c r="G409" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>8.59076118469238</v>
+        <v>8.59075927734375</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211292266846</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36392879486084</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211292266846</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211292266846</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>9.27802181243896</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G434" t="n">
-        <v>9.27802181243896</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>9.27802181243896</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G436" t="n">
-        <v>9.27802181243896</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>9.27802181243896</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>11.5</v>
       </c>
       <c r="G438" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>9.96528244018555</v>
+        <v>9.96528339385986</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>11.5</v>
       </c>
       <c r="G442" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>12</v>
       </c>
       <c r="G445" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12</v>
       </c>
       <c r="G446" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>12</v>
       </c>
       <c r="G447" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>12</v>
       </c>
       <c r="G449" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>10.3948202133179</v>
+        <v>10.3948221206665</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12</v>
       </c>
       <c r="G452" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G457" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>9.62165260314941</v>
+        <v>9.6216516494751</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.96528244018555</v>
+        <v>9.96528339385986</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>11.5</v>
       </c>
       <c r="G464" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.96528244018555</v>
+        <v>9.96528339385986</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>10.5666360855103</v>
+        <v>10.5666351318359</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>10.5666360855103</v>
+        <v>10.5666351318359</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>12</v>
       </c>
       <c r="G472" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G473" t="n">
-        <v>10.3948202133179</v>
+        <v>10.3948221206665</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12</v>
       </c>
       <c r="G474" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>9.96528244018555</v>
+        <v>9.96528339385986</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G477" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0511913299561</v>
+        <v>10.0511894226074</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0511913299561</v>
+        <v>10.0511894226074</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089113235474</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>13</v>
       </c>
       <c r="G493" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679887771606</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>13</v>
       </c>
       <c r="G494" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679887771606</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>13</v>
       </c>
       <c r="G495" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679887771606</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>11.339804649353</v>
+        <v>11.3398036956787</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>11.5116195678711</v>
+        <v>11.5116205215454</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G498" t="n">
-        <v>11.339804649353</v>
+        <v>11.3398036956787</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.4257116317749</v>
+        <v>11.4257106781006</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>11.8552503585815</v>
+        <v>11.8552494049072</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>12.1988792419434</v>
+        <v>12.1988801956177</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>12.3706960678101</v>
+        <v>12.3706951141357</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>13.0579566955566</v>
+        <v>13.0579557418823</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>13.0579566955566</v>
+        <v>13.0579557418823</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720487594604</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720487594604</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720487594604</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G514" t="n">
-        <v>13.0579566955566</v>
+        <v>13.0579557418823</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.8311252593994</v>
+        <v>13.8311243057251</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>13.9170331954956</v>
+        <v>13.9170341491699</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>16</v>
       </c>
       <c r="G517" t="n">
-        <v>13.7452163696289</v>
+        <v>13.7452182769775</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>16.5</v>
       </c>
       <c r="G519" t="n">
-        <v>14.1747560501099</v>
+        <v>14.1747541427612</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>14.2606649398804</v>
+        <v>14.2606630325317</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324779510498</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>16.5</v>
       </c>
       <c r="G522" t="n">
-        <v>14.1747560501099</v>
+        <v>14.1747541427612</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>13.8311252593994</v>
+        <v>13.8311243057251</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>14.2606649398804</v>
+        <v>14.2606630325317</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>14.0029401779175</v>
+        <v>14.0029392242432</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>14.3465700149536</v>
+        <v>14.3465719223022</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324779510498</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042928695679</v>
+        <v>14.6042919158936</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056474685669</v>
+        <v>15.2056493759155</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>15.1197395324707</v>
+        <v>15.1197385787964</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.549277305603</v>
+        <v>15.5492782592773</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>15.7259740829468</v>
+        <v>15.7259731292725</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376285552979</v>
+        <v>15.6376276016235</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>15.7259740829468</v>
+        <v>15.7259731292725</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>17</v>
       </c>
       <c r="G540" t="n">
-        <v>15.0191879272461</v>
+        <v>15.0191869735718</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>15.7259740829468</v>
+        <v>15.7259731292725</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.549277305603</v>
+        <v>15.5492763519287</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>18</v>
       </c>
       <c r="G546" t="n">
-        <v>15.9026699066162</v>
+        <v>15.9026679992676</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>18.5</v>
       </c>
       <c r="G547" t="n">
-        <v>16.3444118499756</v>
+        <v>16.3444080352783</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>16.1677150726318</v>
+        <v>16.1677131652832</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>18.5</v>
       </c>
       <c r="G550" t="n">
-        <v>16.3444118499756</v>
+        <v>16.3444080352783</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.5</v>
       </c>
       <c r="G554" t="n">
-        <v>16.3444118499756</v>
+        <v>16.3444080352783</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>18.5</v>
       </c>
       <c r="G557" t="n">
-        <v>16.3444118499756</v>
+        <v>16.3444080352783</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>16.9628486633301</v>
+        <v>16.9628505706787</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>18.1997222900391</v>
+        <v>18.1997241973877</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G561" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>19.9666862487793</v>
+        <v>19.9666843414307</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>19.9666862487793</v>
+        <v>19.9666843414307</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G567" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>17.4929370880127</v>
+        <v>17.4929351806641</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>18.3764190673828</v>
+        <v>18.3764171600342</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>18.3764190673828</v>
+        <v>18.3764171600342</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>20</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6696338653564</v>
+        <v>17.6696300506592</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278919219971</v>
+        <v>17.2278900146484</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>19</v>
       </c>
       <c r="G576" t="n">
-        <v>16.7861518859863</v>
+        <v>16.7861499786377</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>19</v>
       </c>
       <c r="G581" t="n">
-        <v>16.7861518859863</v>
+        <v>16.7861499786377</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>17.4929370880127</v>
+        <v>17.4929351806641</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>17.6696338653564</v>
+        <v>17.6696300506592</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>18.3764190673828</v>
+        <v>18.3764171600342</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>18.3764190673828</v>
+        <v>18.3764171600342</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>18.9065074920654</v>
+        <v>18.9065055847168</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>22.7938251495361</v>
+        <v>22.7938270568848</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>20.6734733581543</v>
+        <v>20.673469543457</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>20.143383026123</v>
+        <v>20.1433811187744</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>23</v>
       </c>
       <c r="G603" t="n">
-        <v>20.3200759887695</v>
+        <v>20.3200778961182</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>22.2637367248535</v>
+        <v>22.2637386322021</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>22.7938251495361</v>
+        <v>22.7938270568848</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>22.7938251495361</v>
+        <v>22.7938270568848</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>23.6773071289062</v>
+        <v>23.6773090362549</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="G617" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>23.323917388916</v>
+        <v>23.3239154815674</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472206115723</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>26</v>
       </c>
       <c r="G620" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>23.323917388916</v>
+        <v>23.3239154815674</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="G622" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>25.0908813476562</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>35</v>
       </c>
       <c r="G633" t="n">
-        <v>30.9218578338623</v>
+        <v>30.921854019165</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0985546112061</v>
+        <v>31.0985527038574</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.5684604644775</v>
+        <v>30.5684642791748</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>30.5684604644775</v>
+        <v>30.5684642791748</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>29.3315944671631</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082874298096</v>
+        <v>29.5082893371582</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>29.3315944671631</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>25.2675762176514</v>
+        <v>25.2675743103027</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>27.5646305084229</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>27.5646305084229</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811447143555</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.3315944671631</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33</v>
       </c>
       <c r="G663" t="n">
-        <v>29.1548957824707</v>
+        <v>29.1548919677734</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G664" t="n">
-        <v>29.6849803924561</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G665" t="n">
-        <v>29.3315944671631</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>29.3315944671631</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>34</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0383758544922</v>
+        <v>30.0383739471436</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>29.6849803924561</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>29.3315944671631</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>28.978199005127</v>
+        <v>28.9781970977783</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G672" t="n">
-        <v>29.6849803924561</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>28.978199005127</v>
+        <v>28.9781970977783</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>33</v>
       </c>
       <c r="G674" t="n">
-        <v>29.1548957824707</v>
+        <v>29.1548919677734</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>29.3315944671631</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33</v>
       </c>
       <c r="G677" t="n">
-        <v>29.1548957824707</v>
+        <v>29.1548919677734</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>27.9180221557617</v>
+        <v>27.9180183410645</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>28.8015022277832</v>
+        <v>28.8015003204346</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>25.2675762176514</v>
+        <v>25.2675743103027</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>25.7976627349854</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811447143555</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>27.5646305084229</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G707" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>30</v>
       </c>
       <c r="G708" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G717" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>30</v>
       </c>
       <c r="G720" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>30</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>25.0908813476562</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>28</v>
       </c>
       <c r="G741" t="n">
-        <v>24.7374858856201</v>
+        <v>24.7374839782715</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>25.0908813476562</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>25.7976627349854</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>25.2675762176514</v>
+        <v>25.2675743103027</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>25.0908813476562</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>27</v>
       </c>
       <c r="G749" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>23.6773071289062</v>
+        <v>23.6773090362549</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>23.6773071289062</v>
+        <v>23.6773090362549</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>23.323917388916</v>
+        <v>23.3239154815674</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>25</v>
       </c>
       <c r="G755" t="n">
-        <v>22.0870418548584</v>
+        <v>22.0870399475098</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>21.5569534301758</v>
+        <v>21.5569515228271</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>24</v>
       </c>
       <c r="G758" t="n">
-        <v>21.2035617828369</v>
+        <v>21.2035579681396</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>20.8501682281494</v>
+        <v>20.8501644134521</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>25</v>
       </c>
       <c r="G760" t="n">
-        <v>22.0870418548584</v>
+        <v>22.0870399475098</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>28</v>
       </c>
       <c r="G764" t="n">
-        <v>24.7374858856201</v>
+        <v>24.7374839782715</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>28</v>
       </c>
       <c r="G765" t="n">
-        <v>24.7374858856201</v>
+        <v>24.7374839782715</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>25.0908813476562</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811447143555</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>30</v>
       </c>
       <c r="G771" t="n">
-        <v>26.5044479370117</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345363616943</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>27.5646305084229</v>
+        <v>27.5646266937256</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G775" t="n">
-        <v>27.2112331390381</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811447143555</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>25.7976627349854</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G784" t="n">
-        <v>23.9423542022705</v>
+        <v>23.9423522949219</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>24.6491394042969</v>
+        <v>24.6491374969482</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>27</v>
       </c>
       <c r="G786" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G787" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472206115723</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006103515625</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>22.7054786682129</v>
+        <v>22.7054805755615</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>26</v>
       </c>
       <c r="G792" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>26</v>
       </c>
       <c r="G793" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>26</v>
       </c>
       <c r="G794" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>24.3840961456299</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>28.5</v>
       </c>
       <c r="G796" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>28.5</v>
       </c>
       <c r="G797" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>26.5</v>
       </c>
       <c r="G823" t="n">
-        <v>23.8303413391113</v>
+        <v>23.8303394317627</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>23.2907867431641</v>
+        <v>23.2907848358154</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>24.5</v>
       </c>
       <c r="G843" t="n">
-        <v>22.0318260192871</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>21.3124179840088</v>
+        <v>21.3124160766602</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>25</v>
       </c>
       <c r="G849" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>24.5</v>
       </c>
       <c r="G850" t="n">
-        <v>22.0318260192871</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>21.4023418426514</v>
+        <v>21.40234375</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>20.9527149200439</v>
+        <v>20.9527130126953</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>20.9527149200439</v>
+        <v>20.9527130126953</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>19.4239768981934</v>
+        <v>19.4239749908447</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>19.693754196167</v>
+        <v>19.6937522888184</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>21.5</v>
       </c>
       <c r="G864" t="n">
-        <v>19.3340492248535</v>
+        <v>19.3340511322021</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>25</v>
       </c>
       <c r="G869" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.3915271759033</v>
+        <v>22.3915252685547</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>20.5030860900879</v>
+        <v>20.5030841827393</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>23</v>
       </c>
       <c r="G878" t="n">
-        <v>20.682933807373</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>20.5030860900879</v>
+        <v>20.5030841827393</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G883" t="n">
-        <v>19.4239768981934</v>
+        <v>19.4239749908447</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>23</v>
       </c>
       <c r="G890" t="n">
-        <v>20.682933807373</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>23.5</v>
       </c>
       <c r="G891" t="n">
-        <v>21.1325645446777</v>
+        <v>21.132568359375</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>23.2907867431641</v>
+        <v>23.2907848358154</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>21.9418964385986</v>
+        <v>21.9418983459473</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>24.5</v>
       </c>
       <c r="G905" t="n">
-        <v>22.0318260192871</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.3915271759033</v>
+        <v>22.3915252685547</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>24.5</v>
       </c>
       <c r="G913" t="n">
-        <v>22.0318260192871</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.3915271759033</v>
+        <v>22.3915252685547</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>21.9418964385986</v>
+        <v>21.9418983459473</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>25</v>
       </c>
       <c r="G917" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>23.0210075378418</v>
+        <v>23.0210094451904</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>29</v>
       </c>
       <c r="G937" t="n">
-        <v>26.0784873962402</v>
+        <v>26.0784854888916</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>29.5</v>
       </c>
       <c r="G938" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>29.5</v>
       </c>
       <c r="G939" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G940" t="n">
-        <v>25.7187824249268</v>
+        <v>25.7187805175781</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>25.7187824249268</v>
+        <v>25.7187805175781</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>29</v>
       </c>
       <c r="G945" t="n">
-        <v>26.0784873962402</v>
+        <v>26.0784854888916</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>25.7187824249268</v>
+        <v>25.7187805175781</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>28.5</v>
       </c>
       <c r="G947" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288585662842</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>29.5</v>
       </c>
       <c r="G953" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>30.5</v>
       </c>
       <c r="G956" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>30.5</v>
       </c>
       <c r="G961" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>26.7079658508301</v>
+        <v>26.7079677581787</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>26.7079658508301</v>
+        <v>26.7079677581787</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>29.5</v>
       </c>
       <c r="G966" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>29.5</v>
       </c>
       <c r="G967" t="n">
-        <v>26.5281162261963</v>
+        <v>26.5281143188477</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>25.7187824249268</v>
+        <v>25.7187805175781</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>28.5</v>
       </c>
       <c r="G971" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288585662842</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>29</v>
       </c>
       <c r="G972" t="n">
-        <v>26.0784873962402</v>
+        <v>26.0784854888916</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>29</v>
       </c>
       <c r="G973" t="n">
-        <v>26.0784873962402</v>
+        <v>26.0784854888916</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>24.9094505310059</v>
+        <v>24.9094524383545</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>24.9094505310059</v>
+        <v>24.9094524383545</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>25.2691555023193</v>
+        <v>25.2691535949707</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>25.7187824249268</v>
+        <v>25.7187805175781</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>28.5</v>
       </c>
       <c r="G999" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288585662842</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>25.7187824249268</v>
+        <v>25.7187805175781</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>26.4381885528564</v>
+        <v>26.4381866455078</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>31.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>28.3266315460205</v>
+        <v>28.3266296386719</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>28.2367038726807</v>
+        <v>28.2367057800293</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>29.4057426452637</v>
+        <v>29.405740737915</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>29.0460357666016</v>
+        <v>29.0460376739502</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1032" t="n">
-        <v>30.0352191925049</v>
+        <v>30.0352230072021</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>32.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>29.225887298584</v>
+        <v>29.2258892059326</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>32</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.7762584686279</v>
+        <v>28.7762603759766</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1038" t="n">
-        <v>30.844554901123</v>
+        <v>30.8445529937744</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639591217041</v>
+        <v>31.5639572143555</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.8337421417236</v>
+        <v>31.833740234375</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042541503906</v>
+        <v>31.2042560577393</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>32</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7762584686279</v>
+        <v>28.7762603759766</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3049983978271</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150707244873</v>
+        <v>30.2150688171387</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3049983978271</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1058" t="n">
-        <v>29.4057426452637</v>
+        <v>29.405740737915</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>32</v>
       </c>
       <c r="G1061" t="n">
-        <v>28.7762584686279</v>
+        <v>28.7762603759766</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>32.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>29.225887298584</v>
+        <v>29.2258892059326</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1067" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1068" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>32.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>31.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>31.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>31.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>31.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>31.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>32.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>30.1003665924072</v>
+        <v>30.1003646850586</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1118" t="n">
-        <v>30.1003665924072</v>
+        <v>30.1003646850586</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>32.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>32.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>32.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.8786125183105</v>
+        <v>26.8786144256592</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>27.5</v>
       </c>
       <c r="G1169" t="n">
-        <v>25.3137607574463</v>
+        <v>25.3137626647949</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>24.9455623626709</v>
+        <v>24.9455642700195</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966114044189</v>
+        <v>23.1966133117676</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>25</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0125122070312</v>
+        <v>23.0125102996826</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>26.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>24.3932628631592</v>
+        <v>24.3932609558105</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.9455623626709</v>
+        <v>24.9455642700195</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>27</v>
       </c>
       <c r="G1201" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>26.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3932628631592</v>
+        <v>24.3932609558105</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>27</v>
       </c>
       <c r="G1208" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>26.8786125183105</v>
+        <v>26.8786144256592</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>29</v>
       </c>
       <c r="G1223" t="n">
-        <v>26.6945152282715</v>
+        <v>26.6945133209229</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>28</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.7740116119385</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>28</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.7740116119385</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>27.5</v>
       </c>
       <c r="G1240" t="n">
-        <v>25.3137607574463</v>
+        <v>25.3137626647949</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>27</v>
       </c>
       <c r="G1242" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>27</v>
       </c>
       <c r="G1251" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>27</v>
       </c>
       <c r="G1252" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>27</v>
       </c>
       <c r="G1261" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1273" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1274" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>31.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>32.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.0208644866943</v>
+        <v>31.020866394043</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.7447147369385</v>
+        <v>30.7447166442871</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.8367652893066</v>
+        <v>30.836763381958</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>32.5</v>
       </c>
       <c r="G1314" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>30.1003665924072</v>
+        <v>30.1003646850586</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.0954246520996</v>
+        <v>29.095422744751</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851486206055</v>
+        <v>33.7851448059082</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095977783203</v>
+        <v>31.0095996856689</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>27</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>26.5112915039062</v>
+        <v>26.5112934112549</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.6499118804932</v>
+        <v>25.6499137878418</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>25.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.4057025909424</v>
+        <v>24.4057006835938</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7456226348877</v>
+        <v>25.7456207275391</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>29</v>
       </c>
       <c r="G1554" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>29</v>
       </c>
       <c r="G1555" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1570" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -50552,6 +50552,32 @@
         <v>44.9000015258789</v>
       </c>
       <c r="H1930" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1931" t="n">
+        <v>9527</v>
+      </c>
+      <c r="C1931" t="n">
+        <v>45.4000015258789</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>43.4000015258789</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>44.7000007629395</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>44.5999984741211</v>
+      </c>
+      <c r="G1931" t="n">
+        <v>44.5999984741211</v>
+      </c>
+      <c r="H1931" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.28757762908936</v>
+        <v>9.28757953643799</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>9.58129024505615</v>
+        <v>9.58128929138184</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293647766113</v>
+        <v>9.88293552398682</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G6" t="n">
-        <v>9.78767967224121</v>
+        <v>9.78768062591553</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>9.6051025390625</v>
+        <v>9.60510349273682</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>9.23995018005371</v>
+        <v>9.23995113372803</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>9.4463415145874</v>
+        <v>9.44634056091309</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.75</v>
       </c>
       <c r="G13" t="n">
-        <v>9.32726955413818</v>
+        <v>9.32726860046387</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.91468811035156</v>
+        <v>9.91468906402588</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2877798080444</v>
+        <v>10.2877807617188</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2719039916992</v>
+        <v>10.2719030380249</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5259246826172</v>
+        <v>10.5259237289429</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3989143371582</v>
+        <v>10.3989133834839</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G28" t="n">
-        <v>10.256028175354</v>
+        <v>10.2560291290283</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>10.1925230026245</v>
+        <v>10.1925239562988</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>13.5</v>
       </c>
       <c r="G33" t="n">
-        <v>10.716438293457</v>
+        <v>10.7164373397827</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7005624771118</v>
+        <v>10.7005615234375</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>10.5100469589233</v>
+        <v>10.510046005249</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419792175293</v>
+        <v>11.1419801712036</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G38" t="n">
-        <v>11.1087207794189</v>
+        <v>11.1087217330933</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G40" t="n">
-        <v>10.7761240005493</v>
+        <v>10.7761249542236</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G43" t="n">
-        <v>10.6763467788696</v>
+        <v>10.6763458251953</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>10.6763467788696</v>
+        <v>10.6763458251953</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>10.3104887008667</v>
+        <v>10.3104877471924</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G50" t="n">
-        <v>10.3104887008667</v>
+        <v>10.3104877471924</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>10.3104887008667</v>
+        <v>10.3104877471924</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G55" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G56" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G59" t="n">
-        <v>10.3271198272705</v>
+        <v>10.3271207809448</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G81" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833557128906</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>9.67855644226074</v>
+        <v>9.67855548858643</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G85" t="n">
-        <v>9.67855644226074</v>
+        <v>9.67855548858643</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.5</v>
       </c>
       <c r="G88" t="n">
-        <v>9.56214618682861</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G90" t="n">
-        <v>9.69518566131592</v>
+        <v>9.69518661499023</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.56214618682861</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G99" t="n">
-        <v>10.1275615692139</v>
+        <v>10.1275625228882</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12</v>
       </c>
       <c r="G101" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833557128906</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833557128906</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G109" t="n">
-        <v>9.61203670501709</v>
+        <v>9.61203765869141</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529705047607</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529705047607</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148548126221</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12</v>
       </c>
       <c r="G113" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12</v>
       </c>
       <c r="G114" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12</v>
       </c>
       <c r="G117" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G118" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G119" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G120" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12</v>
       </c>
       <c r="G123" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G125" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>10.3936376571655</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G131" t="n">
-        <v>10.4435291290283</v>
+        <v>10.443528175354</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>10.4601573944092</v>
+        <v>10.4601583480835</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12</v>
       </c>
       <c r="G138" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>9.82822418212891</v>
+        <v>9.82822513580322</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148548126221</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148548126221</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G147" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G153" t="n">
-        <v>10.1275615692139</v>
+        <v>10.1275625228882</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G155" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G156" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G161" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>10.3104887008667</v>
+        <v>10.3104877471924</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G164" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3936376571655</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>10.3104887008667</v>
+        <v>10.3104877471924</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G170" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G175" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126174926758</v>
+        <v>9.96126365661621</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12</v>
       </c>
       <c r="G178" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12</v>
       </c>
       <c r="G179" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>10.1109323501587</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G183" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G184" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G185" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>12</v>
       </c>
       <c r="G186" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G188" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G190" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G192" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G198" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G200" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G201" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>12</v>
       </c>
       <c r="G211" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="G213" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>12</v>
       </c>
       <c r="G221" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="G222" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12</v>
       </c>
       <c r="G226" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G228" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="n">
-        <v>9.97789096832275</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G231" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G236" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610427856445</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0943031311035</v>
+        <v>10.0943021774292</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G245" t="n">
-        <v>9.52888774871826</v>
+        <v>9.52888870239258</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>9.41248035430908</v>
+        <v>9.41247940063477</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>9.41248035430908</v>
+        <v>9.41247940063477</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>11.5</v>
       </c>
       <c r="G249" t="n">
-        <v>9.56214618682861</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.11314105987549</v>
+        <v>9.1131420135498</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>8.66413688659668</v>
+        <v>8.664137840271</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>8.44794845581055</v>
+        <v>8.44794940948486</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>8.48120784759521</v>
+        <v>8.48120880126953</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568441390991</v>
+        <v>7.96568536758423</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>8.03220272064209</v>
+        <v>8.03220367431641</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>8.03220272064209</v>
+        <v>8.03220367431641</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10</v>
       </c>
       <c r="G262" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491088867188</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491088867188</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="G264" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491088867188</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491088867188</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.48120784759521</v>
+        <v>8.48120880126953</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39805889129639</v>
+        <v>8.3980598449707</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>8.48120784759521</v>
+        <v>8.48120880126953</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640045166016</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640045166016</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>9.06325244903564</v>
+        <v>9.06325340270996</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>9.36392879486084</v>
+        <v>9.36392974853516</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.19211292266846</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10</v>
       </c>
       <c r="G305" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10</v>
       </c>
       <c r="G307" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10</v>
       </c>
       <c r="G308" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10</v>
       </c>
       <c r="G310" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>10</v>
       </c>
       <c r="G319" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>10</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.75</v>
       </c>
       <c r="G370" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.75</v>
       </c>
       <c r="G373" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.75</v>
       </c>
       <c r="G374" t="n">
-        <v>8.37599086761475</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.20417785644531</v>
+        <v>8.204176902771</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="G383" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>10</v>
       </c>
       <c r="G386" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>10</v>
       </c>
       <c r="G399" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>10</v>
       </c>
       <c r="G408" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>10</v>
       </c>
       <c r="G409" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>8.59075927734375</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.19211292266846</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>9.36392879486084</v>
+        <v>9.36392974853516</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19211292266846</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>9.19211292266846</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>9.2780237197876</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G434" t="n">
-        <v>9.2780237197876</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>9.2780237197876</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G436" t="n">
-        <v>9.2780237197876</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>9.2780237197876</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G439" t="n">
-        <v>9.79346752166748</v>
+        <v>9.79346656799316</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>12</v>
       </c>
       <c r="G445" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12</v>
       </c>
       <c r="G446" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>12</v>
       </c>
       <c r="G447" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807291030884</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>12</v>
       </c>
       <c r="G449" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>10.3948221206665</v>
+        <v>10.3948211669922</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>12</v>
       </c>
       <c r="G452" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G457" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807291030884</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>12</v>
       </c>
       <c r="G472" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G473" t="n">
-        <v>10.3948221206665</v>
+        <v>10.3948211669922</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12</v>
       </c>
       <c r="G474" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G477" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0511894226074</v>
+        <v>10.0511903762817</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0511894226074</v>
+        <v>10.0511903762817</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807291030884</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="n">
-        <v>10.3089113235474</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G484" t="n">
-        <v>10.6525430679321</v>
+        <v>10.6525421142578</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>11.5116205215454</v>
+        <v>11.5116195678711</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>11.8552494049072</v>
+        <v>11.8552503585815</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>12.1988801956177</v>
+        <v>12.1988792419434</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>12.1129741668701</v>
+        <v>12.1129732131958</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>13.9170341491699</v>
+        <v>13.9170322418213</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>16</v>
       </c>
       <c r="G517" t="n">
-        <v>13.7452182769775</v>
+        <v>13.7452173233032</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>14.2606630325317</v>
+        <v>14.2606639862061</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324769973755</v>
+        <v>14.4324779510498</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>14.2606630325317</v>
+        <v>14.2606639862061</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>14.0029392242432</v>
+        <v>14.0029401779175</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>14.3465719223022</v>
+        <v>14.3465709686279</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324769973755</v>
+        <v>14.4324779510498</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>18</v>
       </c>
       <c r="G529" t="n">
-        <v>15.4633684158325</v>
+        <v>15.4633674621582</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>15.2915534973145</v>
+        <v>15.2915525436401</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>18</v>
       </c>
       <c r="G531" t="n">
-        <v>15.4633684158325</v>
+        <v>15.4633674621582</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056493759155</v>
+        <v>15.2056474685669</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>18</v>
       </c>
       <c r="G534" t="n">
-        <v>15.4633684158325</v>
+        <v>15.4633674621582</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="n">
-        <v>15.4633684158325</v>
+        <v>15.4633674621582</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.5492782592773</v>
+        <v>15.549277305603</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>15.7259731292725</v>
+        <v>15.7259721755981</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376276016235</v>
+        <v>15.6376256942749</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>15.7259731292725</v>
+        <v>15.7259721755981</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>15.7259731292725</v>
+        <v>15.7259721755981</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.5492763519287</v>
+        <v>15.549277305603</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>15.81432056427</v>
+        <v>15.8143215179443</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>16.07936668396</v>
+        <v>16.0793685913086</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>18.5</v>
       </c>
       <c r="G547" t="n">
-        <v>16.3444080352783</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>16.4327602386475</v>
+        <v>16.4327583312988</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>18.5</v>
       </c>
       <c r="G550" t="n">
-        <v>16.3444080352783</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.5</v>
       </c>
       <c r="G554" t="n">
-        <v>16.3444080352783</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>16.4327602386475</v>
+        <v>16.4327583312988</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>18.5</v>
       </c>
       <c r="G557" t="n">
-        <v>16.3444080352783</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>16.9628505706787</v>
+        <v>16.9628486633301</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>22</v>
       </c>
       <c r="G565" t="n">
-        <v>19.436595916748</v>
+        <v>19.4365940093994</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G569" t="n">
-        <v>17.8463306427002</v>
+        <v>17.8463287353516</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>17.4929351806641</v>
+        <v>17.4929370880127</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>20</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6696300506592</v>
+        <v>17.6696338653564</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278900146484</v>
+        <v>17.2278919219971</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>17.3162422180176</v>
+        <v>17.3162403106689</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>17.4929351806641</v>
+        <v>17.4929370880127</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>17.6696300506592</v>
+        <v>17.6696338653564</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>17.4045906066895</v>
+        <v>17.4045886993408</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>20.673469543457</v>
+        <v>20.6734714508057</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>19.2598991394043</v>
+        <v>19.2599010467529</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G599" t="n">
-        <v>19.2598991394043</v>
+        <v>19.2599010467529</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>19.2598991394043</v>
+        <v>19.2599010467529</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>22</v>
       </c>
       <c r="G601" t="n">
-        <v>19.436595916748</v>
+        <v>19.4365940093994</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>23</v>
       </c>
       <c r="G603" t="n">
-        <v>20.3200778961182</v>
+        <v>20.3200759887695</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G606" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268611907959</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>22.2637386322021</v>
+        <v>22.2637405395508</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>35</v>
       </c>
       <c r="G633" t="n">
-        <v>30.921854019165</v>
+        <v>30.9218559265137</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0985527038574</v>
+        <v>31.0985546112061</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.5684642791748</v>
+        <v>30.5684623718262</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>30.5684642791748</v>
+        <v>30.5684623718262</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>25.2675743103027</v>
+        <v>25.2675762176514</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>26.6811447143555</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G665" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>28.6248073577881</v>
+        <v>28.6248054504395</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>27.9180183410645</v>
+        <v>27.9180202484131</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>28.6248073577881</v>
+        <v>28.6248054504395</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>25.2675743103027</v>
+        <v>25.2675762176514</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>26.6811447143555</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G699" t="n">
-        <v>28.6248073577881</v>
+        <v>28.6248054504395</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>30</v>
       </c>
       <c r="G708" t="n">
-        <v>26.5044498443604</v>
+        <v>26.5044479370117</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G717" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>30</v>
       </c>
       <c r="G720" t="n">
-        <v>26.5044498443604</v>
+        <v>26.5044479370117</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>30</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5044498443604</v>
+        <v>26.5044479370117</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>24.9141864776611</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>24.9141864776611</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>28</v>
       </c>
       <c r="G741" t="n">
-        <v>24.7374839782715</v>
+        <v>24.7374858856201</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>25.2675743103027</v>
+        <v>25.2675762176514</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>25</v>
       </c>
       <c r="G755" t="n">
-        <v>22.0870399475098</v>
+        <v>22.0870418548584</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>21.5569515228271</v>
+        <v>21.5569534301758</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>24</v>
       </c>
       <c r="G758" t="n">
-        <v>21.2035579681396</v>
+        <v>21.2035598754883</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>25</v>
       </c>
       <c r="G760" t="n">
-        <v>22.0870399475098</v>
+        <v>22.0870418548584</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>24.9141864776611</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>28</v>
       </c>
       <c r="G764" t="n">
-        <v>24.7374839782715</v>
+        <v>24.7374858856201</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>28</v>
       </c>
       <c r="G765" t="n">
-        <v>24.7374839782715</v>
+        <v>24.7374858856201</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>25.9743614196777</v>
+        <v>25.9743595123291</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>26.6811447143555</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>30</v>
       </c>
       <c r="G771" t="n">
-        <v>26.5044498443604</v>
+        <v>26.5044479370117</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G775" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>26.6811447143555</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>22.7054805755615</v>
+        <v>22.7054786682129</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G798" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>25.8986339569092</v>
+        <v>25.8986320495605</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>23.9202651977539</v>
+        <v>23.9202671051025</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>23.7404155731201</v>
+        <v>23.7404136657715</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>23.7404155731201</v>
+        <v>23.7404136657715</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>26.5</v>
       </c>
       <c r="G823" t="n">
-        <v>23.8303394317627</v>
+        <v>23.8303413391113</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>23.5605621337891</v>
+        <v>23.5605640411377</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>24.3698959350586</v>
+        <v>24.36989402771</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>24.3698959350586</v>
+        <v>24.36989402771</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>26</v>
       </c>
       <c r="G829" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>23.5605621337891</v>
+        <v>23.5605640411377</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>26</v>
       </c>
       <c r="G832" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>26</v>
       </c>
       <c r="G833" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>26</v>
       </c>
       <c r="G834" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>23.2907848358154</v>
+        <v>23.2907867431641</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>21.3124160766602</v>
+        <v>21.3124179840088</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>21.40234375</v>
+        <v>21.4023418426514</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>22</v>
       </c>
       <c r="G856" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>22</v>
       </c>
       <c r="G857" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>19.5139007568359</v>
+        <v>19.5139026641846</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038246154785</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>19.4239749908447</v>
+        <v>19.4239768981934</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038246154785</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>21.5</v>
       </c>
       <c r="G864" t="n">
-        <v>19.3340511322021</v>
+        <v>19.3340492248535</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038246154785</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>20.5930118560791</v>
+        <v>20.5930099487305</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>22.3015995025635</v>
+        <v>22.3016014099121</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>20.5030841827393</v>
+        <v>20.5030860900879</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>20.5030841827393</v>
+        <v>20.5030860900879</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>20.5930118560791</v>
+        <v>20.5930099487305</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>22</v>
       </c>
       <c r="G882" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G883" t="n">
-        <v>19.4239749908447</v>
+        <v>19.4239768981934</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>19.1541957855225</v>
+        <v>19.1541976928711</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>22</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>22</v>
       </c>
       <c r="G886" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>22</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>22</v>
       </c>
       <c r="G888" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>22</v>
       </c>
       <c r="G889" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>23.5</v>
       </c>
       <c r="G891" t="n">
-        <v>21.132568359375</v>
+        <v>21.1325664520264</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>26</v>
       </c>
       <c r="G894" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>26</v>
       </c>
       <c r="G895" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>23.2907848358154</v>
+        <v>23.2907867431641</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>26</v>
       </c>
       <c r="G897" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>22.5713787078857</v>
+        <v>22.5713806152344</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>22.3015995025635</v>
+        <v>22.3016014099121</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G921" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>22.5713787078857</v>
+        <v>22.5713806152344</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>23.0210094451904</v>
+        <v>23.0210075378418</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>26</v>
       </c>
       <c r="G931" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G935" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>29</v>
       </c>
       <c r="G937" t="n">
-        <v>26.0784854888916</v>
+        <v>26.0784873962402</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G940" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>29</v>
       </c>
       <c r="G945" t="n">
-        <v>26.0784854888916</v>
+        <v>26.0784873962402</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>28.5</v>
       </c>
       <c r="G947" t="n">
-        <v>25.6288585662842</v>
+        <v>25.6288566589355</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>30.5</v>
       </c>
       <c r="G956" t="n">
-        <v>27.4273738861084</v>
+        <v>27.4273719787598</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G959" t="n">
-        <v>29.3158149719238</v>
+        <v>29.3158130645752</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G960" t="n">
-        <v>29.1359634399414</v>
+        <v>29.13596534729</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>30.5</v>
       </c>
       <c r="G961" t="n">
-        <v>27.4273738861084</v>
+        <v>27.4273719787598</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>27.1575965881348</v>
+        <v>27.1575946807861</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G969" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>25.8986339569092</v>
+        <v>25.8986320495605</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>28.5</v>
       </c>
       <c r="G971" t="n">
-        <v>25.6288585662842</v>
+        <v>25.6288566589355</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>29</v>
       </c>
       <c r="G972" t="n">
-        <v>26.0784854888916</v>
+        <v>26.0784873962402</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>29</v>
       </c>
       <c r="G973" t="n">
-        <v>26.0784854888916</v>
+        <v>26.0784873962402</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>26.1684131622314</v>
+        <v>26.1684112548828</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G981" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>24.9094524383545</v>
+        <v>24.9094505310059</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>24.9094524383545</v>
+        <v>24.9094505310059</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>25.8986339569092</v>
+        <v>25.8986320495605</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>28.5</v>
       </c>
       <c r="G999" t="n">
-        <v>25.6288585662842</v>
+        <v>25.6288566589355</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>25.7187805175781</v>
+        <v>25.7187824249268</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>25.8986339569092</v>
+        <v>25.8986320495605</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>26.4381866455078</v>
+        <v>26.4381885528564</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>27.1575965881348</v>
+        <v>27.1575946807861</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>31.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>28.3266296386719</v>
+        <v>28.3266315460205</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>28.1467781066895</v>
+        <v>28.1467800140381</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>28.2367057800293</v>
+        <v>28.2367038726807</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>29.405740737915</v>
+        <v>29.4057426452637</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>29.0460376739502</v>
+        <v>29.0460357666016</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1032" t="n">
-        <v>30.0352230072021</v>
+        <v>30.0352210998535</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>28.9561138153076</v>
+        <v>28.956111907959</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>32.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>29.2258892059326</v>
+        <v>29.225887298584</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1035" t="n">
-        <v>29.1359634399414</v>
+        <v>29.13596534729</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1037" t="n">
-        <v>29.1359634399414</v>
+        <v>29.13596534729</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1038" t="n">
-        <v>30.8445529937744</v>
+        <v>30.844554901123</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2941818237305</v>
+        <v>31.2941837310791</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>31.2941818237305</v>
+        <v>31.2941837310791</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042560577393</v>
+        <v>31.2042541503906</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150688171387</v>
+        <v>30.2150707244873</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1055" t="n">
-        <v>29.9452934265137</v>
+        <v>29.945291519165</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1058" t="n">
-        <v>29.405740737915</v>
+        <v>29.4057426452637</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>32.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>29.2258892059326</v>
+        <v>29.225887298584</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1067" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1068" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>32.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>31.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>31.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>31.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>31.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>31.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>32.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1118" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>32.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>32.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>32.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.8786144256592</v>
+        <v>26.8786125183105</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>27.5</v>
       </c>
       <c r="G1169" t="n">
-        <v>25.3137626647949</v>
+        <v>25.3137607574463</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966133117676</v>
+        <v>23.1966114044189</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>25</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0125102996826</v>
+        <v>23.0125122070312</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>26.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>27</v>
       </c>
       <c r="G1201" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>26.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>27</v>
       </c>
       <c r="G1208" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>26.8786144256592</v>
+        <v>26.8786125183105</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>29</v>
       </c>
       <c r="G1223" t="n">
-        <v>26.6945133209229</v>
+        <v>26.6945152282715</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>28</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.7740135192871</v>
+        <v>25.7740116119385</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>28</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.7740135192871</v>
+        <v>25.7740116119385</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>27.5</v>
       </c>
       <c r="G1240" t="n">
-        <v>25.3137626647949</v>
+        <v>25.3137607574463</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>27</v>
       </c>
       <c r="G1242" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>27</v>
       </c>
       <c r="G1251" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>27</v>
       </c>
       <c r="G1252" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>27</v>
       </c>
       <c r="G1261" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1273" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1274" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>31.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>32.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.020866394043</v>
+        <v>31.0208644866943</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.7447166442871</v>
+        <v>30.7447147369385</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.836763381958</v>
+        <v>30.8367652893066</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>32.5</v>
       </c>
       <c r="G1314" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.095422744751</v>
+        <v>29.0954246520996</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851448059082</v>
+        <v>33.7851486206055</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095996856689</v>
+        <v>31.0095977783203</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.8413314819336</v>
+        <v>25.841329574585</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>27</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.8413314819336</v>
+        <v>25.841329574585</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>26.5112934112549</v>
+        <v>26.5112915039062</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.6499137878418</v>
+        <v>25.6499118804932</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>25.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.4057006835938</v>
+        <v>24.4057025909424</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7456207275391</v>
+        <v>25.7456226348877</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>29</v>
       </c>
       <c r="G1554" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>29</v>
       </c>
       <c r="G1555" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1570" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -50578,6 +50578,32 @@
         <v>44.5999984741211</v>
       </c>
       <c r="H1931" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1932" t="n">
+        <v>8795</v>
+      </c>
+      <c r="C1932" t="n">
+        <v>46</v>
+      </c>
+      <c r="D1932" t="n">
+        <v>44.2999992370605</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>45.2000007629395</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>45.2999992370605</v>
+      </c>
+      <c r="G1932" t="n">
+        <v>45.2999992370605</v>
+      </c>
+      <c r="H1932" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.28757953643799</v>
+        <v>9.28757858276367</v>
       </c>
       <c r="H2" t="n">
         <v>27300</v>
@@ -485,7 +485,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293552398682</v>
+        <v>9.88293743133545</v>
       </c>
       <c r="H4" t="n">
         <v>14100</v>
@@ -514,7 +514,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.76386642456055</v>
+        <v>9.76386547088623</v>
       </c>
       <c r="H5" t="n">
         <v>9000</v>
@@ -543,7 +543,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G6" t="n">
-        <v>9.78767871856689</v>
+        <v>9.78767967224121</v>
       </c>
       <c r="H6" t="n">
         <v>5550</v>
@@ -572,7 +572,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>9.67654609680176</v>
+        <v>9.67654705047607</v>
       </c>
       <c r="H7" t="n">
         <v>9900</v>
@@ -601,7 +601,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>9.6051025390625</v>
+        <v>9.60510540008545</v>
       </c>
       <c r="H8" t="n">
         <v>3750</v>
@@ -630,7 +630,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>9.23995113372803</v>
+        <v>9.23995018005371</v>
       </c>
       <c r="H9" t="n">
         <v>6000</v>
@@ -659,7 +659,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>9.39871406555176</v>
+        <v>9.39871311187744</v>
       </c>
       <c r="H10" t="n">
         <v>1050</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52572345733643</v>
+        <v>9.52572250366211</v>
       </c>
       <c r="H11" t="n">
         <v>1500</v>
@@ -717,7 +717,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44634056091309</v>
+        <v>9.4463415145874</v>
       </c>
       <c r="H12" t="n">
         <v>1200</v>
@@ -746,7 +746,7 @@
         <v>11.75</v>
       </c>
       <c r="G13" t="n">
-        <v>9.32726955413818</v>
+        <v>9.3272705078125</v>
       </c>
       <c r="H13" t="n">
         <v>1800</v>
@@ -775,7 +775,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.91468906402588</v>
+        <v>9.91468811035156</v>
       </c>
       <c r="H14" t="n">
         <v>3450</v>
@@ -804,7 +804,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3195343017578</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H15" t="n">
         <v>13050</v>
@@ -833,7 +833,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>10.1607694625854</v>
+        <v>10.1607704162598</v>
       </c>
       <c r="H16" t="n">
         <v>4350</v>
@@ -891,7 +891,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>10.3195343017578</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H18" t="n">
         <v>2700</v>
@@ -920,7 +920,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2877798080444</v>
+        <v>10.2877807617188</v>
       </c>
       <c r="H19" t="n">
         <v>4050</v>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.3195343017578</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H20" t="n">
         <v>1500</v>
@@ -1065,7 +1065,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>10.1607694625854</v>
+        <v>10.1607704162598</v>
       </c>
       <c r="H24" t="n">
         <v>2100</v>
@@ -1094,7 +1094,7 @@
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>10.3195343017578</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H25" t="n">
         <v>2550</v>
@@ -1268,7 +1268,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>10.1925230026245</v>
+        <v>10.1925220489502</v>
       </c>
       <c r="H31" t="n">
         <v>5250</v>
@@ -1355,7 +1355,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7005624771118</v>
+        <v>10.7005615234375</v>
       </c>
       <c r="H34" t="n">
         <v>9000</v>
@@ -1384,7 +1384,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>10.5100469589233</v>
+        <v>10.510046005249</v>
       </c>
       <c r="H35" t="n">
         <v>2550</v>
@@ -1413,7 +1413,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588331222534</v>
+        <v>11.0588321685791</v>
       </c>
       <c r="H36" t="n">
         <v>3900</v>
@@ -1442,7 +1442,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419811248779</v>
+        <v>11.1419801712036</v>
       </c>
       <c r="H37" t="n">
         <v>7050</v>
@@ -1471,7 +1471,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G38" t="n">
-        <v>11.1087217330933</v>
+        <v>11.1087207794189</v>
       </c>
       <c r="H38" t="n">
         <v>22800</v>
@@ -1558,7 +1558,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>10.6264572143555</v>
+        <v>10.6264553070068</v>
       </c>
       <c r="H41" t="n">
         <v>19200</v>
@@ -1616,7 +1616,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G43" t="n">
-        <v>10.6763458251953</v>
+        <v>10.676344871521</v>
       </c>
       <c r="H43" t="n">
         <v>13050</v>
@@ -1645,7 +1645,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>10.6763458251953</v>
+        <v>10.676344871521</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="G45" t="n">
-        <v>10.8093843460083</v>
+        <v>10.809383392334</v>
       </c>
       <c r="H45" t="n">
         <v>14250</v>
@@ -1703,7 +1703,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G46" t="n">
-        <v>10.609827041626</v>
+        <v>10.6098260879517</v>
       </c>
       <c r="H46" t="n">
         <v>750</v>
@@ -1732,7 +1732,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G47" t="n">
-        <v>10.3437490463257</v>
+        <v>10.34375</v>
       </c>
       <c r="H47" t="n">
         <v>750</v>
@@ -1761,7 +1761,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H48" t="n">
         <v>7800</v>
@@ -1877,7 +1877,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H52" t="n">
         <v>900</v>
@@ -1906,7 +1906,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H53" t="n">
         <v>6150</v>
@@ -1935,7 +1935,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G54" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H54" t="n">
         <v>2850</v>
@@ -2051,7 +2051,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>10.2772302627563</v>
+        <v>10.2772312164307</v>
       </c>
       <c r="H58" t="n">
         <v>900</v>
@@ -2080,7 +2080,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G59" t="n">
-        <v>10.3271198272705</v>
+        <v>10.3271207809448</v>
       </c>
       <c r="H59" t="n">
         <v>300</v>
@@ -2196,7 +2196,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H63" t="n">
         <v>1800</v>
@@ -2254,7 +2254,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>9.84485530853271</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H65" t="n">
         <v>2850</v>
@@ -2283,7 +2283,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H66" t="n">
         <v>3900</v>
@@ -2370,7 +2370,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H69" t="n">
         <v>1200</v>
@@ -2399,7 +2399,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G70" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H70" t="n">
         <v>99900</v>
@@ -2515,7 +2515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H74" t="n">
         <v>90600</v>
@@ -2544,7 +2544,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H76" t="n">
         <v>600</v>
@@ -2631,7 +2631,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G78" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H78" t="n">
         <v>2550</v>
@@ -2689,7 +2689,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G80" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H80" t="n">
         <v>49800</v>
@@ -2776,7 +2776,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833557128906</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2863,7 +2863,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>9.49562835693359</v>
+        <v>9.49562931060791</v>
       </c>
       <c r="H86" t="n">
         <v>5550</v>
@@ -2892,7 +2892,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G87" t="n">
-        <v>9.49562835693359</v>
+        <v>9.49562931060791</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H92" t="n">
         <v>7050</v>
@@ -3066,7 +3066,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H93" t="n">
         <v>2550</v>
@@ -3211,7 +3211,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G98" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H98" t="n">
         <v>2550</v>
@@ -3269,7 +3269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H100" t="n">
         <v>150</v>
@@ -3327,7 +3327,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811279296875</v>
       </c>
       <c r="H102" t="n">
         <v>3150</v>
@@ -3414,7 +3414,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833557128906</v>
       </c>
       <c r="H105" t="n">
         <v>1200</v>
@@ -3443,7 +3443,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833557128906</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G107" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811279296875</v>
       </c>
       <c r="H107" t="n">
         <v>150</v>
@@ -3501,7 +3501,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G108" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811279296875</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G109" t="n">
-        <v>9.61203670501709</v>
+        <v>9.61203765869141</v>
       </c>
       <c r="H109" t="n">
         <v>300</v>
@@ -3559,7 +3559,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529514312744</v>
+        <v>9.64529800415039</v>
       </c>
       <c r="H110" t="n">
         <v>450</v>
@@ -3588,7 +3588,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529514312744</v>
+        <v>9.64529800415039</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148357391357</v>
       </c>
       <c r="H112" t="n">
         <v>1800</v>
@@ -3733,7 +3733,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G116" t="n">
-        <v>9.84485530853271</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H116" t="n">
         <v>450</v>
@@ -3907,7 +3907,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G122" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811279296875</v>
       </c>
       <c r="H122" t="n">
         <v>600</v>
@@ -3965,7 +3965,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -4081,7 +4081,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G128" t="n">
-        <v>10.2772302627563</v>
+        <v>10.2772312164307</v>
       </c>
       <c r="H128" t="n">
         <v>4650</v>
@@ -4110,7 +4110,7 @@
         <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>10.3936376571655</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H129" t="n">
         <v>7500</v>
@@ -4139,7 +4139,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G130" t="n">
-        <v>10.2772302627563</v>
+        <v>10.2772312164307</v>
       </c>
       <c r="H130" t="n">
         <v>2700</v>
@@ -4284,7 +4284,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0277833938599</v>
+        <v>10.0277824401855</v>
       </c>
       <c r="H135" t="n">
         <v>2400</v>
@@ -4313,7 +4313,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G136" t="n">
-        <v>10.0444116592407</v>
+        <v>10.0444135665894</v>
       </c>
       <c r="H136" t="n">
         <v>150</v>
@@ -4400,7 +4400,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>9.82822608947754</v>
+        <v>9.82822322845459</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4458,7 +4458,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148357391357</v>
       </c>
       <c r="H141" t="n">
         <v>300</v>
@@ -4487,7 +4487,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148357391357</v>
       </c>
       <c r="H142" t="n">
         <v>450</v>
@@ -4603,7 +4603,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159400939941</v>
       </c>
       <c r="H146" t="n">
         <v>3150</v>
@@ -4661,7 +4661,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H148" t="n">
         <v>750</v>
@@ -4690,7 +4690,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H158" t="n">
         <v>600</v>
@@ -5009,7 +5009,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H160" t="n">
         <v>12000</v>
@@ -5125,7 +5125,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G164" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H164" t="n">
         <v>2250</v>
@@ -5154,7 +5154,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>12.5</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3936376571655</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H166" t="n">
         <v>450</v>
@@ -5270,7 +5270,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H169" t="n">
         <v>2400</v>
@@ -5328,7 +5328,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G171" t="n">
-        <v>10.2439708709717</v>
+        <v>10.2439699172974</v>
       </c>
       <c r="H171" t="n">
         <v>450</v>
@@ -5386,7 +5386,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G173" t="n">
-        <v>10.0277833938599</v>
+        <v>10.0277824401855</v>
       </c>
       <c r="H173" t="n">
         <v>300</v>
@@ -5473,7 +5473,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126270294189</v>
+        <v>9.96126174926758</v>
       </c>
       <c r="H176" t="n">
         <v>150</v>
@@ -5879,7 +5879,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G190" t="n">
-        <v>10.2938594818115</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H190" t="n">
         <v>163050</v>
@@ -5937,7 +5937,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G192" t="n">
-        <v>10.2938594818115</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H192" t="n">
         <v>3300</v>
@@ -6082,7 +6082,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6111,7 +6111,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G198" t="n">
-        <v>10.2938594818115</v>
+        <v>10.2938604354858</v>
       </c>
       <c r="H198" t="n">
         <v>150</v>
@@ -6227,7 +6227,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H202" t="n">
         <v>7050</v>
@@ -6256,7 +6256,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G203" t="n">
-        <v>10.0444116592407</v>
+        <v>10.0444135665894</v>
       </c>
       <c r="H203" t="n">
         <v>5250</v>
@@ -6285,7 +6285,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>10.0444116592407</v>
+        <v>10.0444135665894</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G205" t="n">
-        <v>9.84485530853271</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H205" t="n">
         <v>750</v>
@@ -6372,7 +6372,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H207" t="n">
         <v>900</v>
@@ -6430,7 +6430,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G209" t="n">
-        <v>10.2439708709717</v>
+        <v>10.2439699172974</v>
       </c>
       <c r="H209" t="n">
         <v>2850</v>
@@ -6662,7 +6662,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G217" t="n">
-        <v>10.3437490463257</v>
+        <v>10.34375</v>
       </c>
       <c r="H217" t="n">
         <v>12900</v>
@@ -6720,7 +6720,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H219" t="n">
         <v>900</v>
@@ -6836,7 +6836,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>10.1940813064575</v>
+        <v>10.1940803527832</v>
       </c>
       <c r="H223" t="n">
         <v>2400</v>
@@ -6865,7 +6865,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H224" t="n">
         <v>1800</v>
@@ -7010,7 +7010,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603792190552</v>
+        <v>10.3603801727295</v>
       </c>
       <c r="H229" t="n">
         <v>2400</v>
@@ -7097,7 +7097,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H232" t="n">
         <v>2250</v>
@@ -7126,7 +7126,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273397445679</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H237" t="n">
         <v>3000</v>
@@ -7271,7 +7271,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2606000900269</v>
+        <v>10.2606010437012</v>
       </c>
       <c r="H238" t="n">
         <v>1350</v>
@@ -7300,7 +7300,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610427856445</v>
+        <v>10.0610437393188</v>
       </c>
       <c r="H239" t="n">
         <v>2850</v>
@@ -7358,7 +7358,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G241" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811279296875</v>
       </c>
       <c r="H241" t="n">
         <v>7800</v>
@@ -7387,7 +7387,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G242" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811279296875</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87811374664307</v>
+        <v>9.87811279296875</v>
       </c>
       <c r="H243" t="n">
         <v>600</v>
@@ -7445,7 +7445,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H244" t="n">
         <v>300</v>
@@ -7474,7 +7474,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G245" t="n">
-        <v>9.52888870239258</v>
+        <v>9.52888774871826</v>
       </c>
       <c r="H245" t="n">
         <v>1050</v>
@@ -7503,7 +7503,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.17966079711914</v>
+        <v>9.17966175079346</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>9.41247749328613</v>
+        <v>9.41247940063477</v>
       </c>
       <c r="H247" t="n">
         <v>300</v>
@@ -7561,7 +7561,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>9.41247749328613</v>
+        <v>9.41247940063477</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.11314105987549</v>
+        <v>9.11314296722412</v>
       </c>
       <c r="H250" t="n">
         <v>2250</v>
@@ -7648,7 +7648,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>8.664137840271</v>
+        <v>8.66413688659668</v>
       </c>
       <c r="H251" t="n">
         <v>4200</v>
@@ -7677,7 +7677,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>8.64750576019287</v>
+        <v>8.6475076675415</v>
       </c>
       <c r="H252" t="n">
         <v>450</v>
@@ -7764,7 +7764,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>8.48120880126953</v>
+        <v>8.48120784759521</v>
       </c>
       <c r="H255" t="n">
         <v>150</v>
@@ -7880,7 +7880,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568441390991</v>
+        <v>7.96568536758423</v>
       </c>
       <c r="H259" t="n">
         <v>3600</v>
@@ -7909,7 +7909,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>8.03220462799072</v>
+        <v>8.03220367431641</v>
       </c>
       <c r="H260" t="n">
         <v>5400</v>
@@ -7938,7 +7938,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>8.03220462799072</v>
+        <v>8.03220367431641</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333736419678</v>
       </c>
       <c r="H266" t="n">
         <v>450</v>
@@ -8112,7 +8112,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333736419678</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333736419678</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.48120880126953</v>
+        <v>8.48120784759521</v>
       </c>
       <c r="H269" t="n">
         <v>600</v>
@@ -8199,7 +8199,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>8.64750576019287</v>
+        <v>8.6475076675415</v>
       </c>
       <c r="H270" t="n">
         <v>600</v>
@@ -8257,7 +8257,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.64750576019287</v>
+        <v>8.6475076675415</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>8.64750576019287</v>
+        <v>8.6475076675415</v>
       </c>
       <c r="H273" t="n">
         <v>28800</v>
@@ -8315,7 +8315,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>8.64750576019287</v>
+        <v>8.6475076675415</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.64750576019287</v>
+        <v>8.6475076675415</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>8.48120880126953</v>
+        <v>8.48120784759521</v>
       </c>
       <c r="H276" t="n">
         <v>2250</v>
@@ -8402,7 +8402,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333736419678</v>
       </c>
       <c r="H277" t="n">
         <v>1800</v>
@@ -8431,7 +8431,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.64750576019287</v>
+        <v>8.6475076675415</v>
       </c>
       <c r="H278" t="n">
         <v>150</v>
@@ -8460,7 +8460,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640331268311</v>
       </c>
       <c r="H279" t="n">
         <v>19950</v>
@@ -8489,7 +8489,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640331268311</v>
       </c>
       <c r="H280" t="n">
         <v>1350</v>
@@ -8576,7 +8576,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>9.06325340270996</v>
+        <v>9.06325244903564</v>
       </c>
       <c r="H283" t="n">
         <v>900</v>
@@ -8605,7 +8605,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36392879486084</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H286" t="n">
         <v>3750</v>
@@ -8692,7 +8692,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>9.10620594024658</v>
+        <v>9.10620784759521</v>
       </c>
       <c r="H294" t="n">
         <v>1050</v>
@@ -9011,7 +9011,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G298" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H298" t="n">
         <v>300</v>
@@ -9040,7 +9040,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H300" t="n">
         <v>4350</v>
@@ -9098,7 +9098,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H302" t="n">
         <v>300</v>
@@ -9533,7 +9533,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G316" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9591,7 +9591,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H318" t="n">
         <v>1050</v>
@@ -9852,7 +9852,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H327" t="n">
         <v>8100</v>
@@ -9881,7 +9881,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G328" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H328" t="n">
         <v>600</v>
@@ -9910,7 +9910,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H329" t="n">
         <v>750</v>
@@ -9939,7 +9939,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H330" t="n">
         <v>300</v>
@@ -9968,7 +9968,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H334" t="n">
         <v>4950</v>
@@ -10084,7 +10084,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H335" t="n">
         <v>150</v>
@@ -10142,7 +10142,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10171,7 +10171,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H338" t="n">
         <v>1350</v>
@@ -10200,7 +10200,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H339" t="n">
         <v>450</v>
@@ -10229,7 +10229,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H356" t="n">
         <v>1950</v>
@@ -10722,7 +10722,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H357" t="n">
         <v>2550</v>
@@ -10751,7 +10751,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H358" t="n">
         <v>750</v>
@@ -10809,7 +10809,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G360" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H360" t="n">
         <v>1950</v>
@@ -10838,7 +10838,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H361" t="n">
         <v>150</v>
@@ -10867,7 +10867,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G363" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H363" t="n">
         <v>150</v>
@@ -10925,7 +10925,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H366" t="n">
         <v>300</v>
@@ -11012,7 +11012,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H368" t="n">
         <v>150</v>
@@ -11070,7 +11070,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H369" t="n">
         <v>750</v>
@@ -11244,7 +11244,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.20417594909668</v>
+        <v>8.204176902771</v>
       </c>
       <c r="H375" t="n">
         <v>1950</v>
@@ -11389,7 +11389,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H380" t="n">
         <v>600</v>
@@ -11592,7 +11592,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H387" t="n">
         <v>150</v>
@@ -11650,7 +11650,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H389" t="n">
         <v>150</v>
@@ -11679,7 +11679,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H393" t="n">
         <v>450</v>
@@ -11795,7 +11795,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H403" t="n">
         <v>450</v>
@@ -12085,7 +12085,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G405" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H406" t="n">
         <v>1050</v>
@@ -12172,7 +12172,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H410" t="n">
         <v>450</v>
@@ -12288,7 +12288,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780864715576</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>8.41894626617432</v>
+        <v>8.4189453125</v>
       </c>
       <c r="H415" t="n">
         <v>2400</v>
@@ -12491,7 +12491,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H418" t="n">
         <v>450</v>
@@ -12520,7 +12520,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>8.84848499298096</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H423" t="n">
         <v>750</v>
@@ -12665,7 +12665,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G425" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G426" t="n">
-        <v>8.76257610321045</v>
+        <v>8.76257514953613</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>9.10620594024658</v>
+        <v>9.10620784759521</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36392879486084</v>
       </c>
       <c r="H430" t="n">
         <v>450</v>
@@ -13129,7 +13129,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>9.96528148651123</v>
+        <v>9.96528339385986</v>
       </c>
       <c r="H440" t="n">
         <v>21900</v>
@@ -13216,7 +13216,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H443" t="n">
         <v>11400</v>
@@ -13245,7 +13245,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H444" t="n">
         <v>6150</v>
@@ -13274,7 +13274,7 @@
         <v>12</v>
       </c>
       <c r="G445" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H445" t="n">
         <v>3600</v>
@@ -13303,7 +13303,7 @@
         <v>12</v>
       </c>
       <c r="G446" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>12</v>
       </c>
       <c r="G447" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H447" t="n">
         <v>900</v>
@@ -13390,7 +13390,7 @@
         <v>12</v>
       </c>
       <c r="G449" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H449" t="n">
         <v>600</v>
@@ -13419,7 +13419,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H450" t="n">
         <v>300</v>
@@ -13477,7 +13477,7 @@
         <v>12</v>
       </c>
       <c r="G452" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H452" t="n">
         <v>1950</v>
@@ -13506,7 +13506,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H453" t="n">
         <v>4050</v>
@@ -13535,7 +13535,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H455" t="n">
         <v>450</v>
@@ -13593,7 +13593,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H456" t="n">
         <v>5400</v>
@@ -13622,7 +13622,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G457" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H457" t="n">
         <v>17250</v>
@@ -13651,7 +13651,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H458" t="n">
         <v>1350</v>
@@ -13738,7 +13738,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>9.62165260314941</v>
+        <v>9.6216516494751</v>
       </c>
       <c r="H461" t="n">
         <v>2100</v>
@@ -13767,7 +13767,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.96528148651123</v>
+        <v>9.96528339385986</v>
       </c>
       <c r="H462" t="n">
         <v>2850</v>
@@ -13796,7 +13796,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H463" t="n">
         <v>600</v>
@@ -13854,7 +13854,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.96528148651123</v>
+        <v>9.96528339385986</v>
       </c>
       <c r="H465" t="n">
         <v>1200</v>
@@ -13912,7 +13912,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H467" t="n">
         <v>13050</v>
@@ -13941,7 +13941,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H468" t="n">
         <v>3900</v>
@@ -14057,7 +14057,7 @@
         <v>12</v>
       </c>
       <c r="G472" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H472" t="n">
         <v>67350</v>
@@ -14115,7 +14115,7 @@
         <v>12</v>
       </c>
       <c r="G474" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H474" t="n">
         <v>20100</v>
@@ -14144,7 +14144,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H475" t="n">
         <v>150</v>
@@ -14173,7 +14173,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>9.96528148651123</v>
+        <v>9.96528339385986</v>
       </c>
       <c r="H476" t="n">
         <v>750</v>
@@ -14202,7 +14202,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G477" t="n">
-        <v>10.1370983123779</v>
+        <v>10.1370973587036</v>
       </c>
       <c r="H477" t="n">
         <v>600</v>
@@ -14289,7 +14289,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H480" t="n">
         <v>1500</v>
@@ -14318,7 +14318,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H481" t="n">
         <v>150</v>
@@ -14376,7 +14376,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089122772217</v>
       </c>
       <c r="H483" t="n">
         <v>2250</v>
@@ -14434,7 +14434,7 @@
         <v>12.5</v>
       </c>
       <c r="G485" t="n">
-        <v>10.738450050354</v>
+        <v>10.7384519577026</v>
       </c>
       <c r="H485" t="n">
         <v>15600</v>
@@ -14463,7 +14463,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>10.738450050354</v>
+        <v>10.7384519577026</v>
       </c>
       <c r="H486" t="n">
         <v>5100</v>
@@ -14666,7 +14666,7 @@
         <v>13</v>
       </c>
       <c r="G493" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679887771606</v>
       </c>
       <c r="H493" t="n">
         <v>36300</v>
@@ -14695,7 +14695,7 @@
         <v>13</v>
       </c>
       <c r="G494" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679887771606</v>
       </c>
       <c r="H494" t="n">
         <v>7050</v>
@@ -14724,7 +14724,7 @@
         <v>13</v>
       </c>
       <c r="G495" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679887771606</v>
       </c>
       <c r="H495" t="n">
         <v>20850</v>
@@ -14782,7 +14782,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>11.5116205215454</v>
+        <v>11.5116195678711</v>
       </c>
       <c r="H497" t="n">
         <v>6600</v>
@@ -14840,7 +14840,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.4257135391235</v>
+        <v>11.4257116317749</v>
       </c>
       <c r="H499" t="n">
         <v>750</v>
@@ -14985,7 +14985,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>12.3706951141357</v>
+        <v>12.3706970214844</v>
       </c>
       <c r="H504" t="n">
         <v>6900</v>
@@ -15014,7 +15014,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>12.6284170150757</v>
+        <v>12.62841796875</v>
       </c>
       <c r="H505" t="n">
         <v>2400</v>
@@ -15072,7 +15072,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>12.7143268585205</v>
+        <v>12.7143278121948</v>
       </c>
       <c r="H507" t="n">
         <v>2400</v>
@@ -15101,7 +15101,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G508" t="n">
-        <v>12.7143268585205</v>
+        <v>12.7143278121948</v>
       </c>
       <c r="H508" t="n">
         <v>1350</v>
@@ -15130,7 +15130,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>13.0579566955566</v>
+        <v>13.057954788208</v>
       </c>
       <c r="H509" t="n">
         <v>2550</v>
@@ -15159,7 +15159,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>13.0579566955566</v>
+        <v>13.057954788208</v>
       </c>
       <c r="H510" t="n">
         <v>12750</v>
@@ -15275,7 +15275,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G514" t="n">
-        <v>13.0579566955566</v>
+        <v>13.057954788208</v>
       </c>
       <c r="H514" t="n">
         <v>10800</v>
@@ -15304,7 +15304,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.8311262130737</v>
+        <v>13.8311252593994</v>
       </c>
       <c r="H515" t="n">
         <v>23250</v>
@@ -15333,7 +15333,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>13.9170331954956</v>
+        <v>13.9170322418213</v>
       </c>
       <c r="H516" t="n">
         <v>13350</v>
@@ -15362,7 +15362,7 @@
         <v>16</v>
       </c>
       <c r="G517" t="n">
-        <v>13.7452182769775</v>
+        <v>13.7452173233032</v>
       </c>
       <c r="H517" t="n">
         <v>17250</v>
@@ -15391,7 +15391,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>13.4874954223633</v>
+        <v>13.487494468689</v>
       </c>
       <c r="H518" t="n">
         <v>6600</v>
@@ -15420,7 +15420,7 @@
         <v>16.5</v>
       </c>
       <c r="G519" t="n">
-        <v>14.1747560501099</v>
+        <v>14.1747550964355</v>
       </c>
       <c r="H519" t="n">
         <v>8250</v>
@@ -15478,7 +15478,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324760437012</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H521" t="n">
         <v>58800</v>
@@ -15507,7 +15507,7 @@
         <v>16.5</v>
       </c>
       <c r="G522" t="n">
-        <v>14.1747560501099</v>
+        <v>14.1747550964355</v>
       </c>
       <c r="H522" t="n">
         <v>4050</v>
@@ -15536,7 +15536,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>13.8311262130737</v>
+        <v>13.8311252593994</v>
       </c>
       <c r="H523" t="n">
         <v>10950</v>
@@ -15594,7 +15594,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>14.0029392242432</v>
+        <v>14.0029401779175</v>
       </c>
       <c r="H525" t="n">
         <v>33900</v>
@@ -15652,7 +15652,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324760437012</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H527" t="n">
         <v>40350</v>
@@ -15681,7 +15681,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042938232422</v>
+        <v>14.6042947769165</v>
       </c>
       <c r="H528" t="n">
         <v>25200</v>
@@ -15710,7 +15710,7 @@
         <v>18</v>
       </c>
       <c r="G529" t="n">
-        <v>15.4633693695068</v>
+        <v>15.4633712768555</v>
       </c>
       <c r="H529" t="n">
         <v>8700</v>
@@ -15739,7 +15739,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>15.2915554046631</v>
+        <v>15.2915534973145</v>
       </c>
       <c r="H530" t="n">
         <v>3450</v>
@@ -15768,7 +15768,7 @@
         <v>18</v>
       </c>
       <c r="G531" t="n">
-        <v>15.4633693695068</v>
+        <v>15.4633712768555</v>
       </c>
       <c r="H531" t="n">
         <v>3900</v>
@@ -15797,7 +15797,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056484222412</v>
+        <v>15.2056465148926</v>
       </c>
       <c r="H532" t="n">
         <v>8550</v>
@@ -15826,7 +15826,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>15.1197385787964</v>
+        <v>15.1197395324707</v>
       </c>
       <c r="H533" t="n">
         <v>4500</v>
@@ -15855,7 +15855,7 @@
         <v>18</v>
       </c>
       <c r="G534" t="n">
-        <v>15.4633693695068</v>
+        <v>15.4633712768555</v>
       </c>
       <c r="H534" t="n">
         <v>20100</v>
@@ -15884,7 +15884,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="n">
-        <v>15.4633693695068</v>
+        <v>15.4633712768555</v>
       </c>
       <c r="H535" t="n">
         <v>15300</v>
@@ -15942,7 +15942,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>15.7259750366211</v>
+        <v>15.7259721755981</v>
       </c>
       <c r="H537" t="n">
         <v>7800</v>
@@ -15971,7 +15971,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376266479492</v>
+        <v>15.6376237869263</v>
       </c>
       <c r="H538" t="n">
         <v>2250</v>
@@ -16000,7 +16000,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>15.7259750366211</v>
+        <v>15.7259721755981</v>
       </c>
       <c r="H539" t="n">
         <v>4800</v>
@@ -16029,7 +16029,7 @@
         <v>17</v>
       </c>
       <c r="G540" t="n">
-        <v>15.0191879272461</v>
+        <v>15.0191888809204</v>
       </c>
       <c r="H540" t="n">
         <v>3150</v>
@@ -16058,7 +16058,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G541" t="n">
-        <v>15.1958866119385</v>
+        <v>15.1958847045898</v>
       </c>
       <c r="H541" t="n">
         <v>3300</v>
@@ -16087,7 +16087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>15.7259750366211</v>
+        <v>15.7259721755981</v>
       </c>
       <c r="H542" t="n">
         <v>3750</v>
@@ -16145,7 +16145,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>15.8143196105957</v>
+        <v>15.81432056427</v>
       </c>
       <c r="H544" t="n">
         <v>600</v>
@@ -16174,7 +16174,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>16.07936668396</v>
+        <v>16.0793685913086</v>
       </c>
       <c r="H545" t="n">
         <v>36600</v>
@@ -16203,7 +16203,7 @@
         <v>18</v>
       </c>
       <c r="G546" t="n">
-        <v>15.9026689529419</v>
+        <v>15.9026708602905</v>
       </c>
       <c r="H546" t="n">
         <v>3150</v>
@@ -16232,7 +16232,7 @@
         <v>18.5</v>
       </c>
       <c r="G547" t="n">
-        <v>16.3444118499756</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H547" t="n">
         <v>3750</v>
@@ -16290,7 +16290,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>16.1677131652832</v>
+        <v>16.1677150726318</v>
       </c>
       <c r="H549" t="n">
         <v>1500</v>
@@ -16319,7 +16319,7 @@
         <v>18.5</v>
       </c>
       <c r="G550" t="n">
-        <v>16.3444118499756</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H550" t="n">
         <v>1050</v>
@@ -16348,7 +16348,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>16.2560615539551</v>
+        <v>16.2560634613037</v>
       </c>
       <c r="H551" t="n">
         <v>1800</v>
@@ -16377,7 +16377,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>16.2560615539551</v>
+        <v>16.2560634613037</v>
       </c>
       <c r="H552" t="n">
         <v>1800</v>
@@ -16406,7 +16406,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>16.2560615539551</v>
+        <v>16.2560634613037</v>
       </c>
       <c r="H553" t="n">
         <v>17850</v>
@@ -16435,7 +16435,7 @@
         <v>18.5</v>
       </c>
       <c r="G554" t="n">
-        <v>16.3444118499756</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H554" t="n">
         <v>3000</v>
@@ -16464,7 +16464,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>16.2560615539551</v>
+        <v>16.2560634613037</v>
       </c>
       <c r="H555" t="n">
         <v>4950</v>
@@ -16522,7 +16522,7 @@
         <v>18.5</v>
       </c>
       <c r="G557" t="n">
-        <v>16.3444118499756</v>
+        <v>16.344409942627</v>
       </c>
       <c r="H557" t="n">
         <v>5550</v>
@@ -16580,7 +16580,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H559" t="n">
         <v>15150</v>
@@ -16609,7 +16609,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>18.1997241973877</v>
+        <v>18.1997222900391</v>
       </c>
       <c r="H560" t="n">
         <v>4650</v>
@@ -16638,7 +16638,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G561" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H561" t="n">
         <v>3450</v>
@@ -16754,7 +16754,7 @@
         <v>22</v>
       </c>
       <c r="G565" t="n">
-        <v>19.436595916748</v>
+        <v>19.4365978240967</v>
       </c>
       <c r="H565" t="n">
         <v>7350</v>
@@ -16812,7 +16812,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G567" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H567" t="n">
         <v>9150</v>
@@ -16841,7 +16841,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H568" t="n">
         <v>9600</v>
@@ -16986,7 +16986,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H573" t="n">
         <v>8325</v>
@@ -17044,7 +17044,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278938293457</v>
+        <v>17.2278919219971</v>
       </c>
       <c r="H575" t="n">
         <v>2250</v>
@@ -17102,7 +17102,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.1395454406738</v>
+        <v>17.1395435333252</v>
       </c>
       <c r="H577" t="n">
         <v>5250</v>
@@ -17131,7 +17131,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>17.1395454406738</v>
+        <v>17.1395435333252</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>17.0511951446533</v>
+        <v>17.0511932373047</v>
       </c>
       <c r="H579" t="n">
         <v>1650</v>
@@ -17247,7 +17247,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>17.0511951446533</v>
+        <v>17.0511932373047</v>
       </c>
       <c r="H582" t="n">
         <v>12225</v>
@@ -17334,7 +17334,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>17.4045906066895</v>
+        <v>17.4045867919922</v>
       </c>
       <c r="H585" t="n">
         <v>1350</v>
@@ -17392,7 +17392,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H587" t="n">
         <v>16275</v>
@@ -17566,7 +17566,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H593" t="n">
         <v>1500</v>
@@ -17624,7 +17624,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938289642334</v>
       </c>
       <c r="H595" t="n">
         <v>9525</v>
@@ -17682,7 +17682,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H597" t="n">
         <v>13125</v>
@@ -17798,7 +17798,7 @@
         <v>22</v>
       </c>
       <c r="G601" t="n">
-        <v>19.436595916748</v>
+        <v>19.4365978240967</v>
       </c>
       <c r="H601" t="n">
         <v>20550</v>
@@ -17856,7 +17856,7 @@
         <v>23</v>
       </c>
       <c r="G603" t="n">
-        <v>20.3200798034668</v>
+        <v>20.3200778961182</v>
       </c>
       <c r="H603" t="n">
         <v>11400</v>
@@ -17885,7 +17885,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H604" t="n">
         <v>19650</v>
@@ -17914,7 +17914,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H605" t="n">
         <v>10425</v>
@@ -17943,7 +17943,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G606" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H606" t="n">
         <v>10050</v>
@@ -17972,7 +17972,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H607" t="n">
         <v>5250</v>
@@ -18001,7 +18001,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H608" t="n">
         <v>12750</v>
@@ -18030,7 +18030,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H609" t="n">
         <v>13500</v>
@@ -18059,7 +18059,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>22.2637405395508</v>
+        <v>22.2637386322021</v>
       </c>
       <c r="H610" t="n">
         <v>10275</v>
@@ -18088,7 +18088,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938289642334</v>
       </c>
       <c r="H611" t="n">
         <v>7125</v>
@@ -18117,7 +18117,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938289642334</v>
       </c>
       <c r="H612" t="n">
         <v>7575</v>
@@ -18146,7 +18146,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H613" t="n">
         <v>11775</v>
@@ -18175,7 +18175,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>23.6773090362549</v>
+        <v>23.6773071289062</v>
       </c>
       <c r="H614" t="n">
         <v>5175</v>
@@ -18233,7 +18233,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G616" t="n">
-        <v>24.5607891082764</v>
+        <v>24.560791015625</v>
       </c>
       <c r="H616" t="n">
         <v>8400</v>
@@ -18262,7 +18262,7 @@
         <v>27</v>
       </c>
       <c r="G617" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H617" t="n">
         <v>11850</v>
@@ -18320,7 +18320,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472225189209</v>
       </c>
       <c r="H619" t="n">
         <v>8100</v>
@@ -18407,7 +18407,7 @@
         <v>27</v>
       </c>
       <c r="G622" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H622" t="n">
         <v>7575</v>
@@ -18436,7 +18436,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>24.5607891082764</v>
+        <v>24.560791015625</v>
       </c>
       <c r="H623" t="n">
         <v>4650</v>
@@ -18465,7 +18465,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H624" t="n">
         <v>6075</v>
@@ -18552,7 +18552,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481105804443</v>
       </c>
       <c r="H627" t="n">
         <v>16800</v>
@@ -18639,7 +18639,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H630" t="n">
         <v>11250</v>
@@ -18668,7 +18668,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H631" t="n">
         <v>11700</v>
@@ -18726,7 +18726,7 @@
         <v>35</v>
       </c>
       <c r="G633" t="n">
-        <v>30.9218559265137</v>
+        <v>30.9218578338623</v>
       </c>
       <c r="H633" t="n">
         <v>25275</v>
@@ -18871,7 +18871,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G638" t="n">
-        <v>30.391773223877</v>
+        <v>30.3917694091797</v>
       </c>
       <c r="H638" t="n">
         <v>20325</v>
@@ -18900,7 +18900,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H639" t="n">
         <v>8550</v>
@@ -18929,7 +18929,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082893371582</v>
+        <v>29.5082912445068</v>
       </c>
       <c r="H640" t="n">
         <v>11100</v>
@@ -18958,7 +18958,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H641" t="n">
         <v>10875</v>
@@ -19016,7 +19016,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481105804443</v>
       </c>
       <c r="H643" t="n">
         <v>2100</v>
@@ -19103,7 +19103,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H646" t="n">
         <v>10950</v>
@@ -19277,7 +19277,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H652" t="n">
         <v>5025</v>
@@ -19306,7 +19306,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H653" t="n">
         <v>6825</v>
@@ -19364,7 +19364,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H655" t="n">
         <v>9075</v>
@@ -19422,7 +19422,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H657" t="n">
         <v>2325</v>
@@ -19480,7 +19480,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H659" t="n">
         <v>4200</v>
@@ -19509,7 +19509,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H660" t="n">
         <v>2700</v>
@@ -19538,7 +19538,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H661" t="n">
         <v>7575</v>
@@ -19567,7 +19567,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H662" t="n">
         <v>4725</v>
@@ -19654,7 +19654,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G665" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H665" t="n">
         <v>6750</v>
@@ -19683,7 +19683,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H666" t="n">
         <v>8175</v>
@@ -19712,7 +19712,7 @@
         <v>34</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0383758544922</v>
+        <v>30.0383777618408</v>
       </c>
       <c r="H667" t="n">
         <v>6825</v>
@@ -19741,7 +19741,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H668" t="n">
         <v>5550</v>
@@ -19799,7 +19799,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H670" t="n">
         <v>4800</v>
@@ -19944,7 +19944,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H675" t="n">
         <v>7800</v>
@@ -19973,7 +19973,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>29.3315906524658</v>
+        <v>29.3315925598145</v>
       </c>
       <c r="H676" t="n">
         <v>2025</v>
@@ -20031,7 +20031,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>28.6248054504395</v>
+        <v>28.6248073577881</v>
       </c>
       <c r="H678" t="n">
         <v>4500</v>
@@ -20089,7 +20089,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H680" t="n">
         <v>4875</v>
@@ -20147,7 +20147,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H682" t="n">
         <v>5625</v>
@@ -20205,7 +20205,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>28.6248054504395</v>
+        <v>28.6248073577881</v>
       </c>
       <c r="H684" t="n">
         <v>2850</v>
@@ -20234,7 +20234,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481105804443</v>
       </c>
       <c r="H685" t="n">
         <v>8100</v>
@@ -20263,7 +20263,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>28.8015003204346</v>
+        <v>28.8015022277832</v>
       </c>
       <c r="H686" t="n">
         <v>2250</v>
@@ -20321,7 +20321,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H688" t="n">
         <v>9075</v>
@@ -20350,7 +20350,7 @@
         <v>31</v>
       </c>
       <c r="G689" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H689" t="n">
         <v>1500</v>
@@ -20640,7 +20640,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G699" t="n">
-        <v>28.6248054504395</v>
+        <v>28.6248073577881</v>
       </c>
       <c r="H699" t="n">
         <v>5400</v>
@@ -20669,7 +20669,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H700" t="n">
         <v>4500</v>
@@ -20727,7 +20727,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H702" t="n">
         <v>825</v>
@@ -20756,7 +20756,7 @@
         <v>31</v>
       </c>
       <c r="G703" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H703" t="n">
         <v>12375</v>
@@ -20785,7 +20785,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H704" t="n">
         <v>1350</v>
@@ -20814,7 +20814,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H705" t="n">
         <v>2550</v>
@@ -20872,7 +20872,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G707" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H707" t="n">
         <v>4125</v>
@@ -21075,7 +21075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H714" t="n">
         <v>2100</v>
@@ -21104,7 +21104,7 @@
         <v>31</v>
       </c>
       <c r="G715" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H715" t="n">
         <v>2700</v>
@@ -21133,7 +21133,7 @@
         <v>31</v>
       </c>
       <c r="G716" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H716" t="n">
         <v>600</v>
@@ -21191,7 +21191,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H718" t="n">
         <v>375</v>
@@ -21597,7 +21597,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>24.5607891082764</v>
+        <v>24.560791015625</v>
       </c>
       <c r="H732" t="n">
         <v>3375</v>
@@ -21626,7 +21626,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>24.5607891082764</v>
+        <v>24.560791015625</v>
       </c>
       <c r="H733" t="n">
         <v>5250</v>
@@ -21655,7 +21655,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H734" t="n">
         <v>2550</v>
@@ -21684,7 +21684,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>24.9141826629639</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H735" t="n">
         <v>7275</v>
@@ -21713,7 +21713,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>24.5607891082764</v>
+        <v>24.560791015625</v>
       </c>
       <c r="H736" t="n">
         <v>9525</v>
@@ -21742,7 +21742,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H737" t="n">
         <v>15750</v>
@@ -21771,7 +21771,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>24.9141826629639</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H738" t="n">
         <v>825</v>
@@ -21800,7 +21800,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H739" t="n">
         <v>675</v>
@@ -21829,7 +21829,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H740" t="n">
         <v>1650</v>
@@ -21858,7 +21858,7 @@
         <v>28</v>
       </c>
       <c r="G741" t="n">
-        <v>24.7374877929688</v>
+        <v>24.7374858856201</v>
       </c>
       <c r="H741" t="n">
         <v>1275</v>
@@ -21887,7 +21887,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H742" t="n">
         <v>300</v>
@@ -22003,7 +22003,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H746" t="n">
         <v>675</v>
@@ -22032,7 +22032,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>24.5607891082764</v>
+        <v>24.560791015625</v>
       </c>
       <c r="H747" t="n">
         <v>825</v>
@@ -22090,7 +22090,7 @@
         <v>27</v>
       </c>
       <c r="G749" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H749" t="n">
         <v>1875</v>
@@ -22119,7 +22119,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>23.6773090362549</v>
+        <v>23.6773071289062</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>23.6773090362549</v>
+        <v>23.6773071289062</v>
       </c>
       <c r="H751" t="n">
         <v>3525</v>
@@ -22264,7 +22264,7 @@
         <v>25</v>
       </c>
       <c r="G755" t="n">
-        <v>22.0870399475098</v>
+        <v>22.087043762207</v>
       </c>
       <c r="H755" t="n">
         <v>2775</v>
@@ -22293,7 +22293,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H756" t="n">
         <v>6150</v>
@@ -22322,7 +22322,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>21.5569534301758</v>
+        <v>21.5569515228271</v>
       </c>
       <c r="H757" t="n">
         <v>900</v>
@@ -22380,7 +22380,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>20.8501682281494</v>
+        <v>20.8501663208008</v>
       </c>
       <c r="H759" t="n">
         <v>2625</v>
@@ -22409,7 +22409,7 @@
         <v>25</v>
       </c>
       <c r="G760" t="n">
-        <v>22.0870399475098</v>
+        <v>22.087043762207</v>
       </c>
       <c r="H760" t="n">
         <v>9750</v>
@@ -22438,7 +22438,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H761" t="n">
         <v>1500</v>
@@ -22467,7 +22467,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>24.9141826629639</v>
+        <v>24.9141845703125</v>
       </c>
       <c r="H762" t="n">
         <v>1650</v>
@@ -22496,7 +22496,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>24.5607891082764</v>
+        <v>24.560791015625</v>
       </c>
       <c r="H763" t="n">
         <v>525</v>
@@ -22525,7 +22525,7 @@
         <v>28</v>
       </c>
       <c r="G764" t="n">
-        <v>24.7374877929688</v>
+        <v>24.7374858856201</v>
       </c>
       <c r="H764" t="n">
         <v>1200</v>
@@ -22554,7 +22554,7 @@
         <v>28</v>
       </c>
       <c r="G765" t="n">
-        <v>24.7374877929688</v>
+        <v>24.7374858856201</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H766" t="n">
         <v>1500</v>
@@ -22612,7 +22612,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H767" t="n">
         <v>375</v>
@@ -22699,7 +22699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H770" t="n">
         <v>2925</v>
@@ -22757,7 +22757,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H772" t="n">
         <v>1200</v>
@@ -22786,7 +22786,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>27.5646266937256</v>
+        <v>27.5646286010742</v>
       </c>
       <c r="H773" t="n">
         <v>2475</v>
@@ -22815,7 +22815,7 @@
         <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H774" t="n">
         <v>2850</v>
@@ -23018,7 +23018,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>25.532621383667</v>
+        <v>25.5326175689697</v>
       </c>
       <c r="H781" t="n">
         <v>300</v>
@@ -23047,7 +23047,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H782" t="n">
         <v>1650</v>
@@ -23076,7 +23076,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H783" t="n">
         <v>2700</v>
@@ -23163,7 +23163,7 @@
         <v>27</v>
       </c>
       <c r="G786" t="n">
-        <v>23.85400390625</v>
+        <v>23.8540058135986</v>
       </c>
       <c r="H786" t="n">
         <v>1725</v>
@@ -23192,7 +23192,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G787" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472225189209</v>
       </c>
       <c r="H787" t="n">
         <v>1650</v>
@@ -23221,7 +23221,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H788" t="n">
         <v>75</v>
@@ -23250,7 +23250,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H789" t="n">
         <v>300</v>
@@ -23279,7 +23279,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H790" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>24.3840942382812</v>
+        <v>24.3840923309326</v>
       </c>
       <c r="H795" t="n">
         <v>1125</v>
@@ -23453,7 +23453,7 @@
         <v>28.5</v>
       </c>
       <c r="G796" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H796" t="n">
         <v>4875</v>
@@ -23482,7 +23482,7 @@
         <v>28.5</v>
       </c>
       <c r="G797" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H797" t="n">
         <v>1950</v>
@@ -23598,7 +23598,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H801" t="n">
         <v>600</v>
@@ -23685,7 +23685,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>24.1900444030762</v>
+        <v>24.1900424957275</v>
       </c>
       <c r="H804" t="n">
         <v>150</v>
@@ -23714,7 +23714,7 @@
         <v>28</v>
       </c>
       <c r="G805" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H805" t="n">
         <v>1950</v>
@@ -23743,7 +23743,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H806" t="n">
         <v>2175</v>
@@ -23772,7 +23772,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H807" t="n">
         <v>75</v>
@@ -23801,7 +23801,7 @@
         <v>27</v>
       </c>
       <c r="G808" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>27</v>
       </c>
       <c r="G810" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H810" t="n">
         <v>75</v>
@@ -23888,7 +23888,7 @@
         <v>27</v>
       </c>
       <c r="G811" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H811" t="n">
         <v>150</v>
@@ -23917,7 +23917,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>23.7404136657715</v>
+        <v>23.7404117584229</v>
       </c>
       <c r="H812" t="n">
         <v>150</v>
@@ -23975,7 +23975,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>24.100118637085</v>
+        <v>24.1001167297363</v>
       </c>
       <c r="H814" t="n">
         <v>75</v>
@@ -24062,7 +24062,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H817" t="n">
         <v>450</v>
@@ -24091,7 +24091,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H818" t="n">
         <v>375</v>
@@ -24207,7 +24207,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>23.7404136657715</v>
+        <v>23.7404117584229</v>
       </c>
       <c r="H822" t="n">
         <v>4350</v>
@@ -24265,7 +24265,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>23.5605621337891</v>
+        <v>23.5605640411377</v>
       </c>
       <c r="H824" t="n">
         <v>825</v>
@@ -24294,7 +24294,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G825" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598197937012</v>
       </c>
       <c r="H825" t="n">
         <v>300</v>
@@ -24323,7 +24323,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598197937012</v>
       </c>
       <c r="H826" t="n">
         <v>1500</v>
@@ -24410,7 +24410,7 @@
         <v>26</v>
       </c>
       <c r="G829" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H829" t="n">
         <v>1950</v>
@@ -24439,7 +24439,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>23.5605621337891</v>
+        <v>23.5605640411377</v>
       </c>
       <c r="H830" t="n">
         <v>5925</v>
@@ -24468,7 +24468,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>23.2008590698242</v>
+        <v>23.2008609771729</v>
       </c>
       <c r="H831" t="n">
         <v>1725</v>
@@ -24497,7 +24497,7 @@
         <v>26</v>
       </c>
       <c r="G832" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>26</v>
       </c>
       <c r="G833" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H833" t="n">
         <v>825</v>
@@ -24555,7 +24555,7 @@
         <v>26</v>
       </c>
       <c r="G834" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H834" t="n">
         <v>825</v>
@@ -24584,7 +24584,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>23.2907848358154</v>
+        <v>23.2907867431641</v>
       </c>
       <c r="H835" t="n">
         <v>1350</v>
@@ -24613,7 +24613,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>23.2008590698242</v>
+        <v>23.2008609771729</v>
       </c>
       <c r="H836" t="n">
         <v>225</v>
@@ -24671,7 +24671,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>23.2008590698242</v>
+        <v>23.2008609771729</v>
       </c>
       <c r="H838" t="n">
         <v>300</v>
@@ -24700,7 +24700,7 @@
         <v>25.5</v>
       </c>
       <c r="G839" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24729,7 +24729,7 @@
         <v>25.5</v>
       </c>
       <c r="G840" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H840" t="n">
         <v>300</v>
@@ -24758,7 +24758,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>22.6613063812256</v>
+        <v>22.661304473877</v>
       </c>
       <c r="H841" t="n">
         <v>150</v>
@@ -24816,7 +24816,7 @@
         <v>24.5</v>
       </c>
       <c r="G843" t="n">
-        <v>22.0318241119385</v>
+        <v>22.0318222045898</v>
       </c>
       <c r="H843" t="n">
         <v>675</v>
@@ -24874,7 +24874,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>21.3124179840088</v>
+        <v>21.3124160766602</v>
       </c>
       <c r="H845" t="n">
         <v>825</v>
@@ -24990,7 +24990,7 @@
         <v>25</v>
       </c>
       <c r="G849" t="n">
-        <v>22.4814510345459</v>
+        <v>22.4814548492432</v>
       </c>
       <c r="H849" t="n">
         <v>1725</v>
@@ -25019,7 +25019,7 @@
         <v>24.5</v>
       </c>
       <c r="G850" t="n">
-        <v>22.0318241119385</v>
+        <v>22.0318222045898</v>
       </c>
       <c r="H850" t="n">
         <v>825</v>
@@ -25048,7 +25048,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>21.4023418426514</v>
+        <v>21.4023456573486</v>
       </c>
       <c r="H851" t="n">
         <v>300</v>
@@ -25164,7 +25164,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G855" t="n">
-        <v>20.4131622314453</v>
+        <v>20.413158416748</v>
       </c>
       <c r="H855" t="n">
         <v>1050</v>
@@ -25193,7 +25193,7 @@
         <v>22</v>
       </c>
       <c r="G856" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H856" t="n">
         <v>5700</v>
@@ -25222,7 +25222,7 @@
         <v>22</v>
       </c>
       <c r="G857" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H857" t="n">
         <v>2925</v>
@@ -25280,7 +25280,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G859" t="n">
-        <v>19.0642719268799</v>
+        <v>19.0642738342285</v>
       </c>
       <c r="H859" t="n">
         <v>1200</v>
@@ -25309,7 +25309,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038246154785</v>
       </c>
       <c r="H860" t="n">
         <v>1875</v>
@@ -25396,7 +25396,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038246154785</v>
       </c>
       <c r="H863" t="n">
         <v>1275</v>
@@ -25425,7 +25425,7 @@
         <v>21.5</v>
       </c>
       <c r="G864" t="n">
-        <v>19.3340511322021</v>
+        <v>19.3340492248535</v>
       </c>
       <c r="H864" t="n">
         <v>300</v>
@@ -25454,7 +25454,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>19.0642719268799</v>
+        <v>19.0642738342285</v>
       </c>
       <c r="H865" t="n">
         <v>2325</v>
@@ -25483,7 +25483,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>19.6038265228271</v>
+        <v>19.6038246154785</v>
       </c>
       <c r="H866" t="n">
         <v>50100</v>
@@ -25512,7 +25512,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>20.5930099487305</v>
+        <v>20.5930118560791</v>
       </c>
       <c r="H867" t="n">
         <v>19650</v>
@@ -25570,7 +25570,7 @@
         <v>25</v>
       </c>
       <c r="G869" t="n">
-        <v>22.4814510345459</v>
+        <v>22.4814548492432</v>
       </c>
       <c r="H869" t="n">
         <v>5550</v>
@@ -25599,7 +25599,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.3915252685547</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H870" t="n">
         <v>4050</v>
@@ -25686,7 +25686,7 @@
         <v>25.5</v>
       </c>
       <c r="G873" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H873" t="n">
         <v>1650</v>
@@ -25889,7 +25889,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>20.5930099487305</v>
+        <v>20.5930118560791</v>
       </c>
       <c r="H880" t="n">
         <v>525</v>
@@ -25947,7 +25947,7 @@
         <v>22</v>
       </c>
       <c r="G882" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H882" t="n">
         <v>750</v>
@@ -26034,7 +26034,7 @@
         <v>22</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H885" t="n">
         <v>11025</v>
@@ -26063,7 +26063,7 @@
         <v>22</v>
       </c>
       <c r="G886" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H886" t="n">
         <v>4800</v>
@@ -26092,7 +26092,7 @@
         <v>22</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H887" t="n">
         <v>3975</v>
@@ -26121,7 +26121,7 @@
         <v>22</v>
       </c>
       <c r="G888" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H888" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>22</v>
       </c>
       <c r="G889" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H889" t="n">
         <v>1050</v>
@@ -26208,7 +26208,7 @@
         <v>23.5</v>
       </c>
       <c r="G891" t="n">
-        <v>21.1325664520264</v>
+        <v>21.1325645446777</v>
       </c>
       <c r="H891" t="n">
         <v>5475</v>
@@ -26266,7 +26266,7 @@
         <v>27</v>
       </c>
       <c r="G893" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H893" t="n">
         <v>14100</v>
@@ -26295,7 +26295,7 @@
         <v>26</v>
       </c>
       <c r="G894" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H894" t="n">
         <v>4950</v>
@@ -26324,7 +26324,7 @@
         <v>26</v>
       </c>
       <c r="G895" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H895" t="n">
         <v>1650</v>
@@ -26353,7 +26353,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>23.2907848358154</v>
+        <v>23.2907867431641</v>
       </c>
       <c r="H896" t="n">
         <v>1200</v>
@@ -26382,7 +26382,7 @@
         <v>26</v>
       </c>
       <c r="G897" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H897" t="n">
         <v>4875</v>
@@ -26440,7 +26440,7 @@
         <v>25.5</v>
       </c>
       <c r="G899" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H899" t="n">
         <v>16275</v>
@@ -26498,7 +26498,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>22.5713806152344</v>
+        <v>22.5713787078857</v>
       </c>
       <c r="H901" t="n">
         <v>1725</v>
@@ -26527,7 +26527,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>21.9418983459473</v>
+        <v>21.9418964385986</v>
       </c>
       <c r="H902" t="n">
         <v>1950</v>
@@ -26614,7 +26614,7 @@
         <v>24.5</v>
       </c>
       <c r="G905" t="n">
-        <v>22.0318241119385</v>
+        <v>22.0318222045898</v>
       </c>
       <c r="H905" t="n">
         <v>975</v>
@@ -26672,7 +26672,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.3915252685547</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H907" t="n">
         <v>3225</v>
@@ -26730,7 +26730,7 @@
         <v>25.5</v>
       </c>
       <c r="G909" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H909" t="n">
         <v>300</v>
@@ -26846,7 +26846,7 @@
         <v>24.5</v>
       </c>
       <c r="G913" t="n">
-        <v>22.0318241119385</v>
+        <v>22.0318222045898</v>
       </c>
       <c r="H913" t="n">
         <v>300</v>
@@ -26875,7 +26875,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.3915252685547</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H914" t="n">
         <v>75</v>
@@ -26904,7 +26904,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>21.9418983459473</v>
+        <v>21.9418964385986</v>
       </c>
       <c r="H915" t="n">
         <v>5850</v>
@@ -26933,7 +26933,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>23.2008590698242</v>
+        <v>23.2008609771729</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -26962,7 +26962,7 @@
         <v>25</v>
       </c>
       <c r="G917" t="n">
-        <v>22.4814510345459</v>
+        <v>22.4814548492432</v>
       </c>
       <c r="H917" t="n">
         <v>1200</v>
@@ -27252,7 +27252,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>23.2008590698242</v>
+        <v>23.2008609771729</v>
       </c>
       <c r="H927" t="n">
         <v>75</v>
@@ -27281,7 +27281,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>22.5713806152344</v>
+        <v>22.5713787078857</v>
       </c>
       <c r="H928" t="n">
         <v>300</v>
@@ -27368,7 +27368,7 @@
         <v>26</v>
       </c>
       <c r="G931" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H931" t="n">
         <v>600</v>
@@ -27397,7 +27397,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G932" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598197937012</v>
       </c>
       <c r="H932" t="n">
         <v>2625</v>
@@ -27426,7 +27426,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598197937012</v>
       </c>
       <c r="H933" t="n">
         <v>4500</v>
@@ -27513,7 +27513,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.988561630249</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H936" t="n">
         <v>1875</v>
@@ -27716,7 +27716,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H943" t="n">
         <v>21450</v>
@@ -27745,7 +27745,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>28.5</v>
       </c>
       <c r="G947" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288547515869</v>
       </c>
       <c r="H947" t="n">
         <v>525</v>
@@ -27861,7 +27861,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H948" t="n">
         <v>4950</v>
@@ -27890,7 +27890,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.988561630249</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H949" t="n">
         <v>1650</v>
@@ -28064,7 +28064,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.988561630249</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H955" t="n">
         <v>1050</v>
@@ -28296,7 +28296,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>26.7079677581787</v>
+        <v>26.7079658508301</v>
       </c>
       <c r="H963" t="n">
         <v>525</v>
@@ -28325,7 +28325,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>26.7079677581787</v>
+        <v>26.7079658508301</v>
       </c>
       <c r="H964" t="n">
         <v>525</v>
@@ -28354,7 +28354,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>27.1575946807861</v>
+        <v>27.1575965881348</v>
       </c>
       <c r="H965" t="n">
         <v>300</v>
@@ -28441,7 +28441,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H968" t="n">
         <v>450</v>
@@ -28499,7 +28499,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H970" t="n">
         <v>3000</v>
@@ -28528,7 +28528,7 @@
         <v>28.5</v>
       </c>
       <c r="G971" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288547515869</v>
       </c>
       <c r="H971" t="n">
         <v>1350</v>
@@ -28615,7 +28615,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H974" t="n">
         <v>75</v>
@@ -28644,7 +28644,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.988561630249</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H976" t="n">
         <v>375</v>
@@ -28702,7 +28702,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H977" t="n">
         <v>750</v>
@@ -28760,7 +28760,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H979" t="n">
         <v>4275</v>
@@ -28789,7 +28789,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H980" t="n">
         <v>6150</v>
@@ -28847,7 +28847,7 @@
         <v>28</v>
       </c>
       <c r="G982" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H982" t="n">
         <v>75</v>
@@ -28876,7 +28876,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>24.8195247650146</v>
+        <v>24.819522857666</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -28905,7 +28905,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>24.9993743896484</v>
+        <v>24.9993762969971</v>
       </c>
       <c r="H984" t="n">
         <v>3525</v>
@@ -28934,7 +28934,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>24.9094524383545</v>
+        <v>24.9094505310059</v>
       </c>
       <c r="H985" t="n">
         <v>3825</v>
@@ -28963,7 +28963,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>24.9094524383545</v>
+        <v>24.9094505310059</v>
       </c>
       <c r="H986" t="n">
         <v>2850</v>
@@ -28992,7 +28992,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>24.9993743896484</v>
+        <v>24.9993762969971</v>
       </c>
       <c r="H987" t="n">
         <v>1275</v>
@@ -29021,7 +29021,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598197937012</v>
       </c>
       <c r="H988" t="n">
         <v>675</v>
@@ -29079,7 +29079,7 @@
         <v>28</v>
       </c>
       <c r="G990" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H990" t="n">
         <v>1425</v>
@@ -29108,7 +29108,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>25.2691535949707</v>
+        <v>25.2691516876221</v>
       </c>
       <c r="H991" t="n">
         <v>150</v>
@@ -29137,7 +29137,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>24.9993743896484</v>
+        <v>24.9993762969971</v>
       </c>
       <c r="H992" t="n">
         <v>1575</v>
@@ -29195,7 +29195,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H994" t="n">
         <v>8625</v>
@@ -29224,7 +29224,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H995" t="n">
         <v>525</v>
@@ -29253,7 +29253,7 @@
         <v>28</v>
       </c>
       <c r="G996" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H996" t="n">
         <v>1725</v>
@@ -29340,7 +29340,7 @@
         <v>28.5</v>
       </c>
       <c r="G999" t="n">
-        <v>25.6288566589355</v>
+        <v>25.6288547515869</v>
       </c>
       <c r="H999" t="n">
         <v>1575</v>
@@ -29369,7 +29369,7 @@
         <v>28</v>
       </c>
       <c r="G1000" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H1000" t="n">
         <v>3675</v>
@@ -29398,7 +29398,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>25.808708190918</v>
+        <v>25.8087100982666</v>
       </c>
       <c r="H1001" t="n">
         <v>1875</v>
@@ -29427,7 +29427,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>25.808708190918</v>
+        <v>25.8087100982666</v>
       </c>
       <c r="H1002" t="n">
         <v>3450</v>
@@ -29456,7 +29456,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1003" t="n">
-        <v>25.808708190918</v>
+        <v>25.8087100982666</v>
       </c>
       <c r="H1003" t="n">
         <v>1350</v>
@@ -29485,7 +29485,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H1004" t="n">
         <v>1050</v>
@@ -29514,7 +29514,7 @@
         <v>28</v>
       </c>
       <c r="G1005" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H1005" t="n">
         <v>1275</v>
@@ -29601,7 +29601,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H1008" t="n">
         <v>17250</v>
@@ -29630,7 +29630,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>24.8195247650146</v>
+        <v>24.819522857666</v>
       </c>
       <c r="H1009" t="n">
         <v>750</v>
@@ -29659,7 +29659,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>24.9993743896484</v>
+        <v>24.9993762969971</v>
       </c>
       <c r="H1010" t="n">
         <v>975</v>
@@ -29717,7 +29717,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>25.8986320495605</v>
+        <v>25.8986339569092</v>
       </c>
       <c r="H1012" t="n">
         <v>2250</v>
@@ -29746,7 +29746,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>26.4381866455078</v>
+        <v>26.4381885528564</v>
       </c>
       <c r="H1013" t="n">
         <v>2475</v>
@@ -29891,7 +29891,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>27.1575946807861</v>
+        <v>27.1575965881348</v>
       </c>
       <c r="H1018" t="n">
         <v>825</v>
@@ -29920,7 +29920,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1019" t="n">
-        <v>28.0568523406982</v>
+        <v>28.0568542480469</v>
       </c>
       <c r="H1019" t="n">
         <v>1500</v>
@@ -29978,7 +29978,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>27.517297744751</v>
+        <v>27.5172996520996</v>
       </c>
       <c r="H1021" t="n">
         <v>5400</v>
@@ -30007,7 +30007,7 @@
         <v>34</v>
       </c>
       <c r="G1022" t="n">
-        <v>30.5747756958008</v>
+        <v>30.5747776031494</v>
       </c>
       <c r="H1022" t="n">
         <v>5400</v>
@@ -30036,7 +30036,7 @@
         <v>31</v>
       </c>
       <c r="G1023" t="n">
-        <v>27.8770046234131</v>
+        <v>27.8770027160645</v>
       </c>
       <c r="H1023" t="n">
         <v>9450</v>
@@ -30065,7 +30065,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>28.1467800140381</v>
+        <v>28.1467781066895</v>
       </c>
       <c r="H1024" t="n">
         <v>1200</v>
@@ -30094,7 +30094,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>28.2367057800293</v>
+        <v>28.2367038726807</v>
       </c>
       <c r="H1025" t="n">
         <v>2475</v>
@@ -30268,7 +30268,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1031" t="n">
         <v>1050</v>
@@ -30326,7 +30326,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>28.9561138153076</v>
+        <v>28.956111907959</v>
       </c>
       <c r="H1033" t="n">
         <v>1575</v>
@@ -30471,7 +30471,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1038" t="n">
-        <v>30.8445529937744</v>
+        <v>30.844554901123</v>
       </c>
       <c r="H1038" t="n">
         <v>8700</v>
@@ -30500,7 +30500,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1039" t="n">
-        <v>30.3949241638184</v>
+        <v>30.3949222564697</v>
       </c>
       <c r="H1039" t="n">
         <v>2025</v>
@@ -30529,7 +30529,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639572143555</v>
+        <v>31.5639591217041</v>
       </c>
       <c r="H1040" t="n">
         <v>4425</v>
@@ -30558,7 +30558,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.833740234375</v>
+        <v>31.8337364196777</v>
       </c>
       <c r="H1041" t="n">
         <v>7800</v>
@@ -30645,7 +30645,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042560577393</v>
+        <v>31.2042598724365</v>
       </c>
       <c r="H1044" t="n">
         <v>1425</v>
@@ -30674,7 +30674,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1045" t="n">
         <v>10575</v>
@@ -30790,7 +30790,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1049" t="n">
         <v>2100</v>
@@ -30819,7 +30819,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>30.9344825744629</v>
+        <v>30.9344787597656</v>
       </c>
       <c r="H1050" t="n">
         <v>675</v>
@@ -30848,7 +30848,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1051" t="n">
-        <v>30.3949241638184</v>
+        <v>30.3949222564697</v>
       </c>
       <c r="H1051" t="n">
         <v>2100</v>
@@ -30877,7 +30877,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1052" t="n">
         <v>675</v>
@@ -30935,7 +30935,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1054" t="n">
         <v>1050</v>
@@ -30964,7 +30964,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1055" t="n">
-        <v>29.945291519165</v>
+        <v>29.9452953338623</v>
       </c>
       <c r="H1055" t="n">
         <v>450</v>
@@ -31109,7 +31109,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1060" t="n">
-        <v>28.5064830780029</v>
+        <v>28.5064811706543</v>
       </c>
       <c r="H1060" t="n">
         <v>2175</v>
@@ -31196,7 +31196,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1063" t="n">
         <v>1650</v>
@@ -31225,7 +31225,7 @@
         <v>33</v>
       </c>
       <c r="G1064" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765125274658</v>
       </c>
       <c r="H1064" t="n">
         <v>1425</v>
@@ -31254,7 +31254,7 @@
         <v>33</v>
       </c>
       <c r="G1065" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765125274658</v>
       </c>
       <c r="H1065" t="n">
         <v>600</v>
@@ -31283,7 +31283,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>30.0083141326904</v>
+        <v>30.0083122253418</v>
       </c>
       <c r="H1066" t="n">
         <v>450</v>
@@ -31573,7 +31573,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1076" t="n">
         <v>3600</v>
@@ -31660,7 +31660,7 @@
         <v>31.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1079" t="n">
         <v>1350</v>
@@ -31689,7 +31689,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1080" t="n">
         <v>14100</v>
@@ -31718,7 +31718,7 @@
         <v>31.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1081" t="n">
         <v>7125</v>
@@ -31747,7 +31747,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1082" t="n">
         <v>5025</v>
@@ -31776,7 +31776,7 @@
         <v>31.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1083" t="n">
         <v>6450</v>
@@ -31863,7 +31863,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1086" t="n">
         <v>2100</v>
@@ -31979,7 +31979,7 @@
         <v>31.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1090" t="n">
         <v>150</v>
@@ -32008,7 +32008,7 @@
         <v>31.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1091" t="n">
         <v>75</v>
@@ -32066,7 +32066,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>27.9832153320312</v>
+        <v>27.9832134246826</v>
       </c>
       <c r="H1093" t="n">
         <v>1275</v>
@@ -32182,7 +32182,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1097" t="n">
         <v>2400</v>
@@ -32211,7 +32211,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1098" t="n">
         <v>600</v>
@@ -32327,7 +32327,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1102" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1102" t="n">
         <v>5475</v>
@@ -32414,7 +32414,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>28.6275634765625</v>
+        <v>28.6275653839111</v>
       </c>
       <c r="H1105" t="n">
         <v>3261</v>
@@ -32472,7 +32472,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1107" t="n">
-        <v>28.4434642791748</v>
+        <v>28.4434661865234</v>
       </c>
       <c r="H1107" t="n">
         <v>15327</v>
@@ -32501,7 +32501,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1108" t="n">
-        <v>28.2593650817871</v>
+        <v>28.2593669891357</v>
       </c>
       <c r="H1108" t="n">
         <v>17829</v>
@@ -32588,7 +32588,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>28.6275634765625</v>
+        <v>28.6275653839111</v>
       </c>
       <c r="H1111" t="n">
         <v>2539</v>
@@ -32617,7 +32617,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1112" t="n">
-        <v>28.4434642791748</v>
+        <v>28.4434661865234</v>
       </c>
       <c r="H1112" t="n">
         <v>3350</v>
@@ -32646,7 +32646,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1113" t="n">
         <v>40817</v>
@@ -32907,7 +32907,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1122" t="n">
         <v>791</v>
@@ -32936,7 +32936,7 @@
         <v>33</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765125274658</v>
       </c>
       <c r="H1123" t="n">
         <v>1300</v>
@@ -32994,7 +32994,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>30.0083141326904</v>
+        <v>30.0083122253418</v>
       </c>
       <c r="H1125" t="n">
         <v>229</v>
@@ -33023,7 +33023,7 @@
         <v>33</v>
       </c>
       <c r="G1126" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765125274658</v>
       </c>
       <c r="H1126" t="n">
         <v>1180</v>
@@ -33052,7 +33052,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1127" t="n">
-        <v>30.0083141326904</v>
+        <v>30.0083122253418</v>
       </c>
       <c r="H1127" t="n">
         <v>114</v>
@@ -33139,7 +33139,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1130" t="n">
         <v>147</v>
@@ -33400,7 +33400,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1139" t="n">
         <v>5215</v>
@@ -33487,7 +33487,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1142" t="n">
         <v>1568</v>
@@ -33574,7 +33574,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1145" t="n">
         <v>240</v>
@@ -33603,7 +33603,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1146" t="n">
-        <v>28.6275634765625</v>
+        <v>28.6275653839111</v>
       </c>
       <c r="H1146" t="n">
         <v>578</v>
@@ -33632,7 +33632,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>28.2593650817871</v>
+        <v>28.2593669891357</v>
       </c>
       <c r="H1147" t="n">
         <v>440</v>
@@ -33661,7 +33661,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1148" t="n">
-        <v>28.2593650817871</v>
+        <v>28.2593669891357</v>
       </c>
       <c r="H1148" t="n">
         <v>155</v>
@@ -33690,7 +33690,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1149" t="n">
         <v>1616</v>
@@ -33719,7 +33719,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>29.0878162384033</v>
+        <v>29.0878143310547</v>
       </c>
       <c r="H1150" t="n">
         <v>2194</v>
@@ -33777,7 +33777,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1152" t="n">
         <v>442</v>
@@ -33806,7 +33806,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1153" t="n">
         <v>365</v>
@@ -33835,7 +33835,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1154" t="n">
-        <v>28.1673126220703</v>
+        <v>28.1673145294189</v>
       </c>
       <c r="H1154" t="n">
         <v>6213</v>
@@ -33980,7 +33980,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1159" t="n">
-        <v>27.3388652801514</v>
+        <v>27.3388633728027</v>
       </c>
       <c r="H1159" t="n">
         <v>1696</v>
@@ -34038,7 +34038,7 @@
         <v>30</v>
       </c>
       <c r="G1161" t="n">
-        <v>27.6150131225586</v>
+        <v>27.6150150299072</v>
       </c>
       <c r="H1161" t="n">
         <v>1186</v>
@@ -34096,7 +34096,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1163" t="n">
         <v>1128</v>
@@ -34125,7 +34125,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1164" t="n">
         <v>5262</v>
@@ -34154,7 +34154,7 @@
         <v>28.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1165" t="n">
         <v>1365</v>
@@ -34183,7 +34183,7 @@
         <v>28.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1166" t="n">
         <v>12882</v>
@@ -34212,7 +34212,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978618621826</v>
       </c>
       <c r="H1167" t="n">
         <v>1240</v>
@@ -34299,7 +34299,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978618621826</v>
       </c>
       <c r="H1170" t="n">
         <v>1331</v>
@@ -34328,7 +34328,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1171" t="n">
         <v>1864</v>
@@ -34357,7 +34357,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1172" t="n">
         <v>10192</v>
@@ -34386,7 +34386,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1173" t="n">
         <v>27679</v>
@@ -34415,7 +34415,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1174" t="n">
         <v>300</v>
@@ -34444,7 +34444,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1175" t="n">
         <v>596</v>
@@ -34473,7 +34473,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1176" t="n">
         <v>119</v>
@@ -34531,7 +34531,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1178" t="n">
         <v>572</v>
@@ -34560,7 +34560,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>24.301212310791</v>
+        <v>24.3012104034424</v>
       </c>
       <c r="H1179" t="n">
         <v>2003</v>
@@ -34589,7 +34589,7 @@
         <v>25.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>23.4727611541748</v>
+        <v>23.4727630615234</v>
       </c>
       <c r="H1180" t="n">
         <v>2862</v>
@@ -34647,7 +34647,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966133117676</v>
+        <v>23.1966114044189</v>
       </c>
       <c r="H1182" t="n">
         <v>16419</v>
@@ -34676,7 +34676,7 @@
         <v>25</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0125102996826</v>
+        <v>23.0125122070312</v>
       </c>
       <c r="H1183" t="n">
         <v>6634</v>
@@ -34705,7 +34705,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H1184" t="n">
         <v>766</v>
@@ -34734,7 +34734,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1185" t="n">
         <v>3901</v>
@@ -34763,7 +34763,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1186" t="n">
         <v>4535</v>
@@ -34792,7 +34792,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1187" t="n">
         <v>1957</v>
@@ -34821,7 +34821,7 @@
         <v>26.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1188" t="n">
         <v>550</v>
@@ -34850,7 +34850,7 @@
         <v>25.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.4727611541748</v>
+        <v>23.4727630615234</v>
       </c>
       <c r="H1189" t="n">
         <v>4247</v>
@@ -34879,7 +34879,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1190" t="n">
         <v>3364</v>
@@ -34908,7 +34908,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H1191" t="n">
         <v>3743</v>
@@ -34937,7 +34937,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>23.3807125091553</v>
+        <v>23.3807106018066</v>
       </c>
       <c r="H1192" t="n">
         <v>2334</v>
@@ -34966,7 +34966,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1193" t="n">
         <v>5553</v>
@@ -34995,7 +34995,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1194" t="n">
         <v>6387</v>
@@ -35024,7 +35024,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978618621826</v>
       </c>
       <c r="H1195" t="n">
         <v>15303</v>
@@ -35053,7 +35053,7 @@
         <v>28.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1196" t="n">
         <v>2871</v>
@@ -35140,7 +35140,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1199" t="n">
-        <v>25.2217121124268</v>
+        <v>25.2217140197754</v>
       </c>
       <c r="H1199" t="n">
         <v>3638</v>
@@ -35169,7 +35169,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1200" t="n">
         <v>2435</v>
@@ -35227,7 +35227,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1202" t="n">
         <v>3057</v>
@@ -35256,7 +35256,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1203" t="n">
         <v>250</v>
@@ -35285,7 +35285,7 @@
         <v>26.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1204" t="n">
         <v>2078</v>
@@ -35314,7 +35314,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1205" t="n">
         <v>2933</v>
@@ -35372,7 +35372,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>24.301212310791</v>
+        <v>24.3012104034424</v>
       </c>
       <c r="H1207" t="n">
         <v>289</v>
@@ -35430,7 +35430,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>26.1422138214111</v>
+        <v>26.1422119140625</v>
       </c>
       <c r="H1209" t="n">
         <v>6415</v>
@@ -35459,7 +35459,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1210" t="n">
-        <v>26.5104122161865</v>
+        <v>26.5104141235352</v>
       </c>
       <c r="H1210" t="n">
         <v>3821</v>
@@ -35488,7 +35488,7 @@
         <v>28.5</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1211" t="n">
         <v>2877</v>
@@ -35517,7 +35517,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5104122161865</v>
+        <v>26.5104141235352</v>
       </c>
       <c r="H1212" t="n">
         <v>542</v>
@@ -35546,7 +35546,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1213" t="n">
-        <v>27.3388652801514</v>
+        <v>27.3388633728027</v>
       </c>
       <c r="H1213" t="n">
         <v>5222</v>
@@ -35575,7 +35575,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1214" t="n">
         <v>1681</v>
@@ -35633,7 +35633,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.4309139251709</v>
+        <v>27.4309120178223</v>
       </c>
       <c r="H1216" t="n">
         <v>3541</v>
@@ -35662,7 +35662,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.786563873291</v>
+        <v>26.7865619659424</v>
       </c>
       <c r="H1217" t="n">
         <v>2270</v>
@@ -35691,7 +35691,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>26.786563873291</v>
+        <v>26.7865619659424</v>
       </c>
       <c r="H1218" t="n">
         <v>6399</v>
@@ -35749,7 +35749,7 @@
         <v>28.5</v>
       </c>
       <c r="G1220" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1220" t="n">
         <v>2171</v>
@@ -35894,7 +35894,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.3388652801514</v>
+        <v>27.3388633728027</v>
       </c>
       <c r="H1225" t="n">
         <v>2106</v>
@@ -36068,7 +36068,7 @@
         <v>28.5</v>
       </c>
       <c r="G1231" t="n">
-        <v>26.2342643737793</v>
+        <v>26.2342624664307</v>
       </c>
       <c r="H1231" t="n">
         <v>3357</v>
@@ -36097,7 +36097,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1232" t="n">
         <v>4851</v>
@@ -36155,7 +36155,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1234" t="n">
         <v>2409</v>
@@ -36213,7 +36213,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978618621826</v>
       </c>
       <c r="H1236" t="n">
         <v>5154</v>
@@ -36242,7 +36242,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>25.4058132171631</v>
+        <v>25.4058151245117</v>
       </c>
       <c r="H1237" t="n">
         <v>455</v>
@@ -36271,7 +36271,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2217121124268</v>
+        <v>25.2217140197754</v>
       </c>
       <c r="H1238" t="n">
         <v>1033</v>
@@ -36300,7 +36300,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>25.4058132171631</v>
+        <v>25.4058151245117</v>
       </c>
       <c r="H1239" t="n">
         <v>872</v>
@@ -36358,7 +36358,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>25.1296634674072</v>
+        <v>25.1296615600586</v>
       </c>
       <c r="H1241" t="n">
         <v>2635</v>
@@ -36445,7 +36445,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1244" t="n">
         <v>11217</v>
@@ -36503,7 +36503,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1246" t="n">
         <v>16021</v>
@@ -36590,7 +36590,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1249" t="n">
         <v>7712</v>
@@ -36706,7 +36706,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1253" t="n">
         <v>21403</v>
@@ -36735,7 +36735,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1254" t="n">
         <v>4568</v>
@@ -36764,7 +36764,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1255" t="n">
         <v>3149</v>
@@ -36793,7 +36793,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1256" t="n">
         <v>3291</v>
@@ -36822,7 +36822,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1257" t="n">
         <v>2319</v>
@@ -36851,7 +36851,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>24.4853134155273</v>
+        <v>24.4853115081787</v>
       </c>
       <c r="H1258" t="n">
         <v>1947</v>
@@ -36880,7 +36880,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1259" t="n">
         <v>15177</v>
@@ -36909,7 +36909,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>24.0250606536865</v>
+        <v>24.0250625610352</v>
       </c>
       <c r="H1260" t="n">
         <v>10057</v>
@@ -36967,7 +36967,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978618621826</v>
       </c>
       <c r="H1262" t="n">
         <v>10735</v>
@@ -36996,7 +36996,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1263" t="n">
         <v>5803</v>
@@ -37112,7 +37112,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1267" t="n">
         <v>12740</v>
@@ -37170,7 +37170,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>28.6275634765625</v>
+        <v>28.6275653839111</v>
       </c>
       <c r="H1269" t="n">
         <v>11777</v>
@@ -37199,7 +37199,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1270" t="n">
         <v>1818</v>
@@ -37373,7 +37373,7 @@
         <v>31.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1276" t="n">
         <v>13340</v>
@@ -37489,7 +37489,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1280" t="n">
         <v>2808</v>
@@ -37634,7 +37634,7 @@
         <v>33</v>
       </c>
       <c r="G1285" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765125274658</v>
       </c>
       <c r="H1285" t="n">
         <v>9952</v>
@@ -37750,7 +37750,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1289" t="n">
-        <v>30.468563079834</v>
+        <v>30.4685649871826</v>
       </c>
       <c r="H1289" t="n">
         <v>2827</v>
@@ -37837,7 +37837,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.468563079834</v>
+        <v>30.4685649871826</v>
       </c>
       <c r="H1292" t="n">
         <v>3238</v>
@@ -37866,7 +37866,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>30.468563079834</v>
+        <v>30.4685649871826</v>
       </c>
       <c r="H1293" t="n">
         <v>2155</v>
@@ -37895,7 +37895,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1294" t="n">
-        <v>30.468563079834</v>
+        <v>30.4685649871826</v>
       </c>
       <c r="H1294" t="n">
         <v>951</v>
@@ -37924,7 +37924,7 @@
         <v>33</v>
       </c>
       <c r="G1295" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765125274658</v>
       </c>
       <c r="H1295" t="n">
         <v>3140</v>
@@ -37953,7 +37953,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.6526622772217</v>
+        <v>30.6526641845703</v>
       </c>
       <c r="H1296" t="n">
         <v>3034</v>
@@ -37982,7 +37982,7 @@
         <v>33</v>
       </c>
       <c r="G1297" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765125274658</v>
       </c>
       <c r="H1297" t="n">
         <v>1609</v>
@@ -38040,7 +38040,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1299" t="n">
         <v>10536</v>
@@ -38069,7 +38069,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>30.6526622772217</v>
+        <v>30.6526641845703</v>
       </c>
       <c r="H1300" t="n">
         <v>753</v>
@@ -38098,7 +38098,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.836763381958</v>
+        <v>30.8367671966553</v>
       </c>
       <c r="H1301" t="n">
         <v>18694</v>
@@ -38272,7 +38272,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>30.6526622772217</v>
+        <v>30.6526641845703</v>
       </c>
       <c r="H1307" t="n">
         <v>2297</v>
@@ -38301,7 +38301,7 @@
         <v>33</v>
       </c>
       <c r="G1308" t="n">
-        <v>30.3765144348145</v>
+        <v>30.3765125274658</v>
       </c>
       <c r="H1308" t="n">
         <v>4364</v>
@@ -38388,7 +38388,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.5355167388916</v>
+        <v>28.5355129241943</v>
       </c>
       <c r="H1311" t="n">
         <v>14200</v>
@@ -38562,7 +38562,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.095422744751</v>
+        <v>29.0954246520996</v>
       </c>
       <c r="H1317" t="n">
         <v>6125</v>
@@ -38765,7 +38765,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1324" t="n">
         <v>12844</v>
@@ -38823,7 +38823,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1326" t="n">
         <v>9621</v>
@@ -38852,7 +38852,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1327" t="n">
         <v>46167</v>
@@ -38881,7 +38881,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1328" t="n">
         <v>3959</v>
@@ -38997,7 +38997,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1332" t="n">
         <v>24982</v>
@@ -39026,7 +39026,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1333" t="n">
         <v>8601</v>
@@ -39055,7 +39055,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1334" t="n">
         <v>5309</v>
@@ -39084,7 +39084,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1335" t="n">
         <v>21621</v>
@@ -39113,7 +39113,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1336" t="n">
         <v>16181</v>
@@ -39142,7 +39142,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1337" t="n">
         <v>6822</v>
@@ -39171,7 +39171,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1338" t="n">
         <v>3455</v>
@@ -39200,7 +39200,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1339" t="n">
         <v>5494</v>
@@ -39229,7 +39229,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1340" t="n">
         <v>13157</v>
@@ -39258,7 +39258,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1341" t="n">
         <v>2965</v>
@@ -39287,7 +39287,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1342" t="n">
         <v>1570</v>
@@ -39345,7 +39345,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1344" t="n">
         <v>2849</v>
@@ -39374,7 +39374,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1345" t="n">
         <v>4077</v>
@@ -39461,7 +39461,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1348" t="n">
         <v>3503</v>
@@ -39548,7 +39548,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1351" t="n">
         <v>3621</v>
@@ -39693,7 +39693,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1356" t="n">
         <v>1074</v>
@@ -39722,7 +39722,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1357" t="n">
         <v>1555</v>
@@ -39896,7 +39896,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851448059082</v>
+        <v>33.7851486206055</v>
       </c>
       <c r="H1363" t="n">
         <v>12779</v>
@@ -39925,7 +39925,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1364" t="n">
         <v>7910</v>
@@ -40012,7 +40012,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1367" t="n">
         <v>2625</v>
@@ -40157,7 +40157,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1372" t="n">
         <v>2528</v>
@@ -40186,7 +40186,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1373" t="n">
         <v>5370</v>
@@ -40273,7 +40273,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1376" t="n">
         <v>9183</v>
@@ -40302,7 +40302,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1377" t="n">
         <v>4352</v>
@@ -40331,7 +40331,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095996856689</v>
+        <v>31.0095977783203</v>
       </c>
       <c r="H1378" t="n">
         <v>1704</v>
@@ -40360,7 +40360,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1379" t="n">
         <v>553</v>
@@ -40389,7 +40389,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1380" t="n">
         <v>732</v>
@@ -40476,7 +40476,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1383" t="n">
         <v>1248</v>
@@ -40505,7 +40505,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1384" t="n">
         <v>1301</v>
@@ -40563,7 +40563,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1386" t="n">
         <v>1483</v>
@@ -40592,7 +40592,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1387" t="n">
         <v>3214</v>
@@ -40708,7 +40708,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1391" t="n">
         <v>3859</v>
@@ -40737,7 +40737,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1392" t="n">
         <v>1387</v>
@@ -40766,7 +40766,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1393" t="n">
         <v>569</v>
@@ -40795,7 +40795,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1394" t="n">
         <v>1704</v>
@@ -40940,7 +40940,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1399" t="n">
         <v>2679</v>
@@ -40998,7 +40998,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1401" t="n">
         <v>4340</v>
@@ -41027,7 +41027,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1402" t="n">
         <v>3944</v>
@@ -41056,7 +41056,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1403" t="n">
         <v>1728</v>
@@ -41085,7 +41085,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1404" t="n">
         <v>1317</v>
@@ -41114,7 +41114,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1405" t="n">
         <v>2062</v>
@@ -41143,7 +41143,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1406" t="n">
         <v>1291</v>
@@ -41230,7 +41230,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1409" t="n">
         <v>4625</v>
@@ -41346,7 +41346,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1413" t="n">
         <v>2410</v>
@@ -41375,7 +41375,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1414" t="n">
         <v>31931</v>
@@ -41404,7 +41404,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1415" t="n">
         <v>13442</v>
@@ -41549,7 +41549,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1420" t="n">
         <v>2989</v>
@@ -41607,7 +41607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1422" t="n">
         <v>2861</v>
@@ -41636,7 +41636,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1423" t="n">
         <v>3892</v>
@@ -41752,7 +41752,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1427" t="n">
         <v>2872</v>
@@ -41781,7 +41781,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1428" t="n">
         <v>3471</v>
@@ -41810,7 +41810,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1429" t="n">
         <v>457</v>
@@ -41839,7 +41839,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1430" t="n">
         <v>4731</v>
@@ -41868,7 +41868,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1431" t="n">
         <v>1418</v>
@@ -41984,7 +41984,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1435" t="n">
         <v>1616</v>
@@ -42013,7 +42013,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1436" t="n">
         <v>3582</v>
@@ -42042,7 +42042,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1437" t="n">
         <v>2662</v>
@@ -42100,7 +42100,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1439" t="n">
         <v>198</v>
@@ -42129,7 +42129,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1440" t="n">
         <v>1144</v>
@@ -42245,7 +42245,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1444" t="n">
         <v>688</v>
@@ -42274,7 +42274,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1445" t="n">
         <v>1252</v>
@@ -42332,7 +42332,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1447" t="n">
         <v>4488</v>
@@ -42448,7 +42448,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1451" t="n">
         <v>2754</v>
@@ -42477,7 +42477,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1452" t="n">
         <v>793</v>
@@ -42535,7 +42535,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1454" t="n">
         <v>4612</v>
@@ -42622,7 +42622,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1457" t="n">
         <v>3819</v>
@@ -42709,7 +42709,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1460" t="n">
         <v>8292</v>
@@ -42796,7 +42796,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1463" t="n">
         <v>3283</v>
@@ -43028,7 +43028,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1471" t="n">
         <v>1571</v>
@@ -43260,7 +43260,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1479" t="n">
         <v>13</v>
@@ -43347,7 +43347,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1482" t="n">
         <v>5922</v>
@@ -43579,7 +43579,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1490" t="n">
         <v>3936</v>
@@ -43608,7 +43608,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1491" t="n">
         <v>9516</v>
@@ -43637,7 +43637,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1492" t="n">
         <v>12</v>
@@ -43695,7 +43695,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1494" t="n">
         <v>3670</v>
@@ -43782,7 +43782,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1497" t="n">
         <v>1307</v>
@@ -43811,7 +43811,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1498" t="n">
         <v>4115</v>
@@ -43956,7 +43956,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1503" t="n">
         <v>1545</v>
@@ -44043,7 +44043,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1506" t="n">
         <v>2072</v>
@@ -44072,7 +44072,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1507" t="n">
         <v>211</v>
@@ -44101,7 +44101,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1508" t="n">
         <v>907</v>
@@ -44275,7 +44275,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1514" t="n">
         <v>1628</v>
@@ -44333,7 +44333,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.8413314819336</v>
+        <v>25.841329574585</v>
       </c>
       <c r="H1516" t="n">
         <v>5585</v>
@@ -44420,7 +44420,7 @@
         <v>27</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.8413314819336</v>
+        <v>25.841329574585</v>
       </c>
       <c r="H1519" t="n">
         <v>3989</v>
@@ -44623,7 +44623,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>26.5112934112549</v>
+        <v>26.5112915039062</v>
       </c>
       <c r="H1526" t="n">
         <v>4380</v>
@@ -44826,7 +44826,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1533" t="n">
         <v>2355</v>
@@ -45029,7 +45029,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1540" t="n">
         <v>2838</v>
@@ -45174,7 +45174,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.6499137878418</v>
+        <v>25.6499118804932</v>
       </c>
       <c r="H1545" t="n">
         <v>3951</v>
@@ -45232,7 +45232,7 @@
         <v>25.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.4057006835938</v>
+        <v>24.4057025909424</v>
       </c>
       <c r="H1547" t="n">
         <v>2784</v>
@@ -45319,7 +45319,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7456207275391</v>
+        <v>25.7456226348877</v>
       </c>
       <c r="H1550" t="n">
         <v>919</v>
@@ -45377,7 +45377,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1552" t="n">
         <v>4472</v>
@@ -45435,7 +45435,7 @@
         <v>29</v>
       </c>
       <c r="G1554" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1554" t="n">
         <v>252</v>
@@ -45464,7 +45464,7 @@
         <v>29</v>
       </c>
       <c r="G1555" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1555" t="n">
         <v>2314</v>
@@ -45493,7 +45493,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1556" t="n">
         <v>3338</v>
@@ -45580,7 +45580,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1559" t="n">
         <v>612</v>
@@ -45725,7 +45725,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1564" t="n">
         <v>1292</v>
@@ -45899,7 +45899,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1570" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1570" t="n">
         <v>2272</v>
@@ -45928,7 +45928,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1571" t="n">
         <v>388</v>
@@ -56429,9 +56429,38 @@
         <v>44.5999984741211</v>
       </c>
       <c r="H1933" t="n">
-        <v>7053</v>
+        <v>7180</v>
       </c>
       <c r="I1933" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1934" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1934" t="n">
+        <v>44.5999984741211</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>44.7000007629395</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>44.5999984741211</v>
+      </c>
+      <c r="G1934" t="n">
+        <v>44.5999984741211</v>
+      </c>
+      <c r="H1934" t="n">
+        <v>2559</v>
+      </c>
+      <c r="I1934" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.28757858276367</v>
+        <v>9.28757762908936</v>
       </c>
       <c r="H2" t="n">
         <v>27300</v>
@@ -456,7 +456,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>9.58128833770752</v>
+        <v>9.58129024505615</v>
       </c>
       <c r="H3" t="n">
         <v>62400</v>
@@ -485,7 +485,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293743133545</v>
+        <v>9.88293647766113</v>
       </c>
       <c r="H4" t="n">
         <v>14100</v>
@@ -514,7 +514,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.76386547088623</v>
+        <v>9.76386642456055</v>
       </c>
       <c r="H5" t="n">
         <v>9000</v>
@@ -572,7 +572,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>9.67654705047607</v>
+        <v>9.67654609680176</v>
       </c>
       <c r="H7" t="n">
         <v>9900</v>
@@ -601,7 +601,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>9.60510540008545</v>
+        <v>9.60510349273682</v>
       </c>
       <c r="H8" t="n">
         <v>3750</v>
@@ -630,7 +630,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>9.23995018005371</v>
+        <v>9.23995304107666</v>
       </c>
       <c r="H9" t="n">
         <v>6000</v>
@@ -659,7 +659,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>9.39871311187744</v>
+        <v>9.39871406555176</v>
       </c>
       <c r="H10" t="n">
         <v>1050</v>
@@ -717,7 +717,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>9.4463415145874</v>
+        <v>9.44634056091309</v>
       </c>
       <c r="H12" t="n">
         <v>1200</v>
@@ -775,7 +775,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.91468811035156</v>
+        <v>9.9146900177002</v>
       </c>
       <c r="H14" t="n">
         <v>3450</v>
@@ -833,7 +833,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>10.1607704162598</v>
+        <v>10.1607713699341</v>
       </c>
       <c r="H16" t="n">
         <v>4350</v>
@@ -862,7 +862,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147882461548</v>
       </c>
       <c r="H17" t="n">
         <v>4650</v>
@@ -920,7 +920,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2877807617188</v>
+        <v>10.2877798080444</v>
       </c>
       <c r="H19" t="n">
         <v>4050</v>
@@ -978,7 +978,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G21" t="n">
-        <v>10.208399772644</v>
+        <v>10.2083988189697</v>
       </c>
       <c r="H21" t="n">
         <v>4800</v>
@@ -1036,7 +1036,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>10.208399772644</v>
+        <v>10.2083988189697</v>
       </c>
       <c r="H23" t="n">
         <v>1050</v>
@@ -1065,7 +1065,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>10.1607704162598</v>
+        <v>10.1607713699341</v>
       </c>
       <c r="H24" t="n">
         <v>2100</v>
@@ -1123,7 +1123,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5259237289429</v>
+        <v>10.5259227752686</v>
       </c>
       <c r="H26" t="n">
         <v>3000</v>
@@ -1152,7 +1152,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3989133834839</v>
+        <v>10.3989152908325</v>
       </c>
       <c r="H27" t="n">
         <v>750</v>
@@ -1210,7 +1210,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>10.5576763153076</v>
+        <v>10.5576772689819</v>
       </c>
       <c r="H29" t="n">
         <v>2100</v>
@@ -1239,7 +1239,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>10.5576763153076</v>
+        <v>10.5576772689819</v>
       </c>
       <c r="H30" t="n">
         <v>1200</v>
@@ -1268,7 +1268,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>10.1925220489502</v>
+        <v>10.1925230026245</v>
       </c>
       <c r="H31" t="n">
         <v>5250</v>
@@ -1297,7 +1297,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147882461548</v>
       </c>
       <c r="H32" t="n">
         <v>6450</v>
@@ -1326,7 +1326,7 @@
         <v>13.5</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7164373397827</v>
+        <v>10.716438293457</v>
       </c>
       <c r="H33" t="n">
         <v>6300</v>
@@ -1413,7 +1413,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588321685791</v>
+        <v>11.0588312149048</v>
       </c>
       <c r="H36" t="n">
         <v>3900</v>
@@ -1442,7 +1442,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419801712036</v>
+        <v>11.1419792175293</v>
       </c>
       <c r="H37" t="n">
         <v>7050</v>
@@ -1587,7 +1587,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H42" t="n">
         <v>3600</v>
@@ -1703,7 +1703,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G46" t="n">
-        <v>10.6098260879517</v>
+        <v>10.609827041626</v>
       </c>
       <c r="H46" t="n">
         <v>750</v>
@@ -1761,7 +1761,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>10.2273397445679</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H48" t="n">
         <v>7800</v>
@@ -1877,7 +1877,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>10.2273397445679</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H52" t="n">
         <v>900</v>
@@ -1906,7 +1906,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H53" t="n">
         <v>6150</v>
@@ -1935,7 +1935,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G54" t="n">
-        <v>9.9446325302124</v>
+        <v>9.94463348388672</v>
       </c>
       <c r="H54" t="n">
         <v>2850</v>
@@ -1964,7 +1964,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G55" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H55" t="n">
         <v>900</v>
@@ -2051,7 +2051,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>10.2772312164307</v>
+        <v>10.277229309082</v>
       </c>
       <c r="H58" t="n">
         <v>900</v>
@@ -2080,7 +2080,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G59" t="n">
-        <v>10.3271207809448</v>
+        <v>10.3271198272705</v>
       </c>
       <c r="H59" t="n">
         <v>300</v>
@@ -2109,7 +2109,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2138,7 +2138,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H61" t="n">
         <v>1650</v>
@@ -2167,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H62" t="n">
         <v>1950</v>
@@ -2196,7 +2196,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H63" t="n">
         <v>1800</v>
@@ -2225,7 +2225,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H64" t="n">
         <v>7950</v>
@@ -2254,7 +2254,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485340118408</v>
       </c>
       <c r="H65" t="n">
         <v>2850</v>
@@ -2312,7 +2312,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G67" t="n">
-        <v>9.44573783874512</v>
+        <v>9.44573879241943</v>
       </c>
       <c r="H67" t="n">
         <v>2250</v>
@@ -2341,7 +2341,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.4789981842041</v>
+        <v>9.47899723052979</v>
       </c>
       <c r="H68" t="n">
         <v>57450</v>
@@ -2486,7 +2486,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G73" t="n">
-        <v>9.92800331115723</v>
+        <v>9.92800235748291</v>
       </c>
       <c r="H73" t="n">
         <v>1950</v>
@@ -2631,7 +2631,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G78" t="n">
-        <v>9.9446325302124</v>
+        <v>9.94463348388672</v>
       </c>
       <c r="H78" t="n">
         <v>2550</v>
@@ -2660,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2718,7 +2718,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G81" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H81" t="n">
         <v>600</v>
@@ -2863,7 +2863,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>9.49562931060791</v>
+        <v>9.49562835693359</v>
       </c>
       <c r="H86" t="n">
         <v>5550</v>
@@ -2892,7 +2892,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G87" t="n">
-        <v>9.49562931060791</v>
+        <v>9.49562835693359</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>11.5</v>
       </c>
       <c r="G88" t="n">
-        <v>9.56214809417725</v>
+        <v>9.56214618682861</v>
       </c>
       <c r="H88" t="n">
         <v>3000</v>
@@ -3008,7 +3008,7 @@
         <v>11.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.56214809417725</v>
+        <v>9.56214618682861</v>
       </c>
       <c r="H91" t="n">
         <v>300</v>
@@ -3153,7 +3153,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H96" t="n">
         <v>1050</v>
@@ -3182,7 +3182,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G97" t="n">
-        <v>9.92800331115723</v>
+        <v>9.92800235748291</v>
       </c>
       <c r="H97" t="n">
         <v>450</v>
@@ -3211,7 +3211,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G98" t="n">
-        <v>9.9446325302124</v>
+        <v>9.94463348388672</v>
       </c>
       <c r="H98" t="n">
         <v>2550</v>
@@ -3269,7 +3269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H100" t="n">
         <v>150</v>
@@ -3298,7 +3298,7 @@
         <v>12</v>
       </c>
       <c r="G101" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H101" t="n">
         <v>300</v>
@@ -3327,7 +3327,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>9.87811279296875</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H102" t="n">
         <v>3150</v>
@@ -3356,7 +3356,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G103" t="n">
-        <v>9.74507522583008</v>
+        <v>9.74507617950439</v>
       </c>
       <c r="H103" t="n">
         <v>150</v>
@@ -3385,7 +3385,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G104" t="n">
-        <v>9.74507522583008</v>
+        <v>9.74507617950439</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G107" t="n">
-        <v>9.87811279296875</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H107" t="n">
         <v>150</v>
@@ -3501,7 +3501,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G108" t="n">
-        <v>9.87811279296875</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529800415039</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H110" t="n">
         <v>450</v>
@@ -3588,7 +3588,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529800415039</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H112" t="n">
         <v>1800</v>
@@ -3646,7 +3646,7 @@
         <v>12</v>
       </c>
       <c r="G113" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H113" t="n">
         <v>750</v>
@@ -3675,7 +3675,7 @@
         <v>12</v>
       </c>
       <c r="G114" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H114" t="n">
         <v>1200</v>
@@ -3704,7 +3704,7 @@
         <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G116" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485340118408</v>
       </c>
       <c r="H116" t="n">
         <v>450</v>
@@ -3762,7 +3762,7 @@
         <v>12</v>
       </c>
       <c r="G117" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H117" t="n">
         <v>1200</v>
@@ -3878,7 +3878,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H121" t="n">
         <v>150</v>
@@ -3907,7 +3907,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G122" t="n">
-        <v>9.87811279296875</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H122" t="n">
         <v>600</v>
@@ -3936,7 +3936,7 @@
         <v>12</v>
       </c>
       <c r="G123" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H123" t="n">
         <v>900</v>
@@ -3965,7 +3965,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -4081,7 +4081,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G128" t="n">
-        <v>10.2772312164307</v>
+        <v>10.277229309082</v>
       </c>
       <c r="H128" t="n">
         <v>4650</v>
@@ -4110,7 +4110,7 @@
         <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>10.3936386108398</v>
+        <v>10.3936376571655</v>
       </c>
       <c r="H129" t="n">
         <v>7500</v>
@@ -4139,7 +4139,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G130" t="n">
-        <v>10.2772312164307</v>
+        <v>10.277229309082</v>
       </c>
       <c r="H130" t="n">
         <v>2700</v>
@@ -4197,7 +4197,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>10.4601573944092</v>
+        <v>10.4601583480835</v>
       </c>
       <c r="H132" t="n">
         <v>450</v>
@@ -4226,7 +4226,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G133" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H133" t="n">
         <v>300</v>
@@ -4255,7 +4255,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H134" t="n">
         <v>750</v>
@@ -4313,7 +4313,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G136" t="n">
-        <v>10.0444135665894</v>
+        <v>10.0444116592407</v>
       </c>
       <c r="H136" t="n">
         <v>150</v>
@@ -4342,7 +4342,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H137" t="n">
         <v>300</v>
@@ -4371,7 +4371,7 @@
         <v>12</v>
       </c>
       <c r="G138" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H138" t="n">
         <v>600</v>
@@ -4400,7 +4400,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>9.82822322845459</v>
+        <v>9.82822418212891</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4429,7 +4429,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G140" t="n">
-        <v>9.92800331115723</v>
+        <v>9.92800235748291</v>
       </c>
       <c r="H140" t="n">
         <v>1050</v>
@@ -4458,7 +4458,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H141" t="n">
         <v>300</v>
@@ -4487,7 +4487,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H142" t="n">
         <v>450</v>
@@ -4516,7 +4516,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H143" t="n">
         <v>1200</v>
@@ -4545,7 +4545,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G147" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H147" t="n">
         <v>1200</v>
@@ -4661,7 +4661,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H148" t="n">
         <v>750</v>
@@ -4690,7 +4690,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H154" t="n">
         <v>300</v>
@@ -4922,7 +4922,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G157" t="n">
-        <v>9.92800331115723</v>
+        <v>9.92800235748291</v>
       </c>
       <c r="H157" t="n">
         <v>3150</v>
@@ -4951,7 +4951,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H158" t="n">
         <v>600</v>
@@ -5009,7 +5009,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>9.9446325302124</v>
+        <v>9.94463348388672</v>
       </c>
       <c r="H160" t="n">
         <v>12000</v>
@@ -5038,7 +5038,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G161" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H161" t="n">
         <v>300</v>
@@ -5125,7 +5125,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G164" t="n">
-        <v>10.2273397445679</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H164" t="n">
         <v>2250</v>
@@ -5154,7 +5154,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>10.2273397445679</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>12.5</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3936386108398</v>
+        <v>10.3936376571655</v>
       </c>
       <c r="H166" t="n">
         <v>450</v>
@@ -5270,7 +5270,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>10.2273397445679</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H169" t="n">
         <v>2400</v>
@@ -5299,7 +5299,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G170" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H170" t="n">
         <v>150</v>
@@ -5357,7 +5357,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H172" t="n">
         <v>150</v>
@@ -5415,7 +5415,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H174" t="n">
         <v>1950</v>
@@ -5502,7 +5502,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H177" t="n">
         <v>9000</v>
@@ -5531,7 +5531,7 @@
         <v>12</v>
       </c>
       <c r="G178" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H178" t="n">
         <v>9300</v>
@@ -5560,7 +5560,7 @@
         <v>12</v>
       </c>
       <c r="G179" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H179" t="n">
         <v>4500</v>
@@ -5589,7 +5589,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H180" t="n">
         <v>2700</v>
@@ -5618,7 +5618,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G181" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H181" t="n">
         <v>900</v>
@@ -5676,7 +5676,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G183" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H183" t="n">
         <v>450</v>
@@ -5705,7 +5705,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G184" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H184" t="n">
         <v>750</v>
@@ -5734,7 +5734,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G185" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>12</v>
       </c>
       <c r="G186" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H186" t="n">
         <v>1350</v>
@@ -6053,7 +6053,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G196" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H196" t="n">
         <v>450</v>
@@ -6082,7 +6082,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>10.2273397445679</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6140,7 +6140,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H199" t="n">
         <v>16800</v>
@@ -6169,7 +6169,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G200" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H200" t="n">
         <v>15150</v>
@@ -6198,7 +6198,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G201" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H201" t="n">
         <v>1350</v>
@@ -6227,7 +6227,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H202" t="n">
         <v>7050</v>
@@ -6256,7 +6256,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G203" t="n">
-        <v>10.0444135665894</v>
+        <v>10.0444116592407</v>
       </c>
       <c r="H203" t="n">
         <v>5250</v>
@@ -6285,7 +6285,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>10.0444135665894</v>
+        <v>10.0444116592407</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G205" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485340118408</v>
       </c>
       <c r="H205" t="n">
         <v>750</v>
@@ -6343,7 +6343,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H206" t="n">
         <v>450</v>
@@ -6372,7 +6372,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H207" t="n">
         <v>900</v>
@@ -6401,7 +6401,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H208" t="n">
         <v>1200</v>
@@ -6459,7 +6459,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>10.077672958374</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H210" t="n">
         <v>150</v>
@@ -6488,7 +6488,7 @@
         <v>12</v>
       </c>
       <c r="G211" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H211" t="n">
         <v>1650</v>
@@ -6517,7 +6517,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>12</v>
       </c>
       <c r="G213" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H213" t="n">
         <v>1200</v>
@@ -6575,7 +6575,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H214" t="n">
         <v>1350</v>
@@ -6633,7 +6633,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.144190788269</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H216" t="n">
         <v>2550</v>
@@ -6720,7 +6720,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>10.2273397445679</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H219" t="n">
         <v>900</v>
@@ -6749,7 +6749,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H220" t="n">
         <v>16950</v>
@@ -6778,7 +6778,7 @@
         <v>12</v>
       </c>
       <c r="G221" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H221" t="n">
         <v>600</v>
@@ -6807,7 +6807,7 @@
         <v>12</v>
       </c>
       <c r="G222" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>10.1940803527832</v>
+        <v>10.1940813064575</v>
       </c>
       <c r="H223" t="n">
         <v>2400</v>
@@ -6865,7 +6865,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H224" t="n">
         <v>1800</v>
@@ -6894,7 +6894,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>12</v>
       </c>
       <c r="G226" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>10.1608200073242</v>
+        <v>10.1608219146729</v>
       </c>
       <c r="H227" t="n">
         <v>450</v>
@@ -7010,7 +7010,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603801727295</v>
+        <v>10.3603792190552</v>
       </c>
       <c r="H229" t="n">
         <v>2400</v>
@@ -7039,7 +7039,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="n">
-        <v>9.97789287567139</v>
+        <v>9.97789192199707</v>
       </c>
       <c r="H230" t="n">
         <v>1650</v>
@@ -7068,7 +7068,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G231" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H231" t="n">
         <v>600</v>
@@ -7097,7 +7097,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>10.2273397445679</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H232" t="n">
         <v>2250</v>
@@ -7126,7 +7126,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.2273397445679</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G236" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111532211304</v>
       </c>
       <c r="H236" t="n">
         <v>750</v>
@@ -7242,7 +7242,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H237" t="n">
         <v>3000</v>
@@ -7271,7 +7271,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2606010437012</v>
+        <v>10.2606000900269</v>
       </c>
       <c r="H238" t="n">
         <v>1350</v>
@@ -7300,7 +7300,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610437393188</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H239" t="n">
         <v>2850</v>
@@ -7358,7 +7358,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G241" t="n">
-        <v>9.87811279296875</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H241" t="n">
         <v>7800</v>
@@ -7387,7 +7387,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G242" t="n">
-        <v>9.87811279296875</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87811279296875</v>
+        <v>9.87811470031738</v>
       </c>
       <c r="H243" t="n">
         <v>600</v>
@@ -7503,7 +7503,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.17966175079346</v>
+        <v>9.17966270446777</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7590,7 +7590,7 @@
         <v>11.5</v>
       </c>
       <c r="G249" t="n">
-        <v>9.56214809417725</v>
+        <v>9.56214618682861</v>
       </c>
       <c r="H249" t="n">
         <v>3300</v>
@@ -7619,7 +7619,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.11314296722412</v>
+        <v>9.11314392089844</v>
       </c>
       <c r="H250" t="n">
         <v>2250</v>
@@ -7648,7 +7648,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>8.66413688659668</v>
+        <v>8.664137840271</v>
       </c>
       <c r="H251" t="n">
         <v>4200</v>
@@ -7677,7 +7677,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>8.6475076675415</v>
+        <v>8.64750671386719</v>
       </c>
       <c r="H252" t="n">
         <v>450</v>
@@ -7706,7 +7706,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>8.44794940948486</v>
+        <v>8.44794845581055</v>
       </c>
       <c r="H253" t="n">
         <v>150</v>
@@ -7822,7 +7822,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.14861297607422</v>
+        <v>8.1486120223999</v>
       </c>
       <c r="H257" t="n">
         <v>450</v>
@@ -7851,7 +7851,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.14861297607422</v>
+        <v>8.1486120223999</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568536758423</v>
+        <v>7.96568441390991</v>
       </c>
       <c r="H259" t="n">
         <v>3600</v>
@@ -7967,7 +7967,7 @@
         <v>10</v>
       </c>
       <c r="G262" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H262" t="n">
         <v>1950</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>10</v>
       </c>
       <c r="G264" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>8.31491088867188</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>8.27333736419678</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H266" t="n">
         <v>450</v>
@@ -8112,7 +8112,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.27333736419678</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>8.27333736419678</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>8.6475076675415</v>
+        <v>8.64750671386719</v>
       </c>
       <c r="H270" t="n">
         <v>600</v>
@@ -8257,7 +8257,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.6475076675415</v>
+        <v>8.64750671386719</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>8.6475076675415</v>
+        <v>8.64750671386719</v>
       </c>
       <c r="H273" t="n">
         <v>28800</v>
@@ -8315,7 +8315,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>8.6475076675415</v>
+        <v>8.64750671386719</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>8.6475076675415</v>
+        <v>8.64750671386719</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>8.27333736419678</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H277" t="n">
         <v>1800</v>
@@ -8431,7 +8431,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>8.6475076675415</v>
+        <v>8.64750671386719</v>
       </c>
       <c r="H278" t="n">
         <v>150</v>
@@ -8460,7 +8460,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640331268311</v>
+        <v>9.14640140533447</v>
       </c>
       <c r="H279" t="n">
         <v>19950</v>
@@ -8489,7 +8489,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640331268311</v>
+        <v>9.14640140533447</v>
       </c>
       <c r="H280" t="n">
         <v>1350</v>
@@ -8721,7 +8721,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H288" t="n">
         <v>300</v>
@@ -8750,7 +8750,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H292" t="n">
         <v>2250</v>
@@ -8866,7 +8866,7 @@
         <v>10.5</v>
       </c>
       <c r="G293" t="n">
-        <v>9.02029991149902</v>
+        <v>9.02029895782471</v>
       </c>
       <c r="H293" t="n">
         <v>750</v>
@@ -8895,7 +8895,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>9.10620784759521</v>
+        <v>9.1062068939209</v>
       </c>
       <c r="H294" t="n">
         <v>1050</v>
@@ -8924,7 +8924,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H295" t="n">
         <v>1050</v>
@@ -8953,7 +8953,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H296" t="n">
         <v>750</v>
@@ -8982,7 +8982,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H302" t="n">
         <v>300</v>
@@ -9156,7 +9156,7 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H304" t="n">
         <v>22950</v>
@@ -9214,7 +9214,7 @@
         <v>10</v>
       </c>
       <c r="G305" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>10</v>
       </c>
       <c r="G307" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>10</v>
       </c>
       <c r="G308" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>10</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>10</v>
       </c>
       <c r="G310" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H312" t="n">
         <v>750</v>
@@ -9446,7 +9446,7 @@
         <v>10.5</v>
       </c>
       <c r="G313" t="n">
-        <v>9.02029991149902</v>
+        <v>9.02029895782471</v>
       </c>
       <c r="H313" t="n">
         <v>2550</v>
@@ -9475,7 +9475,7 @@
         <v>10.5</v>
       </c>
       <c r="G314" t="n">
-        <v>9.02029991149902</v>
+        <v>9.02029895782471</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>10.5</v>
       </c>
       <c r="G315" t="n">
-        <v>9.02029991149902</v>
+        <v>9.02029895782471</v>
       </c>
       <c r="H315" t="n">
         <v>150</v>
@@ -9562,7 +9562,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H317" t="n">
         <v>1050</v>
@@ -9591,7 +9591,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46189880371094</v>
       </c>
       <c r="H318" t="n">
         <v>1050</v>
@@ -9620,7 +9620,7 @@
         <v>10</v>
       </c>
       <c r="G319" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H319" t="n">
         <v>150</v>
@@ -9649,7 +9649,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H326" t="n">
         <v>2250</v>
@@ -9881,7 +9881,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G328" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H328" t="n">
         <v>600</v>
@@ -9910,7 +9910,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H329" t="n">
         <v>750</v>
@@ -9939,7 +9939,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H330" t="n">
         <v>300</v>
@@ -9968,7 +9968,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H332" t="n">
         <v>300</v>
@@ -10026,7 +10026,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G334" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H334" t="n">
         <v>4950</v>
@@ -10084,7 +10084,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H335" t="n">
         <v>150</v>
@@ -10113,7 +10113,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H336" t="n">
         <v>300</v>
@@ -10171,7 +10171,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46189880371094</v>
       </c>
       <c r="H338" t="n">
         <v>1350</v>
@@ -10200,7 +10200,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46189880371094</v>
       </c>
       <c r="H339" t="n">
         <v>450</v>
@@ -10229,7 +10229,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46189880371094</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H345" t="n">
         <v>600</v>
@@ -10403,7 +10403,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H346" t="n">
         <v>5550</v>
@@ -10432,7 +10432,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H347" t="n">
         <v>600</v>
@@ -10461,7 +10461,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H350" t="n">
         <v>900</v>
@@ -10693,7 +10693,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46189880371094</v>
       </c>
       <c r="H356" t="n">
         <v>1950</v>
@@ -10722,7 +10722,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H357" t="n">
         <v>2550</v>
@@ -10751,7 +10751,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H358" t="n">
         <v>750</v>
@@ -10780,7 +10780,7 @@
         <v>10</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H359" t="n">
         <v>750</v>
@@ -10809,7 +10809,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G360" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H360" t="n">
         <v>1950</v>
@@ -10838,7 +10838,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H361" t="n">
         <v>150</v>
@@ -10867,7 +10867,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H369" t="n">
         <v>750</v>
@@ -11099,7 +11099,7 @@
         <v>9.75</v>
       </c>
       <c r="G370" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H370" t="n">
         <v>3750</v>
@@ -11128,7 +11128,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H371" t="n">
         <v>3000</v>
@@ -11157,7 +11157,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>9.75</v>
       </c>
       <c r="G373" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>9.75</v>
       </c>
       <c r="G374" t="n">
-        <v>8.37599182128906</v>
+        <v>8.37599277496338</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.204176902771</v>
+        <v>8.20417785644531</v>
       </c>
       <c r="H375" t="n">
         <v>1950</v>
@@ -11302,7 +11302,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H377" t="n">
         <v>2550</v>
@@ -11331,7 +11331,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H378" t="n">
         <v>4200</v>
@@ -11360,7 +11360,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H379" t="n">
         <v>1200</v>
@@ -11389,7 +11389,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H380" t="n">
         <v>600</v>
@@ -11418,7 +11418,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H381" t="n">
         <v>1500</v>
@@ -11447,7 +11447,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>10</v>
       </c>
       <c r="G383" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H383" t="n">
         <v>750</v>
@@ -11505,7 +11505,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H384" t="n">
         <v>2850</v>
@@ -11534,7 +11534,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>10</v>
       </c>
       <c r="G386" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H386" t="n">
         <v>300</v>
@@ -11592,7 +11592,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H387" t="n">
         <v>150</v>
@@ -11621,7 +11621,7 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H388" t="n">
         <v>300</v>
@@ -11650,7 +11650,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H389" t="n">
         <v>150</v>
@@ -11679,7 +11679,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H391" t="n">
         <v>150</v>
@@ -11737,7 +11737,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H393" t="n">
         <v>450</v>
@@ -11795,7 +11795,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H396" t="n">
         <v>300</v>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H398" t="n">
         <v>600</v>
@@ -11940,7 +11940,7 @@
         <v>10</v>
       </c>
       <c r="G399" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H401" t="n">
         <v>1800</v>
@@ -12027,7 +12027,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H403" t="n">
         <v>450</v>
@@ -12085,7 +12085,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G405" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>10</v>
       </c>
       <c r="G408" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H408" t="n">
         <v>150</v>
@@ -12230,7 +12230,7 @@
         <v>10</v>
       </c>
       <c r="G409" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H409" t="n">
         <v>450</v>
@@ -12259,7 +12259,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H410" t="n">
         <v>450</v>
@@ -12288,7 +12288,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>8.54780864715576</v>
+        <v>8.54780769348145</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H413" t="n">
         <v>5400</v>
@@ -12375,7 +12375,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H414" t="n">
         <v>150</v>
@@ -12433,7 +12433,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H416" t="n">
         <v>600</v>
@@ -12462,7 +12462,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H421" t="n">
         <v>750</v>
@@ -12607,7 +12607,7 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>8.59076118469238</v>
+        <v>8.5907621383667</v>
       </c>
       <c r="H422" t="n">
         <v>150</v>
@@ -12636,7 +12636,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H423" t="n">
         <v>750</v>
@@ -12665,7 +12665,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G425" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G426" t="n">
-        <v>8.76257514953613</v>
+        <v>8.76257610321045</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H427" t="n">
         <v>450</v>
@@ -12810,7 +12810,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>9.10620784759521</v>
+        <v>9.1062068939209</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -13129,7 +13129,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H440" t="n">
         <v>21900</v>
@@ -13274,7 +13274,7 @@
         <v>12</v>
       </c>
       <c r="G445" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H445" t="n">
         <v>3600</v>
@@ -13303,7 +13303,7 @@
         <v>12</v>
       </c>
       <c r="G446" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>12</v>
       </c>
       <c r="G447" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H447" t="n">
         <v>900</v>
@@ -13361,7 +13361,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807271957397</v>
       </c>
       <c r="H448" t="n">
         <v>600</v>
@@ -13390,7 +13390,7 @@
         <v>12</v>
       </c>
       <c r="G449" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H449" t="n">
         <v>600</v>
@@ -13477,7 +13477,7 @@
         <v>12</v>
       </c>
       <c r="G452" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H452" t="n">
         <v>1950</v>
@@ -13593,7 +13593,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H456" t="n">
         <v>5400</v>
@@ -13738,7 +13738,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>9.6216516494751</v>
+        <v>9.62165260314941</v>
       </c>
       <c r="H461" t="n">
         <v>2100</v>
@@ -13767,7 +13767,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H462" t="n">
         <v>2850</v>
@@ -13854,7 +13854,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H465" t="n">
         <v>1200</v>
@@ -13941,7 +13941,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H468" t="n">
         <v>3900</v>
@@ -13970,7 +13970,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807271957397</v>
       </c>
       <c r="H469" t="n">
         <v>7500</v>
@@ -14057,7 +14057,7 @@
         <v>12</v>
       </c>
       <c r="G472" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H472" t="n">
         <v>67350</v>
@@ -14115,7 +14115,7 @@
         <v>12</v>
       </c>
       <c r="G474" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H474" t="n">
         <v>20100</v>
@@ -14173,7 +14173,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>9.96528339385986</v>
+        <v>9.96528244018555</v>
       </c>
       <c r="H476" t="n">
         <v>750</v>
@@ -14347,7 +14347,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>10.4807281494141</v>
+        <v>10.4807271957397</v>
       </c>
       <c r="H482" t="n">
         <v>26700</v>
@@ -14376,7 +14376,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="n">
-        <v>10.3089122772217</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H483" t="n">
         <v>2250</v>
@@ -14405,7 +14405,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G484" t="n">
-        <v>10.6525440216064</v>
+        <v>10.6525430679321</v>
       </c>
       <c r="H484" t="n">
         <v>24150</v>
@@ -14492,7 +14492,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.9102659225464</v>
+        <v>10.9102668762207</v>
       </c>
       <c r="H487" t="n">
         <v>4650</v>
@@ -14521,7 +14521,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.9102659225464</v>
+        <v>10.9102668762207</v>
       </c>
       <c r="H488" t="n">
         <v>4350</v>
@@ -14550,7 +14550,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>10.9102659225464</v>
+        <v>10.9102668762207</v>
       </c>
       <c r="H489" t="n">
         <v>14100</v>
@@ -14579,7 +14579,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H490" t="n">
         <v>6450</v>
@@ -14608,7 +14608,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H491" t="n">
         <v>6450</v>
@@ -14637,7 +14637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H492" t="n">
         <v>5100</v>
@@ -14753,7 +14753,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>11.3398036956787</v>
+        <v>11.339804649353</v>
       </c>
       <c r="H496" t="n">
         <v>6150</v>
@@ -14782,7 +14782,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>11.5116195678711</v>
+        <v>11.5116205215454</v>
       </c>
       <c r="H497" t="n">
         <v>6600</v>
@@ -14811,7 +14811,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G498" t="n">
-        <v>11.3398036956787</v>
+        <v>11.339804649353</v>
       </c>
       <c r="H498" t="n">
         <v>2250</v>
@@ -14985,7 +14985,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>12.3706970214844</v>
+        <v>12.3706960678101</v>
       </c>
       <c r="H504" t="n">
         <v>6900</v>
@@ -15014,7 +15014,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>12.62841796875</v>
+        <v>12.6284170150757</v>
       </c>
       <c r="H505" t="n">
         <v>2400</v>
@@ -15072,7 +15072,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>12.7143278121948</v>
+        <v>12.7143268585205</v>
       </c>
       <c r="H507" t="n">
         <v>2400</v>
@@ -15101,7 +15101,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G508" t="n">
-        <v>12.7143278121948</v>
+        <v>12.7143268585205</v>
       </c>
       <c r="H508" t="n">
         <v>1350</v>
@@ -15130,7 +15130,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>13.057954788208</v>
+        <v>13.0579566955566</v>
       </c>
       <c r="H509" t="n">
         <v>2550</v>
@@ -15159,7 +15159,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>13.057954788208</v>
+        <v>13.0579566955566</v>
       </c>
       <c r="H510" t="n">
         <v>12750</v>
@@ -15188,7 +15188,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>12.9720487594604</v>
+        <v>12.9720497131348</v>
       </c>
       <c r="H511" t="n">
         <v>86100</v>
@@ -15217,7 +15217,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>12.9720487594604</v>
+        <v>12.9720497131348</v>
       </c>
       <c r="H512" t="n">
         <v>750</v>
@@ -15246,7 +15246,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9720487594604</v>
+        <v>12.9720497131348</v>
       </c>
       <c r="H513" t="n">
         <v>3750</v>
@@ -15275,7 +15275,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G514" t="n">
-        <v>13.057954788208</v>
+        <v>13.0579566955566</v>
       </c>
       <c r="H514" t="n">
         <v>10800</v>
@@ -15333,7 +15333,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>13.9170322418213</v>
+        <v>13.9170331954956</v>
       </c>
       <c r="H516" t="n">
         <v>13350</v>
@@ -15420,7 +15420,7 @@
         <v>16.5</v>
       </c>
       <c r="G519" t="n">
-        <v>14.1747550964355</v>
+        <v>14.1747560501099</v>
       </c>
       <c r="H519" t="n">
         <v>8250</v>
@@ -15478,7 +15478,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324769973755</v>
+        <v>14.4324760437012</v>
       </c>
       <c r="H521" t="n">
         <v>58800</v>
@@ -15507,7 +15507,7 @@
         <v>16.5</v>
       </c>
       <c r="G522" t="n">
-        <v>14.1747550964355</v>
+        <v>14.1747560501099</v>
       </c>
       <c r="H522" t="n">
         <v>4050</v>
@@ -15652,7 +15652,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324769973755</v>
+        <v>14.4324760437012</v>
       </c>
       <c r="H527" t="n">
         <v>40350</v>
@@ -15681,7 +15681,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042947769165</v>
+        <v>14.6042938232422</v>
       </c>
       <c r="H528" t="n">
         <v>25200</v>
@@ -15710,7 +15710,7 @@
         <v>18</v>
       </c>
       <c r="G529" t="n">
-        <v>15.4633712768555</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H529" t="n">
         <v>8700</v>
@@ -15739,7 +15739,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>15.2915534973145</v>
+        <v>15.2915515899658</v>
       </c>
       <c r="H530" t="n">
         <v>3450</v>
@@ -15768,7 +15768,7 @@
         <v>18</v>
       </c>
       <c r="G531" t="n">
-        <v>15.4633712768555</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H531" t="n">
         <v>3900</v>
@@ -15797,7 +15797,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056465148926</v>
+        <v>15.2056484222412</v>
       </c>
       <c r="H532" t="n">
         <v>8550</v>
@@ -15826,7 +15826,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>15.1197395324707</v>
+        <v>15.1197376251221</v>
       </c>
       <c r="H533" t="n">
         <v>4500</v>
@@ -15855,7 +15855,7 @@
         <v>18</v>
       </c>
       <c r="G534" t="n">
-        <v>15.4633712768555</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H534" t="n">
         <v>20100</v>
@@ -15884,7 +15884,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="n">
-        <v>15.4633712768555</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H535" t="n">
         <v>15300</v>
@@ -15913,7 +15913,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.549277305603</v>
+        <v>15.5492792129517</v>
       </c>
       <c r="H536" t="n">
         <v>3000</v>
@@ -15942,7 +15942,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>15.7259721755981</v>
+        <v>15.7259712219238</v>
       </c>
       <c r="H537" t="n">
         <v>7800</v>
@@ -15971,7 +15971,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376237869263</v>
+        <v>15.6376266479492</v>
       </c>
       <c r="H538" t="n">
         <v>2250</v>
@@ -16000,7 +16000,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>15.7259721755981</v>
+        <v>15.7259712219238</v>
       </c>
       <c r="H539" t="n">
         <v>4800</v>
@@ -16058,7 +16058,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G541" t="n">
-        <v>15.1958847045898</v>
+        <v>15.1958866119385</v>
       </c>
       <c r="H541" t="n">
         <v>3300</v>
@@ -16087,7 +16087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>15.7259721755981</v>
+        <v>15.7259712219238</v>
       </c>
       <c r="H542" t="n">
         <v>3750</v>
@@ -16116,7 +16116,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.549277305603</v>
+        <v>15.5492753982544</v>
       </c>
       <c r="H543" t="n">
         <v>3600</v>
@@ -16145,7 +16145,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>15.81432056427</v>
+        <v>15.8143224716187</v>
       </c>
       <c r="H544" t="n">
         <v>600</v>
@@ -16174,7 +16174,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>16.0793685913086</v>
+        <v>16.07936668396</v>
       </c>
       <c r="H545" t="n">
         <v>36600</v>
@@ -16203,7 +16203,7 @@
         <v>18</v>
       </c>
       <c r="G546" t="n">
-        <v>15.9026708602905</v>
+        <v>15.9026699066162</v>
       </c>
       <c r="H546" t="n">
         <v>3150</v>
@@ -16667,7 +16667,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>19.0832042694092</v>
+        <v>19.0832023620605</v>
       </c>
       <c r="H562" t="n">
         <v>10050</v>
@@ -17044,7 +17044,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278919219971</v>
+        <v>17.2278938293457</v>
       </c>
       <c r="H575" t="n">
         <v>2250</v>
@@ -17160,7 +17160,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>17.0511932373047</v>
+        <v>17.051197052002</v>
       </c>
       <c r="H579" t="n">
         <v>1650</v>
@@ -17247,7 +17247,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>17.0511932373047</v>
+        <v>17.051197052002</v>
       </c>
       <c r="H582" t="n">
         <v>12225</v>
@@ -17334,7 +17334,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>17.4045867919922</v>
+        <v>17.4045906066895</v>
       </c>
       <c r="H585" t="n">
         <v>1350</v>
@@ -17624,7 +17624,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>22.7938289642334</v>
+        <v>22.7938251495361</v>
       </c>
       <c r="H595" t="n">
         <v>9525</v>
@@ -17653,7 +17653,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>20.6734714508057</v>
+        <v>20.673469543457</v>
       </c>
       <c r="H596" t="n">
         <v>39600</v>
@@ -17711,7 +17711,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>19.2598991394043</v>
+        <v>19.2598972320557</v>
       </c>
       <c r="H598" t="n">
         <v>41625</v>
@@ -17740,7 +17740,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G599" t="n">
-        <v>19.2598991394043</v>
+        <v>19.2598972320557</v>
       </c>
       <c r="H599" t="n">
         <v>9225</v>
@@ -17769,7 +17769,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>19.2598991394043</v>
+        <v>19.2598972320557</v>
       </c>
       <c r="H600" t="n">
         <v>18750</v>
@@ -18001,7 +18001,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>21.7336502075195</v>
+        <v>21.7336483001709</v>
       </c>
       <c r="H608" t="n">
         <v>12750</v>
@@ -18030,7 +18030,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>21.7336502075195</v>
+        <v>21.7336483001709</v>
       </c>
       <c r="H609" t="n">
         <v>13500</v>
@@ -18088,7 +18088,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>22.7938289642334</v>
+        <v>22.7938251495361</v>
       </c>
       <c r="H611" t="n">
         <v>7125</v>
@@ -18117,7 +18117,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>22.7938289642334</v>
+        <v>22.7938251495361</v>
       </c>
       <c r="H612" t="n">
         <v>7575</v>
@@ -18175,7 +18175,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>23.6773071289062</v>
+        <v>23.6773090362549</v>
       </c>
       <c r="H614" t="n">
         <v>5175</v>
@@ -18204,7 +18204,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H615" t="n">
         <v>7875</v>
@@ -18320,7 +18320,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>23.1472225189209</v>
+        <v>23.1472187042236</v>
       </c>
       <c r="H619" t="n">
         <v>8100</v>
@@ -18349,7 +18349,7 @@
         <v>26</v>
       </c>
       <c r="G620" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H620" t="n">
         <v>4800</v>
@@ -18465,7 +18465,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H624" t="n">
         <v>6075</v>
@@ -18639,7 +18639,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947189331055</v>
       </c>
       <c r="H630" t="n">
         <v>11250</v>
@@ -18668,7 +18668,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>29.8616790771484</v>
+        <v>29.8616809844971</v>
       </c>
       <c r="H631" t="n">
         <v>11700</v>
@@ -18697,7 +18697,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>30.7451629638672</v>
+        <v>30.7451648712158</v>
       </c>
       <c r="H632" t="n">
         <v>23025</v>
@@ -18755,7 +18755,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0985546112061</v>
+        <v>31.0985507965088</v>
       </c>
       <c r="H634" t="n">
         <v>8625</v>
@@ -18784,7 +18784,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.5684623718262</v>
+        <v>30.5684642791748</v>
       </c>
       <c r="H635" t="n">
         <v>3900</v>
@@ -18813,7 +18813,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>30.5684623718262</v>
+        <v>30.5684642791748</v>
       </c>
       <c r="H636" t="n">
         <v>21300</v>
@@ -18842,7 +18842,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>30.7451629638672</v>
+        <v>30.7451648712158</v>
       </c>
       <c r="H637" t="n">
         <v>1725</v>
@@ -18871,7 +18871,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G638" t="n">
-        <v>30.3917694091797</v>
+        <v>30.391773223877</v>
       </c>
       <c r="H638" t="n">
         <v>20325</v>
@@ -18900,7 +18900,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H639" t="n">
         <v>8550</v>
@@ -18929,7 +18929,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082912445068</v>
+        <v>29.5082893371582</v>
       </c>
       <c r="H640" t="n">
         <v>11100</v>
@@ -18958,7 +18958,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H641" t="n">
         <v>10875</v>
@@ -19103,7 +19103,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947189331055</v>
       </c>
       <c r="H646" t="n">
         <v>10950</v>
@@ -19219,7 +19219,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H650" t="n">
         <v>15450</v>
@@ -19451,7 +19451,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H658" t="n">
         <v>975</v>
@@ -19480,7 +19480,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H659" t="n">
         <v>4200</v>
@@ -19509,7 +19509,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H660" t="n">
         <v>2700</v>
@@ -19567,7 +19567,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H662" t="n">
         <v>4725</v>
@@ -19625,7 +19625,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G664" t="n">
-        <v>29.6849803924561</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H664" t="n">
         <v>4500</v>
@@ -19654,7 +19654,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G665" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H665" t="n">
         <v>6750</v>
@@ -19683,7 +19683,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H666" t="n">
         <v>8175</v>
@@ -19741,7 +19741,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>29.8616790771484</v>
+        <v>29.8616809844971</v>
       </c>
       <c r="H668" t="n">
         <v>5550</v>
@@ -19770,7 +19770,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>29.6849803924561</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H669" t="n">
         <v>10575</v>
@@ -19799,7 +19799,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H670" t="n">
         <v>4800</v>
@@ -19857,7 +19857,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G672" t="n">
-        <v>29.6849803924561</v>
+        <v>29.6849822998047</v>
       </c>
       <c r="H672" t="n">
         <v>2475</v>
@@ -19944,7 +19944,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>29.8616790771484</v>
+        <v>29.8616809844971</v>
       </c>
       <c r="H675" t="n">
         <v>7800</v>
@@ -19973,7 +19973,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>29.3315925598145</v>
+        <v>29.3315906524658</v>
       </c>
       <c r="H676" t="n">
         <v>2025</v>
@@ -20031,7 +20031,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>28.6248073577881</v>
+        <v>28.6248054504395</v>
       </c>
       <c r="H678" t="n">
         <v>4500</v>
@@ -20147,7 +20147,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947189331055</v>
       </c>
       <c r="H682" t="n">
         <v>5625</v>
@@ -20205,7 +20205,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>28.6248073577881</v>
+        <v>28.6248054504395</v>
       </c>
       <c r="H684" t="n">
         <v>2850</v>
@@ -20466,7 +20466,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>25.4442710876465</v>
+        <v>25.4442729949951</v>
       </c>
       <c r="H693" t="n">
         <v>5025</v>
@@ -20553,7 +20553,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H696" t="n">
         <v>5775</v>
@@ -20582,7 +20582,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H697" t="n">
         <v>1800</v>
@@ -20640,7 +20640,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G699" t="n">
-        <v>28.6248073577881</v>
+        <v>28.6248054504395</v>
       </c>
       <c r="H699" t="n">
         <v>5400</v>
@@ -20785,7 +20785,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H704" t="n">
         <v>1350</v>
@@ -20872,7 +20872,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G707" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H707" t="n">
         <v>4125</v>
@@ -20901,7 +20901,7 @@
         <v>30</v>
       </c>
       <c r="G708" t="n">
-        <v>26.5044498443604</v>
+        <v>26.504451751709</v>
       </c>
       <c r="H708" t="n">
         <v>5700</v>
@@ -21191,7 +21191,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H718" t="n">
         <v>375</v>
@@ -21249,7 +21249,7 @@
         <v>30</v>
       </c>
       <c r="G720" t="n">
-        <v>26.5044498443604</v>
+        <v>26.504451751709</v>
       </c>
       <c r="H720" t="n">
         <v>4350</v>
@@ -21278,7 +21278,7 @@
         <v>30</v>
       </c>
       <c r="G721" t="n">
-        <v>26.5044498443604</v>
+        <v>26.504451751709</v>
       </c>
       <c r="H721" t="n">
         <v>675</v>
@@ -21568,7 +21568,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>25.4442710876465</v>
+        <v>25.4442729949951</v>
       </c>
       <c r="H731" t="n">
         <v>750</v>
@@ -21655,7 +21655,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H734" t="n">
         <v>2550</v>
@@ -21742,7 +21742,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H737" t="n">
         <v>15750</v>
@@ -21800,7 +21800,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H739" t="n">
         <v>675</v>
@@ -21829,7 +21829,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H740" t="n">
         <v>1650</v>
@@ -21887,7 +21887,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H742" t="n">
         <v>300</v>
@@ -21916,7 +21916,7 @@
         <v>29</v>
       </c>
       <c r="G743" t="n">
-        <v>25.6209678649902</v>
+        <v>25.6209697723389</v>
       </c>
       <c r="H743" t="n">
         <v>1425</v>
@@ -21945,7 +21945,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H744" t="n">
         <v>6825</v>
@@ -22003,7 +22003,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H746" t="n">
         <v>675</v>
@@ -22061,7 +22061,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H748" t="n">
         <v>2025</v>
@@ -22119,7 +22119,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>23.6773071289062</v>
+        <v>23.6773090362549</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>23.6773071289062</v>
+        <v>23.6773090362549</v>
       </c>
       <c r="H751" t="n">
         <v>3525</v>
@@ -22264,7 +22264,7 @@
         <v>25</v>
       </c>
       <c r="G755" t="n">
-        <v>22.087043762207</v>
+        <v>22.0870418548584</v>
       </c>
       <c r="H755" t="n">
         <v>2775</v>
@@ -22293,7 +22293,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>21.7336502075195</v>
+        <v>21.7336483001709</v>
       </c>
       <c r="H756" t="n">
         <v>6150</v>
@@ -22322,7 +22322,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>21.5569515228271</v>
+        <v>21.5569496154785</v>
       </c>
       <c r="H757" t="n">
         <v>900</v>
@@ -22351,7 +22351,7 @@
         <v>24</v>
       </c>
       <c r="G758" t="n">
-        <v>21.2035598754883</v>
+        <v>21.2035617828369</v>
       </c>
       <c r="H758" t="n">
         <v>2250</v>
@@ -22409,7 +22409,7 @@
         <v>25</v>
       </c>
       <c r="G760" t="n">
-        <v>22.087043762207</v>
+        <v>22.0870418548584</v>
       </c>
       <c r="H760" t="n">
         <v>9750</v>
@@ -22583,7 +22583,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H766" t="n">
         <v>1500</v>
@@ -22612,7 +22612,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H767" t="n">
         <v>375</v>
@@ -22670,7 +22670,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H769" t="n">
         <v>2025</v>
@@ -22728,7 +22728,7 @@
         <v>30</v>
       </c>
       <c r="G771" t="n">
-        <v>26.5044498443604</v>
+        <v>26.504451751709</v>
       </c>
       <c r="H771" t="n">
         <v>1275</v>
@@ -22873,7 +22873,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H776" t="n">
         <v>2550</v>
@@ -22902,7 +22902,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>25.4442710876465</v>
+        <v>25.4442729949951</v>
       </c>
       <c r="H777" t="n">
         <v>8550</v>
@@ -22960,7 +22960,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H779" t="n">
         <v>2400</v>
@@ -22989,7 +22989,7 @@
         <v>29</v>
       </c>
       <c r="G780" t="n">
-        <v>25.6209678649902</v>
+        <v>25.6209697723389</v>
       </c>
       <c r="H780" t="n">
         <v>2100</v>
@@ -23018,7 +23018,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>25.5326175689697</v>
+        <v>25.5326194763184</v>
       </c>
       <c r="H781" t="n">
         <v>300</v>
@@ -23047,7 +23047,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H782" t="n">
         <v>1650</v>
@@ -23076,7 +23076,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H783" t="n">
         <v>2700</v>
@@ -23192,7 +23192,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G787" t="n">
-        <v>23.1472225189209</v>
+        <v>23.1472187042236</v>
       </c>
       <c r="H787" t="n">
         <v>1650</v>
@@ -23337,7 +23337,7 @@
         <v>26</v>
       </c>
       <c r="G792" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H792" t="n">
         <v>2325</v>
@@ -23366,7 +23366,7 @@
         <v>26</v>
       </c>
       <c r="G793" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>26</v>
       </c>
       <c r="G794" t="n">
-        <v>22.9705238342285</v>
+        <v>22.9705219268799</v>
       </c>
       <c r="H794" t="n">
         <v>2250</v>
@@ -23424,7 +23424,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>24.3840923309326</v>
+        <v>24.3840942382812</v>
       </c>
       <c r="H795" t="n">
         <v>1125</v>
@@ -23511,7 +23511,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G798" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H798" t="n">
         <v>2025</v>
@@ -23540,7 +23540,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H799" t="n">
         <v>1275</v>
@@ -23569,7 +23569,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>25.4490051269531</v>
+        <v>25.4490032196045</v>
       </c>
       <c r="H800" t="n">
         <v>2925</v>
@@ -23627,7 +23627,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H802" t="n">
         <v>150</v>
@@ -23656,7 +23656,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>23.9202671051025</v>
+        <v>23.9202651977539</v>
       </c>
       <c r="H803" t="n">
         <v>2625</v>
@@ -23830,7 +23830,7 @@
         <v>27.5</v>
       </c>
       <c r="G809" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H809" t="n">
         <v>225</v>
@@ -23917,7 +23917,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>23.7404117584229</v>
+        <v>23.7404136657715</v>
       </c>
       <c r="H812" t="n">
         <v>150</v>
@@ -24004,7 +24004,7 @@
         <v>27.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H815" t="n">
         <v>300</v>
@@ -24033,7 +24033,7 @@
         <v>27.5</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H816" t="n">
         <v>75</v>
@@ -24120,7 +24120,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H819" t="n">
         <v>2100</v>
@@ -24149,7 +24149,7 @@
         <v>27.5</v>
       </c>
       <c r="G820" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H820" t="n">
         <v>1050</v>
@@ -24178,7 +24178,7 @@
         <v>27.5</v>
       </c>
       <c r="G821" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H821" t="n">
         <v>750</v>
@@ -24207,7 +24207,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>23.7404117584229</v>
+        <v>23.7404136657715</v>
       </c>
       <c r="H822" t="n">
         <v>4350</v>
@@ -24294,7 +24294,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G825" t="n">
-        <v>24.4598197937012</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H825" t="n">
         <v>300</v>
@@ -24323,7 +24323,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>24.4598197937012</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H826" t="n">
         <v>1500</v>
@@ -24410,7 +24410,7 @@
         <v>26</v>
       </c>
       <c r="G829" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H829" t="n">
         <v>1950</v>
@@ -24468,7 +24468,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>23.2008609771729</v>
+        <v>23.2008590698242</v>
       </c>
       <c r="H831" t="n">
         <v>1725</v>
@@ -24497,7 +24497,7 @@
         <v>26</v>
       </c>
       <c r="G832" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>26</v>
       </c>
       <c r="G833" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H833" t="n">
         <v>825</v>
@@ -24555,7 +24555,7 @@
         <v>26</v>
       </c>
       <c r="G834" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H834" t="n">
         <v>825</v>
@@ -24584,7 +24584,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>23.2907867431641</v>
+        <v>23.2907848358154</v>
       </c>
       <c r="H835" t="n">
         <v>1350</v>
@@ -24613,7 +24613,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>23.2008609771729</v>
+        <v>23.2008590698242</v>
       </c>
       <c r="H836" t="n">
         <v>225</v>
@@ -24671,7 +24671,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>23.2008609771729</v>
+        <v>23.2008590698242</v>
       </c>
       <c r="H838" t="n">
         <v>300</v>
@@ -24816,7 +24816,7 @@
         <v>24.5</v>
       </c>
       <c r="G843" t="n">
-        <v>22.0318222045898</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H843" t="n">
         <v>675</v>
@@ -24932,7 +24932,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H847" t="n">
         <v>300</v>
@@ -25019,7 +25019,7 @@
         <v>24.5</v>
       </c>
       <c r="G850" t="n">
-        <v>22.0318222045898</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H850" t="n">
         <v>825</v>
@@ -25164,7 +25164,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G855" t="n">
-        <v>20.413158416748</v>
+        <v>20.4131603240967</v>
       </c>
       <c r="H855" t="n">
         <v>1050</v>
@@ -25193,7 +25193,7 @@
         <v>22</v>
       </c>
       <c r="G856" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H856" t="n">
         <v>5700</v>
@@ -25222,7 +25222,7 @@
         <v>22</v>
       </c>
       <c r="G857" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H857" t="n">
         <v>2925</v>
@@ -25251,7 +25251,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>19.5139007568359</v>
+        <v>19.5139026641846</v>
       </c>
       <c r="H858" t="n">
         <v>1275</v>
@@ -25280,7 +25280,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G859" t="n">
-        <v>19.0642738342285</v>
+        <v>19.0642719268799</v>
       </c>
       <c r="H859" t="n">
         <v>1200</v>
@@ -25309,7 +25309,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>19.6038246154785</v>
+        <v>19.6038265228271</v>
       </c>
       <c r="H860" t="n">
         <v>1875</v>
@@ -25367,7 +25367,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>19.6937522888184</v>
+        <v>19.693754196167</v>
       </c>
       <c r="H862" t="n">
         <v>1500</v>
@@ -25396,7 +25396,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>19.6038246154785</v>
+        <v>19.6038265228271</v>
       </c>
       <c r="H863" t="n">
         <v>1275</v>
@@ -25454,7 +25454,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>19.0642738342285</v>
+        <v>19.0642719268799</v>
       </c>
       <c r="H865" t="n">
         <v>2325</v>
@@ -25483,7 +25483,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>19.6038246154785</v>
+        <v>19.6038265228271</v>
       </c>
       <c r="H866" t="n">
         <v>50100</v>
@@ -25599,7 +25599,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.3915271759033</v>
+        <v>22.391529083252</v>
       </c>
       <c r="H870" t="n">
         <v>4050</v>
@@ -25628,7 +25628,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>22.3016014099121</v>
+        <v>22.3015995025635</v>
       </c>
       <c r="H871" t="n">
         <v>1575</v>
@@ -25802,7 +25802,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>20.5030841827393</v>
+        <v>20.5030860900879</v>
       </c>
       <c r="H877" t="n">
         <v>6075</v>
@@ -25860,7 +25860,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>20.5030841827393</v>
+        <v>20.5030860900879</v>
       </c>
       <c r="H879" t="n">
         <v>1200</v>
@@ -25947,7 +25947,7 @@
         <v>22</v>
       </c>
       <c r="G882" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H882" t="n">
         <v>750</v>
@@ -26005,7 +26005,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>19.1541976928711</v>
+        <v>19.1541957855225</v>
       </c>
       <c r="H884" t="n">
         <v>4800</v>
@@ -26034,7 +26034,7 @@
         <v>22</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H885" t="n">
         <v>11025</v>
@@ -26063,7 +26063,7 @@
         <v>22</v>
       </c>
       <c r="G886" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H886" t="n">
         <v>4800</v>
@@ -26092,7 +26092,7 @@
         <v>22</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H887" t="n">
         <v>3975</v>
@@ -26121,7 +26121,7 @@
         <v>22</v>
       </c>
       <c r="G888" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H888" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>22</v>
       </c>
       <c r="G889" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H889" t="n">
         <v>1050</v>
@@ -26208,7 +26208,7 @@
         <v>23.5</v>
       </c>
       <c r="G891" t="n">
-        <v>21.1325645446777</v>
+        <v>21.1325664520264</v>
       </c>
       <c r="H891" t="n">
         <v>5475</v>
@@ -26295,7 +26295,7 @@
         <v>26</v>
       </c>
       <c r="G894" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H894" t="n">
         <v>4950</v>
@@ -26324,7 +26324,7 @@
         <v>26</v>
       </c>
       <c r="G895" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H895" t="n">
         <v>1650</v>
@@ -26353,7 +26353,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>23.2907867431641</v>
+        <v>23.2907848358154</v>
       </c>
       <c r="H896" t="n">
         <v>1200</v>
@@ -26382,7 +26382,7 @@
         <v>26</v>
       </c>
       <c r="G897" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H897" t="n">
         <v>4875</v>
@@ -26614,7 +26614,7 @@
         <v>24.5</v>
       </c>
       <c r="G905" t="n">
-        <v>22.0318222045898</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H905" t="n">
         <v>975</v>
@@ -26672,7 +26672,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.3915271759033</v>
+        <v>22.391529083252</v>
       </c>
       <c r="H907" t="n">
         <v>3225</v>
@@ -26788,7 +26788,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H911" t="n">
         <v>225</v>
@@ -26817,7 +26817,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>22.3016014099121</v>
+        <v>22.3015995025635</v>
       </c>
       <c r="H912" t="n">
         <v>900</v>
@@ -26846,7 +26846,7 @@
         <v>24.5</v>
       </c>
       <c r="G913" t="n">
-        <v>22.0318222045898</v>
+        <v>22.0318241119385</v>
       </c>
       <c r="H913" t="n">
         <v>300</v>
@@ -26875,7 +26875,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.3915271759033</v>
+        <v>22.391529083252</v>
       </c>
       <c r="H914" t="n">
         <v>75</v>
@@ -26933,7 +26933,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>23.2008609771729</v>
+        <v>23.2008590698242</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -26991,7 +26991,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H918" t="n">
         <v>5175</v>
@@ -27107,7 +27107,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H922" t="n">
         <v>1050</v>
@@ -27136,7 +27136,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>23.2008609771729</v>
+        <v>23.2008590698242</v>
       </c>
       <c r="H927" t="n">
         <v>75</v>
@@ -27368,7 +27368,7 @@
         <v>26</v>
       </c>
       <c r="G931" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H931" t="n">
         <v>600</v>
@@ -27397,7 +27397,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G932" t="n">
-        <v>24.4598197937012</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H932" t="n">
         <v>2625</v>
@@ -27426,7 +27426,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>24.4598197937012</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H933" t="n">
         <v>4500</v>
@@ -27455,7 +27455,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G934" t="n">
-        <v>25.0893020629883</v>
+        <v>25.0893001556396</v>
       </c>
       <c r="H934" t="n">
         <v>6075</v>
@@ -27484,7 +27484,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G935" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H935" t="n">
         <v>4050</v>
@@ -27513,7 +27513,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H936" t="n">
         <v>1875</v>
@@ -27687,7 +27687,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>25.0893020629883</v>
+        <v>25.0893001556396</v>
       </c>
       <c r="H942" t="n">
         <v>7350</v>
@@ -27716,7 +27716,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H943" t="n">
         <v>21450</v>
@@ -27745,7 +27745,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>28.5</v>
       </c>
       <c r="G947" t="n">
-        <v>25.6288547515869</v>
+        <v>25.6288566589355</v>
       </c>
       <c r="H947" t="n">
         <v>525</v>
@@ -27861,7 +27861,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H948" t="n">
         <v>4950</v>
@@ -27890,7 +27890,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H949" t="n">
         <v>1650</v>
@@ -28035,7 +28035,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>26.7978916168213</v>
+        <v>26.7978935241699</v>
       </c>
       <c r="H954" t="n">
         <v>69075</v>
@@ -28064,7 +28064,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H955" t="n">
         <v>1050</v>
@@ -28093,7 +28093,7 @@
         <v>30.5</v>
       </c>
       <c r="G956" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H956" t="n">
         <v>3300</v>
@@ -28151,7 +28151,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>28.4165573120117</v>
+        <v>28.4165592193604</v>
       </c>
       <c r="H958" t="n">
         <v>6825</v>
@@ -28180,7 +28180,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G959" t="n">
-        <v>29.3158130645752</v>
+        <v>29.3158149719238</v>
       </c>
       <c r="H959" t="n">
         <v>6600</v>
@@ -28238,7 +28238,7 @@
         <v>30.5</v>
       </c>
       <c r="G961" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H961" t="n">
         <v>5175</v>
@@ -28267,7 +28267,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G962" t="n">
-        <v>27.2475204467773</v>
+        <v>27.2475185394287</v>
       </c>
       <c r="H962" t="n">
         <v>1950</v>
@@ -28296,7 +28296,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>26.7079658508301</v>
+        <v>26.7079677581787</v>
       </c>
       <c r="H963" t="n">
         <v>525</v>
@@ -28325,7 +28325,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G964" t="n">
-        <v>26.7079658508301</v>
+        <v>26.7079677581787</v>
       </c>
       <c r="H964" t="n">
         <v>525</v>
@@ -28441,7 +28441,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H968" t="n">
         <v>450</v>
@@ -28528,7 +28528,7 @@
         <v>28.5</v>
       </c>
       <c r="G971" t="n">
-        <v>25.6288547515869</v>
+        <v>25.6288566589355</v>
       </c>
       <c r="H971" t="n">
         <v>1350</v>
@@ -28615,7 +28615,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H974" t="n">
         <v>75</v>
@@ -28644,7 +28644,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H976" t="n">
         <v>375</v>
@@ -28702,7 +28702,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H977" t="n">
         <v>750</v>
@@ -28760,7 +28760,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H979" t="n">
         <v>4275</v>
@@ -28789,7 +28789,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H980" t="n">
         <v>6150</v>
@@ -28818,7 +28818,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G981" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H981" t="n">
         <v>825</v>
@@ -28934,7 +28934,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>24.9094505310059</v>
+        <v>24.9094524383545</v>
       </c>
       <c r="H985" t="n">
         <v>3825</v>
@@ -28963,7 +28963,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>24.9094505310059</v>
+        <v>24.9094524383545</v>
       </c>
       <c r="H986" t="n">
         <v>2850</v>
@@ -29021,7 +29021,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>24.4598197937012</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H988" t="n">
         <v>675</v>
@@ -29050,7 +29050,7 @@
         <v>27.5</v>
       </c>
       <c r="G989" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H989" t="n">
         <v>2025</v>
@@ -29108,7 +29108,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>25.2691516876221</v>
+        <v>25.2691535949707</v>
       </c>
       <c r="H991" t="n">
         <v>150</v>
@@ -29166,7 +29166,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>25.0893020629883</v>
+        <v>25.0893001556396</v>
       </c>
       <c r="H993" t="n">
         <v>12975</v>
@@ -29224,7 +29224,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H995" t="n">
         <v>525</v>
@@ -29311,7 +29311,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H998" t="n">
         <v>525</v>
@@ -29340,7 +29340,7 @@
         <v>28.5</v>
       </c>
       <c r="G999" t="n">
-        <v>25.6288547515869</v>
+        <v>25.6288566589355</v>
       </c>
       <c r="H999" t="n">
         <v>1575</v>
@@ -29398,7 +29398,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>25.8087100982666</v>
+        <v>25.808708190918</v>
       </c>
       <c r="H1001" t="n">
         <v>1875</v>
@@ -29427,7 +29427,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>25.8087100982666</v>
+        <v>25.808708190918</v>
       </c>
       <c r="H1002" t="n">
         <v>3450</v>
@@ -29456,7 +29456,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1003" t="n">
-        <v>25.8087100982666</v>
+        <v>25.808708190918</v>
       </c>
       <c r="H1003" t="n">
         <v>1350</v>
@@ -29485,7 +29485,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H1004" t="n">
         <v>1050</v>
@@ -29543,7 +29543,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>25.3590793609619</v>
+        <v>25.3590812683105</v>
       </c>
       <c r="H1006" t="n">
         <v>3600</v>
@@ -29572,7 +29572,7 @@
         <v>27.5</v>
       </c>
       <c r="G1007" t="n">
-        <v>24.7295989990234</v>
+        <v>24.7295970916748</v>
       </c>
       <c r="H1007" t="n">
         <v>1500</v>
@@ -29804,7 +29804,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>27.2475204467773</v>
+        <v>27.2475185394287</v>
       </c>
       <c r="H1015" t="n">
         <v>2625</v>
@@ -30123,7 +30123,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>29.405740737915</v>
+        <v>29.4057426452637</v>
       </c>
       <c r="H1026" t="n">
         <v>2025</v>
@@ -30268,7 +30268,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1031" t="n">
         <v>1050</v>
@@ -30297,7 +30297,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1032" t="n">
-        <v>30.0352230072021</v>
+        <v>30.0352210998535</v>
       </c>
       <c r="H1032" t="n">
         <v>975</v>
@@ -30326,7 +30326,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>28.956111907959</v>
+        <v>28.9561100006104</v>
       </c>
       <c r="H1033" t="n">
         <v>1575</v>
@@ -30529,7 +30529,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639591217041</v>
+        <v>31.5639610290527</v>
       </c>
       <c r="H1040" t="n">
         <v>4425</v>
@@ -30645,7 +30645,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042598724365</v>
+        <v>31.2042579650879</v>
       </c>
       <c r="H1044" t="n">
         <v>1425</v>
@@ -30674,7 +30674,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1045" t="n">
         <v>10575</v>
@@ -30790,7 +30790,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3049983978271</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1049" t="n">
         <v>2100</v>
@@ -30819,7 +30819,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>30.9344787597656</v>
+        <v>30.9344844818115</v>
       </c>
       <c r="H1050" t="n">
         <v>675</v>
@@ -30877,7 +30877,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1052" t="n">
         <v>675</v>
@@ -30935,7 +30935,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3049983978271</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1054" t="n">
         <v>1050</v>
@@ -30964,7 +30964,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1055" t="n">
-        <v>29.9452953338623</v>
+        <v>29.9452934265137</v>
       </c>
       <c r="H1055" t="n">
         <v>450</v>
@@ -31051,7 +31051,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1058" t="n">
-        <v>29.405740737915</v>
+        <v>29.4057426452637</v>
       </c>
       <c r="H1058" t="n">
         <v>1575</v>
@@ -31109,7 +31109,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1060" t="n">
-        <v>28.5064811706543</v>
+        <v>28.5064849853516</v>
       </c>
       <c r="H1060" t="n">
         <v>2175</v>
@@ -31196,7 +31196,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1063" t="n">
         <v>1650</v>
@@ -31225,7 +31225,7 @@
         <v>33</v>
       </c>
       <c r="G1064" t="n">
-        <v>30.3765125274658</v>
+        <v>30.3765144348145</v>
       </c>
       <c r="H1064" t="n">
         <v>1425</v>
@@ -31254,7 +31254,7 @@
         <v>33</v>
       </c>
       <c r="G1065" t="n">
-        <v>30.3765125274658</v>
+        <v>30.3765144348145</v>
       </c>
       <c r="H1065" t="n">
         <v>600</v>
@@ -31283,7 +31283,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>30.0083122253418</v>
+        <v>30.0083141326904</v>
       </c>
       <c r="H1066" t="n">
         <v>450</v>
@@ -31573,7 +31573,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1076" t="n">
         <v>3600</v>
@@ -31660,7 +31660,7 @@
         <v>31.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1079" t="n">
         <v>1350</v>
@@ -31689,7 +31689,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1080" t="n">
         <v>14100</v>
@@ -31718,7 +31718,7 @@
         <v>31.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1081" t="n">
         <v>7125</v>
@@ -31747,7 +31747,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1082" t="n">
         <v>5025</v>
@@ -31776,7 +31776,7 @@
         <v>31.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1083" t="n">
         <v>6450</v>
@@ -31863,7 +31863,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1086" t="n">
         <v>2100</v>
@@ -31979,7 +31979,7 @@
         <v>31.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1090" t="n">
         <v>150</v>
@@ -32008,7 +32008,7 @@
         <v>31.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1091" t="n">
         <v>75</v>
@@ -32066,7 +32066,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>27.9832134246826</v>
+        <v>27.9832153320312</v>
       </c>
       <c r="H1093" t="n">
         <v>1275</v>
@@ -32182,7 +32182,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1097" t="n">
         <v>2400</v>
@@ -32211,7 +32211,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1098" t="n">
         <v>600</v>
@@ -32327,7 +32327,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1102" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1102" t="n">
         <v>5475</v>
@@ -32414,7 +32414,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1105" t="n">
         <v>3261</v>
@@ -32472,7 +32472,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1107" t="n">
-        <v>28.4434661865234</v>
+        <v>28.4434642791748</v>
       </c>
       <c r="H1107" t="n">
         <v>15327</v>
@@ -32501,7 +32501,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1108" t="n">
-        <v>28.2593669891357</v>
+        <v>28.2593650817871</v>
       </c>
       <c r="H1108" t="n">
         <v>17829</v>
@@ -32588,7 +32588,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1111" t="n">
         <v>2539</v>
@@ -32617,7 +32617,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1112" t="n">
-        <v>28.4434661865234</v>
+        <v>28.4434642791748</v>
       </c>
       <c r="H1112" t="n">
         <v>3350</v>
@@ -32646,7 +32646,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1113" t="n">
         <v>40817</v>
@@ -32907,7 +32907,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1122" t="n">
         <v>791</v>
@@ -32936,7 +32936,7 @@
         <v>33</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.3765125274658</v>
+        <v>30.3765144348145</v>
       </c>
       <c r="H1123" t="n">
         <v>1300</v>
@@ -32994,7 +32994,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1125" t="n">
-        <v>30.0083122253418</v>
+        <v>30.0083141326904</v>
       </c>
       <c r="H1125" t="n">
         <v>229</v>
@@ -33023,7 +33023,7 @@
         <v>33</v>
       </c>
       <c r="G1126" t="n">
-        <v>30.3765125274658</v>
+        <v>30.3765144348145</v>
       </c>
       <c r="H1126" t="n">
         <v>1180</v>
@@ -33052,7 +33052,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1127" t="n">
-        <v>30.0083122253418</v>
+        <v>30.0083141326904</v>
       </c>
       <c r="H1127" t="n">
         <v>114</v>
@@ -33139,7 +33139,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1130" t="n">
         <v>147</v>
@@ -33400,7 +33400,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1139" t="n">
         <v>5215</v>
@@ -33487,7 +33487,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1142" t="n">
         <v>1568</v>
@@ -33574,7 +33574,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1145" t="n">
         <v>240</v>
@@ -33603,7 +33603,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1146" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1146" t="n">
         <v>578</v>
@@ -33632,7 +33632,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>28.2593669891357</v>
+        <v>28.2593650817871</v>
       </c>
       <c r="H1147" t="n">
         <v>440</v>
@@ -33661,7 +33661,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1148" t="n">
-        <v>28.2593669891357</v>
+        <v>28.2593650817871</v>
       </c>
       <c r="H1148" t="n">
         <v>155</v>
@@ -33690,7 +33690,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1149" t="n">
         <v>1616</v>
@@ -33719,7 +33719,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>29.0878143310547</v>
+        <v>29.0878162384033</v>
       </c>
       <c r="H1150" t="n">
         <v>2194</v>
@@ -33777,7 +33777,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1152" t="n">
         <v>442</v>
@@ -33806,7 +33806,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1153" t="n">
         <v>365</v>
@@ -33835,7 +33835,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1154" t="n">
-        <v>28.1673145294189</v>
+        <v>28.1673126220703</v>
       </c>
       <c r="H1154" t="n">
         <v>6213</v>
@@ -33980,7 +33980,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1159" t="n">
-        <v>27.3388633728027</v>
+        <v>27.3388652801514</v>
       </c>
       <c r="H1159" t="n">
         <v>1696</v>
@@ -34038,7 +34038,7 @@
         <v>30</v>
       </c>
       <c r="G1161" t="n">
-        <v>27.6150150299072</v>
+        <v>27.6150131225586</v>
       </c>
       <c r="H1161" t="n">
         <v>1186</v>
@@ -34096,7 +34096,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1163" t="n">
         <v>1128</v>
@@ -34125,7 +34125,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1164" t="n">
         <v>5262</v>
@@ -34154,7 +34154,7 @@
         <v>28.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1165" t="n">
         <v>1365</v>
@@ -34183,7 +34183,7 @@
         <v>28.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1166" t="n">
         <v>12882</v>
@@ -34212,7 +34212,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>25.4978618621826</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1167" t="n">
         <v>1240</v>
@@ -34299,7 +34299,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>25.4978618621826</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1170" t="n">
         <v>1331</v>
@@ -34328,7 +34328,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1171" t="n">
         <v>1864</v>
@@ -34357,7 +34357,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1172" t="n">
         <v>10192</v>
@@ -34386,7 +34386,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1173" t="n">
         <v>27679</v>
@@ -34415,7 +34415,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1174" t="n">
         <v>300</v>
@@ -34444,7 +34444,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>24.9455623626709</v>
+        <v>24.9455642700195</v>
       </c>
       <c r="H1175" t="n">
         <v>596</v>
@@ -34473,7 +34473,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1176" t="n">
         <v>119</v>
@@ -34531,7 +34531,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1178" t="n">
         <v>572</v>
@@ -34560,7 +34560,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>24.3012104034424</v>
+        <v>24.301212310791</v>
       </c>
       <c r="H1179" t="n">
         <v>2003</v>
@@ -34589,7 +34589,7 @@
         <v>25.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>23.4727630615234</v>
+        <v>23.4727611541748</v>
       </c>
       <c r="H1180" t="n">
         <v>2862</v>
@@ -34647,7 +34647,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966114044189</v>
+        <v>23.1966133117676</v>
       </c>
       <c r="H1182" t="n">
         <v>16419</v>
@@ -34676,7 +34676,7 @@
         <v>25</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0125122070312</v>
+        <v>23.0125102996826</v>
       </c>
       <c r="H1183" t="n">
         <v>6634</v>
@@ -34705,7 +34705,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H1184" t="n">
         <v>766</v>
@@ -34734,7 +34734,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1185" t="n">
         <v>3901</v>
@@ -34763,7 +34763,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1186" t="n">
         <v>4535</v>
@@ -34792,7 +34792,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1187" t="n">
         <v>1957</v>
@@ -34821,7 +34821,7 @@
         <v>26.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>24.3932628631592</v>
+        <v>24.3932609558105</v>
       </c>
       <c r="H1188" t="n">
         <v>550</v>
@@ -34850,7 +34850,7 @@
         <v>25.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.4727630615234</v>
+        <v>23.4727611541748</v>
       </c>
       <c r="H1189" t="n">
         <v>4247</v>
@@ -34879,7 +34879,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1190" t="n">
         <v>3364</v>
@@ -34908,7 +34908,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H1191" t="n">
         <v>3743</v>
@@ -34937,7 +34937,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>23.3807106018066</v>
+        <v>23.3807125091553</v>
       </c>
       <c r="H1192" t="n">
         <v>2334</v>
@@ -34966,7 +34966,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1193" t="n">
         <v>5553</v>
@@ -34995,7 +34995,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1194" t="n">
         <v>6387</v>
@@ -35024,7 +35024,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>25.4978618621826</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1195" t="n">
         <v>15303</v>
@@ -35053,7 +35053,7 @@
         <v>28.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1196" t="n">
         <v>2871</v>
@@ -35140,7 +35140,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1199" t="n">
-        <v>25.2217140197754</v>
+        <v>25.2217121124268</v>
       </c>
       <c r="H1199" t="n">
         <v>3638</v>
@@ -35169,7 +35169,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.9455623626709</v>
+        <v>24.9455642700195</v>
       </c>
       <c r="H1200" t="n">
         <v>2435</v>
@@ -35227,7 +35227,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1202" t="n">
         <v>3057</v>
@@ -35256,7 +35256,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1203" t="n">
         <v>250</v>
@@ -35285,7 +35285,7 @@
         <v>26.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3932628631592</v>
+        <v>24.3932609558105</v>
       </c>
       <c r="H1204" t="n">
         <v>2078</v>
@@ -35314,7 +35314,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1205" t="n">
         <v>2933</v>
@@ -35372,7 +35372,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>24.3012104034424</v>
+        <v>24.301212310791</v>
       </c>
       <c r="H1207" t="n">
         <v>289</v>
@@ -35430,7 +35430,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>26.1422119140625</v>
+        <v>26.1422138214111</v>
       </c>
       <c r="H1209" t="n">
         <v>6415</v>
@@ -35459,7 +35459,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1210" t="n">
-        <v>26.5104141235352</v>
+        <v>26.5104122161865</v>
       </c>
       <c r="H1210" t="n">
         <v>3821</v>
@@ -35488,7 +35488,7 @@
         <v>28.5</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1211" t="n">
         <v>2877</v>
@@ -35517,7 +35517,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5104141235352</v>
+        <v>26.5104122161865</v>
       </c>
       <c r="H1212" t="n">
         <v>542</v>
@@ -35546,7 +35546,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1213" t="n">
-        <v>27.3388633728027</v>
+        <v>27.3388652801514</v>
       </c>
       <c r="H1213" t="n">
         <v>5222</v>
@@ -35575,7 +35575,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1214" t="n">
         <v>1681</v>
@@ -35633,7 +35633,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.4309120178223</v>
+        <v>27.4309139251709</v>
       </c>
       <c r="H1216" t="n">
         <v>3541</v>
@@ -35662,7 +35662,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.7865619659424</v>
+        <v>26.786563873291</v>
       </c>
       <c r="H1217" t="n">
         <v>2270</v>
@@ -35691,7 +35691,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>26.7865619659424</v>
+        <v>26.786563873291</v>
       </c>
       <c r="H1218" t="n">
         <v>6399</v>
@@ -35749,7 +35749,7 @@
         <v>28.5</v>
       </c>
       <c r="G1220" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1220" t="n">
         <v>2171</v>
@@ -35894,7 +35894,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.3388633728027</v>
+        <v>27.3388652801514</v>
       </c>
       <c r="H1225" t="n">
         <v>2106</v>
@@ -36068,7 +36068,7 @@
         <v>28.5</v>
       </c>
       <c r="G1231" t="n">
-        <v>26.2342624664307</v>
+        <v>26.2342643737793</v>
       </c>
       <c r="H1231" t="n">
         <v>3357</v>
@@ -36097,7 +36097,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1232" t="n">
         <v>4851</v>
@@ -36155,7 +36155,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1234" t="n">
         <v>2409</v>
@@ -36213,7 +36213,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.4978618621826</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1236" t="n">
         <v>5154</v>
@@ -36242,7 +36242,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>25.4058151245117</v>
+        <v>25.4058132171631</v>
       </c>
       <c r="H1237" t="n">
         <v>455</v>
@@ -36271,7 +36271,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2217140197754</v>
+        <v>25.2217121124268</v>
       </c>
       <c r="H1238" t="n">
         <v>1033</v>
@@ -36300,7 +36300,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>25.4058151245117</v>
+        <v>25.4058132171631</v>
       </c>
       <c r="H1239" t="n">
         <v>872</v>
@@ -36358,7 +36358,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>25.1296615600586</v>
+        <v>25.1296634674072</v>
       </c>
       <c r="H1241" t="n">
         <v>2635</v>
@@ -36445,7 +36445,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1244" t="n">
         <v>11217</v>
@@ -36503,7 +36503,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1246" t="n">
         <v>16021</v>
@@ -36590,7 +36590,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1249" t="n">
         <v>7712</v>
@@ -36706,7 +36706,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1253" t="n">
         <v>21403</v>
@@ -36735,7 +36735,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1254" t="n">
         <v>4568</v>
@@ -36764,7 +36764,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1255" t="n">
         <v>3149</v>
@@ -36793,7 +36793,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1256" t="n">
         <v>3291</v>
@@ -36822,7 +36822,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1257" t="n">
         <v>2319</v>
@@ -36851,7 +36851,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>24.4853115081787</v>
+        <v>24.4853134155273</v>
       </c>
       <c r="H1258" t="n">
         <v>1947</v>
@@ -36880,7 +36880,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1259" t="n">
         <v>15177</v>
@@ -36909,7 +36909,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1260" t="n">
-        <v>24.0250625610352</v>
+        <v>24.0250606536865</v>
       </c>
       <c r="H1260" t="n">
         <v>10057</v>
@@ -36967,7 +36967,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>25.4978618621826</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1262" t="n">
         <v>10735</v>
@@ -36996,7 +36996,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1263" t="n">
         <v>5803</v>
@@ -37112,7 +37112,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1267" t="n">
         <v>12740</v>
@@ -37170,7 +37170,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>28.6275653839111</v>
+        <v>28.6275634765625</v>
       </c>
       <c r="H1269" t="n">
         <v>11777</v>
@@ -37199,7 +37199,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1270" t="n">
         <v>1818</v>
@@ -37373,7 +37373,7 @@
         <v>31.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1276" t="n">
         <v>13340</v>
@@ -37489,7 +37489,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1280" t="n">
         <v>2808</v>
@@ -37634,7 +37634,7 @@
         <v>33</v>
       </c>
       <c r="G1285" t="n">
-        <v>30.3765125274658</v>
+        <v>30.3765144348145</v>
       </c>
       <c r="H1285" t="n">
         <v>9952</v>
@@ -37750,7 +37750,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1289" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1289" t="n">
         <v>2827</v>
@@ -37837,7 +37837,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1292" t="n">
         <v>3238</v>
@@ -37866,7 +37866,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1293" t="n">
         <v>2155</v>
@@ -37895,7 +37895,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1294" t="n">
-        <v>30.4685649871826</v>
+        <v>30.468563079834</v>
       </c>
       <c r="H1294" t="n">
         <v>951</v>
@@ -37924,7 +37924,7 @@
         <v>33</v>
       </c>
       <c r="G1295" t="n">
-        <v>30.3765125274658</v>
+        <v>30.3765144348145</v>
       </c>
       <c r="H1295" t="n">
         <v>3140</v>
@@ -37953,7 +37953,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526622772217</v>
       </c>
       <c r="H1296" t="n">
         <v>3034</v>
@@ -37982,7 +37982,7 @@
         <v>33</v>
       </c>
       <c r="G1297" t="n">
-        <v>30.3765125274658</v>
+        <v>30.3765144348145</v>
       </c>
       <c r="H1297" t="n">
         <v>1609</v>
@@ -38040,7 +38040,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1299" t="n">
         <v>10536</v>
@@ -38069,7 +38069,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526622772217</v>
       </c>
       <c r="H1300" t="n">
         <v>753</v>
@@ -38098,7 +38098,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.8367671966553</v>
+        <v>30.836763381958</v>
       </c>
       <c r="H1301" t="n">
         <v>18694</v>
@@ -38272,7 +38272,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>30.6526641845703</v>
+        <v>30.6526622772217</v>
       </c>
       <c r="H1307" t="n">
         <v>2297</v>
@@ -38301,7 +38301,7 @@
         <v>33</v>
       </c>
       <c r="G1308" t="n">
-        <v>30.3765125274658</v>
+        <v>30.3765144348145</v>
       </c>
       <c r="H1308" t="n">
         <v>4364</v>
@@ -38388,7 +38388,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.5355129241943</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1311" t="n">
         <v>14200</v>
@@ -38562,7 +38562,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.0954246520996</v>
+        <v>29.095422744751</v>
       </c>
       <c r="H1317" t="n">
         <v>6125</v>
@@ -38765,7 +38765,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1324" t="n">
         <v>12844</v>
@@ -38823,7 +38823,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1326" t="n">
         <v>9621</v>
@@ -38852,7 +38852,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1327" t="n">
         <v>46167</v>
@@ -38881,7 +38881,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1328" t="n">
         <v>3959</v>
@@ -38997,7 +38997,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1332" t="n">
         <v>24982</v>
@@ -39026,7 +39026,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1333" t="n">
         <v>8601</v>
@@ -39055,7 +39055,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1334" t="n">
         <v>5309</v>
@@ -39084,7 +39084,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1335" t="n">
         <v>21621</v>
@@ -39113,7 +39113,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1336" t="n">
         <v>16181</v>
@@ -39142,7 +39142,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1337" t="n">
         <v>6822</v>
@@ -39171,7 +39171,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1338" t="n">
         <v>3455</v>
@@ -39200,7 +39200,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1339" t="n">
         <v>5494</v>
@@ -39229,7 +39229,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1340" t="n">
         <v>13157</v>
@@ -39258,7 +39258,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1341" t="n">
         <v>2965</v>
@@ -39287,7 +39287,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1342" t="n">
         <v>1570</v>
@@ -39345,7 +39345,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1344" t="n">
         <v>2849</v>
@@ -39374,7 +39374,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1345" t="n">
         <v>4077</v>
@@ -39461,7 +39461,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1348" t="n">
         <v>3503</v>
@@ -39548,7 +39548,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1351" t="n">
         <v>3621</v>
@@ -39693,7 +39693,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1356" t="n">
         <v>1074</v>
@@ -39722,7 +39722,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1357" t="n">
         <v>1555</v>
@@ -39896,7 +39896,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851486206055</v>
+        <v>33.7851448059082</v>
       </c>
       <c r="H1363" t="n">
         <v>12779</v>
@@ -39925,7 +39925,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1364" t="n">
         <v>7910</v>
@@ -40012,7 +40012,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1367" t="n">
         <v>2625</v>
@@ -40157,7 +40157,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1372" t="n">
         <v>2528</v>
@@ -40186,7 +40186,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1373" t="n">
         <v>5370</v>
@@ -40273,7 +40273,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1376" t="n">
         <v>9183</v>
@@ -40302,7 +40302,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1377" t="n">
         <v>4352</v>
@@ -40331,7 +40331,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095977783203</v>
+        <v>31.0095996856689</v>
       </c>
       <c r="H1378" t="n">
         <v>1704</v>
@@ -40360,7 +40360,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1379" t="n">
         <v>553</v>
@@ -40389,7 +40389,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1380" t="n">
         <v>732</v>
@@ -40476,7 +40476,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1383" t="n">
         <v>1248</v>
@@ -40505,7 +40505,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1384" t="n">
         <v>1301</v>
@@ -40563,7 +40563,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1386" t="n">
         <v>1483</v>
@@ -40592,7 +40592,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1387" t="n">
         <v>3214</v>
@@ -40708,7 +40708,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1391" t="n">
         <v>3859</v>
@@ -40737,7 +40737,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1392" t="n">
         <v>1387</v>
@@ -40766,7 +40766,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1393" t="n">
         <v>569</v>
@@ -40795,7 +40795,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1394" t="n">
         <v>1704</v>
@@ -40940,7 +40940,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1399" t="n">
         <v>2679</v>
@@ -40998,7 +40998,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1401" t="n">
         <v>4340</v>
@@ -41027,7 +41027,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1402" t="n">
         <v>3944</v>
@@ -41056,7 +41056,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1403" t="n">
         <v>1728</v>
@@ -41085,7 +41085,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1404" t="n">
         <v>1317</v>
@@ -41114,7 +41114,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1405" t="n">
         <v>2062</v>
@@ -41143,7 +41143,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1406" t="n">
         <v>1291</v>
@@ -41230,7 +41230,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1409" t="n">
         <v>4625</v>
@@ -41346,7 +41346,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1413" t="n">
         <v>2410</v>
@@ -41375,7 +41375,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1414" t="n">
         <v>31931</v>
@@ -41404,7 +41404,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1415" t="n">
         <v>13442</v>
@@ -41549,7 +41549,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1420" t="n">
         <v>2989</v>
@@ -41607,7 +41607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1422" t="n">
         <v>2861</v>
@@ -41636,7 +41636,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1423" t="n">
         <v>3892</v>
@@ -41752,7 +41752,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1427" t="n">
         <v>2872</v>
@@ -41781,7 +41781,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1428" t="n">
         <v>3471</v>
@@ -41810,7 +41810,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1429" t="n">
         <v>457</v>
@@ -41839,7 +41839,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1430" t="n">
         <v>4731</v>
@@ -41868,7 +41868,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1431" t="n">
         <v>1418</v>
@@ -41984,7 +41984,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1435" t="n">
         <v>1616</v>
@@ -42013,7 +42013,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1436" t="n">
         <v>3582</v>
@@ -42042,7 +42042,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1437" t="n">
         <v>2662</v>
@@ -42100,7 +42100,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1439" t="n">
         <v>198</v>
@@ -42129,7 +42129,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1440" t="n">
         <v>1144</v>
@@ -42245,7 +42245,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1444" t="n">
         <v>688</v>
@@ -42274,7 +42274,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1445" t="n">
         <v>1252</v>
@@ -42332,7 +42332,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1447" t="n">
         <v>4488</v>
@@ -42448,7 +42448,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1451" t="n">
         <v>2754</v>
@@ -42477,7 +42477,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1452" t="n">
         <v>793</v>
@@ -42535,7 +42535,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1454" t="n">
         <v>4612</v>
@@ -42622,7 +42622,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1457" t="n">
         <v>3819</v>
@@ -42709,7 +42709,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1460" t="n">
         <v>8292</v>
@@ -42796,7 +42796,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1463" t="n">
         <v>3283</v>
@@ -43028,7 +43028,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1471" t="n">
         <v>1571</v>
@@ -43260,7 +43260,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1479" t="n">
         <v>13</v>
@@ -43347,7 +43347,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1482" t="n">
         <v>5922</v>
@@ -43579,7 +43579,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1490" t="n">
         <v>3936</v>
@@ -43608,7 +43608,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1491" t="n">
         <v>9516</v>
@@ -43637,7 +43637,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1492" t="n">
         <v>12</v>
@@ -43695,7 +43695,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1494" t="n">
         <v>3670</v>
@@ -43782,7 +43782,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1497" t="n">
         <v>1307</v>
@@ -43811,7 +43811,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1498" t="n">
         <v>4115</v>
@@ -43956,7 +43956,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1503" t="n">
         <v>1545</v>
@@ -44043,7 +44043,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1506" t="n">
         <v>2072</v>
@@ -44072,7 +44072,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1507" t="n">
         <v>211</v>
@@ -44101,7 +44101,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1508" t="n">
         <v>907</v>
@@ -44275,7 +44275,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1514" t="n">
         <v>1628</v>
@@ -44333,7 +44333,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1516" t="n">
         <v>5585</v>
@@ -44420,7 +44420,7 @@
         <v>27</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1519" t="n">
         <v>3989</v>
@@ -44623,7 +44623,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>26.5112915039062</v>
+        <v>26.5112934112549</v>
       </c>
       <c r="H1526" t="n">
         <v>4380</v>
@@ -44826,7 +44826,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1533" t="n">
         <v>2355</v>
@@ -45029,7 +45029,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1540" t="n">
         <v>2838</v>
@@ -45174,7 +45174,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.6499118804932</v>
+        <v>25.6499137878418</v>
       </c>
       <c r="H1545" t="n">
         <v>3951</v>
@@ -45232,7 +45232,7 @@
         <v>25.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.4057025909424</v>
+        <v>24.4057006835938</v>
       </c>
       <c r="H1547" t="n">
         <v>2784</v>
@@ -45319,7 +45319,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7456226348877</v>
+        <v>25.7456207275391</v>
       </c>
       <c r="H1550" t="n">
         <v>919</v>
@@ -45377,7 +45377,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1552" t="n">
         <v>4472</v>
@@ -45435,7 +45435,7 @@
         <v>29</v>
       </c>
       <c r="G1554" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1554" t="n">
         <v>252</v>
@@ -45464,7 +45464,7 @@
         <v>29</v>
       </c>
       <c r="G1555" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1555" t="n">
         <v>2314</v>
@@ -45493,7 +45493,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1556" t="n">
         <v>3338</v>
@@ -45580,7 +45580,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1559" t="n">
         <v>612</v>
@@ -45725,7 +45725,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1564" t="n">
         <v>1292</v>
@@ -45899,7 +45899,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1570" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1570" t="n">
         <v>2272</v>
@@ -45928,7 +45928,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1571" t="n">
         <v>388</v>
@@ -56461,6 +56461,35 @@
         <v>2559</v>
       </c>
       <c r="I1934" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1935" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1935" t="n">
+        <v>44.2000007629395</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>45.2000007629395</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>44.2000007629395</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G1935" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="H1935" t="n">
+        <v>619</v>
+      </c>
+      <c r="I1935" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.28757762908936</v>
+        <v>9.28757858276367</v>
       </c>
       <c r="H2" t="n">
         <v>27300</v>
@@ -485,7 +485,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293647766113</v>
+        <v>9.88293743133545</v>
       </c>
       <c r="H4" t="n">
         <v>14100</v>
@@ -514,7 +514,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.76386642456055</v>
+        <v>9.76386547088623</v>
       </c>
       <c r="H5" t="n">
         <v>9000</v>
@@ -572,7 +572,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>9.67654609680176</v>
+        <v>9.67654705047607</v>
       </c>
       <c r="H7" t="n">
         <v>9900</v>
@@ -630,7 +630,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>9.23995304107666</v>
+        <v>9.23995113372803</v>
       </c>
       <c r="H9" t="n">
         <v>6000</v>
@@ -659,7 +659,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>9.39871406555176</v>
+        <v>9.39871215820312</v>
       </c>
       <c r="H10" t="n">
         <v>1050</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52572250366211</v>
+        <v>9.52572154998779</v>
       </c>
       <c r="H11" t="n">
         <v>1500</v>
@@ -833,7 +833,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>10.1607713699341</v>
+        <v>10.1607704162598</v>
       </c>
       <c r="H16" t="n">
         <v>4350</v>
@@ -862,7 +862,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4147882461548</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H17" t="n">
         <v>4650</v>
@@ -1065,7 +1065,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>10.1607713699341</v>
+        <v>10.1607704162598</v>
       </c>
       <c r="H24" t="n">
         <v>2100</v>
@@ -1123,7 +1123,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5259227752686</v>
+        <v>10.5259237289429</v>
       </c>
       <c r="H26" t="n">
         <v>3000</v>
@@ -1152,7 +1152,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3989152908325</v>
+        <v>10.3989143371582</v>
       </c>
       <c r="H27" t="n">
         <v>750</v>
@@ -1181,7 +1181,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G28" t="n">
-        <v>10.256028175354</v>
+        <v>10.2560262680054</v>
       </c>
       <c r="H28" t="n">
         <v>1650</v>
@@ -1210,7 +1210,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>10.5576772689819</v>
+        <v>10.5576763153076</v>
       </c>
       <c r="H29" t="n">
         <v>2100</v>
@@ -1239,7 +1239,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>10.5576772689819</v>
+        <v>10.5576763153076</v>
       </c>
       <c r="H30" t="n">
         <v>1200</v>
@@ -1297,7 +1297,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>10.4147882461548</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H32" t="n">
         <v>6450</v>
@@ -1326,7 +1326,7 @@
         <v>13.5</v>
       </c>
       <c r="G33" t="n">
-        <v>10.716438293457</v>
+        <v>10.7164363861084</v>
       </c>
       <c r="H33" t="n">
         <v>6300</v>
@@ -1355,7 +1355,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7005615234375</v>
+        <v>10.7005624771118</v>
       </c>
       <c r="H34" t="n">
         <v>9000</v>
@@ -1384,7 +1384,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>10.510046005249</v>
+        <v>10.5100469589233</v>
       </c>
       <c r="H35" t="n">
         <v>2550</v>
@@ -1413,7 +1413,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588312149048</v>
+        <v>11.0588321685791</v>
       </c>
       <c r="H36" t="n">
         <v>3900</v>
@@ -1442,7 +1442,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419792175293</v>
+        <v>11.1419801712036</v>
       </c>
       <c r="H37" t="n">
         <v>7050</v>
@@ -1500,7 +1500,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G39" t="n">
-        <v>10.842643737793</v>
+        <v>10.8426427841187</v>
       </c>
       <c r="H39" t="n">
         <v>14250</v>
@@ -1587,7 +1587,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H42" t="n">
         <v>3600</v>
@@ -1616,7 +1616,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G43" t="n">
-        <v>10.676344871521</v>
+        <v>10.6763458251953</v>
       </c>
       <c r="H43" t="n">
         <v>13050</v>
@@ -1645,7 +1645,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>10.676344871521</v>
+        <v>10.6763458251953</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="G45" t="n">
-        <v>10.809383392334</v>
+        <v>10.8093852996826</v>
       </c>
       <c r="H45" t="n">
         <v>14250</v>
@@ -1703,7 +1703,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G46" t="n">
-        <v>10.609827041626</v>
+        <v>10.6098279953003</v>
       </c>
       <c r="H46" t="n">
         <v>750</v>
@@ -1732,7 +1732,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G47" t="n">
-        <v>10.34375</v>
+        <v>10.3437490463257</v>
       </c>
       <c r="H47" t="n">
         <v>750</v>
@@ -1761,7 +1761,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H48" t="n">
         <v>7800</v>
@@ -1790,7 +1790,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H49" t="n">
         <v>3750</v>
@@ -1819,7 +1819,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G50" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H51" t="n">
         <v>600</v>
@@ -1877,7 +1877,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H52" t="n">
         <v>900</v>
@@ -1906,7 +1906,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H53" t="n">
         <v>6150</v>
@@ -1935,7 +1935,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G54" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H54" t="n">
         <v>2850</v>
@@ -1964,7 +1964,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G55" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H55" t="n">
         <v>900</v>
@@ -1993,7 +1993,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G56" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H56" t="n">
         <v>750</v>
@@ -2022,7 +2022,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G59" t="n">
-        <v>10.3271198272705</v>
+        <v>10.3271188735962</v>
       </c>
       <c r="H59" t="n">
         <v>300</v>
@@ -2109,7 +2109,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2138,7 +2138,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H61" t="n">
         <v>1650</v>
@@ -2167,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H62" t="n">
         <v>1950</v>
@@ -2196,7 +2196,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H63" t="n">
         <v>1800</v>
@@ -2225,7 +2225,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H64" t="n">
         <v>7950</v>
@@ -2254,7 +2254,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>9.84485340118408</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H65" t="n">
         <v>2850</v>
@@ -2341,7 +2341,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.47899723052979</v>
+        <v>9.47899913787842</v>
       </c>
       <c r="H68" t="n">
         <v>57450</v>
@@ -2428,7 +2428,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H71" t="n">
         <v>2400</v>
@@ -2457,7 +2457,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H72" t="n">
         <v>750</v>
@@ -2602,7 +2602,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G77" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H77" t="n">
         <v>1800</v>
@@ -2631,7 +2631,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G78" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H78" t="n">
         <v>2550</v>
@@ -2660,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2718,7 +2718,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G81" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H81" t="n">
         <v>600</v>
@@ -2747,7 +2747,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H82" t="n">
         <v>3900</v>
@@ -2805,7 +2805,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>9.67855548858643</v>
+        <v>9.67855644226074</v>
       </c>
       <c r="H84" t="n">
         <v>1350</v>
@@ -2834,7 +2834,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G85" t="n">
-        <v>9.67855548858643</v>
+        <v>9.67855644226074</v>
       </c>
       <c r="H85" t="n">
         <v>44700</v>
@@ -2863,7 +2863,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>9.49562835693359</v>
+        <v>9.49562740325928</v>
       </c>
       <c r="H86" t="n">
         <v>5550</v>
@@ -2892,7 +2892,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G87" t="n">
-        <v>9.49562835693359</v>
+        <v>9.49562740325928</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>11.5</v>
       </c>
       <c r="G88" t="n">
-        <v>9.56214618682861</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H88" t="n">
         <v>3000</v>
@@ -2950,7 +2950,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>9.71181583404541</v>
+        <v>9.71181488037109</v>
       </c>
       <c r="H89" t="n">
         <v>900</v>
@@ -3008,7 +3008,7 @@
         <v>11.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.56214618682861</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H91" t="n">
         <v>300</v>
@@ -3095,7 +3095,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H94" t="n">
         <v>1050</v>
@@ -3124,7 +3124,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H95" t="n">
         <v>2550</v>
@@ -3153,7 +3153,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.1441917419434</v>
+        <v>10.1441898345947</v>
       </c>
       <c r="H96" t="n">
         <v>1050</v>
@@ -3211,7 +3211,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G98" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H98" t="n">
         <v>2550</v>
@@ -3269,7 +3269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H100" t="n">
         <v>150</v>
@@ -3298,7 +3298,7 @@
         <v>12</v>
       </c>
       <c r="G101" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H101" t="n">
         <v>300</v>
@@ -3327,7 +3327,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H102" t="n">
         <v>3150</v>
@@ -3356,7 +3356,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G103" t="n">
-        <v>9.74507617950439</v>
+        <v>9.74507522583008</v>
       </c>
       <c r="H103" t="n">
         <v>150</v>
@@ -3385,7 +3385,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G104" t="n">
-        <v>9.74507617950439</v>
+        <v>9.74507522583008</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G107" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H107" t="n">
         <v>150</v>
@@ -3501,7 +3501,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G108" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529609680176</v>
+        <v>9.64529800415039</v>
       </c>
       <c r="H110" t="n">
         <v>450</v>
@@ -3588,7 +3588,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529609680176</v>
+        <v>9.64529800415039</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>12</v>
       </c>
       <c r="G113" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H113" t="n">
         <v>750</v>
@@ -3675,7 +3675,7 @@
         <v>12</v>
       </c>
       <c r="G114" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H114" t="n">
         <v>1200</v>
@@ -3704,7 +3704,7 @@
         <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G116" t="n">
-        <v>9.84485340118408</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H116" t="n">
         <v>450</v>
@@ -3762,7 +3762,7 @@
         <v>12</v>
       </c>
       <c r="G117" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H117" t="n">
         <v>1200</v>
@@ -3791,7 +3791,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G118" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H118" t="n">
         <v>1350</v>
@@ -3820,7 +3820,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G119" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H119" t="n">
         <v>1500</v>
@@ -3849,7 +3849,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G120" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H120" t="n">
         <v>300</v>
@@ -3878,7 +3878,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>10.1441917419434</v>
+        <v>10.1441898345947</v>
       </c>
       <c r="H121" t="n">
         <v>150</v>
@@ -3907,7 +3907,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G122" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H122" t="n">
         <v>600</v>
@@ -3936,7 +3936,7 @@
         <v>12</v>
       </c>
       <c r="G123" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H123" t="n">
         <v>900</v>
@@ -3965,7 +3965,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -3994,7 +3994,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G125" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H125" t="n">
         <v>1500</v>
@@ -4023,7 +4023,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H126" t="n">
         <v>750</v>
@@ -4052,7 +4052,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H127" t="n">
         <v>13050</v>
@@ -4110,7 +4110,7 @@
         <v>12.5</v>
       </c>
       <c r="G129" t="n">
-        <v>10.3936376571655</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H129" t="n">
         <v>7500</v>
@@ -4197,7 +4197,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>10.4601583480835</v>
+        <v>10.4601564407349</v>
       </c>
       <c r="H132" t="n">
         <v>450</v>
@@ -4226,7 +4226,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G133" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H133" t="n">
         <v>300</v>
@@ -4255,7 +4255,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>10.1441917419434</v>
+        <v>10.1441898345947</v>
       </c>
       <c r="H134" t="n">
         <v>750</v>
@@ -4284,7 +4284,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0277824401855</v>
+        <v>10.0277833938599</v>
       </c>
       <c r="H135" t="n">
         <v>2400</v>
@@ -4313,7 +4313,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G136" t="n">
-        <v>10.0444116592407</v>
+        <v>10.044412612915</v>
       </c>
       <c r="H136" t="n">
         <v>150</v>
@@ -4342,7 +4342,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>10.1441917419434</v>
+        <v>10.1441898345947</v>
       </c>
       <c r="H137" t="n">
         <v>300</v>
@@ -4371,7 +4371,7 @@
         <v>12</v>
       </c>
       <c r="G138" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H138" t="n">
         <v>600</v>
@@ -4516,7 +4516,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>10.0111532211304</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H143" t="n">
         <v>1200</v>
@@ -4545,7 +4545,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>10.0111532211304</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0111532211304</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G147" t="n">
-        <v>10.0111532211304</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H147" t="n">
         <v>1200</v>
@@ -4661,7 +4661,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H148" t="n">
         <v>750</v>
@@ -4690,7 +4690,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H154" t="n">
         <v>300</v>
@@ -4864,7 +4864,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G155" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H155" t="n">
         <v>150</v>
@@ -4893,7 +4893,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G156" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H158" t="n">
         <v>600</v>
@@ -4980,7 +4980,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H159" t="n">
         <v>15750</v>
@@ -5009,7 +5009,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G160" t="n">
-        <v>9.94463348388672</v>
+        <v>9.9446325302124</v>
       </c>
       <c r="H160" t="n">
         <v>12000</v>
@@ -5038,7 +5038,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G161" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H161" t="n">
         <v>300</v>
@@ -5067,7 +5067,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H162" t="n">
         <v>150</v>
@@ -5096,7 +5096,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H163" t="n">
         <v>16200</v>
@@ -5125,7 +5125,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G164" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H164" t="n">
         <v>2250</v>
@@ -5154,7 +5154,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>12.5</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3936376571655</v>
+        <v>10.3936386108398</v>
       </c>
       <c r="H166" t="n">
         <v>450</v>
@@ -5212,7 +5212,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H167" t="n">
         <v>1500</v>
@@ -5241,7 +5241,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>10.310489654541</v>
+        <v>10.3104887008667</v>
       </c>
       <c r="H168" t="n">
         <v>9300</v>
@@ -5270,7 +5270,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H169" t="n">
         <v>2400</v>
@@ -5299,7 +5299,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G170" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H170" t="n">
         <v>150</v>
@@ -5357,7 +5357,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H172" t="n">
         <v>150</v>
@@ -5386,7 +5386,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G173" t="n">
-        <v>10.0277824401855</v>
+        <v>10.0277833938599</v>
       </c>
       <c r="H173" t="n">
         <v>300</v>
@@ -5415,7 +5415,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>10.1441917419434</v>
+        <v>10.1441898345947</v>
       </c>
       <c r="H174" t="n">
         <v>1950</v>
@@ -5444,7 +5444,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G175" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H175" t="n">
         <v>450</v>
@@ -5473,7 +5473,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126174926758</v>
+        <v>9.96126365661621</v>
       </c>
       <c r="H176" t="n">
         <v>150</v>
@@ -5502,7 +5502,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H177" t="n">
         <v>9000</v>
@@ -5531,7 +5531,7 @@
         <v>12</v>
       </c>
       <c r="G178" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H178" t="n">
         <v>9300</v>
@@ -5560,7 +5560,7 @@
         <v>12</v>
       </c>
       <c r="G179" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H179" t="n">
         <v>4500</v>
@@ -5589,7 +5589,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H180" t="n">
         <v>2700</v>
@@ -5618,7 +5618,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G181" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H181" t="n">
         <v>900</v>
@@ -5647,7 +5647,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H182" t="n">
         <v>1350</v>
@@ -5676,7 +5676,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G183" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H183" t="n">
         <v>450</v>
@@ -5705,7 +5705,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G184" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H184" t="n">
         <v>750</v>
@@ -5734,7 +5734,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>12</v>
       </c>
       <c r="G186" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H186" t="n">
         <v>1350</v>
@@ -5792,7 +5792,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>9.89474391937256</v>
+        <v>9.89474296569824</v>
       </c>
       <c r="H187" t="n">
         <v>1050</v>
@@ -5821,7 +5821,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G188" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H188" t="n">
         <v>1050</v>
@@ -5850,7 +5850,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G189" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G191" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H191" t="n">
         <v>600</v>
@@ -5966,7 +5966,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H193" t="n">
         <v>150</v>
@@ -5995,7 +5995,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H194" t="n">
         <v>150</v>
@@ -6024,7 +6024,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G195" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G196" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H196" t="n">
         <v>450</v>
@@ -6082,7 +6082,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6140,7 +6140,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H199" t="n">
         <v>16800</v>
@@ -6169,7 +6169,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G200" t="n">
-        <v>10.0111532211304</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H200" t="n">
         <v>15150</v>
@@ -6198,7 +6198,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G201" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H201" t="n">
         <v>1350</v>
@@ -6227,7 +6227,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H202" t="n">
         <v>7050</v>
@@ -6256,7 +6256,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G203" t="n">
-        <v>10.0444116592407</v>
+        <v>10.044412612915</v>
       </c>
       <c r="H203" t="n">
         <v>5250</v>
@@ -6285,7 +6285,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>10.0444116592407</v>
+        <v>10.044412612915</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G205" t="n">
-        <v>9.84485340118408</v>
+        <v>9.8448543548584</v>
       </c>
       <c r="H205" t="n">
         <v>750</v>
@@ -6343,7 +6343,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H206" t="n">
         <v>450</v>
@@ -6372,7 +6372,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H207" t="n">
         <v>900</v>
@@ -6401,7 +6401,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H208" t="n">
         <v>1200</v>
@@ -6459,7 +6459,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>10.0776720046997</v>
+        <v>10.0776710510254</v>
       </c>
       <c r="H210" t="n">
         <v>150</v>
@@ -6488,7 +6488,7 @@
         <v>12</v>
       </c>
       <c r="G211" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H211" t="n">
         <v>1650</v>
@@ -6517,7 +6517,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>12</v>
       </c>
       <c r="G213" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H213" t="n">
         <v>1200</v>
@@ -6575,7 +6575,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H214" t="n">
         <v>1350</v>
@@ -6604,7 +6604,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G215" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H215" t="n">
         <v>3300</v>
@@ -6633,7 +6633,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.1441917419434</v>
+        <v>10.1441898345947</v>
       </c>
       <c r="H216" t="n">
         <v>2550</v>
@@ -6662,7 +6662,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G217" t="n">
-        <v>10.34375</v>
+        <v>10.3437490463257</v>
       </c>
       <c r="H217" t="n">
         <v>12900</v>
@@ -6691,7 +6691,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2107105255127</v>
+        <v>10.2107095718384</v>
       </c>
       <c r="H218" t="n">
         <v>7950</v>
@@ -6720,7 +6720,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H219" t="n">
         <v>900</v>
@@ -6749,7 +6749,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H220" t="n">
         <v>16950</v>
@@ -6778,7 +6778,7 @@
         <v>12</v>
       </c>
       <c r="G221" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H221" t="n">
         <v>600</v>
@@ -6807,7 +6807,7 @@
         <v>12</v>
       </c>
       <c r="G222" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H224" t="n">
         <v>1800</v>
@@ -6894,7 +6894,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>12</v>
       </c>
       <c r="G226" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>10.1608219146729</v>
+        <v>10.1608209609985</v>
       </c>
       <c r="H227" t="n">
         <v>450</v>
@@ -6981,7 +6981,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G228" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H228" t="n">
         <v>2850</v>
@@ -7010,7 +7010,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603792190552</v>
+        <v>10.3603782653809</v>
       </c>
       <c r="H229" t="n">
         <v>2400</v>
@@ -7039,7 +7039,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="n">
-        <v>9.97789192199707</v>
+        <v>9.97789287567139</v>
       </c>
       <c r="H230" t="n">
         <v>1650</v>
@@ -7068,7 +7068,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G231" t="n">
-        <v>10.0111532211304</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H231" t="n">
         <v>600</v>
@@ -7097,7 +7097,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H232" t="n">
         <v>2250</v>
@@ -7126,7 +7126,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.2273406982422</v>
+        <v>10.2273416519165</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G234" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H234" t="n">
         <v>900</v>
@@ -7184,7 +7184,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G235" t="n">
-        <v>9.99452304840088</v>
+        <v>9.9945240020752</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G236" t="n">
-        <v>10.0111532211304</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H236" t="n">
         <v>750</v>
@@ -7242,7 +7242,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H237" t="n">
         <v>3000</v>
@@ -7271,7 +7271,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2606000900269</v>
+        <v>10.2605991363525</v>
       </c>
       <c r="H238" t="n">
         <v>1350</v>
@@ -7300,7 +7300,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610418319702</v>
+        <v>10.0610408782959</v>
       </c>
       <c r="H239" t="n">
         <v>2850</v>
@@ -7329,7 +7329,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0943021774292</v>
+        <v>10.0943031311035</v>
       </c>
       <c r="H240" t="n">
         <v>1800</v>
@@ -7358,7 +7358,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G241" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H241" t="n">
         <v>7800</v>
@@ -7387,7 +7387,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G242" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87811470031738</v>
+        <v>9.87811374664307</v>
       </c>
       <c r="H243" t="n">
         <v>600</v>
@@ -7503,7 +7503,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.17966270446777</v>
+        <v>9.17966175079346</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41247844696045</v>
       </c>
       <c r="H247" t="n">
         <v>300</v>
@@ -7561,7 +7561,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>9.41247940063477</v>
+        <v>9.41247844696045</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>11.5</v>
       </c>
       <c r="G249" t="n">
-        <v>9.56214618682861</v>
+        <v>9.56214714050293</v>
       </c>
       <c r="H249" t="n">
         <v>3300</v>
@@ -7619,7 +7619,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.11314392089844</v>
+        <v>9.1131420135498</v>
       </c>
       <c r="H250" t="n">
         <v>2250</v>
@@ -7648,7 +7648,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>8.664137840271</v>
+        <v>8.66413688659668</v>
       </c>
       <c r="H251" t="n">
         <v>4200</v>
@@ -7706,7 +7706,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>8.44794845581055</v>
+        <v>8.44794940948486</v>
       </c>
       <c r="H253" t="n">
         <v>150</v>
@@ -7735,7 +7735,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G254" t="n">
-        <v>8.13198280334473</v>
+        <v>8.13198184967041</v>
       </c>
       <c r="H254" t="n">
         <v>750</v>
@@ -7822,7 +7822,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.1486120223999</v>
+        <v>8.14861392974854</v>
       </c>
       <c r="H257" t="n">
         <v>450</v>
@@ -7851,7 +7851,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.1486120223999</v>
+        <v>8.14861392974854</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568441390991</v>
+        <v>7.96568489074707</v>
       </c>
       <c r="H259" t="n">
         <v>3600</v>
@@ -7909,7 +7909,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>8.03220367431641</v>
+        <v>8.03220272064209</v>
       </c>
       <c r="H260" t="n">
         <v>5400</v>
@@ -7938,7 +7938,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>8.03220367431641</v>
+        <v>8.03220272064209</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>10</v>
       </c>
       <c r="G262" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491184234619</v>
       </c>
       <c r="H262" t="n">
         <v>1950</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491184234619</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>10</v>
       </c>
       <c r="G264" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491184234619</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>8.31490993499756</v>
+        <v>8.31491184234619</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H266" t="n">
         <v>450</v>
@@ -8112,7 +8112,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G271" t="n">
-        <v>8.3980598449707</v>
+        <v>8.39806079864502</v>
       </c>
       <c r="H271" t="n">
         <v>1500</v>
@@ -8402,7 +8402,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>8.27333641052246</v>
+        <v>8.27333545684814</v>
       </c>
       <c r="H277" t="n">
         <v>1800</v>
@@ -8460,7 +8460,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640235900879</v>
       </c>
       <c r="H279" t="n">
         <v>19950</v>
@@ -8489,7 +8489,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640140533447</v>
+        <v>9.14640235900879</v>
       </c>
       <c r="H280" t="n">
         <v>1350</v>
@@ -8605,7 +8605,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>9.36392879486084</v>
+        <v>9.36392974853516</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.19211483001709</v>
+        <v>9.19211578369141</v>
       </c>
       <c r="H285" t="n">
         <v>2700</v>
@@ -8663,7 +8663,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H286" t="n">
         <v>3750</v>
@@ -8692,7 +8692,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H288" t="n">
         <v>300</v>
@@ -8750,7 +8750,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H292" t="n">
         <v>2250</v>
@@ -8895,7 +8895,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>9.1062068939209</v>
+        <v>9.10620594024658</v>
       </c>
       <c r="H294" t="n">
         <v>1050</v>
@@ -8924,7 +8924,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H295" t="n">
         <v>1050</v>
@@ -8953,7 +8953,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H296" t="n">
         <v>750</v>
@@ -8982,7 +8982,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G298" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H298" t="n">
         <v>300</v>
@@ -9040,7 +9040,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H300" t="n">
         <v>4350</v>
@@ -9098,7 +9098,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H312" t="n">
         <v>750</v>
@@ -9533,7 +9533,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G316" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9591,7 +9591,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H318" t="n">
         <v>1050</v>
@@ -9765,7 +9765,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>8.33303737640381</v>
+        <v>8.33303833007812</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.33303737640381</v>
+        <v>8.33303833007812</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>8.33303737640381</v>
+        <v>8.33303833007812</v>
       </c>
       <c r="H326" t="n">
         <v>2250</v>
@@ -9852,7 +9852,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.4189453125</v>
+        <v>8.41894626617432</v>
       </c>
       <c r="H327" t="n">
         <v>8100</v>
@@ -9939,7 +9939,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H330" t="n">
         <v>300</v>
@@ -9968,7 +9968,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G335" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H335" t="n">
         <v>150</v>
@@ -10113,7 +10113,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H336" t="n">
         <v>300</v>
@@ -10142,7 +10142,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10171,7 +10171,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H338" t="n">
         <v>1350</v>
@@ -10200,7 +10200,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H339" t="n">
         <v>450</v>
@@ -10229,7 +10229,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H350" t="n">
         <v>900</v>
@@ -10693,7 +10693,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>8.46189880371094</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H356" t="n">
         <v>1950</v>
@@ -10809,7 +10809,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G360" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H360" t="n">
         <v>1950</v>
@@ -10838,7 +10838,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H361" t="n">
         <v>150</v>
@@ -10867,7 +10867,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G362" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G363" t="n">
-        <v>8.4189453125</v>
+        <v>8.41894626617432</v>
       </c>
       <c r="H363" t="n">
         <v>150</v>
@@ -10925,7 +10925,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.4189453125</v>
+        <v>8.41894626617432</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.4189453125</v>
+        <v>8.41894626617432</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.4189453125</v>
+        <v>8.41894626617432</v>
       </c>
       <c r="H366" t="n">
         <v>300</v>
@@ -11012,7 +11012,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.4189453125</v>
+        <v>8.41894626617432</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>8.4189453125</v>
+        <v>8.41894626617432</v>
       </c>
       <c r="H368" t="n">
         <v>150</v>
@@ -11070,7 +11070,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H369" t="n">
         <v>750</v>
@@ -11244,7 +11244,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.20417785644531</v>
+        <v>8.204176902771</v>
       </c>
       <c r="H375" t="n">
         <v>1950</v>
@@ -11302,7 +11302,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H377" t="n">
         <v>2550</v>
@@ -11331,7 +11331,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H378" t="n">
         <v>4200</v>
@@ -11418,7 +11418,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H381" t="n">
         <v>1500</v>
@@ -11447,7 +11447,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H384" t="n">
         <v>2850</v>
@@ -11534,7 +11534,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H401" t="n">
         <v>1800</v>
@@ -12027,7 +12027,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H406" t="n">
         <v>1050</v>
@@ -12172,7 +12172,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G410" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H410" t="n">
         <v>450</v>
@@ -12288,7 +12288,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>8.54780769348145</v>
+        <v>8.54780673980713</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H413" t="n">
         <v>5400</v>
@@ -12375,7 +12375,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H414" t="n">
         <v>150</v>
@@ -12404,7 +12404,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>8.4189453125</v>
+        <v>8.41894626617432</v>
       </c>
       <c r="H415" t="n">
         <v>2400</v>
@@ -12433,7 +12433,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H416" t="n">
         <v>600</v>
@@ -12462,7 +12462,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H418" t="n">
         <v>450</v>
@@ -12520,7 +12520,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>8.67666912078857</v>
+        <v>8.67666816711426</v>
       </c>
       <c r="H421" t="n">
         <v>750</v>
@@ -12752,7 +12752,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>8.93439102172852</v>
+        <v>8.9343900680542</v>
       </c>
       <c r="H427" t="n">
         <v>450</v>
@@ -12781,7 +12781,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.19211483001709</v>
+        <v>9.19211578369141</v>
       </c>
       <c r="H428" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>9.1062068939209</v>
+        <v>9.10620594024658</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>9.36392879486084</v>
+        <v>9.36392974853516</v>
       </c>
       <c r="H430" t="n">
         <v>450</v>
@@ -12868,7 +12868,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19211483001709</v>
+        <v>9.19211578369141</v>
       </c>
       <c r="H431" t="n">
         <v>300</v>
@@ -12897,7 +12897,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>9.19211483001709</v>
+        <v>9.19211578369141</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>9.27802181243896</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H433" t="n">
         <v>5700</v>
@@ -12955,7 +12955,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G434" t="n">
-        <v>9.27802181243896</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H434" t="n">
         <v>3750</v>
@@ -12984,7 +12984,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>9.27802181243896</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H435" t="n">
         <v>6750</v>
@@ -13013,7 +13013,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G436" t="n">
-        <v>9.27802181243896</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H436" t="n">
         <v>900</v>
@@ -13042,7 +13042,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>9.27802181243896</v>
+        <v>9.27802276611328</v>
       </c>
       <c r="H437" t="n">
         <v>1650</v>
@@ -13071,7 +13071,7 @@
         <v>11.5</v>
       </c>
       <c r="G438" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H438" t="n">
         <v>1350</v>
@@ -13100,7 +13100,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G439" t="n">
-        <v>9.79346752166748</v>
+        <v>9.79346656799316</v>
       </c>
       <c r="H439" t="n">
         <v>8400</v>
@@ -13158,7 +13158,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.70755958557129</v>
+        <v>9.70756053924561</v>
       </c>
       <c r="H441" t="n">
         <v>750</v>
@@ -13187,7 +13187,7 @@
         <v>11.5</v>
       </c>
       <c r="G442" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H442" t="n">
         <v>300</v>
@@ -13216,7 +13216,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>10.2230062484741</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H443" t="n">
         <v>11400</v>
@@ -13245,7 +13245,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>10.2230062484741</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H444" t="n">
         <v>6150</v>
@@ -13274,7 +13274,7 @@
         <v>12</v>
       </c>
       <c r="G445" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H445" t="n">
         <v>3600</v>
@@ -13303,7 +13303,7 @@
         <v>12</v>
       </c>
       <c r="G446" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>12</v>
       </c>
       <c r="G447" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H447" t="n">
         <v>900</v>
@@ -13361,7 +13361,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>10.4807271957397</v>
+        <v>10.4807291030884</v>
       </c>
       <c r="H448" t="n">
         <v>600</v>
@@ -13390,7 +13390,7 @@
         <v>12</v>
       </c>
       <c r="G449" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H449" t="n">
         <v>600</v>
@@ -13419,7 +13419,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>10.2230062484741</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H450" t="n">
         <v>300</v>
@@ -13477,7 +13477,7 @@
         <v>12</v>
       </c>
       <c r="G452" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H452" t="n">
         <v>1950</v>
@@ -13506,7 +13506,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H453" t="n">
         <v>4050</v>
@@ -13535,7 +13535,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H455" t="n">
         <v>450</v>
@@ -13593,7 +13593,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H456" t="n">
         <v>5400</v>
@@ -13622,7 +13622,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G457" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H457" t="n">
         <v>17250</v>
@@ -13651,7 +13651,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H458" t="n">
         <v>1350</v>
@@ -13680,7 +13680,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>9.70755958557129</v>
+        <v>9.70756053924561</v>
       </c>
       <c r="H459" t="n">
         <v>4650</v>
@@ -13709,7 +13709,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G460" t="n">
-        <v>9.70755958557129</v>
+        <v>9.70756053924561</v>
       </c>
       <c r="H460" t="n">
         <v>1950</v>
@@ -13796,7 +13796,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H463" t="n">
         <v>600</v>
@@ -13825,7 +13825,7 @@
         <v>11.5</v>
       </c>
       <c r="G464" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H464" t="n">
         <v>750</v>
@@ -13883,7 +13883,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G466" t="n">
-        <v>9.70755958557129</v>
+        <v>9.70756053924561</v>
       </c>
       <c r="H466" t="n">
         <v>3450</v>
@@ -13912,7 +13912,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H467" t="n">
         <v>13050</v>
@@ -13941,7 +13941,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H468" t="n">
         <v>3900</v>
@@ -13970,7 +13970,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>10.4807271957397</v>
+        <v>10.4807291030884</v>
       </c>
       <c r="H469" t="n">
         <v>7500</v>
@@ -14057,7 +14057,7 @@
         <v>12</v>
       </c>
       <c r="G472" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H472" t="n">
         <v>67350</v>
@@ -14115,7 +14115,7 @@
         <v>12</v>
       </c>
       <c r="G474" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H474" t="n">
         <v>20100</v>
@@ -14144,7 +14144,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H475" t="n">
         <v>150</v>
@@ -14202,7 +14202,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G477" t="n">
-        <v>10.1370973587036</v>
+        <v>10.1370964050293</v>
       </c>
       <c r="H477" t="n">
         <v>600</v>
@@ -14231,7 +14231,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0511903762817</v>
+        <v>10.0511913299561</v>
       </c>
       <c r="H478" t="n">
         <v>1500</v>
@@ -14260,7 +14260,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0511903762817</v>
+        <v>10.0511913299561</v>
       </c>
       <c r="H479" t="n">
         <v>600</v>
@@ -14289,7 +14289,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2230062484741</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H480" t="n">
         <v>1500</v>
@@ -14318,7 +14318,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2230062484741</v>
+        <v>10.2230052947998</v>
       </c>
       <c r="H481" t="n">
         <v>150</v>
@@ -14347,7 +14347,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>10.4807271957397</v>
+        <v>10.4807291030884</v>
       </c>
       <c r="H482" t="n">
         <v>26700</v>
@@ -14376,7 +14376,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="n">
-        <v>10.308913230896</v>
+        <v>10.3089141845703</v>
       </c>
       <c r="H483" t="n">
         <v>2250</v>
@@ -14434,7 +14434,7 @@
         <v>12.5</v>
       </c>
       <c r="G485" t="n">
-        <v>10.7384519577026</v>
+        <v>10.7384510040283</v>
       </c>
       <c r="H485" t="n">
         <v>15600</v>
@@ -14463,7 +14463,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>10.7384519577026</v>
+        <v>10.7384510040283</v>
       </c>
       <c r="H486" t="n">
         <v>5100</v>
@@ -14579,7 +14579,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H490" t="n">
         <v>6450</v>
@@ -14608,7 +14608,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H491" t="n">
         <v>6450</v>
@@ -14637,7 +14637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H492" t="n">
         <v>5100</v>
@@ -14666,7 +14666,7 @@
         <v>13</v>
       </c>
       <c r="G493" t="n">
-        <v>11.1679887771606</v>
+        <v>11.167989730835</v>
       </c>
       <c r="H493" t="n">
         <v>36300</v>
@@ -14695,7 +14695,7 @@
         <v>13</v>
       </c>
       <c r="G494" t="n">
-        <v>11.1679887771606</v>
+        <v>11.167989730835</v>
       </c>
       <c r="H494" t="n">
         <v>7050</v>
@@ -14724,7 +14724,7 @@
         <v>13</v>
       </c>
       <c r="G495" t="n">
-        <v>11.1679887771606</v>
+        <v>11.167989730835</v>
       </c>
       <c r="H495" t="n">
         <v>20850</v>
@@ -14782,7 +14782,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>11.5116205215454</v>
+        <v>11.5116195678711</v>
       </c>
       <c r="H497" t="n">
         <v>6600</v>
@@ -14840,7 +14840,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.4257116317749</v>
+        <v>11.4257135391235</v>
       </c>
       <c r="H499" t="n">
         <v>750</v>
@@ -14985,7 +14985,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>12.3706960678101</v>
+        <v>12.3706951141357</v>
       </c>
       <c r="H504" t="n">
         <v>6900</v>
@@ -15014,7 +15014,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>12.6284170150757</v>
+        <v>12.6284189224243</v>
       </c>
       <c r="H505" t="n">
         <v>2400</v>
@@ -15304,7 +15304,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.8311252593994</v>
+        <v>13.8311262130737</v>
       </c>
       <c r="H515" t="n">
         <v>23250</v>
@@ -15333,7 +15333,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>13.9170331954956</v>
+        <v>13.9170341491699</v>
       </c>
       <c r="H516" t="n">
         <v>13350</v>
@@ -15362,7 +15362,7 @@
         <v>16</v>
       </c>
       <c r="G517" t="n">
-        <v>13.7452173233032</v>
+        <v>13.7452182769775</v>
       </c>
       <c r="H517" t="n">
         <v>17250</v>
@@ -15391,7 +15391,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>13.487494468689</v>
+        <v>13.4874963760376</v>
       </c>
       <c r="H518" t="n">
         <v>6600</v>
@@ -15478,7 +15478,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324760437012</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H521" t="n">
         <v>58800</v>
@@ -15536,7 +15536,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>13.8311252593994</v>
+        <v>13.8311262130737</v>
       </c>
       <c r="H523" t="n">
         <v>10950</v>
@@ -15594,7 +15594,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>14.0029401779175</v>
+        <v>14.0029392242432</v>
       </c>
       <c r="H525" t="n">
         <v>33900</v>
@@ -15623,7 +15623,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>14.3465719223022</v>
+        <v>14.3465700149536</v>
       </c>
       <c r="H526" t="n">
         <v>6750</v>
@@ -15652,7 +15652,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324760437012</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H527" t="n">
         <v>40350</v>
@@ -15681,7 +15681,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042938232422</v>
+        <v>14.6042947769165</v>
       </c>
       <c r="H528" t="n">
         <v>25200</v>
@@ -15710,7 +15710,7 @@
         <v>18</v>
       </c>
       <c r="G529" t="n">
-        <v>15.4633693695068</v>
+        <v>15.4633703231812</v>
       </c>
       <c r="H529" t="n">
         <v>8700</v>
@@ -15739,7 +15739,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>15.2915515899658</v>
+        <v>15.2915534973145</v>
       </c>
       <c r="H530" t="n">
         <v>3450</v>
@@ -15768,7 +15768,7 @@
         <v>18</v>
       </c>
       <c r="G531" t="n">
-        <v>15.4633693695068</v>
+        <v>15.4633703231812</v>
       </c>
       <c r="H531" t="n">
         <v>3900</v>
@@ -15797,7 +15797,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056484222412</v>
+        <v>15.2056465148926</v>
       </c>
       <c r="H532" t="n">
         <v>8550</v>
@@ -15826,7 +15826,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>15.1197376251221</v>
+        <v>15.1197385787964</v>
       </c>
       <c r="H533" t="n">
         <v>4500</v>
@@ -15855,7 +15855,7 @@
         <v>18</v>
       </c>
       <c r="G534" t="n">
-        <v>15.4633693695068</v>
+        <v>15.4633703231812</v>
       </c>
       <c r="H534" t="n">
         <v>20100</v>
@@ -15884,7 +15884,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="n">
-        <v>15.4633693695068</v>
+        <v>15.4633703231812</v>
       </c>
       <c r="H535" t="n">
         <v>15300</v>
@@ -15913,7 +15913,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.5492792129517</v>
+        <v>15.549277305603</v>
       </c>
       <c r="H536" t="n">
         <v>3000</v>
@@ -15942,7 +15942,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>15.7259712219238</v>
+        <v>15.7259750366211</v>
       </c>
       <c r="H537" t="n">
         <v>7800</v>
@@ -15971,7 +15971,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376266479492</v>
+        <v>15.6376256942749</v>
       </c>
       <c r="H538" t="n">
         <v>2250</v>
@@ -16000,7 +16000,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>15.7259712219238</v>
+        <v>15.7259750366211</v>
       </c>
       <c r="H539" t="n">
         <v>4800</v>
@@ -16058,7 +16058,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G541" t="n">
-        <v>15.1958866119385</v>
+        <v>15.1958875656128</v>
       </c>
       <c r="H541" t="n">
         <v>3300</v>
@@ -16087,7 +16087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>15.7259712219238</v>
+        <v>15.7259750366211</v>
       </c>
       <c r="H542" t="n">
         <v>3750</v>
@@ -16116,7 +16116,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.5492753982544</v>
+        <v>15.549277305603</v>
       </c>
       <c r="H543" t="n">
         <v>3600</v>
@@ -16145,7 +16145,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>15.8143224716187</v>
+        <v>15.8143215179443</v>
       </c>
       <c r="H544" t="n">
         <v>600</v>
@@ -16203,7 +16203,7 @@
         <v>18</v>
       </c>
       <c r="G546" t="n">
-        <v>15.9026699066162</v>
+        <v>15.9026689529419</v>
       </c>
       <c r="H546" t="n">
         <v>3150</v>
@@ -16261,7 +16261,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>16.4327602386475</v>
+        <v>16.4327583312988</v>
       </c>
       <c r="H548" t="n">
         <v>5700</v>
@@ -16493,7 +16493,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>16.4327602386475</v>
+        <v>16.4327583312988</v>
       </c>
       <c r="H556" t="n">
         <v>3900</v>
@@ -16580,7 +16580,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230236053467</v>
       </c>
       <c r="H559" t="n">
         <v>15150</v>
@@ -16638,7 +16638,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G561" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230236053467</v>
       </c>
       <c r="H561" t="n">
         <v>3450</v>
@@ -16667,7 +16667,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>19.0832023620605</v>
+        <v>19.0832042694092</v>
       </c>
       <c r="H562" t="n">
         <v>10050</v>
@@ -16696,7 +16696,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>19.9666843414307</v>
+        <v>19.9666862487793</v>
       </c>
       <c r="H563" t="n">
         <v>31500</v>
@@ -16725,7 +16725,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>19.9666843414307</v>
+        <v>19.9666862487793</v>
       </c>
       <c r="H564" t="n">
         <v>4200</v>
@@ -16812,7 +16812,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G567" t="n">
-        <v>18.7298126220703</v>
+        <v>18.7298107147217</v>
       </c>
       <c r="H567" t="n">
         <v>9150</v>
@@ -16841,7 +16841,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230236053467</v>
       </c>
       <c r="H568" t="n">
         <v>9600</v>
@@ -16986,7 +16986,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>18.0230255126953</v>
+        <v>18.0230236053467</v>
       </c>
       <c r="H573" t="n">
         <v>8325</v>
@@ -17015,7 +17015,7 @@
         <v>20</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6696338653564</v>
+        <v>17.6696357727051</v>
       </c>
       <c r="H574" t="n">
         <v>5250</v>
@@ -17044,7 +17044,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278938293457</v>
+        <v>17.2278919219971</v>
       </c>
       <c r="H575" t="n">
         <v>2250</v>
@@ -17073,7 +17073,7 @@
         <v>19</v>
       </c>
       <c r="G576" t="n">
-        <v>16.7861518859863</v>
+        <v>16.7861499786377</v>
       </c>
       <c r="H576" t="n">
         <v>14175</v>
@@ -17160,7 +17160,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>17.051197052002</v>
+        <v>17.0511951446533</v>
       </c>
       <c r="H579" t="n">
         <v>1650</v>
@@ -17218,7 +17218,7 @@
         <v>19</v>
       </c>
       <c r="G581" t="n">
-        <v>16.7861518859863</v>
+        <v>16.7861499786377</v>
       </c>
       <c r="H581" t="n">
         <v>8400</v>
@@ -17247,7 +17247,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>17.051197052002</v>
+        <v>17.0511951446533</v>
       </c>
       <c r="H582" t="n">
         <v>12225</v>
@@ -17305,7 +17305,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>17.6696338653564</v>
+        <v>17.6696357727051</v>
       </c>
       <c r="H584" t="n">
         <v>1050</v>
@@ -17392,7 +17392,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>18.7298126220703</v>
+        <v>18.7298107147217</v>
       </c>
       <c r="H587" t="n">
         <v>16275</v>
@@ -17566,7 +17566,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>18.7298126220703</v>
+        <v>18.7298107147217</v>
       </c>
       <c r="H593" t="n">
         <v>1500</v>
@@ -17595,7 +17595,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>18.9065074920654</v>
+        <v>18.9065093994141</v>
       </c>
       <c r="H594" t="n">
         <v>9375</v>
@@ -17624,7 +17624,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>22.7938251495361</v>
+        <v>22.7938270568848</v>
       </c>
       <c r="H595" t="n">
         <v>9525</v>
@@ -17653,7 +17653,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>20.673469543457</v>
+        <v>20.6734714508057</v>
       </c>
       <c r="H596" t="n">
         <v>39600</v>
@@ -17682,7 +17682,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H597" t="n">
         <v>13125</v>
@@ -17711,7 +17711,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>19.2598972320557</v>
+        <v>19.2598991394043</v>
       </c>
       <c r="H598" t="n">
         <v>41625</v>
@@ -17740,7 +17740,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G599" t="n">
-        <v>19.2598972320557</v>
+        <v>19.2598991394043</v>
       </c>
       <c r="H599" t="n">
         <v>9225</v>
@@ -17769,7 +17769,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>19.2598972320557</v>
+        <v>19.2598991394043</v>
       </c>
       <c r="H600" t="n">
         <v>18750</v>
@@ -17885,7 +17885,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H604" t="n">
         <v>19650</v>
@@ -17914,7 +17914,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H605" t="n">
         <v>10425</v>
@@ -17943,7 +17943,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G606" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H606" t="n">
         <v>10050</v>
@@ -17972,7 +17972,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H607" t="n">
         <v>5250</v>
@@ -18001,7 +18001,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G608" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H608" t="n">
         <v>12750</v>
@@ -18030,7 +18030,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H609" t="n">
         <v>13500</v>
@@ -18059,7 +18059,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>22.2637386322021</v>
+        <v>22.2637405395508</v>
       </c>
       <c r="H610" t="n">
         <v>10275</v>
@@ -18088,7 +18088,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>22.7938251495361</v>
+        <v>22.7938270568848</v>
       </c>
       <c r="H611" t="n">
         <v>7125</v>
@@ -18117,7 +18117,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>22.7938251495361</v>
+        <v>22.7938270568848</v>
       </c>
       <c r="H612" t="n">
         <v>7575</v>
@@ -18146,7 +18146,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006141662598</v>
       </c>
       <c r="H613" t="n">
         <v>11775</v>
@@ -18175,7 +18175,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>23.6773090362549</v>
+        <v>23.6773071289062</v>
       </c>
       <c r="H614" t="n">
         <v>5175</v>
@@ -18204,7 +18204,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>24.2073993682861</v>
+        <v>24.2073974609375</v>
       </c>
       <c r="H615" t="n">
         <v>7875</v>
@@ -18262,7 +18262,7 @@
         <v>27</v>
       </c>
       <c r="G617" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H617" t="n">
         <v>11850</v>
@@ -18349,7 +18349,7 @@
         <v>26</v>
       </c>
       <c r="G620" t="n">
-        <v>22.9705219268799</v>
+        <v>22.9705238342285</v>
       </c>
       <c r="H620" t="n">
         <v>4800</v>
@@ -18407,7 +18407,7 @@
         <v>27</v>
       </c>
       <c r="G622" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H622" t="n">
         <v>7575</v>
@@ -18465,7 +18465,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H624" t="n">
         <v>6075</v>
@@ -18494,7 +18494,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H625" t="n">
         <v>17550</v>
@@ -18552,7 +18552,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>28.4481105804443</v>
+        <v>28.448112487793</v>
       </c>
       <c r="H627" t="n">
         <v>16800</v>
@@ -18581,7 +18581,7 @@
         <v>32</v>
       </c>
       <c r="G628" t="n">
-        <v>28.2714138031006</v>
+        <v>28.271411895752</v>
       </c>
       <c r="H628" t="n">
         <v>13350</v>
@@ -18610,7 +18610,7 @@
         <v>32</v>
       </c>
       <c r="G629" t="n">
-        <v>28.2714138031006</v>
+        <v>28.271411895752</v>
       </c>
       <c r="H629" t="n">
         <v>15375</v>
@@ -18639,7 +18639,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>28.0947189331055</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H630" t="n">
         <v>11250</v>
@@ -18668,7 +18668,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H631" t="n">
         <v>11700</v>
@@ -18697,7 +18697,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>30.7451648712158</v>
+        <v>30.7451610565186</v>
       </c>
       <c r="H632" t="n">
         <v>23025</v>
@@ -18755,7 +18755,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0985507965088</v>
+        <v>31.0985546112061</v>
       </c>
       <c r="H634" t="n">
         <v>8625</v>
@@ -18784,7 +18784,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.5684642791748</v>
+        <v>30.5684604644775</v>
       </c>
       <c r="H635" t="n">
         <v>3900</v>
@@ -18813,7 +18813,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>30.5684642791748</v>
+        <v>30.5684604644775</v>
       </c>
       <c r="H636" t="n">
         <v>21300</v>
@@ -18842,7 +18842,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>30.7451648712158</v>
+        <v>30.7451610565186</v>
       </c>
       <c r="H637" t="n">
         <v>1725</v>
@@ -18871,7 +18871,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G638" t="n">
-        <v>30.391773223877</v>
+        <v>30.3917751312256</v>
       </c>
       <c r="H638" t="n">
         <v>20325</v>
@@ -18929,7 +18929,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082893371582</v>
+        <v>29.5082874298096</v>
       </c>
       <c r="H640" t="n">
         <v>11100</v>
@@ -19016,7 +19016,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>28.4481105804443</v>
+        <v>28.448112487793</v>
       </c>
       <c r="H643" t="n">
         <v>2100</v>
@@ -19074,7 +19074,7 @@
         <v>32</v>
       </c>
       <c r="G645" t="n">
-        <v>28.2714138031006</v>
+        <v>28.271411895752</v>
       </c>
       <c r="H645" t="n">
         <v>9750</v>
@@ -19103,7 +19103,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.0947189331055</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H646" t="n">
         <v>10950</v>
@@ -19219,7 +19219,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>24.2073993682861</v>
+        <v>24.2073974609375</v>
       </c>
       <c r="H650" t="n">
         <v>15450</v>
@@ -19248,7 +19248,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H651" t="n">
         <v>10050</v>
@@ -19277,7 +19277,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H652" t="n">
         <v>5025</v>
@@ -19335,7 +19335,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H654" t="n">
         <v>6300</v>
@@ -19393,7 +19393,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H656" t="n">
         <v>5550</v>
@@ -19422,7 +19422,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H657" t="n">
         <v>2325</v>
@@ -19538,7 +19538,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H661" t="n">
         <v>7575</v>
@@ -19596,7 +19596,7 @@
         <v>33</v>
       </c>
       <c r="G663" t="n">
-        <v>29.1548957824707</v>
+        <v>29.1548976898193</v>
       </c>
       <c r="H663" t="n">
         <v>5700</v>
@@ -19741,7 +19741,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H668" t="n">
         <v>5550</v>
@@ -19915,7 +19915,7 @@
         <v>33</v>
       </c>
       <c r="G674" t="n">
-        <v>29.1548957824707</v>
+        <v>29.1548976898193</v>
       </c>
       <c r="H674" t="n">
         <v>2400</v>
@@ -19944,7 +19944,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>29.8616809844971</v>
+        <v>29.8616790771484</v>
       </c>
       <c r="H675" t="n">
         <v>7800</v>
@@ -20002,7 +20002,7 @@
         <v>33</v>
       </c>
       <c r="G677" t="n">
-        <v>29.1548957824707</v>
+        <v>29.1548976898193</v>
       </c>
       <c r="H677" t="n">
         <v>6300</v>
@@ -20060,7 +20060,7 @@
         <v>32</v>
       </c>
       <c r="G679" t="n">
-        <v>28.2714138031006</v>
+        <v>28.271411895752</v>
       </c>
       <c r="H679" t="n">
         <v>11925</v>
@@ -20089,7 +20089,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H680" t="n">
         <v>4875</v>
@@ -20147,7 +20147,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>28.0947189331055</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H682" t="n">
         <v>5625</v>
@@ -20176,7 +20176,7 @@
         <v>32</v>
       </c>
       <c r="G683" t="n">
-        <v>28.2714138031006</v>
+        <v>28.271411895752</v>
       </c>
       <c r="H683" t="n">
         <v>2400</v>
@@ -20234,7 +20234,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>28.4481105804443</v>
+        <v>28.448112487793</v>
       </c>
       <c r="H685" t="n">
         <v>8100</v>
@@ -20263,7 +20263,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>28.8015022277832</v>
+        <v>28.8015003204346</v>
       </c>
       <c r="H686" t="n">
         <v>2250</v>
@@ -20292,7 +20292,7 @@
         <v>32</v>
       </c>
       <c r="G687" t="n">
-        <v>28.2714138031006</v>
+        <v>28.271411895752</v>
       </c>
       <c r="H687" t="n">
         <v>6750</v>
@@ -20321,7 +20321,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H688" t="n">
         <v>9075</v>
@@ -20350,7 +20350,7 @@
         <v>31</v>
       </c>
       <c r="G689" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H689" t="n">
         <v>1500</v>
@@ -20408,7 +20408,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H691" t="n">
         <v>5250</v>
@@ -20495,7 +20495,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H694" t="n">
         <v>24825</v>
@@ -20524,7 +20524,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H695" t="n">
         <v>7800</v>
@@ -20553,7 +20553,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>25.7976665496826</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H696" t="n">
         <v>5775</v>
@@ -20611,7 +20611,7 @@
         <v>32</v>
       </c>
       <c r="G698" t="n">
-        <v>28.2714138031006</v>
+        <v>28.271411895752</v>
       </c>
       <c r="H698" t="n">
         <v>4950</v>
@@ -20698,7 +20698,7 @@
         <v>32</v>
       </c>
       <c r="G701" t="n">
-        <v>28.2714138031006</v>
+        <v>28.271411895752</v>
       </c>
       <c r="H701" t="n">
         <v>1875</v>
@@ -20727,7 +20727,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H702" t="n">
         <v>825</v>
@@ -20756,7 +20756,7 @@
         <v>31</v>
       </c>
       <c r="G703" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H703" t="n">
         <v>12375</v>
@@ -20814,7 +20814,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H705" t="n">
         <v>2550</v>
@@ -20843,7 +20843,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H706" t="n">
         <v>750</v>
@@ -20901,7 +20901,7 @@
         <v>30</v>
       </c>
       <c r="G708" t="n">
-        <v>26.504451751709</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H708" t="n">
         <v>5700</v>
@@ -20930,7 +20930,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H709" t="n">
         <v>15675</v>
@@ -21046,7 +21046,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H713" t="n">
         <v>900</v>
@@ -21075,7 +21075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H714" t="n">
         <v>2100</v>
@@ -21104,7 +21104,7 @@
         <v>31</v>
       </c>
       <c r="G715" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H715" t="n">
         <v>2700</v>
@@ -21133,7 +21133,7 @@
         <v>31</v>
       </c>
       <c r="G716" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H716" t="n">
         <v>600</v>
@@ -21162,7 +21162,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G717" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H717" t="n">
         <v>150</v>
@@ -21220,7 +21220,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H719" t="n">
         <v>600</v>
@@ -21249,7 +21249,7 @@
         <v>30</v>
       </c>
       <c r="G720" t="n">
-        <v>26.504451751709</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H720" t="n">
         <v>4350</v>
@@ -21278,7 +21278,7 @@
         <v>30</v>
       </c>
       <c r="G721" t="n">
-        <v>26.504451751709</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H721" t="n">
         <v>675</v>
@@ -21365,7 +21365,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H724" t="n">
         <v>2550</v>
@@ -21394,7 +21394,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H725" t="n">
         <v>4425</v>
@@ -21452,7 +21452,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>26.1510581970215</v>
+        <v>26.1510562896729</v>
       </c>
       <c r="H727" t="n">
         <v>3900</v>
@@ -21481,7 +21481,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H728" t="n">
         <v>3300</v>
@@ -21539,7 +21539,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H730" t="n">
         <v>7350</v>
@@ -21655,7 +21655,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H734" t="n">
         <v>2550</v>
@@ -21887,7 +21887,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H742" t="n">
         <v>300</v>
@@ -21916,7 +21916,7 @@
         <v>29</v>
       </c>
       <c r="G743" t="n">
-        <v>25.6209697723389</v>
+        <v>25.6209678649902</v>
       </c>
       <c r="H743" t="n">
         <v>1425</v>
@@ -21945,7 +21945,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>25.7976665496826</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H744" t="n">
         <v>6825</v>
@@ -22003,7 +22003,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H746" t="n">
         <v>675</v>
@@ -22061,7 +22061,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>24.2073993682861</v>
+        <v>24.2073974609375</v>
       </c>
       <c r="H748" t="n">
         <v>2025</v>
@@ -22090,7 +22090,7 @@
         <v>27</v>
       </c>
       <c r="G749" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H749" t="n">
         <v>1875</v>
@@ -22119,7 +22119,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>23.6773090362549</v>
+        <v>23.6773071289062</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>23.6773090362549</v>
+        <v>23.6773071289062</v>
       </c>
       <c r="H751" t="n">
         <v>3525</v>
@@ -22293,7 +22293,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>21.7336483001709</v>
+        <v>21.7336502075195</v>
       </c>
       <c r="H756" t="n">
         <v>6150</v>
@@ -22322,7 +22322,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>21.5569496154785</v>
+        <v>21.5569515228271</v>
       </c>
       <c r="H757" t="n">
         <v>900</v>
@@ -22351,7 +22351,7 @@
         <v>24</v>
       </c>
       <c r="G758" t="n">
-        <v>21.2035617828369</v>
+        <v>21.2035598754883</v>
       </c>
       <c r="H758" t="n">
         <v>2250</v>
@@ -22380,7 +22380,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>20.8501663208008</v>
+        <v>20.8501682281494</v>
       </c>
       <c r="H759" t="n">
         <v>2625</v>
@@ -22438,7 +22438,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H761" t="n">
         <v>1500</v>
@@ -22612,7 +22612,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>25.0908794403076</v>
+        <v>25.090877532959</v>
       </c>
       <c r="H767" t="n">
         <v>375</v>
@@ -22641,7 +22641,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>25.9743595123291</v>
+        <v>25.9743614196777</v>
       </c>
       <c r="H768" t="n">
         <v>900</v>
@@ -22699,7 +22699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H770" t="n">
         <v>2925</v>
@@ -22728,7 +22728,7 @@
         <v>30</v>
       </c>
       <c r="G771" t="n">
-        <v>26.504451751709</v>
+        <v>26.5044498443604</v>
       </c>
       <c r="H771" t="n">
         <v>1275</v>
@@ -22757,7 +22757,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H772" t="n">
         <v>1200</v>
@@ -22815,7 +22815,7 @@
         <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>27.3879318237305</v>
+        <v>27.3879299163818</v>
       </c>
       <c r="H774" t="n">
         <v>2850</v>
@@ -22844,7 +22844,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G775" t="n">
-        <v>27.2112350463867</v>
+        <v>27.2112369537354</v>
       </c>
       <c r="H775" t="n">
         <v>3675</v>
@@ -22960,7 +22960,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>25.7976665496826</v>
+        <v>25.797664642334</v>
       </c>
       <c r="H779" t="n">
         <v>2400</v>
@@ -22989,7 +22989,7 @@
         <v>29</v>
       </c>
       <c r="G780" t="n">
-        <v>25.6209697723389</v>
+        <v>25.6209678649902</v>
       </c>
       <c r="H780" t="n">
         <v>2100</v>
@@ -23018,7 +23018,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>25.5326194763184</v>
+        <v>25.5326175689697</v>
       </c>
       <c r="H781" t="n">
         <v>300</v>
@@ -23134,7 +23134,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>24.6491394042969</v>
+        <v>24.6491374969482</v>
       </c>
       <c r="H785" t="n">
         <v>2100</v>
@@ -23163,7 +23163,7 @@
         <v>27</v>
       </c>
       <c r="G786" t="n">
-        <v>23.8540058135986</v>
+        <v>23.85400390625</v>
       </c>
       <c r="H786" t="n">
         <v>1725</v>
@@ -23221,7 +23221,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006141662598</v>
       </c>
       <c r="H788" t="n">
         <v>75</v>
@@ -23250,7 +23250,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006141662598</v>
       </c>
       <c r="H789" t="n">
         <v>300</v>
@@ -23279,7 +23279,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>23.5006122589111</v>
+        <v>23.5006141662598</v>
       </c>
       <c r="H790" t="n">
         <v>0</v>
@@ -23308,7 +23308,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>22.7054786682129</v>
+        <v>22.7054805755615</v>
       </c>
       <c r="H791" t="n">
         <v>2550</v>
@@ -23337,7 +23337,7 @@
         <v>26</v>
       </c>
       <c r="G792" t="n">
-        <v>22.9705219268799</v>
+        <v>22.9705238342285</v>
       </c>
       <c r="H792" t="n">
         <v>2325</v>
@@ -23366,7 +23366,7 @@
         <v>26</v>
       </c>
       <c r="G793" t="n">
-        <v>22.9705219268799</v>
+        <v>22.9705238342285</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>26</v>
       </c>
       <c r="G794" t="n">
-        <v>22.9705219268799</v>
+        <v>22.9705238342285</v>
       </c>
       <c r="H794" t="n">
         <v>2250</v>
@@ -23453,7 +23453,7 @@
         <v>28.5</v>
       </c>
       <c r="G796" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H796" t="n">
         <v>4875</v>
@@ -23482,7 +23482,7 @@
         <v>28.5</v>
       </c>
       <c r="G797" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H797" t="n">
         <v>1950</v>
@@ -23569,7 +23569,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>25.4490032196045</v>
+        <v>25.4490051269531</v>
       </c>
       <c r="H800" t="n">
         <v>2925</v>
@@ -23656,7 +23656,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>23.9202651977539</v>
+        <v>23.9202671051025</v>
       </c>
       <c r="H803" t="n">
         <v>2625</v>
@@ -23743,7 +23743,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H806" t="n">
         <v>2175</v>
@@ -23772,7 +23772,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H807" t="n">
         <v>75</v>
@@ -23801,7 +23801,7 @@
         <v>27</v>
       </c>
       <c r="G808" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>27</v>
       </c>
       <c r="G810" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H810" t="n">
         <v>75</v>
@@ -23888,7 +23888,7 @@
         <v>27</v>
       </c>
       <c r="G811" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H811" t="n">
         <v>150</v>
@@ -24062,7 +24062,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H817" t="n">
         <v>450</v>
@@ -24091,7 +24091,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H818" t="n">
         <v>375</v>
@@ -24236,7 +24236,7 @@
         <v>26.5</v>
       </c>
       <c r="G823" t="n">
-        <v>23.8303394317627</v>
+        <v>23.8303413391113</v>
       </c>
       <c r="H823" t="n">
         <v>825</v>
@@ -24265,7 +24265,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>23.5605640411377</v>
+        <v>23.5605621337891</v>
       </c>
       <c r="H824" t="n">
         <v>825</v>
@@ -24294,7 +24294,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G825" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H825" t="n">
         <v>300</v>
@@ -24323,7 +24323,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H826" t="n">
         <v>1500</v>
@@ -24439,7 +24439,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>23.5605640411377</v>
+        <v>23.5605621337891</v>
       </c>
       <c r="H830" t="n">
         <v>5925</v>
@@ -24700,7 +24700,7 @@
         <v>25.5</v>
       </c>
       <c r="G839" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24729,7 +24729,7 @@
         <v>25.5</v>
       </c>
       <c r="G840" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H840" t="n">
         <v>300</v>
@@ -24758,7 +24758,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>22.661304473877</v>
+        <v>22.6613063812256</v>
       </c>
       <c r="H841" t="n">
         <v>150</v>
@@ -24787,7 +24787,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>22.1217498779297</v>
+        <v>22.1217517852783</v>
       </c>
       <c r="H842" t="n">
         <v>825</v>
@@ -24874,7 +24874,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>21.3124160766602</v>
+        <v>21.3124179840088</v>
       </c>
       <c r="H845" t="n">
         <v>825</v>
@@ -24903,7 +24903,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>21.6721210479736</v>
+        <v>21.6721229553223</v>
       </c>
       <c r="H846" t="n">
         <v>2550</v>
@@ -24932,7 +24932,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H847" t="n">
         <v>300</v>
@@ -24961,7 +24961,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H848" t="n">
         <v>2100</v>
@@ -24990,7 +24990,7 @@
         <v>25</v>
       </c>
       <c r="G849" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H849" t="n">
         <v>1725</v>
@@ -25048,7 +25048,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>21.4023456573486</v>
+        <v>21.4023418426514</v>
       </c>
       <c r="H851" t="n">
         <v>300</v>
@@ -25193,7 +25193,7 @@
         <v>22</v>
       </c>
       <c r="G856" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H856" t="n">
         <v>5700</v>
@@ -25222,7 +25222,7 @@
         <v>22</v>
       </c>
       <c r="G857" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H857" t="n">
         <v>2925</v>
@@ -25251,7 +25251,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>19.5139026641846</v>
+        <v>19.5139007568359</v>
       </c>
       <c r="H858" t="n">
         <v>1275</v>
@@ -25367,7 +25367,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>19.693754196167</v>
+        <v>19.6937522888184</v>
       </c>
       <c r="H862" t="n">
         <v>1500</v>
@@ -25425,7 +25425,7 @@
         <v>21.5</v>
       </c>
       <c r="G864" t="n">
-        <v>19.3340492248535</v>
+        <v>19.3340511322021</v>
       </c>
       <c r="H864" t="n">
         <v>300</v>
@@ -25541,7 +25541,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G868" t="n">
-        <v>21.6721210479736</v>
+        <v>21.6721229553223</v>
       </c>
       <c r="H868" t="n">
         <v>6300</v>
@@ -25570,7 +25570,7 @@
         <v>25</v>
       </c>
       <c r="G869" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H869" t="n">
         <v>5550</v>
@@ -25599,7 +25599,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.391529083252</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H870" t="n">
         <v>4050</v>
@@ -25657,7 +25657,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H872" t="n">
         <v>2475</v>
@@ -25686,7 +25686,7 @@
         <v>25.5</v>
       </c>
       <c r="G873" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H873" t="n">
         <v>1650</v>
@@ -25715,7 +25715,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H874" t="n">
         <v>2400</v>
@@ -25744,7 +25744,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>21.4922695159912</v>
+        <v>21.4922676086426</v>
       </c>
       <c r="H876" t="n">
         <v>7725</v>
@@ -25802,7 +25802,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>20.5030860900879</v>
+        <v>20.5030841827393</v>
       </c>
       <c r="H877" t="n">
         <v>6075</v>
@@ -25831,7 +25831,7 @@
         <v>23</v>
       </c>
       <c r="G878" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H878" t="n">
         <v>10800</v>
@@ -25860,7 +25860,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>20.5030860900879</v>
+        <v>20.5030841827393</v>
       </c>
       <c r="H879" t="n">
         <v>1200</v>
@@ -25947,7 +25947,7 @@
         <v>22</v>
       </c>
       <c r="G882" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H882" t="n">
         <v>750</v>
@@ -26034,7 +26034,7 @@
         <v>22</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H885" t="n">
         <v>11025</v>
@@ -26063,7 +26063,7 @@
         <v>22</v>
       </c>
       <c r="G886" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H886" t="n">
         <v>4800</v>
@@ -26092,7 +26092,7 @@
         <v>22</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H887" t="n">
         <v>3975</v>
@@ -26121,7 +26121,7 @@
         <v>22</v>
       </c>
       <c r="G888" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H888" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>22</v>
       </c>
       <c r="G889" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H889" t="n">
         <v>1050</v>
@@ -26179,7 +26179,7 @@
         <v>23</v>
       </c>
       <c r="G890" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H890" t="n">
         <v>31200</v>
@@ -26266,7 +26266,7 @@
         <v>27</v>
       </c>
       <c r="G893" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H893" t="n">
         <v>14100</v>
@@ -26411,7 +26411,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>23.110933303833</v>
+        <v>23.1109352111816</v>
       </c>
       <c r="H898" t="n">
         <v>26925</v>
@@ -26440,7 +26440,7 @@
         <v>25.5</v>
       </c>
       <c r="G899" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H899" t="n">
         <v>16275</v>
@@ -26469,7 +26469,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H900" t="n">
         <v>1125</v>
@@ -26498,7 +26498,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>22.5713787078857</v>
+        <v>22.5713806152344</v>
       </c>
       <c r="H901" t="n">
         <v>1725</v>
@@ -26643,7 +26643,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>22.1217498779297</v>
+        <v>22.1217517852783</v>
       </c>
       <c r="H906" t="n">
         <v>1200</v>
@@ -26672,7 +26672,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.391529083252</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H907" t="n">
         <v>3225</v>
@@ -26730,7 +26730,7 @@
         <v>25.5</v>
       </c>
       <c r="G909" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H909" t="n">
         <v>300</v>
@@ -26759,7 +26759,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H910" t="n">
         <v>2250</v>
@@ -26788,7 +26788,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H911" t="n">
         <v>225</v>
@@ -26875,7 +26875,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.391529083252</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H914" t="n">
         <v>75</v>
@@ -26962,7 +26962,7 @@
         <v>25</v>
       </c>
       <c r="G917" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H917" t="n">
         <v>1200</v>
@@ -26991,7 +26991,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H918" t="n">
         <v>5175</v>
@@ -27107,7 +27107,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H922" t="n">
         <v>1050</v>
@@ -27136,7 +27136,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>23.110933303833</v>
+        <v>23.1109352111816</v>
       </c>
       <c r="H925" t="n">
         <v>375</v>
@@ -27223,7 +27223,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>23.110933303833</v>
+        <v>23.1109352111816</v>
       </c>
       <c r="H926" t="n">
         <v>825</v>
@@ -27281,7 +27281,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>22.5713787078857</v>
+        <v>22.5713806152344</v>
       </c>
       <c r="H928" t="n">
         <v>300</v>
@@ -27397,7 +27397,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G932" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H932" t="n">
         <v>2625</v>
@@ -27426,7 +27426,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H933" t="n">
         <v>4500</v>
@@ -27513,7 +27513,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H936" t="n">
         <v>1875</v>
@@ -27716,7 +27716,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H943" t="n">
         <v>21450</v>
@@ -27745,7 +27745,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H948" t="n">
         <v>4950</v>
@@ -27890,7 +27890,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H949" t="n">
         <v>1650</v>
@@ -27919,7 +27919,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H950" t="n">
         <v>6600</v>
@@ -27948,7 +27948,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H951" t="n">
         <v>3300</v>
@@ -27977,7 +27977,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H952" t="n">
         <v>2325</v>
@@ -28035,7 +28035,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>26.7978935241699</v>
+        <v>26.7978916168213</v>
       </c>
       <c r="H954" t="n">
         <v>69075</v>
@@ -28064,7 +28064,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H955" t="n">
         <v>1050</v>
@@ -28093,7 +28093,7 @@
         <v>30.5</v>
       </c>
       <c r="G956" t="n">
-        <v>27.4273738861084</v>
+        <v>27.4273719787598</v>
       </c>
       <c r="H956" t="n">
         <v>3300</v>
@@ -28122,7 +28122,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>27.6971492767334</v>
+        <v>27.697151184082</v>
       </c>
       <c r="H957" t="n">
         <v>10950</v>
@@ -28151,7 +28151,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>28.4165592193604</v>
+        <v>28.4165573120117</v>
       </c>
       <c r="H958" t="n">
         <v>6825</v>
@@ -28180,7 +28180,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G959" t="n">
-        <v>29.3158149719238</v>
+        <v>29.3158130645752</v>
       </c>
       <c r="H959" t="n">
         <v>6600</v>
@@ -28238,7 +28238,7 @@
         <v>30.5</v>
       </c>
       <c r="G961" t="n">
-        <v>27.4273738861084</v>
+        <v>27.4273719787598</v>
       </c>
       <c r="H961" t="n">
         <v>5175</v>
@@ -28267,7 +28267,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G962" t="n">
-        <v>27.2475185394287</v>
+        <v>27.247522354126</v>
       </c>
       <c r="H962" t="n">
         <v>1950</v>
@@ -28441,7 +28441,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H968" t="n">
         <v>450</v>
@@ -28615,7 +28615,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H974" t="n">
         <v>75</v>
@@ -28644,7 +28644,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H976" t="n">
         <v>375</v>
@@ -28702,7 +28702,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H977" t="n">
         <v>750</v>
@@ -28731,7 +28731,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>26.1684112548828</v>
+        <v>26.1684131622314</v>
       </c>
       <c r="H978" t="n">
         <v>450</v>
@@ -28760,7 +28760,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H979" t="n">
         <v>4275</v>
@@ -28789,7 +28789,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H980" t="n">
         <v>6150</v>
@@ -28876,7 +28876,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>24.819522857666</v>
+        <v>24.8195247650146</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -29021,7 +29021,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H988" t="n">
         <v>675</v>
@@ -29224,7 +29224,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H995" t="n">
         <v>525</v>
@@ -29485,7 +29485,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H1004" t="n">
         <v>1050</v>
@@ -29601,7 +29601,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H1008" t="n">
         <v>17250</v>
@@ -29630,7 +29630,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>24.819522857666</v>
+        <v>24.8195247650146</v>
       </c>
       <c r="H1009" t="n">
         <v>750</v>
@@ -29775,7 +29775,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H1014" t="n">
         <v>2175</v>
@@ -29804,7 +29804,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>27.2475185394287</v>
+        <v>27.247522354126</v>
       </c>
       <c r="H1015" t="n">
         <v>2625</v>
@@ -29978,7 +29978,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>27.5172996520996</v>
+        <v>27.517297744751</v>
       </c>
       <c r="H1021" t="n">
         <v>5400</v>
@@ -30036,7 +30036,7 @@
         <v>31</v>
       </c>
       <c r="G1023" t="n">
-        <v>27.8770027160645</v>
+        <v>27.8770008087158</v>
       </c>
       <c r="H1023" t="n">
         <v>9450</v>
@@ -30065,7 +30065,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>28.1467781066895</v>
+        <v>28.1467800140381</v>
       </c>
       <c r="H1024" t="n">
         <v>1200</v>
@@ -30094,7 +30094,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>28.2367038726807</v>
+        <v>28.2367057800293</v>
       </c>
       <c r="H1025" t="n">
         <v>2475</v>
@@ -30123,7 +30123,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>29.4057426452637</v>
+        <v>29.405740737915</v>
       </c>
       <c r="H1026" t="n">
         <v>2025</v>
@@ -30181,7 +30181,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>29.0460357666016</v>
+        <v>29.0460376739502</v>
       </c>
       <c r="H1028" t="n">
         <v>4350</v>
@@ -30210,7 +30210,7 @@
         <v>33</v>
       </c>
       <c r="G1029" t="n">
-        <v>29.6755180358887</v>
+        <v>29.6755199432373</v>
       </c>
       <c r="H1029" t="n">
         <v>2700</v>
@@ -30268,7 +30268,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1031" t="n">
         <v>1050</v>
@@ -30326,7 +30326,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>28.9561100006104</v>
+        <v>28.9561138153076</v>
       </c>
       <c r="H1033" t="n">
         <v>1575</v>
@@ -30355,7 +30355,7 @@
         <v>32.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>29.2258892059326</v>
+        <v>29.225887298584</v>
       </c>
       <c r="H1034" t="n">
         <v>1500</v>
@@ -30413,7 +30413,7 @@
         <v>32</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.7762603759766</v>
+        <v>28.7762584686279</v>
       </c>
       <c r="H1036" t="n">
         <v>3075</v>
@@ -30529,7 +30529,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639610290527</v>
+        <v>31.5639591217041</v>
       </c>
       <c r="H1040" t="n">
         <v>4425</v>
@@ -30558,7 +30558,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.8337364196777</v>
+        <v>31.8337383270264</v>
       </c>
       <c r="H1041" t="n">
         <v>7800</v>
@@ -30587,7 +30587,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2941837310791</v>
+        <v>31.2941818237305</v>
       </c>
       <c r="H1042" t="n">
         <v>4200</v>
@@ -30616,7 +30616,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>31.2941837310791</v>
+        <v>31.2941818237305</v>
       </c>
       <c r="H1043" t="n">
         <v>3750</v>
@@ -30645,7 +30645,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042579650879</v>
+        <v>31.2042541503906</v>
       </c>
       <c r="H1044" t="n">
         <v>1425</v>
@@ -30674,7 +30674,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1045" t="n">
         <v>10575</v>
@@ -30732,7 +30732,7 @@
         <v>32</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7762603759766</v>
+        <v>28.7762584686279</v>
       </c>
       <c r="H1047" t="n">
         <v>14700</v>
@@ -30790,7 +30790,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1049" t="n">
         <v>2100</v>
@@ -30877,7 +30877,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1052" t="n">
         <v>675</v>
@@ -30906,7 +30906,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150688171387</v>
+        <v>30.2150707244873</v>
       </c>
       <c r="H1053" t="n">
         <v>525</v>
@@ -30935,7 +30935,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1054" t="n">
         <v>1050</v>
@@ -31051,7 +31051,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1058" t="n">
-        <v>29.4057426452637</v>
+        <v>29.405740737915</v>
       </c>
       <c r="H1058" t="n">
         <v>1575</v>
@@ -31109,7 +31109,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1060" t="n">
-        <v>28.5064849853516</v>
+        <v>28.5064830780029</v>
       </c>
       <c r="H1060" t="n">
         <v>2175</v>
@@ -31138,7 +31138,7 @@
         <v>32</v>
       </c>
       <c r="G1061" t="n">
-        <v>28.7762603759766</v>
+        <v>28.7762584686279</v>
       </c>
       <c r="H1061" t="n">
         <v>95700</v>
@@ -31167,7 +31167,7 @@
         <v>32.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>29.2258892059326</v>
+        <v>29.225887298584</v>
       </c>
       <c r="H1062" t="n">
         <v>1050</v>
@@ -31196,7 +31196,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1063" t="n">
         <v>1650</v>
@@ -31312,7 +31312,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1067" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1067" t="n">
         <v>5775</v>
@@ -31341,7 +31341,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1068" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1068" t="n">
         <v>525</v>
@@ -31515,7 +31515,7 @@
         <v>32.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1074" t="n">
         <v>975</v>
@@ -31573,7 +31573,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1076" t="n">
         <v>3600</v>
@@ -31602,7 +31602,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1077" t="n">
         <v>450</v>
@@ -31631,7 +31631,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1078" t="n">
         <v>300</v>
@@ -31660,7 +31660,7 @@
         <v>31.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1079" t="n">
         <v>1350</v>
@@ -31689,7 +31689,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1080" t="n">
         <v>14100</v>
@@ -31718,7 +31718,7 @@
         <v>31.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1081" t="n">
         <v>7125</v>
@@ -31776,7 +31776,7 @@
         <v>31.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1083" t="n">
         <v>6450</v>
@@ -31863,7 +31863,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1086" t="n">
         <v>2100</v>
@@ -31979,7 +31979,7 @@
         <v>31.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1090" t="n">
         <v>150</v>
@@ -32008,7 +32008,7 @@
         <v>31.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1091" t="n">
         <v>75</v>
@@ -32037,7 +32037,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1092" t="n">
         <v>450</v>
@@ -32124,7 +32124,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1095" t="n">
         <v>600</v>
@@ -32153,7 +32153,7 @@
         <v>32.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1096" t="n">
         <v>2550</v>
@@ -32182,7 +32182,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1097" t="n">
         <v>2400</v>
@@ -32704,7 +32704,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1115" t="n">
         <v>1069</v>
@@ -32762,7 +32762,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1117" t="n">
         <v>874</v>
@@ -32791,7 +32791,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1118" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1118" t="n">
         <v>404</v>
@@ -32820,7 +32820,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1119" t="n">
         <v>1426</v>
@@ -32849,7 +32849,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1120" t="n">
         <v>683</v>
@@ -32907,7 +32907,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1122" t="n">
         <v>791</v>
@@ -33139,7 +33139,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1130" t="n">
         <v>147</v>
@@ -33197,7 +33197,7 @@
         <v>32.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1132" t="n">
         <v>235</v>
@@ -33226,7 +33226,7 @@
         <v>32.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1133" t="n">
         <v>397</v>
@@ -33255,7 +33255,7 @@
         <v>32.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1134" t="n">
         <v>300</v>
@@ -33458,7 +33458,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1141" t="n">
         <v>1405</v>
@@ -33487,7 +33487,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1142" t="n">
         <v>1568</v>
@@ -33574,7 +33574,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1145" t="n">
         <v>240</v>
@@ -33690,7 +33690,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1149" t="n">
         <v>1616</v>
@@ -33748,7 +33748,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1151" t="n">
         <v>773</v>
@@ -33777,7 +33777,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1152" t="n">
         <v>442</v>
@@ -33806,7 +33806,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1153" t="n">
         <v>365</v>
@@ -34009,7 +34009,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.8786144256592</v>
+        <v>26.8786125183105</v>
       </c>
       <c r="H1160" t="n">
         <v>1105</v>
@@ -34096,7 +34096,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1163" t="n">
         <v>1128</v>
@@ -34125,7 +34125,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1164" t="n">
         <v>5262</v>
@@ -34212,7 +34212,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1167" t="n">
         <v>1240</v>
@@ -34241,7 +34241,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1168" t="n">
         <v>7918</v>
@@ -34270,7 +34270,7 @@
         <v>27.5</v>
       </c>
       <c r="G1169" t="n">
-        <v>25.3137626647949</v>
+        <v>25.3137607574463</v>
       </c>
       <c r="H1169" t="n">
         <v>3413</v>
@@ -34299,7 +34299,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1170" t="n">
         <v>1331</v>
@@ -34328,7 +34328,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1171" t="n">
         <v>1864</v>
@@ -34357,7 +34357,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1172" t="n">
         <v>10192</v>
@@ -34386,7 +34386,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1173" t="n">
         <v>27679</v>
@@ -34415,7 +34415,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1174" t="n">
         <v>300</v>
@@ -34444,7 +34444,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1175" t="n">
         <v>596</v>
@@ -34473,7 +34473,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1176" t="n">
         <v>119</v>
@@ -34502,7 +34502,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1177" t="n">
         <v>572</v>
@@ -34531,7 +34531,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1178" t="n">
         <v>572</v>
@@ -34647,7 +34647,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966133117676</v>
+        <v>23.1966114044189</v>
       </c>
       <c r="H1182" t="n">
         <v>16419</v>
@@ -34676,7 +34676,7 @@
         <v>25</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0125102996826</v>
+        <v>23.0125122070312</v>
       </c>
       <c r="H1183" t="n">
         <v>6634</v>
@@ -34734,7 +34734,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1185" t="n">
         <v>3901</v>
@@ -34763,7 +34763,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1186" t="n">
         <v>4535</v>
@@ -34792,7 +34792,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1187" t="n">
         <v>1957</v>
@@ -34821,7 +34821,7 @@
         <v>26.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1188" t="n">
         <v>550</v>
@@ -34879,7 +34879,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1190" t="n">
         <v>3364</v>
@@ -34966,7 +34966,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1193" t="n">
         <v>5553</v>
@@ -34995,7 +34995,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1194" t="n">
         <v>6387</v>
@@ -35024,7 +35024,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1195" t="n">
         <v>15303</v>
@@ -35169,7 +35169,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1200" t="n">
         <v>2435</v>
@@ -35198,7 +35198,7 @@
         <v>27</v>
       </c>
       <c r="G1201" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1201" t="n">
         <v>345</v>
@@ -35256,7 +35256,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1203" t="n">
         <v>250</v>
@@ -35285,7 +35285,7 @@
         <v>26.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1204" t="n">
         <v>2078</v>
@@ -35401,7 +35401,7 @@
         <v>27</v>
       </c>
       <c r="G1208" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1208" t="n">
         <v>6977</v>
@@ -35575,7 +35575,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1214" t="n">
         <v>1681</v>
@@ -35604,7 +35604,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>26.8786144256592</v>
+        <v>26.8786125183105</v>
       </c>
       <c r="H1215" t="n">
         <v>2568</v>
@@ -35836,7 +35836,7 @@
         <v>29</v>
       </c>
       <c r="G1223" t="n">
-        <v>26.6945133209229</v>
+        <v>26.6945152282715</v>
       </c>
       <c r="H1223" t="n">
         <v>4183</v>
@@ -36010,7 +36010,7 @@
         <v>28</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.7740135192871</v>
+        <v>25.7740116119385</v>
       </c>
       <c r="H1229" t="n">
         <v>4634</v>
@@ -36097,7 +36097,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1232" t="n">
         <v>4851</v>
@@ -36155,7 +36155,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1234" t="n">
         <v>2409</v>
@@ -36184,7 +36184,7 @@
         <v>28</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.7740135192871</v>
+        <v>25.7740116119385</v>
       </c>
       <c r="H1235" t="n">
         <v>2267</v>
@@ -36213,7 +36213,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1236" t="n">
         <v>5154</v>
@@ -36329,7 +36329,7 @@
         <v>27.5</v>
       </c>
       <c r="G1240" t="n">
-        <v>25.3137626647949</v>
+        <v>25.3137607574463</v>
       </c>
       <c r="H1240" t="n">
         <v>499</v>
@@ -36387,7 +36387,7 @@
         <v>27</v>
       </c>
       <c r="G1242" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1242" t="n">
         <v>4303</v>
@@ -36416,7 +36416,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1243" t="n">
         <v>11050</v>
@@ -36445,7 +36445,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1244" t="n">
         <v>11217</v>
@@ -36474,7 +36474,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1245" t="n">
         <v>11733</v>
@@ -36503,7 +36503,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1246" t="n">
         <v>16021</v>
@@ -36532,7 +36532,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1247" t="n">
         <v>8843</v>
@@ -36561,7 +36561,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1248" t="n">
         <v>10327</v>
@@ -36590,7 +36590,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1249" t="n">
         <v>7712</v>
@@ -36619,7 +36619,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1250" t="n">
         <v>7483</v>
@@ -36648,7 +36648,7 @@
         <v>27</v>
       </c>
       <c r="G1251" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1251" t="n">
         <v>2164</v>
@@ -36677,7 +36677,7 @@
         <v>27</v>
       </c>
       <c r="G1252" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1252" t="n">
         <v>1117</v>
@@ -36764,7 +36764,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1255" t="n">
         <v>3149</v>
@@ -36793,7 +36793,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1256" t="n">
         <v>3291</v>
@@ -36822,7 +36822,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1257" t="n">
         <v>2319</v>
@@ -36880,7 +36880,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1259" t="n">
         <v>15177</v>
@@ -36938,7 +36938,7 @@
         <v>27</v>
       </c>
       <c r="G1261" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1261" t="n">
         <v>4013</v>
@@ -36967,7 +36967,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1262" t="n">
         <v>10735</v>
@@ -36996,7 +36996,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1263" t="n">
         <v>5803</v>
@@ -37112,7 +37112,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1267" t="n">
         <v>12740</v>
@@ -37199,7 +37199,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1270" t="n">
         <v>1818</v>
@@ -37257,7 +37257,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1272" t="n">
         <v>50004</v>
@@ -37286,7 +37286,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1273" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1273" t="n">
         <v>8005</v>
@@ -37315,7 +37315,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1274" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1274" t="n">
         <v>4136</v>
@@ -37373,7 +37373,7 @@
         <v>31.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1276" t="n">
         <v>13340</v>
@@ -37489,7 +37489,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1280" t="n">
         <v>2808</v>
@@ -37518,7 +37518,7 @@
         <v>32.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1281" t="n">
         <v>5505</v>
@@ -37547,7 +37547,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1282" t="n">
         <v>10071</v>
@@ -37576,7 +37576,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1283" t="n">
         <v>7498</v>
@@ -37721,7 +37721,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.020866394043</v>
+        <v>31.0208644866943</v>
       </c>
       <c r="H1288" t="n">
         <v>4493</v>
@@ -37808,7 +37808,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.7447166442871</v>
+        <v>30.7447147369385</v>
       </c>
       <c r="H1291" t="n">
         <v>10264</v>
@@ -38040,7 +38040,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1299" t="n">
         <v>10536</v>
@@ -38098,7 +38098,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.836763381958</v>
+        <v>30.8367652893066</v>
       </c>
       <c r="H1301" t="n">
         <v>18694</v>
@@ -38185,7 +38185,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1304" t="n">
         <v>2779</v>
@@ -38243,7 +38243,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1306" t="n">
         <v>1787</v>
@@ -38330,7 +38330,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1309" t="n">
         <v>8681</v>
@@ -38388,7 +38388,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1311" t="n">
         <v>14200</v>
@@ -38475,7 +38475,7 @@
         <v>32.5</v>
       </c>
       <c r="G1314" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1314" t="n">
         <v>4455</v>
@@ -38504,7 +38504,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1315" t="n">
         <v>12589</v>
@@ -38562,7 +38562,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.095422744751</v>
+        <v>29.0954246520996</v>
       </c>
       <c r="H1317" t="n">
         <v>6125</v>
@@ -38765,7 +38765,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1324" t="n">
         <v>12844</v>
@@ -38823,7 +38823,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1326" t="n">
         <v>9621</v>
@@ -38852,7 +38852,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1327" t="n">
         <v>46167</v>
@@ -38881,7 +38881,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1328" t="n">
         <v>3959</v>
@@ -38997,7 +38997,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1332" t="n">
         <v>24982</v>
@@ -39026,7 +39026,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1333" t="n">
         <v>8601</v>
@@ -39055,7 +39055,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1334" t="n">
         <v>5309</v>
@@ -39084,7 +39084,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1335" t="n">
         <v>21621</v>
@@ -39113,7 +39113,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1336" t="n">
         <v>16181</v>
@@ -39142,7 +39142,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1337" t="n">
         <v>6822</v>
@@ -39171,7 +39171,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1338" t="n">
         <v>3455</v>
@@ -39200,7 +39200,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1339" t="n">
         <v>5494</v>
@@ -39229,7 +39229,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1340" t="n">
         <v>13157</v>
@@ -39258,7 +39258,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1341" t="n">
         <v>2965</v>
@@ -39287,7 +39287,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1342" t="n">
         <v>1570</v>
@@ -39345,7 +39345,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1344" t="n">
         <v>2849</v>
@@ -39374,7 +39374,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1345" t="n">
         <v>4077</v>
@@ -39461,7 +39461,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1348" t="n">
         <v>3503</v>
@@ -39548,7 +39548,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1351" t="n">
         <v>3621</v>
@@ -39693,7 +39693,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1356" t="n">
         <v>1074</v>
@@ -39722,7 +39722,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1357" t="n">
         <v>1555</v>
@@ -39896,7 +39896,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851448059082</v>
+        <v>33.7851486206055</v>
       </c>
       <c r="H1363" t="n">
         <v>12779</v>
@@ -39925,7 +39925,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1364" t="n">
         <v>7910</v>
@@ -40012,7 +40012,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1367" t="n">
         <v>2625</v>
@@ -40157,7 +40157,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1372" t="n">
         <v>2528</v>
@@ -40186,7 +40186,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1373" t="n">
         <v>5370</v>
@@ -40273,7 +40273,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1376" t="n">
         <v>9183</v>
@@ -40302,7 +40302,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1377" t="n">
         <v>4352</v>
@@ -40331,7 +40331,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095996856689</v>
+        <v>31.0095977783203</v>
       </c>
       <c r="H1378" t="n">
         <v>1704</v>
@@ -40360,7 +40360,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1379" t="n">
         <v>553</v>
@@ -40389,7 +40389,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1380" t="n">
         <v>732</v>
@@ -40476,7 +40476,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1383" t="n">
         <v>1248</v>
@@ -40505,7 +40505,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1384" t="n">
         <v>1301</v>
@@ -40563,7 +40563,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1386" t="n">
         <v>1483</v>
@@ -40592,7 +40592,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1387" t="n">
         <v>3214</v>
@@ -40708,7 +40708,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1391" t="n">
         <v>3859</v>
@@ -40737,7 +40737,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1392" t="n">
         <v>1387</v>
@@ -40766,7 +40766,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1393" t="n">
         <v>569</v>
@@ -40795,7 +40795,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1394" t="n">
         <v>1704</v>
@@ -40940,7 +40940,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1399" t="n">
         <v>2679</v>
@@ -40998,7 +40998,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1401" t="n">
         <v>4340</v>
@@ -41027,7 +41027,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1402" t="n">
         <v>3944</v>
@@ -41056,7 +41056,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1403" t="n">
         <v>1728</v>
@@ -41085,7 +41085,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1404" t="n">
         <v>1317</v>
@@ -41114,7 +41114,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1405" t="n">
         <v>2062</v>
@@ -41143,7 +41143,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1406" t="n">
         <v>1291</v>
@@ -41230,7 +41230,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1409" t="n">
         <v>4625</v>
@@ -41346,7 +41346,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1413" t="n">
         <v>2410</v>
@@ -41375,7 +41375,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1414" t="n">
         <v>31931</v>
@@ -41404,7 +41404,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1415" t="n">
         <v>13442</v>
@@ -41549,7 +41549,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1420" t="n">
         <v>2989</v>
@@ -41607,7 +41607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1422" t="n">
         <v>2861</v>
@@ -41636,7 +41636,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1423" t="n">
         <v>3892</v>
@@ -41752,7 +41752,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1427" t="n">
         <v>2872</v>
@@ -41781,7 +41781,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1428" t="n">
         <v>3471</v>
@@ -41810,7 +41810,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1429" t="n">
         <v>457</v>
@@ -41839,7 +41839,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1430" t="n">
         <v>4731</v>
@@ -41868,7 +41868,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1431" t="n">
         <v>1418</v>
@@ -41984,7 +41984,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1435" t="n">
         <v>1616</v>
@@ -42013,7 +42013,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1436" t="n">
         <v>3582</v>
@@ -42042,7 +42042,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1437" t="n">
         <v>2662</v>
@@ -42100,7 +42100,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1439" t="n">
         <v>198</v>
@@ -42129,7 +42129,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1440" t="n">
         <v>1144</v>
@@ -42245,7 +42245,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1444" t="n">
         <v>688</v>
@@ -42274,7 +42274,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1445" t="n">
         <v>1252</v>
@@ -42332,7 +42332,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1447" t="n">
         <v>4488</v>
@@ -42448,7 +42448,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1451" t="n">
         <v>2754</v>
@@ -42477,7 +42477,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1452" t="n">
         <v>793</v>
@@ -42535,7 +42535,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1454" t="n">
         <v>4612</v>
@@ -42622,7 +42622,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1457" t="n">
         <v>3819</v>
@@ -42709,7 +42709,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1460" t="n">
         <v>8292</v>
@@ -42796,7 +42796,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1463" t="n">
         <v>3283</v>
@@ -43028,7 +43028,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1471" t="n">
         <v>1571</v>
@@ -43260,7 +43260,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1479" t="n">
         <v>13</v>
@@ -43347,7 +43347,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1482" t="n">
         <v>5922</v>
@@ -43579,7 +43579,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1490" t="n">
         <v>3936</v>
@@ -43608,7 +43608,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1491" t="n">
         <v>9516</v>
@@ -43637,7 +43637,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1492" t="n">
         <v>12</v>
@@ -43695,7 +43695,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1494" t="n">
         <v>3670</v>
@@ -43782,7 +43782,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1497" t="n">
         <v>1307</v>
@@ -43811,7 +43811,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1498" t="n">
         <v>4115</v>
@@ -43956,7 +43956,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1503" t="n">
         <v>1545</v>
@@ -44043,7 +44043,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1506" t="n">
         <v>2072</v>
@@ -44072,7 +44072,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1507" t="n">
         <v>211</v>
@@ -44101,7 +44101,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1508" t="n">
         <v>907</v>
@@ -44275,7 +44275,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1514" t="n">
         <v>1628</v>
@@ -44333,7 +44333,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.8413314819336</v>
+        <v>25.841329574585</v>
       </c>
       <c r="H1516" t="n">
         <v>5585</v>
@@ -44420,7 +44420,7 @@
         <v>27</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.8413314819336</v>
+        <v>25.841329574585</v>
       </c>
       <c r="H1519" t="n">
         <v>3989</v>
@@ -44623,7 +44623,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>26.5112934112549</v>
+        <v>26.5112915039062</v>
       </c>
       <c r="H1526" t="n">
         <v>4380</v>
@@ -44826,7 +44826,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1533" t="n">
         <v>2355</v>
@@ -45029,7 +45029,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1540" t="n">
         <v>2838</v>
@@ -45174,7 +45174,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.6499137878418</v>
+        <v>25.6499118804932</v>
       </c>
       <c r="H1545" t="n">
         <v>3951</v>
@@ -45232,7 +45232,7 @@
         <v>25.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.4057006835938</v>
+        <v>24.4057025909424</v>
       </c>
       <c r="H1547" t="n">
         <v>2784</v>
@@ -45319,7 +45319,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7456207275391</v>
+        <v>25.7456226348877</v>
       </c>
       <c r="H1550" t="n">
         <v>919</v>
@@ -45377,7 +45377,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1552" t="n">
         <v>4472</v>
@@ -45435,7 +45435,7 @@
         <v>29</v>
       </c>
       <c r="G1554" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1554" t="n">
         <v>252</v>
@@ -45464,7 +45464,7 @@
         <v>29</v>
       </c>
       <c r="G1555" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1555" t="n">
         <v>2314</v>
@@ -45493,7 +45493,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1556" t="n">
         <v>3338</v>
@@ -45580,7 +45580,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1559" t="n">
         <v>612</v>
@@ -45725,7 +45725,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1564" t="n">
         <v>1292</v>
@@ -45899,7 +45899,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1570" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1570" t="n">
         <v>2272</v>
@@ -45928,7 +45928,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1571" t="n">
         <v>388</v>
@@ -56490,6 +56490,35 @@
         <v>619</v>
       </c>
       <c r="I1935" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1936" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1936" t="n">
+        <v>43.7999992370605</v>
+      </c>
+      <c r="D1936" t="n">
+        <v>44.7000007629395</v>
+      </c>
+      <c r="E1936" t="n">
+        <v>43.7999992370605</v>
+      </c>
+      <c r="F1936" t="n">
+        <v>43.7999992370605</v>
+      </c>
+      <c r="G1936" t="n">
+        <v>43.7999992370605</v>
+      </c>
+      <c r="H1936" t="n">
+        <v>2918</v>
+      </c>
+      <c r="I1936" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.28757858276367</v>
+        <v>9.2875804901123</v>
       </c>
       <c r="H2" t="n">
         <v>27300</v>
@@ -456,7 +456,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>9.58129024505615</v>
+        <v>9.58128929138184</v>
       </c>
       <c r="H3" t="n">
         <v>62400</v>
@@ -485,7 +485,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293743133545</v>
+        <v>9.88293647766113</v>
       </c>
       <c r="H4" t="n">
         <v>14100</v>
@@ -543,7 +543,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G6" t="n">
-        <v>9.78767967224121</v>
+        <v>9.78768062591553</v>
       </c>
       <c r="H6" t="n">
         <v>5550</v>
@@ -572,7 +572,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>9.67654705047607</v>
+        <v>9.67654609680176</v>
       </c>
       <c r="H7" t="n">
         <v>9900</v>
@@ -630,7 +630,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>9.23995113372803</v>
+        <v>9.23995018005371</v>
       </c>
       <c r="H9" t="n">
         <v>6000</v>
@@ -659,7 +659,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>9.39871215820312</v>
+        <v>9.39871311187744</v>
       </c>
       <c r="H10" t="n">
         <v>1050</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52572154998779</v>
+        <v>9.52572345733643</v>
       </c>
       <c r="H11" t="n">
         <v>1500</v>
@@ -717,7 +717,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>9.44634056091309</v>
+        <v>9.4463415145874</v>
       </c>
       <c r="H12" t="n">
         <v>1200</v>
@@ -775,7 +775,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.9146900177002</v>
+        <v>9.91468906402588</v>
       </c>
       <c r="H14" t="n">
         <v>3450</v>
@@ -804,7 +804,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H15" t="n">
         <v>13050</v>
@@ -862,7 +862,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4147901535034</v>
+        <v>10.4147891998291</v>
       </c>
       <c r="H17" t="n">
         <v>4650</v>
@@ -891,7 +891,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H18" t="n">
         <v>2700</v>
@@ -920,7 +920,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2877798080444</v>
+        <v>10.2877807617188</v>
       </c>
       <c r="H19" t="n">
         <v>4050</v>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H20" t="n">
         <v>1500</v>
@@ -978,7 +978,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G21" t="n">
-        <v>10.2083988189697</v>
+        <v>10.208399772644</v>
       </c>
       <c r="H21" t="n">
         <v>4800</v>
@@ -1007,7 +1007,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2719039916992</v>
+        <v>10.2719049453735</v>
       </c>
       <c r="H22" t="n">
         <v>3150</v>
@@ -1036,7 +1036,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>10.2083988189697</v>
+        <v>10.208399772644</v>
       </c>
       <c r="H23" t="n">
         <v>1050</v>
@@ -1094,7 +1094,7 @@
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>10.3195323944092</v>
+        <v>10.3195333480835</v>
       </c>
       <c r="H25" t="n">
         <v>2550</v>
@@ -1181,7 +1181,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G28" t="n">
-        <v>10.2560262680054</v>
+        <v>10.2560291290283</v>
       </c>
       <c r="H28" t="n">
         <v>1650</v>
@@ -1297,7 +1297,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>10.4147901535034</v>
+        <v>10.4147891998291</v>
       </c>
       <c r="H32" t="n">
         <v>6450</v>
@@ -1326,7 +1326,7 @@
         <v>13.5</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7164363861084</v>
+        <v>10.7164373397827</v>
       </c>
       <c r="H33" t="n">
         <v>6300</v>
@@ -1355,7 +1355,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7005624771118</v>
+        <v>10.7005615234375</v>
       </c>
       <c r="H34" t="n">
         <v>9000</v>
@@ -1413,7 +1413,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588321685791</v>
+        <v>11.0588312149048</v>
       </c>
       <c r="H36" t="n">
         <v>3900</v>
@@ -1442,7 +1442,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419801712036</v>
+        <v>11.1419792175293</v>
       </c>
       <c r="H37" t="n">
         <v>7050</v>
@@ -1471,7 +1471,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G38" t="n">
-        <v>11.1087207794189</v>
+        <v>11.1087198257446</v>
       </c>
       <c r="H38" t="n">
         <v>22800</v>
@@ -1529,7 +1529,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G40" t="n">
-        <v>10.7761249542236</v>
+        <v>10.7761240005493</v>
       </c>
       <c r="H40" t="n">
         <v>3150</v>
@@ -1558,7 +1558,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G41" t="n">
-        <v>10.6264553070068</v>
+        <v>10.6264562606812</v>
       </c>
       <c r="H41" t="n">
         <v>19200</v>
@@ -1703,7 +1703,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G46" t="n">
-        <v>10.6098279953003</v>
+        <v>10.6098260879517</v>
       </c>
       <c r="H46" t="n">
         <v>750</v>
@@ -1761,7 +1761,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H48" t="n">
         <v>7800</v>
@@ -1790,7 +1790,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H49" t="n">
         <v>3750</v>
@@ -1819,7 +1819,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G50" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H51" t="n">
         <v>600</v>
@@ -1877,7 +1877,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H52" t="n">
         <v>900</v>
@@ -1906,7 +1906,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H53" t="n">
         <v>6150</v>
@@ -1964,7 +1964,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G55" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H55" t="n">
         <v>900</v>
@@ -1993,7 +1993,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G56" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H56" t="n">
         <v>750</v>
@@ -2022,7 +2022,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2196,7 +2196,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H63" t="n">
         <v>1800</v>
@@ -2254,7 +2254,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485530853271</v>
       </c>
       <c r="H65" t="n">
         <v>2850</v>
@@ -2283,7 +2283,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H66" t="n">
         <v>3900</v>
@@ -2312,7 +2312,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G67" t="n">
-        <v>9.44573879241943</v>
+        <v>9.44573783874512</v>
       </c>
       <c r="H67" t="n">
         <v>2250</v>
@@ -2341,7 +2341,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.47899913787842</v>
+        <v>9.4789981842041</v>
       </c>
       <c r="H68" t="n">
         <v>57450</v>
@@ -2370,7 +2370,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H69" t="n">
         <v>1200</v>
@@ -2399,7 +2399,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G70" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H70" t="n">
         <v>99900</v>
@@ -2486,7 +2486,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G73" t="n">
-        <v>9.92800235748291</v>
+        <v>9.92800331115723</v>
       </c>
       <c r="H73" t="n">
         <v>1950</v>
@@ -2515,7 +2515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H74" t="n">
         <v>90600</v>
@@ -2544,7 +2544,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H76" t="n">
         <v>600</v>
@@ -2602,7 +2602,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G77" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H77" t="n">
         <v>1800</v>
@@ -2689,7 +2689,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G80" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H80" t="n">
         <v>49800</v>
@@ -2718,7 +2718,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G81" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H81" t="n">
         <v>600</v>
@@ -2776,7 +2776,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>9.77833557128906</v>
+        <v>9.77833652496338</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>9.67855644226074</v>
+        <v>9.67855739593506</v>
       </c>
       <c r="H84" t="n">
         <v>1350</v>
@@ -2834,7 +2834,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G85" t="n">
-        <v>9.67855644226074</v>
+        <v>9.67855739593506</v>
       </c>
       <c r="H85" t="n">
         <v>44700</v>
@@ -2921,7 +2921,7 @@
         <v>11.5</v>
       </c>
       <c r="G88" t="n">
-        <v>9.56214714050293</v>
+        <v>9.56214809417725</v>
       </c>
       <c r="H88" t="n">
         <v>3000</v>
@@ -2950,7 +2950,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>9.71181488037109</v>
+        <v>9.71181583404541</v>
       </c>
       <c r="H89" t="n">
         <v>900</v>
@@ -2979,7 +2979,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G90" t="n">
-        <v>9.69518566131592</v>
+        <v>9.6951847076416</v>
       </c>
       <c r="H90" t="n">
         <v>1350</v>
@@ -3008,7 +3008,7 @@
         <v>11.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.56214714050293</v>
+        <v>9.56214809417725</v>
       </c>
       <c r="H91" t="n">
         <v>300</v>
@@ -3037,7 +3037,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H92" t="n">
         <v>7050</v>
@@ -3066,7 +3066,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H93" t="n">
         <v>2550</v>
@@ -3153,7 +3153,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>10.1441898345947</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H96" t="n">
         <v>1050</v>
@@ -3182,7 +3182,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G97" t="n">
-        <v>9.92800235748291</v>
+        <v>9.92800331115723</v>
       </c>
       <c r="H97" t="n">
         <v>450</v>
@@ -3240,7 +3240,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G99" t="n">
-        <v>10.1275615692139</v>
+        <v>10.1275625228882</v>
       </c>
       <c r="H99" t="n">
         <v>300</v>
@@ -3269,7 +3269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H100" t="n">
         <v>150</v>
@@ -3356,7 +3356,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G103" t="n">
-        <v>9.74507522583008</v>
+        <v>9.74507427215576</v>
       </c>
       <c r="H103" t="n">
         <v>150</v>
@@ -3385,7 +3385,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G104" t="n">
-        <v>9.74507522583008</v>
+        <v>9.74507427215576</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.77833557128906</v>
+        <v>9.77833652496338</v>
       </c>
       <c r="H105" t="n">
         <v>1200</v>
@@ -3443,7 +3443,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>9.77833557128906</v>
+        <v>9.77833652496338</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>9.64529800415039</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H110" t="n">
         <v>450</v>
@@ -3588,7 +3588,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>9.64529800415039</v>
+        <v>9.64529609680176</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148357391357</v>
       </c>
       <c r="H112" t="n">
         <v>1800</v>
@@ -3733,7 +3733,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G116" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485530853271</v>
       </c>
       <c r="H116" t="n">
         <v>450</v>
@@ -3820,7 +3820,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G119" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H119" t="n">
         <v>1500</v>
@@ -3878,7 +3878,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>10.1441898345947</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H121" t="n">
         <v>150</v>
@@ -3965,7 +3965,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -3994,7 +3994,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G125" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H125" t="n">
         <v>1500</v>
@@ -4023,7 +4023,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H126" t="n">
         <v>750</v>
@@ -4197,7 +4197,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>10.4601564407349</v>
+        <v>10.4601573944092</v>
       </c>
       <c r="H132" t="n">
         <v>450</v>
@@ -4255,7 +4255,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>10.1441898345947</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H134" t="n">
         <v>750</v>
@@ -4284,7 +4284,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0277833938599</v>
+        <v>10.0277824401855</v>
       </c>
       <c r="H135" t="n">
         <v>2400</v>
@@ -4313,7 +4313,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G136" t="n">
-        <v>10.044412612915</v>
+        <v>10.0444116592407</v>
       </c>
       <c r="H136" t="n">
         <v>150</v>
@@ -4342,7 +4342,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>10.1441898345947</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H137" t="n">
         <v>300</v>
@@ -4400,7 +4400,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>9.82822418212891</v>
+        <v>9.82822322845459</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4429,7 +4429,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G140" t="n">
-        <v>9.92800235748291</v>
+        <v>9.92800331115723</v>
       </c>
       <c r="H140" t="n">
         <v>1050</v>
@@ -4458,7 +4458,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148357391357</v>
       </c>
       <c r="H141" t="n">
         <v>300</v>
@@ -4487,7 +4487,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148452758789</v>
+        <v>9.86148357391357</v>
       </c>
       <c r="H142" t="n">
         <v>450</v>
@@ -4516,7 +4516,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H143" t="n">
         <v>1200</v>
@@ -4545,7 +4545,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.81159400939941</v>
+        <v>9.81159496307373</v>
       </c>
       <c r="H146" t="n">
         <v>3150</v>
@@ -4632,7 +4632,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G147" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H147" t="n">
         <v>1200</v>
@@ -4661,7 +4661,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H148" t="n">
         <v>750</v>
@@ -4690,7 +4690,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G153" t="n">
-        <v>10.1275615692139</v>
+        <v>10.1275625228882</v>
       </c>
       <c r="H153" t="n">
         <v>150</v>
@@ -4922,7 +4922,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G157" t="n">
-        <v>9.92800235748291</v>
+        <v>9.92800331115723</v>
       </c>
       <c r="H157" t="n">
         <v>3150</v>
@@ -4951,7 +4951,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H158" t="n">
         <v>600</v>
@@ -5038,7 +5038,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G161" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H161" t="n">
         <v>300</v>
@@ -5096,7 +5096,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H163" t="n">
         <v>16200</v>
@@ -5125,7 +5125,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G164" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H164" t="n">
         <v>2250</v>
@@ -5154,7 +5154,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H167" t="n">
         <v>1500</v>
@@ -5241,7 +5241,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>10.3104887008667</v>
+        <v>10.310489654541</v>
       </c>
       <c r="H168" t="n">
         <v>9300</v>
@@ -5270,7 +5270,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H169" t="n">
         <v>2400</v>
@@ -5299,7 +5299,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G170" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H170" t="n">
         <v>150</v>
@@ -5328,7 +5328,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G171" t="n">
-        <v>10.2439699172974</v>
+        <v>10.2439708709717</v>
       </c>
       <c r="H171" t="n">
         <v>450</v>
@@ -5386,7 +5386,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G173" t="n">
-        <v>10.0277833938599</v>
+        <v>10.0277824401855</v>
       </c>
       <c r="H173" t="n">
         <v>300</v>
@@ -5415,7 +5415,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G174" t="n">
-        <v>10.1441898345947</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H174" t="n">
         <v>1950</v>
@@ -5444,7 +5444,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G175" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H175" t="n">
         <v>450</v>
@@ -5473,7 +5473,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126365661621</v>
+        <v>9.96126174926758</v>
       </c>
       <c r="H176" t="n">
         <v>150</v>
@@ -5589,7 +5589,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G180" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H180" t="n">
         <v>2700</v>
@@ -5647,7 +5647,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>10.1109304428101</v>
+        <v>10.1109313964844</v>
       </c>
       <c r="H182" t="n">
         <v>1350</v>
@@ -5676,7 +5676,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G183" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H183" t="n">
         <v>450</v>
@@ -5705,7 +5705,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G184" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H184" t="n">
         <v>750</v>
@@ -5734,7 +5734,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G191" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H191" t="n">
         <v>600</v>
@@ -5966,7 +5966,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H193" t="n">
         <v>150</v>
@@ -5995,7 +5995,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H194" t="n">
         <v>150</v>
@@ -6024,7 +6024,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G195" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6169,7 +6169,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G200" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H200" t="n">
         <v>15150</v>
@@ -6198,7 +6198,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G201" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H201" t="n">
         <v>1350</v>
@@ -6227,7 +6227,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H202" t="n">
         <v>7050</v>
@@ -6256,7 +6256,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G203" t="n">
-        <v>10.044412612915</v>
+        <v>10.0444116592407</v>
       </c>
       <c r="H203" t="n">
         <v>5250</v>
@@ -6285,7 +6285,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>10.044412612915</v>
+        <v>10.0444116592407</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G205" t="n">
-        <v>9.8448543548584</v>
+        <v>9.84485530853271</v>
       </c>
       <c r="H205" t="n">
         <v>750</v>
@@ -6372,7 +6372,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H207" t="n">
         <v>900</v>
@@ -6430,7 +6430,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G209" t="n">
-        <v>10.2439699172974</v>
+        <v>10.2439708709717</v>
       </c>
       <c r="H209" t="n">
         <v>2850</v>
@@ -6459,7 +6459,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>10.0776710510254</v>
+        <v>10.0776720046997</v>
       </c>
       <c r="H210" t="n">
         <v>150</v>
@@ -6604,7 +6604,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G215" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H215" t="n">
         <v>3300</v>
@@ -6633,7 +6633,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>10.1441898345947</v>
+        <v>10.1441917419434</v>
       </c>
       <c r="H216" t="n">
         <v>2550</v>
@@ -6691,7 +6691,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2107095718384</v>
+        <v>10.2107105255127</v>
       </c>
       <c r="H218" t="n">
         <v>7950</v>
@@ -6720,7 +6720,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H219" t="n">
         <v>900</v>
@@ -6865,7 +6865,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H224" t="n">
         <v>1800</v>
@@ -7010,7 +7010,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603782653809</v>
+        <v>10.3603792190552</v>
       </c>
       <c r="H229" t="n">
         <v>2400</v>
@@ -7068,7 +7068,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G231" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H231" t="n">
         <v>600</v>
@@ -7097,7 +7097,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H232" t="n">
         <v>2250</v>
@@ -7126,7 +7126,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G233" t="n">
-        <v>10.2273416519165</v>
+        <v>10.2273406982422</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G234" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H234" t="n">
         <v>900</v>
@@ -7184,7 +7184,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G235" t="n">
-        <v>9.9945240020752</v>
+        <v>9.99452304840088</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G236" t="n">
-        <v>10.0111522674561</v>
+        <v>10.0111513137817</v>
       </c>
       <c r="H236" t="n">
         <v>750</v>
@@ -7242,7 +7242,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H237" t="n">
         <v>3000</v>
@@ -7271,7 +7271,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2605991363525</v>
+        <v>10.2606000900269</v>
       </c>
       <c r="H238" t="n">
         <v>1350</v>
@@ -7300,7 +7300,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0610408782959</v>
+        <v>10.0610418319702</v>
       </c>
       <c r="H239" t="n">
         <v>2850</v>
@@ -7445,7 +7445,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>9.72844505310059</v>
+        <v>9.7284460067749</v>
       </c>
       <c r="H244" t="n">
         <v>300</v>
@@ -7474,7 +7474,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G245" t="n">
-        <v>9.52888774871826</v>
+        <v>9.52888870239258</v>
       </c>
       <c r="H245" t="n">
         <v>1050</v>
@@ -7503,7 +7503,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.17966175079346</v>
+        <v>9.17966079711914</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7590,7 +7590,7 @@
         <v>11.5</v>
       </c>
       <c r="G249" t="n">
-        <v>9.56214714050293</v>
+        <v>9.56214809417725</v>
       </c>
       <c r="H249" t="n">
         <v>3300</v>
@@ -7619,7 +7619,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.1131420135498</v>
+        <v>9.11314392089844</v>
       </c>
       <c r="H250" t="n">
         <v>2250</v>
@@ -7735,7 +7735,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G254" t="n">
-        <v>8.13198184967041</v>
+        <v>8.13198375701904</v>
       </c>
       <c r="H254" t="n">
         <v>750</v>
@@ -7764,7 +7764,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>8.48120784759521</v>
+        <v>8.48120880126953</v>
       </c>
       <c r="H255" t="n">
         <v>150</v>
@@ -7793,7 +7793,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G256" t="n">
-        <v>7.42521572113037</v>
+        <v>7.42521619796753</v>
       </c>
       <c r="H256" t="n">
         <v>2400</v>
@@ -7822,7 +7822,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.14861392974854</v>
+        <v>8.14861297607422</v>
       </c>
       <c r="H257" t="n">
         <v>450</v>
@@ -7851,7 +7851,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.14861392974854</v>
+        <v>8.14861297607422</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568489074707</v>
+        <v>7.96568536758423</v>
       </c>
       <c r="H259" t="n">
         <v>3600</v>
@@ -7909,7 +7909,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>8.03220272064209</v>
+        <v>8.03220367431641</v>
       </c>
       <c r="H260" t="n">
         <v>5400</v>
@@ -7938,7 +7938,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G261" t="n">
-        <v>8.03220272064209</v>
+        <v>8.03220367431641</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>10</v>
       </c>
       <c r="G262" t="n">
-        <v>8.31491184234619</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H262" t="n">
         <v>1950</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>8.31491184234619</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>10</v>
       </c>
       <c r="G264" t="n">
-        <v>8.31491184234619</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>8.31491184234619</v>
+        <v>8.31490993499756</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.48120784759521</v>
+        <v>8.48120880126953</v>
       </c>
       <c r="H269" t="n">
         <v>600</v>
@@ -8228,7 +8228,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39806079864502</v>
+        <v>8.3980598449707</v>
       </c>
       <c r="H271" t="n">
         <v>1500</v>
@@ -8373,7 +8373,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>8.48120784759521</v>
+        <v>8.48120880126953</v>
       </c>
       <c r="H276" t="n">
         <v>2250</v>
@@ -8460,7 +8460,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640235900879</v>
+        <v>9.14640331268311</v>
       </c>
       <c r="H279" t="n">
         <v>19950</v>
@@ -8489,7 +8489,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640235900879</v>
+        <v>9.14640331268311</v>
       </c>
       <c r="H280" t="n">
         <v>1350</v>
@@ -8518,7 +8518,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>8.98010349273682</v>
+        <v>8.98010444641113</v>
       </c>
       <c r="H281" t="n">
         <v>1050</v>
@@ -8547,7 +8547,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>8.98010349273682</v>
+        <v>8.98010444641113</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>9.06325244903564</v>
+        <v>9.06325340270996</v>
       </c>
       <c r="H283" t="n">
         <v>900</v>
@@ -8605,7 +8605,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36392879486084</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.19211578369141</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H285" t="n">
         <v>2700</v>
@@ -8663,7 +8663,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H286" t="n">
         <v>3750</v>
@@ -8692,7 +8692,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H288" t="n">
         <v>300</v>
@@ -8750,7 +8750,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H292" t="n">
         <v>2250</v>
@@ -8866,7 +8866,7 @@
         <v>10.5</v>
       </c>
       <c r="G293" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H293" t="n">
         <v>750</v>
@@ -8924,7 +8924,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H295" t="n">
         <v>1050</v>
@@ -8953,7 +8953,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H296" t="n">
         <v>750</v>
@@ -8982,7 +8982,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G298" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H298" t="n">
         <v>300</v>
@@ -9040,7 +9040,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H300" t="n">
         <v>4350</v>
@@ -9098,7 +9098,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H304" t="n">
         <v>22950</v>
@@ -9214,7 +9214,7 @@
         <v>10</v>
       </c>
       <c r="G305" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>10</v>
       </c>
       <c r="G307" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>10</v>
       </c>
       <c r="G308" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>10</v>
       </c>
       <c r="G309" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>10</v>
       </c>
       <c r="G310" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G311" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H311" t="n">
         <v>150</v>
@@ -9417,7 +9417,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H312" t="n">
         <v>750</v>
@@ -9446,7 +9446,7 @@
         <v>10.5</v>
       </c>
       <c r="G313" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H313" t="n">
         <v>2550</v>
@@ -9475,7 +9475,7 @@
         <v>10.5</v>
       </c>
       <c r="G314" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>10.5</v>
       </c>
       <c r="G315" t="n">
-        <v>9.02029895782471</v>
+        <v>9.02029800415039</v>
       </c>
       <c r="H315" t="n">
         <v>150</v>
@@ -9533,7 +9533,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G316" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9562,7 +9562,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H317" t="n">
         <v>1050</v>
@@ -9591,7 +9591,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H318" t="n">
         <v>1050</v>
@@ -9620,7 +9620,7 @@
         <v>10</v>
       </c>
       <c r="G319" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H319" t="n">
         <v>150</v>
@@ -9649,7 +9649,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G321" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H321" t="n">
         <v>600</v>
@@ -9707,7 +9707,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G322" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G323" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>8.33303833007812</v>
+        <v>8.33303737640381</v>
       </c>
       <c r="H326" t="n">
         <v>2250</v>
@@ -9997,7 +9997,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H332" t="n">
         <v>300</v>
@@ -10026,7 +10026,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H336" t="n">
         <v>300</v>
@@ -10142,7 +10142,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10171,7 +10171,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H338" t="n">
         <v>1350</v>
@@ -10200,7 +10200,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H339" t="n">
         <v>450</v>
@@ -10229,7 +10229,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H341" t="n">
         <v>150</v>
@@ -10287,7 +10287,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H343" t="n">
         <v>6000</v>
@@ -10345,7 +10345,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H345" t="n">
         <v>600</v>
@@ -10403,7 +10403,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H346" t="n">
         <v>5550</v>
@@ -10432,7 +10432,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H347" t="n">
         <v>600</v>
@@ -10461,7 +10461,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H350" t="n">
         <v>900</v>
@@ -10548,7 +10548,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H351" t="n">
         <v>450</v>
@@ -10577,7 +10577,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G352" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G353" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G354" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H355" t="n">
         <v>1800</v>
@@ -10693,7 +10693,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>8.46190071105957</v>
+        <v>8.46189975738525</v>
       </c>
       <c r="H356" t="n">
         <v>1950</v>
@@ -10780,7 +10780,7 @@
         <v>10</v>
       </c>
       <c r="G359" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H359" t="n">
         <v>750</v>
@@ -11273,7 +11273,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>8.50485229492188</v>
+        <v>8.50485324859619</v>
       </c>
       <c r="H376" t="n">
         <v>1800</v>
@@ -11302,7 +11302,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H377" t="n">
         <v>2550</v>
@@ -11331,7 +11331,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H378" t="n">
         <v>4200</v>
@@ -11360,7 +11360,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H379" t="n">
         <v>1200</v>
@@ -11418,7 +11418,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H381" t="n">
         <v>1500</v>
@@ -11447,7 +11447,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>10</v>
       </c>
       <c r="G383" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H383" t="n">
         <v>750</v>
@@ -11505,7 +11505,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H384" t="n">
         <v>2850</v>
@@ -11534,7 +11534,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>10</v>
       </c>
       <c r="G386" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H386" t="n">
         <v>300</v>
@@ -11621,7 +11621,7 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H388" t="n">
         <v>300</v>
@@ -11708,7 +11708,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H391" t="n">
         <v>150</v>
@@ -11737,7 +11737,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H396" t="n">
         <v>300</v>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H398" t="n">
         <v>600</v>
@@ -11940,7 +11940,7 @@
         <v>10</v>
       </c>
       <c r="G399" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H401" t="n">
         <v>1800</v>
@@ -12027,7 +12027,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H406" t="n">
         <v>1050</v>
@@ -12172,7 +12172,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>10</v>
       </c>
       <c r="G408" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H408" t="n">
         <v>150</v>
@@ -12230,7 +12230,7 @@
         <v>10</v>
       </c>
       <c r="G409" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H409" t="n">
         <v>450</v>
@@ -12346,7 +12346,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H413" t="n">
         <v>5400</v>
@@ -12375,7 +12375,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H414" t="n">
         <v>150</v>
@@ -12433,7 +12433,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H416" t="n">
         <v>600</v>
@@ -12462,7 +12462,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H418" t="n">
         <v>450</v>
@@ -12520,7 +12520,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>8.84848403930664</v>
+        <v>8.84848308563232</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>8.67666816711426</v>
+        <v>8.67666912078857</v>
       </c>
       <c r="H421" t="n">
         <v>750</v>
@@ -12607,7 +12607,7 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>8.5907621383667</v>
+        <v>8.59076023101807</v>
       </c>
       <c r="H422" t="n">
         <v>150</v>
@@ -12752,7 +12752,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>8.9343900680542</v>
+        <v>8.93439197540283</v>
       </c>
       <c r="H427" t="n">
         <v>450</v>
@@ -12781,7 +12781,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.19211578369141</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H428" t="n">
         <v>900</v>
@@ -12839,7 +12839,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>9.36392974853516</v>
+        <v>9.36392879486084</v>
       </c>
       <c r="H430" t="n">
         <v>450</v>
@@ -12868,7 +12868,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19211578369141</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H431" t="n">
         <v>300</v>
@@ -12897,7 +12897,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>9.19211578369141</v>
+        <v>9.19211387634277</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>11.5</v>
       </c>
       <c r="G438" t="n">
-        <v>9.87937450408936</v>
+        <v>9.87937545776367</v>
       </c>
       <c r="H438" t="n">
         <v>1350</v>
@@ -13100,7 +13100,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G439" t="n">
-        <v>9.79346656799316</v>
+        <v>9.79346752166748</v>
       </c>
       <c r="H439" t="n">
         <v>8400</v>
@@ -13158,7 +13158,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.70756053924561</v>
+        <v>9.70755958557129</v>
       </c>
       <c r="H441" t="n">
         <v>750</v>
@@ -13187,7 +13187,7 @@
         <v>11.5</v>
       </c>
       <c r="G442" t="n">
-        <v>9.87937450408936</v>
+        <v>9.87937545776367</v>
       </c>
       <c r="H442" t="n">
         <v>300</v>
@@ -13216,7 +13216,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H443" t="n">
         <v>11400</v>
@@ -13245,7 +13245,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H444" t="n">
         <v>6150</v>
@@ -13274,7 +13274,7 @@
         <v>12</v>
       </c>
       <c r="G445" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H445" t="n">
         <v>3600</v>
@@ -13303,7 +13303,7 @@
         <v>12</v>
       </c>
       <c r="G446" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>12</v>
       </c>
       <c r="G447" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H447" t="n">
         <v>900</v>
@@ -13361,7 +13361,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>10.4807291030884</v>
+        <v>10.4807281494141</v>
       </c>
       <c r="H448" t="n">
         <v>600</v>
@@ -13390,7 +13390,7 @@
         <v>12</v>
       </c>
       <c r="G449" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H449" t="n">
         <v>600</v>
@@ -13419,7 +13419,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H450" t="n">
         <v>300</v>
@@ -13477,7 +13477,7 @@
         <v>12</v>
       </c>
       <c r="G452" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H452" t="n">
         <v>1950</v>
@@ -13506,7 +13506,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H453" t="n">
         <v>4050</v>
@@ -13535,7 +13535,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G454" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H455" t="n">
         <v>450</v>
@@ -13593,7 +13593,7 @@
         <v>12</v>
       </c>
       <c r="G456" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H456" t="n">
         <v>5400</v>
@@ -13622,7 +13622,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G457" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H457" t="n">
         <v>17250</v>
@@ -13651,7 +13651,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H458" t="n">
         <v>1350</v>
@@ -13680,7 +13680,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>9.70756053924561</v>
+        <v>9.70755958557129</v>
       </c>
       <c r="H459" t="n">
         <v>4650</v>
@@ -13709,7 +13709,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G460" t="n">
-        <v>9.70756053924561</v>
+        <v>9.70755958557129</v>
       </c>
       <c r="H460" t="n">
         <v>1950</v>
@@ -13738,7 +13738,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>9.62165260314941</v>
+        <v>9.62165355682373</v>
       </c>
       <c r="H461" t="n">
         <v>2100</v>
@@ -13796,7 +13796,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G463" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H463" t="n">
         <v>600</v>
@@ -13825,7 +13825,7 @@
         <v>11.5</v>
       </c>
       <c r="G464" t="n">
-        <v>9.87937450408936</v>
+        <v>9.87937545776367</v>
       </c>
       <c r="H464" t="n">
         <v>750</v>
@@ -13883,7 +13883,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G466" t="n">
-        <v>9.70756053924561</v>
+        <v>9.70755958557129</v>
       </c>
       <c r="H466" t="n">
         <v>3450</v>
@@ -13912,7 +13912,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H467" t="n">
         <v>13050</v>
@@ -13941,7 +13941,7 @@
         <v>12</v>
       </c>
       <c r="G468" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H468" t="n">
         <v>3900</v>
@@ -13970,7 +13970,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>10.4807291030884</v>
+        <v>10.4807281494141</v>
       </c>
       <c r="H469" t="n">
         <v>7500</v>
@@ -14057,7 +14057,7 @@
         <v>12</v>
       </c>
       <c r="G472" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H472" t="n">
         <v>67350</v>
@@ -14115,7 +14115,7 @@
         <v>12</v>
       </c>
       <c r="G474" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H474" t="n">
         <v>20100</v>
@@ -14144,7 +14144,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H475" t="n">
         <v>150</v>
@@ -14202,7 +14202,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G477" t="n">
-        <v>10.1370964050293</v>
+        <v>10.1370983123779</v>
       </c>
       <c r="H477" t="n">
         <v>600</v>
@@ -14231,7 +14231,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0511913299561</v>
+        <v>10.0511903762817</v>
       </c>
       <c r="H478" t="n">
         <v>1500</v>
@@ -14260,7 +14260,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0511913299561</v>
+        <v>10.0511903762817</v>
       </c>
       <c r="H479" t="n">
         <v>600</v>
@@ -14289,7 +14289,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H480" t="n">
         <v>1500</v>
@@ -14318,7 +14318,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2230052947998</v>
+        <v>10.2230043411255</v>
       </c>
       <c r="H481" t="n">
         <v>150</v>
@@ -14347,7 +14347,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>10.4807291030884</v>
+        <v>10.4807281494141</v>
       </c>
       <c r="H482" t="n">
         <v>26700</v>
@@ -14376,7 +14376,7 @@
         <v>12</v>
       </c>
       <c r="G483" t="n">
-        <v>10.3089141845703</v>
+        <v>10.308913230896</v>
       </c>
       <c r="H483" t="n">
         <v>2250</v>
@@ -14579,7 +14579,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H490" t="n">
         <v>6450</v>
@@ -14608,7 +14608,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H491" t="n">
         <v>6450</v>
@@ -14637,7 +14637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>10.8243598937988</v>
+        <v>10.8243589401245</v>
       </c>
       <c r="H492" t="n">
         <v>5100</v>
@@ -14666,7 +14666,7 @@
         <v>13</v>
       </c>
       <c r="G493" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679906845093</v>
       </c>
       <c r="H493" t="n">
         <v>36300</v>
@@ -14695,7 +14695,7 @@
         <v>13</v>
       </c>
       <c r="G494" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679906845093</v>
       </c>
       <c r="H494" t="n">
         <v>7050</v>
@@ -14724,7 +14724,7 @@
         <v>13</v>
       </c>
       <c r="G495" t="n">
-        <v>11.167989730835</v>
+        <v>11.1679906845093</v>
       </c>
       <c r="H495" t="n">
         <v>20850</v>
@@ -14840,7 +14840,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.4257135391235</v>
+        <v>11.4257125854492</v>
       </c>
       <c r="H499" t="n">
         <v>750</v>
@@ -14869,7 +14869,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>11.8552503585815</v>
+        <v>11.8552513122559</v>
       </c>
       <c r="H500" t="n">
         <v>5400</v>
@@ -15072,7 +15072,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>12.7143268585205</v>
+        <v>12.7143259048462</v>
       </c>
       <c r="H507" t="n">
         <v>2400</v>
@@ -15101,7 +15101,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G508" t="n">
-        <v>12.7143268585205</v>
+        <v>12.7143259048462</v>
       </c>
       <c r="H508" t="n">
         <v>1350</v>
@@ -15130,7 +15130,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>13.0579566955566</v>
+        <v>13.057957649231</v>
       </c>
       <c r="H509" t="n">
         <v>2550</v>
@@ -15159,7 +15159,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>13.0579566955566</v>
+        <v>13.057957649231</v>
       </c>
       <c r="H510" t="n">
         <v>12750</v>
@@ -15275,7 +15275,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G514" t="n">
-        <v>13.0579566955566</v>
+        <v>13.057957649231</v>
       </c>
       <c r="H514" t="n">
         <v>10800</v>
@@ -15304,7 +15304,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.8311262130737</v>
+        <v>13.8311252593994</v>
       </c>
       <c r="H515" t="n">
         <v>23250</v>
@@ -15362,7 +15362,7 @@
         <v>16</v>
       </c>
       <c r="G517" t="n">
-        <v>13.7452182769775</v>
+        <v>13.7452173233032</v>
       </c>
       <c r="H517" t="n">
         <v>17250</v>
@@ -15391,7 +15391,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>13.4874963760376</v>
+        <v>13.4874935150146</v>
       </c>
       <c r="H518" t="n">
         <v>6600</v>
@@ -15420,7 +15420,7 @@
         <v>16.5</v>
       </c>
       <c r="G519" t="n">
-        <v>14.1747560501099</v>
+        <v>14.1747550964355</v>
       </c>
       <c r="H519" t="n">
         <v>8250</v>
@@ -15449,7 +15449,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>14.2606630325317</v>
+        <v>14.2606649398804</v>
       </c>
       <c r="H520" t="n">
         <v>5700</v>
@@ -15478,7 +15478,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324769973755</v>
+        <v>14.4324779510498</v>
       </c>
       <c r="H521" t="n">
         <v>58800</v>
@@ -15507,7 +15507,7 @@
         <v>16.5</v>
       </c>
       <c r="G522" t="n">
-        <v>14.1747560501099</v>
+        <v>14.1747550964355</v>
       </c>
       <c r="H522" t="n">
         <v>4050</v>
@@ -15536,7 +15536,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>13.8311262130737</v>
+        <v>13.8311252593994</v>
       </c>
       <c r="H523" t="n">
         <v>10950</v>
@@ -15565,7 +15565,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>14.2606630325317</v>
+        <v>14.2606649398804</v>
       </c>
       <c r="H524" t="n">
         <v>2250</v>
@@ -15623,7 +15623,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>14.3465700149536</v>
+        <v>14.3465709686279</v>
       </c>
       <c r="H526" t="n">
         <v>6750</v>
@@ -15652,7 +15652,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324769973755</v>
+        <v>14.4324779510498</v>
       </c>
       <c r="H527" t="n">
         <v>40350</v>
@@ -15681,7 +15681,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042947769165</v>
+        <v>14.6042919158936</v>
       </c>
       <c r="H528" t="n">
         <v>25200</v>
@@ -15739,7 +15739,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>15.2915534973145</v>
+        <v>15.2915544509888</v>
       </c>
       <c r="H530" t="n">
         <v>3450</v>
@@ -15797,7 +15797,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056465148926</v>
+        <v>15.2056474685669</v>
       </c>
       <c r="H532" t="n">
         <v>8550</v>
@@ -15826,7 +15826,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>15.1197385787964</v>
+        <v>15.119740486145</v>
       </c>
       <c r="H533" t="n">
         <v>4500</v>
@@ -15913,7 +15913,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.549277305603</v>
+        <v>15.5492763519287</v>
       </c>
       <c r="H536" t="n">
         <v>3000</v>
@@ -15942,7 +15942,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>15.7259750366211</v>
+        <v>15.7259721755981</v>
       </c>
       <c r="H537" t="n">
         <v>7800</v>
@@ -16000,7 +16000,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>15.7259750366211</v>
+        <v>15.7259721755981</v>
       </c>
       <c r="H539" t="n">
         <v>4800</v>
@@ -16029,7 +16029,7 @@
         <v>17</v>
       </c>
       <c r="G540" t="n">
-        <v>15.0191888809204</v>
+        <v>15.0191898345947</v>
       </c>
       <c r="H540" t="n">
         <v>3150</v>
@@ -16087,7 +16087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>15.7259750366211</v>
+        <v>15.7259721755981</v>
       </c>
       <c r="H542" t="n">
         <v>3750</v>
@@ -16116,7 +16116,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.549277305603</v>
+        <v>15.5492763519287</v>
       </c>
       <c r="H543" t="n">
         <v>3600</v>
@@ -16145,7 +16145,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>15.8143215179443</v>
+        <v>15.81432056427</v>
       </c>
       <c r="H544" t="n">
         <v>600</v>
@@ -16203,7 +16203,7 @@
         <v>18</v>
       </c>
       <c r="G546" t="n">
-        <v>15.9026689529419</v>
+        <v>15.9026699066162</v>
       </c>
       <c r="H546" t="n">
         <v>3150</v>
@@ -16261,7 +16261,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>16.4327583312988</v>
+        <v>16.4327602386475</v>
       </c>
       <c r="H548" t="n">
         <v>5700</v>
@@ -16493,7 +16493,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>16.4327583312988</v>
+        <v>16.4327602386475</v>
       </c>
       <c r="H556" t="n">
         <v>3900</v>
@@ -16696,7 +16696,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>19.9666862487793</v>
+        <v>19.9666843414307</v>
       </c>
       <c r="H563" t="n">
         <v>31500</v>
@@ -16725,7 +16725,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>19.9666862487793</v>
+        <v>19.9666843414307</v>
       </c>
       <c r="H564" t="n">
         <v>4200</v>
@@ -16783,7 +16783,7 @@
         <v>21</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531177520752</v>
       </c>
       <c r="H566" t="n">
         <v>12300</v>
@@ -16812,7 +16812,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G567" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H567" t="n">
         <v>9150</v>
@@ -17015,7 +17015,7 @@
         <v>20</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6696357727051</v>
+        <v>17.6696319580078</v>
       </c>
       <c r="H574" t="n">
         <v>5250</v>
@@ -17044,7 +17044,7 @@
         <v>19.5</v>
       </c>
       <c r="G575" t="n">
-        <v>17.2278919219971</v>
+        <v>17.2278938293457</v>
       </c>
       <c r="H575" t="n">
         <v>2250</v>
@@ -17073,7 +17073,7 @@
         <v>19</v>
       </c>
       <c r="G576" t="n">
-        <v>16.7861499786377</v>
+        <v>16.7861518859863</v>
       </c>
       <c r="H576" t="n">
         <v>14175</v>
@@ -17102,7 +17102,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.1395435333252</v>
+        <v>17.1395454406738</v>
       </c>
       <c r="H577" t="n">
         <v>5250</v>
@@ -17131,7 +17131,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>17.1395435333252</v>
+        <v>17.1395454406738</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17218,7 +17218,7 @@
         <v>19</v>
       </c>
       <c r="G581" t="n">
-        <v>16.7861499786377</v>
+        <v>16.7861518859863</v>
       </c>
       <c r="H581" t="n">
         <v>8400</v>
@@ -17305,7 +17305,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>17.6696357727051</v>
+        <v>17.6696319580078</v>
       </c>
       <c r="H584" t="n">
         <v>1050</v>
@@ -17363,7 +17363,7 @@
         <v>21</v>
       </c>
       <c r="G586" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531177520752</v>
       </c>
       <c r="H586" t="n">
         <v>11325</v>
@@ -17392,7 +17392,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H587" t="n">
         <v>16275</v>
@@ -17450,7 +17450,7 @@
         <v>21</v>
       </c>
       <c r="G589" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531177520752</v>
       </c>
       <c r="H589" t="n">
         <v>900</v>
@@ -17479,7 +17479,7 @@
         <v>21</v>
       </c>
       <c r="G590" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531177520752</v>
       </c>
       <c r="H590" t="n">
         <v>20100</v>
@@ -17537,7 +17537,7 @@
         <v>21</v>
       </c>
       <c r="G592" t="n">
-        <v>18.5531158447266</v>
+        <v>18.5531177520752</v>
       </c>
       <c r="H592" t="n">
         <v>2325</v>
@@ -17566,7 +17566,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>18.7298107147217</v>
+        <v>18.7298126220703</v>
       </c>
       <c r="H593" t="n">
         <v>1500</v>
@@ -17595,7 +17595,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>18.9065093994141</v>
+        <v>18.9065074920654</v>
       </c>
       <c r="H594" t="n">
         <v>9375</v>
@@ -17653,7 +17653,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>20.6734714508057</v>
+        <v>20.673469543457</v>
       </c>
       <c r="H596" t="n">
         <v>39600</v>
@@ -17682,7 +17682,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H597" t="n">
         <v>13125</v>
@@ -17827,7 +17827,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>20.1433811187744</v>
+        <v>20.143383026123</v>
       </c>
       <c r="H602" t="n">
         <v>21825</v>
@@ -17856,7 +17856,7 @@
         <v>23</v>
       </c>
       <c r="G603" t="n">
-        <v>20.3200778961182</v>
+        <v>20.3200798034668</v>
       </c>
       <c r="H603" t="n">
         <v>11400</v>
@@ -17885,7 +17885,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H604" t="n">
         <v>19650</v>
@@ -17914,7 +17914,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H605" t="n">
         <v>10425</v>
@@ -17943,7 +17943,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G606" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H606" t="n">
         <v>10050</v>
@@ -17972,7 +17972,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>21.0268630981445</v>
+        <v>21.0268650054932</v>
       </c>
       <c r="H607" t="n">
         <v>5250</v>
@@ -18059,7 +18059,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>22.2637405395508</v>
+        <v>22.2637386322021</v>
       </c>
       <c r="H610" t="n">
         <v>10275</v>
@@ -18146,7 +18146,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G613" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H613" t="n">
         <v>11775</v>
@@ -18204,7 +18204,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H615" t="n">
         <v>7875</v>
@@ -18320,7 +18320,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472206115723</v>
       </c>
       <c r="H619" t="n">
         <v>8100</v>
@@ -18465,7 +18465,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H624" t="n">
         <v>6075</v>
@@ -18494,7 +18494,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H625" t="n">
         <v>17550</v>
@@ -18552,7 +18552,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H627" t="n">
         <v>16800</v>
@@ -18581,7 +18581,7 @@
         <v>32</v>
       </c>
       <c r="G628" t="n">
-        <v>28.271411895752</v>
+        <v>28.2714138031006</v>
       </c>
       <c r="H628" t="n">
         <v>13350</v>
@@ -18610,7 +18610,7 @@
         <v>32</v>
       </c>
       <c r="G629" t="n">
-        <v>28.271411895752</v>
+        <v>28.2714138031006</v>
       </c>
       <c r="H629" t="n">
         <v>15375</v>
@@ -18639,7 +18639,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H630" t="n">
         <v>11250</v>
@@ -18697,7 +18697,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>30.7451610565186</v>
+        <v>30.7451629638672</v>
       </c>
       <c r="H632" t="n">
         <v>23025</v>
@@ -18755,7 +18755,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0985546112061</v>
+        <v>31.0985527038574</v>
       </c>
       <c r="H634" t="n">
         <v>8625</v>
@@ -18784,7 +18784,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.5684604644775</v>
+        <v>30.5684661865234</v>
       </c>
       <c r="H635" t="n">
         <v>3900</v>
@@ -18813,7 +18813,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>30.5684604644775</v>
+        <v>30.5684661865234</v>
       </c>
       <c r="H636" t="n">
         <v>21300</v>
@@ -18842,7 +18842,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>30.7451610565186</v>
+        <v>30.7451629638672</v>
       </c>
       <c r="H637" t="n">
         <v>1725</v>
@@ -18929,7 +18929,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082874298096</v>
+        <v>29.5082855224609</v>
       </c>
       <c r="H640" t="n">
         <v>11100</v>
@@ -19016,7 +19016,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H643" t="n">
         <v>2100</v>
@@ -19074,7 +19074,7 @@
         <v>32</v>
       </c>
       <c r="G645" t="n">
-        <v>28.271411895752</v>
+        <v>28.2714138031006</v>
       </c>
       <c r="H645" t="n">
         <v>9750</v>
@@ -19103,7 +19103,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H646" t="n">
         <v>10950</v>
@@ -19219,7 +19219,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H650" t="n">
         <v>15450</v>
@@ -19277,7 +19277,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H652" t="n">
         <v>5025</v>
@@ -19422,7 +19422,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H657" t="n">
         <v>2325</v>
@@ -19451,7 +19451,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H658" t="n">
         <v>975</v>
@@ -19480,7 +19480,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H659" t="n">
         <v>4200</v>
@@ -19509,7 +19509,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H660" t="n">
         <v>2700</v>
@@ -19538,7 +19538,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H661" t="n">
         <v>7575</v>
@@ -19596,7 +19596,7 @@
         <v>33</v>
       </c>
       <c r="G663" t="n">
-        <v>29.1548976898193</v>
+        <v>29.1548938751221</v>
       </c>
       <c r="H663" t="n">
         <v>5700</v>
@@ -19712,7 +19712,7 @@
         <v>34</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0383777618408</v>
+        <v>30.0383796691895</v>
       </c>
       <c r="H667" t="n">
         <v>6825</v>
@@ -19915,7 +19915,7 @@
         <v>33</v>
       </c>
       <c r="G674" t="n">
-        <v>29.1548976898193</v>
+        <v>29.1548938751221</v>
       </c>
       <c r="H674" t="n">
         <v>2400</v>
@@ -20002,7 +20002,7 @@
         <v>33</v>
       </c>
       <c r="G677" t="n">
-        <v>29.1548976898193</v>
+        <v>29.1548938751221</v>
       </c>
       <c r="H677" t="n">
         <v>6300</v>
@@ -20060,7 +20060,7 @@
         <v>32</v>
       </c>
       <c r="G679" t="n">
-        <v>28.271411895752</v>
+        <v>28.2714138031006</v>
       </c>
       <c r="H679" t="n">
         <v>11925</v>
@@ -20089,7 +20089,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H680" t="n">
         <v>4875</v>
@@ -20147,7 +20147,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>28.0947151184082</v>
+        <v>28.0947170257568</v>
       </c>
       <c r="H682" t="n">
         <v>5625</v>
@@ -20176,7 +20176,7 @@
         <v>32</v>
       </c>
       <c r="G683" t="n">
-        <v>28.271411895752</v>
+        <v>28.2714138031006</v>
       </c>
       <c r="H683" t="n">
         <v>2400</v>
@@ -20234,7 +20234,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>28.448112487793</v>
+        <v>28.4481086730957</v>
       </c>
       <c r="H685" t="n">
         <v>8100</v>
@@ -20263,7 +20263,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>28.8015003204346</v>
+        <v>28.8015022277832</v>
       </c>
       <c r="H686" t="n">
         <v>2250</v>
@@ -20292,7 +20292,7 @@
         <v>32</v>
       </c>
       <c r="G687" t="n">
-        <v>28.271411895752</v>
+        <v>28.2714138031006</v>
       </c>
       <c r="H687" t="n">
         <v>6750</v>
@@ -20321,7 +20321,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H688" t="n">
         <v>9075</v>
@@ -20350,7 +20350,7 @@
         <v>31</v>
       </c>
       <c r="G689" t="n">
-        <v>27.3879299163818</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H689" t="n">
         <v>1500</v>
@@ -20408,7 +20408,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H691" t="n">
         <v>5250</v>
@@ -20466,7 +20466,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>25.4442729949951</v>
+        <v>25.4442710876465</v>
       </c>
       <c r="H693" t="n">
         <v>5025</v>
@@ -20495,7 +20495,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H694" t="n">
         <v>24825</v>
@@ -20582,7 +20582,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H697" t="n">
         <v>1800</v>
@@ -20611,7 +20611,7 @@
         <v>32</v>
       </c>
       <c r="G698" t="n">
-        <v>28.271411895752</v>
+        <v>28.2714138031006</v>
       </c>
       <c r="H698" t="n">
         <v>4950</v>
@@ -20698,7 +20698,7 @@
         <v>32</v>
       </c>
       <c r="G701" t="n">
-        <v>28.271411895752</v>
+        <v>28.2714138031006</v>
       </c>
       <c r="H701" t="n">
         <v>1875</v>
@@ -20727,7 +20727,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.741325378418</v>
+        <v>27.7413234710693</v>
       </c>
       <c r="H702" t="n">
         <v>825</v>
@@ -20756,7 +20756,7 @@
         <v>31</v>
       </c>
       <c r="G703" t="n">
-        <v>27.3879299163818</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H703" t="n">
         <v>12375</v>
@@ -20785,7 +20785,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H704" t="n">
         <v>1350</v>
@@ -20814,7 +20814,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H705" t="n">
         <v>2550</v>
@@ -20872,7 +20872,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G707" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H707" t="n">
         <v>4125</v>
@@ -21046,7 +21046,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H713" t="n">
         <v>900</v>
@@ -21075,7 +21075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H714" t="n">
         <v>2100</v>
@@ -21104,7 +21104,7 @@
         <v>31</v>
       </c>
       <c r="G715" t="n">
-        <v>27.3879299163818</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H715" t="n">
         <v>2700</v>
@@ -21133,7 +21133,7 @@
         <v>31</v>
       </c>
       <c r="G716" t="n">
-        <v>27.3879299163818</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H716" t="n">
         <v>600</v>
@@ -21191,7 +21191,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>26.8578433990479</v>
+        <v>26.8578414916992</v>
       </c>
       <c r="H718" t="n">
         <v>375</v>
@@ -21365,7 +21365,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H724" t="n">
         <v>2550</v>
@@ -21394,7 +21394,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H725" t="n">
         <v>4425</v>
@@ -21452,7 +21452,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>26.1510562896729</v>
+        <v>26.1510581970215</v>
       </c>
       <c r="H727" t="n">
         <v>3900</v>
@@ -21568,7 +21568,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>25.4442729949951</v>
+        <v>25.4442710876465</v>
       </c>
       <c r="H731" t="n">
         <v>750</v>
@@ -21655,7 +21655,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H734" t="n">
         <v>2550</v>
@@ -21684,7 +21684,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H735" t="n">
         <v>7275</v>
@@ -21771,7 +21771,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H738" t="n">
         <v>825</v>
@@ -21887,7 +21887,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H742" t="n">
         <v>300</v>
@@ -21916,7 +21916,7 @@
         <v>29</v>
       </c>
       <c r="G743" t="n">
-        <v>25.6209678649902</v>
+        <v>25.6209697723389</v>
       </c>
       <c r="H743" t="n">
         <v>1425</v>
@@ -22003,7 +22003,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H746" t="n">
         <v>675</v>
@@ -22061,7 +22061,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>24.2073974609375</v>
+        <v>24.2073993682861</v>
       </c>
       <c r="H748" t="n">
         <v>2025</v>
@@ -22264,7 +22264,7 @@
         <v>25</v>
       </c>
       <c r="G755" t="n">
-        <v>22.0870418548584</v>
+        <v>22.087043762207</v>
       </c>
       <c r="H755" t="n">
         <v>2775</v>
@@ -22380,7 +22380,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>20.8501682281494</v>
+        <v>20.8501644134521</v>
       </c>
       <c r="H759" t="n">
         <v>2625</v>
@@ -22409,7 +22409,7 @@
         <v>25</v>
       </c>
       <c r="G760" t="n">
-        <v>22.0870418548584</v>
+        <v>22.087043762207</v>
       </c>
       <c r="H760" t="n">
         <v>9750</v>
@@ -22467,7 +22467,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>24.9141845703125</v>
+        <v>24.9141864776611</v>
       </c>
       <c r="H762" t="n">
         <v>1650</v>
@@ -22612,7 +22612,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>25.090877532959</v>
+        <v>25.0908794403076</v>
       </c>
       <c r="H767" t="n">
         <v>375</v>
@@ -22670,7 +22670,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H769" t="n">
         <v>2025</v>
@@ -22699,7 +22699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H770" t="n">
         <v>2925</v>
@@ -22757,7 +22757,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>27.034538269043</v>
+        <v>27.0345401763916</v>
       </c>
       <c r="H772" t="n">
         <v>1200</v>
@@ -22815,7 +22815,7 @@
         <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>27.3879299163818</v>
+        <v>27.3879337310791</v>
       </c>
       <c r="H774" t="n">
         <v>2850</v>
@@ -22873,7 +22873,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>26.6811485290527</v>
+        <v>26.6811466217041</v>
       </c>
       <c r="H776" t="n">
         <v>2550</v>
@@ -22902,7 +22902,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>25.4442729949951</v>
+        <v>25.4442710876465</v>
       </c>
       <c r="H777" t="n">
         <v>8550</v>
@@ -22989,7 +22989,7 @@
         <v>29</v>
       </c>
       <c r="G780" t="n">
-        <v>25.6209678649902</v>
+        <v>25.6209697723389</v>
       </c>
       <c r="H780" t="n">
         <v>2100</v>
@@ -23018,7 +23018,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>25.5326175689697</v>
+        <v>25.532621383667</v>
       </c>
       <c r="H781" t="n">
         <v>300</v>
@@ -23192,7 +23192,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G787" t="n">
-        <v>23.1472187042236</v>
+        <v>23.1472206115723</v>
       </c>
       <c r="H787" t="n">
         <v>1650</v>
@@ -23221,7 +23221,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H788" t="n">
         <v>75</v>
@@ -23250,7 +23250,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H789" t="n">
         <v>300</v>
@@ -23279,7 +23279,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>23.5006141662598</v>
+        <v>23.5006122589111</v>
       </c>
       <c r="H790" t="n">
         <v>0</v>
@@ -23308,7 +23308,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>22.7054805755615</v>
+        <v>22.7054786682129</v>
       </c>
       <c r="H791" t="n">
         <v>2550</v>
@@ -23453,7 +23453,7 @@
         <v>28.5</v>
       </c>
       <c r="G796" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H796" t="n">
         <v>4875</v>
@@ -23482,7 +23482,7 @@
         <v>28.5</v>
       </c>
       <c r="G797" t="n">
-        <v>25.1792278289795</v>
+        <v>25.1792259216309</v>
       </c>
       <c r="H797" t="n">
         <v>1950</v>
@@ -23569,7 +23569,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>25.4490051269531</v>
+        <v>25.4490032196045</v>
       </c>
       <c r="H800" t="n">
         <v>2925</v>
@@ -23656,7 +23656,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>23.9202671051025</v>
+        <v>23.9202651977539</v>
       </c>
       <c r="H803" t="n">
         <v>2625</v>
@@ -23743,7 +23743,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H806" t="n">
         <v>2175</v>
@@ -23772,7 +23772,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H807" t="n">
         <v>75</v>
@@ -23801,7 +23801,7 @@
         <v>27</v>
       </c>
       <c r="G808" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>27</v>
       </c>
       <c r="G810" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H810" t="n">
         <v>75</v>
@@ -23888,7 +23888,7 @@
         <v>27</v>
       </c>
       <c r="G811" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H811" t="n">
         <v>150</v>
@@ -24062,7 +24062,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H817" t="n">
         <v>450</v>
@@ -24091,7 +24091,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H818" t="n">
         <v>375</v>
@@ -24236,7 +24236,7 @@
         <v>26.5</v>
       </c>
       <c r="G823" t="n">
-        <v>23.8303413391113</v>
+        <v>23.8303394317627</v>
       </c>
       <c r="H823" t="n">
         <v>825</v>
@@ -24265,7 +24265,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>23.5605621337891</v>
+        <v>23.5605640411377</v>
       </c>
       <c r="H824" t="n">
         <v>825</v>
@@ -24294,7 +24294,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G825" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H825" t="n">
         <v>300</v>
@@ -24323,7 +24323,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H826" t="n">
         <v>1500</v>
@@ -24439,7 +24439,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>23.5605621337891</v>
+        <v>23.5605640411377</v>
       </c>
       <c r="H830" t="n">
         <v>5925</v>
@@ -24700,7 +24700,7 @@
         <v>25.5</v>
       </c>
       <c r="G839" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24729,7 +24729,7 @@
         <v>25.5</v>
       </c>
       <c r="G840" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H840" t="n">
         <v>300</v>
@@ -24758,7 +24758,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>22.6613063812256</v>
+        <v>22.661304473877</v>
       </c>
       <c r="H841" t="n">
         <v>150</v>
@@ -24787,7 +24787,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>22.1217517852783</v>
+        <v>22.1217498779297</v>
       </c>
       <c r="H842" t="n">
         <v>825</v>
@@ -24874,7 +24874,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>21.3124179840088</v>
+        <v>21.3124160766602</v>
       </c>
       <c r="H845" t="n">
         <v>825</v>
@@ -24903,7 +24903,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>21.6721229553223</v>
+        <v>21.6721210479736</v>
       </c>
       <c r="H846" t="n">
         <v>2550</v>
@@ -24932,7 +24932,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H847" t="n">
         <v>300</v>
@@ -24961,7 +24961,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H848" t="n">
         <v>2100</v>
@@ -24990,7 +24990,7 @@
         <v>25</v>
       </c>
       <c r="G849" t="n">
-        <v>22.4814529418945</v>
+        <v>22.4814548492432</v>
       </c>
       <c r="H849" t="n">
         <v>1725</v>
@@ -25048,7 +25048,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>21.4023418426514</v>
+        <v>21.4023456573486</v>
       </c>
       <c r="H851" t="n">
         <v>300</v>
@@ -25193,7 +25193,7 @@
         <v>22</v>
       </c>
       <c r="G856" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H856" t="n">
         <v>5700</v>
@@ -25222,7 +25222,7 @@
         <v>22</v>
       </c>
       <c r="G857" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H857" t="n">
         <v>2925</v>
@@ -25251,7 +25251,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>19.5139007568359</v>
+        <v>19.5139026641846</v>
       </c>
       <c r="H858" t="n">
         <v>1275</v>
@@ -25367,7 +25367,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>19.6937522888184</v>
+        <v>19.693754196167</v>
       </c>
       <c r="H862" t="n">
         <v>1500</v>
@@ -25425,7 +25425,7 @@
         <v>21.5</v>
       </c>
       <c r="G864" t="n">
-        <v>19.3340511322021</v>
+        <v>19.3340492248535</v>
       </c>
       <c r="H864" t="n">
         <v>300</v>
@@ -25541,7 +25541,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G868" t="n">
-        <v>21.6721229553223</v>
+        <v>21.6721210479736</v>
       </c>
       <c r="H868" t="n">
         <v>6300</v>
@@ -25570,7 +25570,7 @@
         <v>25</v>
       </c>
       <c r="G869" t="n">
-        <v>22.4814529418945</v>
+        <v>22.4814548492432</v>
       </c>
       <c r="H869" t="n">
         <v>5550</v>
@@ -25599,7 +25599,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.3915271759033</v>
+        <v>22.391529083252</v>
       </c>
       <c r="H870" t="n">
         <v>4050</v>
@@ -25657,7 +25657,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H872" t="n">
         <v>2475</v>
@@ -25686,7 +25686,7 @@
         <v>25.5</v>
       </c>
       <c r="G873" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H873" t="n">
         <v>1650</v>
@@ -25715,7 +25715,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H874" t="n">
         <v>2400</v>
@@ -25744,7 +25744,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>21.4922676086426</v>
+        <v>21.4922695159912</v>
       </c>
       <c r="H876" t="n">
         <v>7725</v>
@@ -25802,7 +25802,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>20.5030841827393</v>
+        <v>20.5030860900879</v>
       </c>
       <c r="H877" t="n">
         <v>6075</v>
@@ -25831,7 +25831,7 @@
         <v>23</v>
       </c>
       <c r="G878" t="n">
-        <v>20.6829357147217</v>
+        <v>20.6829376220703</v>
       </c>
       <c r="H878" t="n">
         <v>10800</v>
@@ -25860,7 +25860,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>20.5030841827393</v>
+        <v>20.5030860900879</v>
       </c>
       <c r="H879" t="n">
         <v>1200</v>
@@ -25947,7 +25947,7 @@
         <v>22</v>
       </c>
       <c r="G882" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H882" t="n">
         <v>750</v>
@@ -26034,7 +26034,7 @@
         <v>22</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H885" t="n">
         <v>11025</v>
@@ -26063,7 +26063,7 @@
         <v>22</v>
       </c>
       <c r="G886" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H886" t="n">
         <v>4800</v>
@@ -26092,7 +26092,7 @@
         <v>22</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H887" t="n">
         <v>3975</v>
@@ -26121,7 +26121,7 @@
         <v>22</v>
       </c>
       <c r="G888" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H888" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>22</v>
       </c>
       <c r="G889" t="n">
-        <v>19.7836799621582</v>
+        <v>19.7836780548096</v>
       </c>
       <c r="H889" t="n">
         <v>1050</v>
@@ -26179,7 +26179,7 @@
         <v>23</v>
       </c>
       <c r="G890" t="n">
-        <v>20.6829357147217</v>
+        <v>20.6829376220703</v>
       </c>
       <c r="H890" t="n">
         <v>31200</v>
@@ -26266,7 +26266,7 @@
         <v>27</v>
       </c>
       <c r="G893" t="n">
-        <v>24.2799682617188</v>
+        <v>24.2799701690674</v>
       </c>
       <c r="H893" t="n">
         <v>14100</v>
@@ -26411,7 +26411,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>23.1109352111816</v>
+        <v>23.110933303833</v>
       </c>
       <c r="H898" t="n">
         <v>26925</v>
@@ -26440,7 +26440,7 @@
         <v>25.5</v>
       </c>
       <c r="G899" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H899" t="n">
         <v>16275</v>
@@ -26469,7 +26469,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H900" t="n">
         <v>1125</v>
@@ -26498,7 +26498,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>22.5713806152344</v>
+        <v>22.5713787078857</v>
       </c>
       <c r="H901" t="n">
         <v>1725</v>
@@ -26643,7 +26643,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>22.1217517852783</v>
+        <v>22.1217498779297</v>
       </c>
       <c r="H906" t="n">
         <v>1200</v>
@@ -26672,7 +26672,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.3915271759033</v>
+        <v>22.391529083252</v>
       </c>
       <c r="H907" t="n">
         <v>3225</v>
@@ -26730,7 +26730,7 @@
         <v>25.5</v>
       </c>
       <c r="G909" t="n">
-        <v>22.9310817718506</v>
+        <v>22.931079864502</v>
       </c>
       <c r="H909" t="n">
         <v>300</v>
@@ -26759,7 +26759,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>22.841157913208</v>
+        <v>22.8411560058594</v>
       </c>
       <c r="H910" t="n">
         <v>2250</v>
@@ -26788,7 +26788,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H911" t="n">
         <v>225</v>
@@ -26875,7 +26875,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.3915271759033</v>
+        <v>22.391529083252</v>
       </c>
       <c r="H914" t="n">
         <v>75</v>
@@ -26962,7 +26962,7 @@
         <v>25</v>
       </c>
       <c r="G917" t="n">
-        <v>22.4814529418945</v>
+        <v>22.4814548492432</v>
       </c>
       <c r="H917" t="n">
         <v>1200</v>
@@ -26991,7 +26991,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H918" t="n">
         <v>5175</v>
@@ -27107,7 +27107,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H922" t="n">
         <v>1050</v>
@@ -27136,7 +27136,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>22.7512283325195</v>
+        <v>22.7512302398682</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>23.1109352111816</v>
+        <v>23.110933303833</v>
       </c>
       <c r="H925" t="n">
         <v>375</v>
@@ -27223,7 +27223,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>23.1109352111816</v>
+        <v>23.110933303833</v>
       </c>
       <c r="H926" t="n">
         <v>825</v>
@@ -27281,7 +27281,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>22.5713806152344</v>
+        <v>22.5713787078857</v>
       </c>
       <c r="H928" t="n">
         <v>300</v>
@@ -27397,7 +27397,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G932" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H932" t="n">
         <v>2625</v>
@@ -27426,7 +27426,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H933" t="n">
         <v>4500</v>
@@ -27513,7 +27513,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H936" t="n">
         <v>1875</v>
@@ -27716,7 +27716,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H943" t="n">
         <v>21450</v>
@@ -27745,7 +27745,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H948" t="n">
         <v>4950</v>
@@ -27890,7 +27890,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H949" t="n">
         <v>1650</v>
@@ -27919,7 +27919,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H950" t="n">
         <v>6600</v>
@@ -27948,7 +27948,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H951" t="n">
         <v>3300</v>
@@ -27977,7 +27977,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H952" t="n">
         <v>2325</v>
@@ -28035,7 +28035,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>26.7978916168213</v>
+        <v>26.7978935241699</v>
       </c>
       <c r="H954" t="n">
         <v>69075</v>
@@ -28064,7 +28064,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H955" t="n">
         <v>1050</v>
@@ -28093,7 +28093,7 @@
         <v>30.5</v>
       </c>
       <c r="G956" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H956" t="n">
         <v>3300</v>
@@ -28122,7 +28122,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>27.697151184082</v>
+        <v>27.6971492767334</v>
       </c>
       <c r="H957" t="n">
         <v>10950</v>
@@ -28151,7 +28151,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>28.4165573120117</v>
+        <v>28.4165592193604</v>
       </c>
       <c r="H958" t="n">
         <v>6825</v>
@@ -28180,7 +28180,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G959" t="n">
-        <v>29.3158130645752</v>
+        <v>29.3158149719238</v>
       </c>
       <c r="H959" t="n">
         <v>6600</v>
@@ -28238,7 +28238,7 @@
         <v>30.5</v>
       </c>
       <c r="G961" t="n">
-        <v>27.4273719787598</v>
+        <v>27.4273738861084</v>
       </c>
       <c r="H961" t="n">
         <v>5175</v>
@@ -28267,7 +28267,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G962" t="n">
-        <v>27.247522354126</v>
+        <v>27.2475185394287</v>
       </c>
       <c r="H962" t="n">
         <v>1950</v>
@@ -28441,7 +28441,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H968" t="n">
         <v>450</v>
@@ -28615,7 +28615,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H974" t="n">
         <v>75</v>
@@ -28644,7 +28644,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.9885578155518</v>
+        <v>25.9885597229004</v>
       </c>
       <c r="H976" t="n">
         <v>375</v>
@@ -28702,7 +28702,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H977" t="n">
         <v>750</v>
@@ -28731,7 +28731,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>26.1684131622314</v>
+        <v>26.1684112548828</v>
       </c>
       <c r="H978" t="n">
         <v>450</v>
@@ -28760,7 +28760,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>26.3482608795166</v>
+        <v>26.3482627868652</v>
       </c>
       <c r="H979" t="n">
         <v>4275</v>
@@ -28789,7 +28789,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H980" t="n">
         <v>6150</v>
@@ -28876,7 +28876,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>24.8195247650146</v>
+        <v>24.819522857666</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -29021,7 +29021,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>24.4598236083984</v>
+        <v>24.4598217010498</v>
       </c>
       <c r="H988" t="n">
         <v>675</v>
@@ -29224,7 +29224,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H995" t="n">
         <v>525</v>
@@ -29485,7 +29485,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>25.5389289855957</v>
+        <v>25.5389308929443</v>
       </c>
       <c r="H1004" t="n">
         <v>1050</v>
@@ -29601,7 +29601,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>24.6396713256836</v>
+        <v>24.6396732330322</v>
       </c>
       <c r="H1008" t="n">
         <v>17250</v>
@@ -29630,7 +29630,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>24.8195247650146</v>
+        <v>24.819522857666</v>
       </c>
       <c r="H1009" t="n">
         <v>750</v>
@@ -29775,7 +29775,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>26.6180400848389</v>
+        <v>26.6180419921875</v>
       </c>
       <c r="H1014" t="n">
         <v>2175</v>
@@ -29804,7 +29804,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>27.247522354126</v>
+        <v>27.2475185394287</v>
       </c>
       <c r="H1015" t="n">
         <v>2625</v>
@@ -29978,7 +29978,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>27.517297744751</v>
+        <v>27.5172996520996</v>
       </c>
       <c r="H1021" t="n">
         <v>5400</v>
@@ -30036,7 +30036,7 @@
         <v>31</v>
       </c>
       <c r="G1023" t="n">
-        <v>27.8770008087158</v>
+        <v>27.8770027160645</v>
       </c>
       <c r="H1023" t="n">
         <v>9450</v>
@@ -30065,7 +30065,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>28.1467800140381</v>
+        <v>28.1467781066895</v>
       </c>
       <c r="H1024" t="n">
         <v>1200</v>
@@ -30094,7 +30094,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>28.2367057800293</v>
+        <v>28.2367038726807</v>
       </c>
       <c r="H1025" t="n">
         <v>2475</v>
@@ -30123,7 +30123,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>29.405740737915</v>
+        <v>29.4057426452637</v>
       </c>
       <c r="H1026" t="n">
         <v>2025</v>
@@ -30181,7 +30181,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>29.0460376739502</v>
+        <v>29.0460357666016</v>
       </c>
       <c r="H1028" t="n">
         <v>4350</v>
@@ -30210,7 +30210,7 @@
         <v>33</v>
       </c>
       <c r="G1029" t="n">
-        <v>29.6755199432373</v>
+        <v>29.6755180358887</v>
       </c>
       <c r="H1029" t="n">
         <v>2700</v>
@@ -30268,7 +30268,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1031" t="n">
         <v>1050</v>
@@ -30326,7 +30326,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>28.9561138153076</v>
+        <v>28.9561100006104</v>
       </c>
       <c r="H1033" t="n">
         <v>1575</v>
@@ -30355,7 +30355,7 @@
         <v>32.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>29.225887298584</v>
+        <v>29.2258892059326</v>
       </c>
       <c r="H1034" t="n">
         <v>1500</v>
@@ -30413,7 +30413,7 @@
         <v>32</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.7762584686279</v>
+        <v>28.7762603759766</v>
       </c>
       <c r="H1036" t="n">
         <v>3075</v>
@@ -30529,7 +30529,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639591217041</v>
+        <v>31.5639610290527</v>
       </c>
       <c r="H1040" t="n">
         <v>4425</v>
@@ -30558,7 +30558,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.8337383270264</v>
+        <v>31.8337364196777</v>
       </c>
       <c r="H1041" t="n">
         <v>7800</v>
@@ -30587,7 +30587,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2941818237305</v>
+        <v>31.2941837310791</v>
       </c>
       <c r="H1042" t="n">
         <v>4200</v>
@@ -30616,7 +30616,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>31.2941818237305</v>
+        <v>31.2941837310791</v>
       </c>
       <c r="H1043" t="n">
         <v>3750</v>
@@ -30645,7 +30645,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042541503906</v>
+        <v>31.2042579650879</v>
       </c>
       <c r="H1044" t="n">
         <v>1425</v>
@@ -30674,7 +30674,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1045" t="n">
         <v>10575</v>
@@ -30732,7 +30732,7 @@
         <v>32</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7762584686279</v>
+        <v>28.7762603759766</v>
       </c>
       <c r="H1047" t="n">
         <v>14700</v>
@@ -30790,7 +30790,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3049983978271</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1049" t="n">
         <v>2100</v>
@@ -30877,7 +30877,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251468658447</v>
+        <v>30.1251449584961</v>
       </c>
       <c r="H1052" t="n">
         <v>675</v>
@@ -30906,7 +30906,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150707244873</v>
+        <v>30.2150688171387</v>
       </c>
       <c r="H1053" t="n">
         <v>525</v>
@@ -30935,7 +30935,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3049983978271</v>
+        <v>30.3050003051758</v>
       </c>
       <c r="H1054" t="n">
         <v>1050</v>
@@ -31051,7 +31051,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1058" t="n">
-        <v>29.405740737915</v>
+        <v>29.4057426452637</v>
       </c>
       <c r="H1058" t="n">
         <v>1575</v>
@@ -31109,7 +31109,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1060" t="n">
-        <v>28.5064830780029</v>
+        <v>28.5064849853516</v>
       </c>
       <c r="H1060" t="n">
         <v>2175</v>
@@ -31138,7 +31138,7 @@
         <v>32</v>
       </c>
       <c r="G1061" t="n">
-        <v>28.7762584686279</v>
+        <v>28.7762603759766</v>
       </c>
       <c r="H1061" t="n">
         <v>95700</v>
@@ -31167,7 +31167,7 @@
         <v>32.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>29.225887298584</v>
+        <v>29.2258892059326</v>
       </c>
       <c r="H1062" t="n">
         <v>1050</v>
@@ -31196,7 +31196,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1063" t="n">
         <v>1650</v>
@@ -31312,7 +31312,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1067" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1067" t="n">
         <v>5775</v>
@@ -31341,7 +31341,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1068" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1068" t="n">
         <v>525</v>
@@ -31515,7 +31515,7 @@
         <v>32.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1074" t="n">
         <v>975</v>
@@ -31573,7 +31573,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1076" t="n">
         <v>3600</v>
@@ -31602,7 +31602,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1077" t="n">
         <v>450</v>
@@ -31631,7 +31631,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1078" t="n">
         <v>300</v>
@@ -31660,7 +31660,7 @@
         <v>31.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1079" t="n">
         <v>1350</v>
@@ -31689,7 +31689,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1080" t="n">
         <v>14100</v>
@@ -31718,7 +31718,7 @@
         <v>31.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1081" t="n">
         <v>7125</v>
@@ -31776,7 +31776,7 @@
         <v>31.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1083" t="n">
         <v>6450</v>
@@ -31863,7 +31863,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1086" t="n">
         <v>2100</v>
@@ -31979,7 +31979,7 @@
         <v>31.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1090" t="n">
         <v>150</v>
@@ -32008,7 +32008,7 @@
         <v>31.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1091" t="n">
         <v>75</v>
@@ -32037,7 +32037,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1092" t="n">
         <v>450</v>
@@ -32124,7 +32124,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1095" t="n">
         <v>600</v>
@@ -32153,7 +32153,7 @@
         <v>32.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1096" t="n">
         <v>2550</v>
@@ -32182,7 +32182,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1097" t="n">
         <v>2400</v>
@@ -32704,7 +32704,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1115" t="n">
         <v>1069</v>
@@ -32762,7 +32762,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>30.1003665924072</v>
+        <v>30.1003646850586</v>
       </c>
       <c r="H1117" t="n">
         <v>874</v>
@@ -32791,7 +32791,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1118" t="n">
-        <v>30.1003665924072</v>
+        <v>30.1003646850586</v>
       </c>
       <c r="H1118" t="n">
         <v>404</v>
@@ -32820,7 +32820,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1119" t="n">
         <v>1426</v>
@@ -32849,7 +32849,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1120" t="n">
         <v>683</v>
@@ -32907,7 +32907,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1122" t="n">
         <v>791</v>
@@ -33139,7 +33139,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1130" t="n">
         <v>147</v>
@@ -33197,7 +33197,7 @@
         <v>32.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1132" t="n">
         <v>235</v>
@@ -33226,7 +33226,7 @@
         <v>32.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1133" t="n">
         <v>397</v>
@@ -33255,7 +33255,7 @@
         <v>32.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1134" t="n">
         <v>300</v>
@@ -33458,7 +33458,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1141" t="n">
         <v>1405</v>
@@ -33487,7 +33487,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1142" t="n">
         <v>1568</v>
@@ -33574,7 +33574,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1145" t="n">
         <v>240</v>
@@ -33690,7 +33690,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1149" t="n">
         <v>1616</v>
@@ -33748,7 +33748,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1151" t="n">
         <v>773</v>
@@ -33777,7 +33777,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1152" t="n">
         <v>442</v>
@@ -33806,7 +33806,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1153" t="n">
         <v>365</v>
@@ -34009,7 +34009,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.8786125183105</v>
+        <v>26.8786144256592</v>
       </c>
       <c r="H1160" t="n">
         <v>1105</v>
@@ -34096,7 +34096,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1163" t="n">
         <v>1128</v>
@@ -34125,7 +34125,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1164" t="n">
         <v>5262</v>
@@ -34212,7 +34212,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1167" t="n">
         <v>1240</v>
@@ -34241,7 +34241,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1168" t="n">
         <v>7918</v>
@@ -34270,7 +34270,7 @@
         <v>27.5</v>
       </c>
       <c r="G1169" t="n">
-        <v>25.3137607574463</v>
+        <v>25.3137626647949</v>
       </c>
       <c r="H1169" t="n">
         <v>3413</v>
@@ -34299,7 +34299,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1170" t="n">
         <v>1331</v>
@@ -34328,7 +34328,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1171" t="n">
         <v>1864</v>
@@ -34357,7 +34357,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1172" t="n">
         <v>10192</v>
@@ -34386,7 +34386,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1173" t="n">
         <v>27679</v>
@@ -34415,7 +34415,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1174" t="n">
         <v>300</v>
@@ -34444,7 +34444,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>24.9455623626709</v>
+        <v>24.9455642700195</v>
       </c>
       <c r="H1175" t="n">
         <v>596</v>
@@ -34473,7 +34473,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1176" t="n">
         <v>119</v>
@@ -34502,7 +34502,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1177" t="n">
         <v>572</v>
@@ -34531,7 +34531,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1178" t="n">
         <v>572</v>
@@ -34647,7 +34647,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966114044189</v>
+        <v>23.1966133117676</v>
       </c>
       <c r="H1182" t="n">
         <v>16419</v>
@@ -34676,7 +34676,7 @@
         <v>25</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0125122070312</v>
+        <v>23.0125102996826</v>
       </c>
       <c r="H1183" t="n">
         <v>6634</v>
@@ -34734,7 +34734,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1185" t="n">
         <v>3901</v>
@@ -34763,7 +34763,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1186" t="n">
         <v>4535</v>
@@ -34792,7 +34792,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1187" t="n">
         <v>1957</v>
@@ -34821,7 +34821,7 @@
         <v>26.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>24.3932628631592</v>
+        <v>24.3932609558105</v>
       </c>
       <c r="H1188" t="n">
         <v>550</v>
@@ -34879,7 +34879,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1190" t="n">
         <v>3364</v>
@@ -34966,7 +34966,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171131134033</v>
+        <v>24.1171112060547</v>
       </c>
       <c r="H1193" t="n">
         <v>5553</v>
@@ -34995,7 +34995,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1194" t="n">
         <v>6387</v>
@@ -35024,7 +35024,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1195" t="n">
         <v>15303</v>
@@ -35169,7 +35169,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.9455623626709</v>
+        <v>24.9455642700195</v>
       </c>
       <c r="H1200" t="n">
         <v>2435</v>
@@ -35198,7 +35198,7 @@
         <v>27</v>
       </c>
       <c r="G1201" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1201" t="n">
         <v>345</v>
@@ -35256,7 +35256,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1203" t="n">
         <v>250</v>
@@ -35285,7 +35285,7 @@
         <v>26.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3932628631592</v>
+        <v>24.3932609558105</v>
       </c>
       <c r="H1204" t="n">
         <v>2078</v>
@@ -35401,7 +35401,7 @@
         <v>27</v>
       </c>
       <c r="G1208" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1208" t="n">
         <v>6977</v>
@@ -35575,7 +35575,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1214" t="n">
         <v>1681</v>
@@ -35604,7 +35604,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>26.8786125183105</v>
+        <v>26.8786144256592</v>
       </c>
       <c r="H1215" t="n">
         <v>2568</v>
@@ -35836,7 +35836,7 @@
         <v>29</v>
       </c>
       <c r="G1223" t="n">
-        <v>26.6945152282715</v>
+        <v>26.6945133209229</v>
       </c>
       <c r="H1223" t="n">
         <v>4183</v>
@@ -36010,7 +36010,7 @@
         <v>28</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.7740116119385</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1229" t="n">
         <v>4634</v>
@@ -36097,7 +36097,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1232" t="n">
         <v>4851</v>
@@ -36155,7 +36155,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1234" t="n">
         <v>2409</v>
@@ -36184,7 +36184,7 @@
         <v>28</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.7740116119385</v>
+        <v>25.7740135192871</v>
       </c>
       <c r="H1235" t="n">
         <v>2267</v>
@@ -36213,7 +36213,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1236" t="n">
         <v>5154</v>
@@ -36329,7 +36329,7 @@
         <v>27.5</v>
       </c>
       <c r="G1240" t="n">
-        <v>25.3137607574463</v>
+        <v>25.3137626647949</v>
       </c>
       <c r="H1240" t="n">
         <v>499</v>
@@ -36387,7 +36387,7 @@
         <v>27</v>
       </c>
       <c r="G1242" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1242" t="n">
         <v>4303</v>
@@ -36416,7 +36416,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1243" t="n">
         <v>11050</v>
@@ -36445,7 +36445,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376129150391</v>
+        <v>25.0376148223877</v>
       </c>
       <c r="H1244" t="n">
         <v>11217</v>
@@ -36474,7 +36474,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1245" t="n">
         <v>11733</v>
@@ -36503,7 +36503,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1246" t="n">
         <v>16021</v>
@@ -36532,7 +36532,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1247" t="n">
         <v>8843</v>
@@ -36561,7 +36561,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1248" t="n">
         <v>10327</v>
@@ -36590,7 +36590,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.6694107055664</v>
+        <v>24.669412612915</v>
       </c>
       <c r="H1249" t="n">
         <v>7712</v>
@@ -36619,7 +36619,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>24.7614612579346</v>
+        <v>24.7614631652832</v>
       </c>
       <c r="H1250" t="n">
         <v>7483</v>
@@ -36648,7 +36648,7 @@
         <v>27</v>
       </c>
       <c r="G1251" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1251" t="n">
         <v>2164</v>
@@ -36677,7 +36677,7 @@
         <v>27</v>
       </c>
       <c r="G1252" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1252" t="n">
         <v>1117</v>
@@ -36764,7 +36764,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1255" t="n">
         <v>3149</v>
@@ -36793,7 +36793,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1256" t="n">
         <v>3291</v>
@@ -36822,7 +36822,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>24.5773639678955</v>
+        <v>24.5773620605469</v>
       </c>
       <c r="H1257" t="n">
         <v>2319</v>
@@ -36880,7 +36880,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.933012008667</v>
+        <v>23.9330139160156</v>
       </c>
       <c r="H1259" t="n">
         <v>15177</v>
@@ -36938,7 +36938,7 @@
         <v>27</v>
       </c>
       <c r="G1261" t="n">
-        <v>24.8535137176514</v>
+        <v>24.8535118103027</v>
       </c>
       <c r="H1261" t="n">
         <v>4013</v>
@@ -36967,7 +36967,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>25.4978637695312</v>
+        <v>25.4978656768799</v>
       </c>
       <c r="H1262" t="n">
         <v>10735</v>
@@ -36996,7 +36996,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>25.9581146240234</v>
+        <v>25.9581127166748</v>
       </c>
       <c r="H1263" t="n">
         <v>5803</v>
@@ -37112,7 +37112,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627136230469</v>
+        <v>27.0627117156982</v>
       </c>
       <c r="H1267" t="n">
         <v>12740</v>
@@ -37199,7 +37199,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1270" t="n">
         <v>1818</v>
@@ -37257,7 +37257,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1272" t="n">
         <v>50004</v>
@@ -37286,7 +37286,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1273" t="n">
-        <v>28.7196159362793</v>
+        <v>28.7196140289307</v>
       </c>
       <c r="H1273" t="n">
         <v>8005</v>
@@ -37315,7 +37315,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1274" t="n">
-        <v>28.9037132263184</v>
+        <v>28.903715133667</v>
       </c>
       <c r="H1274" t="n">
         <v>4136</v>
@@ -37373,7 +37373,7 @@
         <v>31.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>28.9957656860352</v>
+        <v>28.9957637786865</v>
       </c>
       <c r="H1276" t="n">
         <v>13340</v>
@@ -37489,7 +37489,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.640115737915</v>
+        <v>29.6401176452637</v>
       </c>
       <c r="H1280" t="n">
         <v>2808</v>
@@ -37518,7 +37518,7 @@
         <v>32.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1281" t="n">
         <v>5505</v>
@@ -37547,7 +37547,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1282" t="n">
         <v>10071</v>
@@ -37576,7 +37576,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1283" t="n">
         <v>7498</v>
@@ -37721,7 +37721,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.0208644866943</v>
+        <v>31.020866394043</v>
       </c>
       <c r="H1288" t="n">
         <v>4493</v>
@@ -37808,7 +37808,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.7447147369385</v>
+        <v>30.7447166442871</v>
       </c>
       <c r="H1291" t="n">
         <v>10264</v>
@@ -38040,7 +38040,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288139343262</v>
+        <v>30.9288120269775</v>
       </c>
       <c r="H1299" t="n">
         <v>10536</v>
@@ -38098,7 +38098,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.8367652893066</v>
+        <v>30.836763381958</v>
       </c>
       <c r="H1301" t="n">
         <v>18694</v>
@@ -38185,7 +38185,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1304" t="n">
         <v>2779</v>
@@ -38243,7 +38243,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>30.5606174468994</v>
+        <v>30.5606155395508</v>
       </c>
       <c r="H1306" t="n">
         <v>1787</v>
@@ -38330,7 +38330,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>29.8242168426514</v>
+        <v>29.8242149353027</v>
       </c>
       <c r="H1309" t="n">
         <v>8681</v>
@@ -38388,7 +38388,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.535514831543</v>
+        <v>28.5355167388916</v>
       </c>
       <c r="H1311" t="n">
         <v>14200</v>
@@ -38475,7 +38475,7 @@
         <v>32.5</v>
       </c>
       <c r="G1314" t="n">
-        <v>29.9162635803223</v>
+        <v>29.9162654876709</v>
       </c>
       <c r="H1314" t="n">
         <v>4455</v>
@@ -38504,7 +38504,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>30.1003665924072</v>
+        <v>30.1003646850586</v>
       </c>
       <c r="H1315" t="n">
         <v>12589</v>
@@ -38562,7 +38562,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.0954246520996</v>
+        <v>29.095422744751</v>
       </c>
       <c r="H1317" t="n">
         <v>6125</v>
@@ -38765,7 +38765,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1324" t="n">
         <v>12844</v>
@@ -38823,7 +38823,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1326" t="n">
         <v>9621</v>
@@ -38852,7 +38852,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1327" t="n">
         <v>46167</v>
@@ -38881,7 +38881,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1328" t="n">
         <v>3959</v>
@@ -38997,7 +38997,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1332" t="n">
         <v>24982</v>
@@ -39026,7 +39026,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1333" t="n">
         <v>8601</v>
@@ -39055,7 +39055,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1334" t="n">
         <v>5309</v>
@@ -39084,7 +39084,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1335" t="n">
         <v>21621</v>
@@ -39113,7 +39113,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1336" t="n">
         <v>16181</v>
@@ -39142,7 +39142,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1337" t="n">
         <v>6822</v>
@@ -39171,7 +39171,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1338" t="n">
         <v>3455</v>
@@ -39200,7 +39200,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1339" t="n">
         <v>5494</v>
@@ -39229,7 +39229,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1340" t="n">
         <v>13157</v>
@@ -39258,7 +39258,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1341" t="n">
         <v>2965</v>
@@ -39287,7 +39287,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1342" t="n">
         <v>1570</v>
@@ -39345,7 +39345,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1344" t="n">
         <v>2849</v>
@@ -39374,7 +39374,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1345" t="n">
         <v>4077</v>
@@ -39461,7 +39461,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1348" t="n">
         <v>3503</v>
@@ -39548,7 +39548,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1351" t="n">
         <v>3621</v>
@@ -39693,7 +39693,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1356" t="n">
         <v>1074</v>
@@ -39722,7 +39722,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1357" t="n">
         <v>1555</v>
@@ -39896,7 +39896,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851486206055</v>
+        <v>33.7851448059082</v>
       </c>
       <c r="H1363" t="n">
         <v>12779</v>
@@ -39925,7 +39925,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1364" t="n">
         <v>7910</v>
@@ -40012,7 +40012,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1367" t="n">
         <v>2625</v>
@@ -40157,7 +40157,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1372" t="n">
         <v>2528</v>
@@ -40186,7 +40186,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1373" t="n">
         <v>5370</v>
@@ -40273,7 +40273,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1376" t="n">
         <v>9183</v>
@@ -40302,7 +40302,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1377" t="n">
         <v>4352</v>
@@ -40331,7 +40331,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095977783203</v>
+        <v>31.0095996856689</v>
       </c>
       <c r="H1378" t="n">
         <v>1704</v>
@@ -40360,7 +40360,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1379" t="n">
         <v>553</v>
@@ -40389,7 +40389,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1380" t="n">
         <v>732</v>
@@ -40476,7 +40476,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1383" t="n">
         <v>1248</v>
@@ -40505,7 +40505,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053066253662</v>
+        <v>31.1053047180176</v>
       </c>
       <c r="H1384" t="n">
         <v>1301</v>
@@ -40563,7 +40563,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1386" t="n">
         <v>1483</v>
@@ -40592,7 +40592,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1387" t="n">
         <v>3214</v>
@@ -40708,7 +40708,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1391" t="n">
         <v>3859</v>
@@ -40737,7 +40737,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1392" t="n">
         <v>1387</v>
@@ -40766,7 +40766,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1393" t="n">
         <v>569</v>
@@ -40795,7 +40795,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010116577148</v>
+        <v>31.2010135650635</v>
       </c>
       <c r="H1394" t="n">
         <v>1704</v>
@@ -40940,7 +40940,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1399" t="n">
         <v>2679</v>
@@ -40998,7 +40998,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1401" t="n">
         <v>4340</v>
@@ -41027,7 +41027,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1402" t="n">
         <v>3944</v>
@@ -41056,7 +41056,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1403" t="n">
         <v>1728</v>
@@ -41085,7 +41085,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1404" t="n">
         <v>1317</v>
@@ -41114,7 +41114,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1405" t="n">
         <v>2062</v>
@@ -41143,7 +41143,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1406" t="n">
         <v>1291</v>
@@ -41230,7 +41230,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.636646270752</v>
+        <v>32.6366424560547</v>
       </c>
       <c r="H1409" t="n">
         <v>4625</v>
@@ -41346,7 +41346,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1413" t="n">
         <v>2410</v>
@@ -41375,7 +41375,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1414" t="n">
         <v>31931</v>
@@ -41404,7 +41404,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1415" t="n">
         <v>13442</v>
@@ -41549,7 +41549,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1420" t="n">
         <v>2989</v>
@@ -41607,7 +41607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1422" t="n">
         <v>2861</v>
@@ -41636,7 +41636,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1423" t="n">
         <v>3892</v>
@@ -41752,7 +41752,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1427" t="n">
         <v>2872</v>
@@ -41781,7 +41781,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.679557800293</v>
+        <v>31.6795558929443</v>
       </c>
       <c r="H1428" t="n">
         <v>3471</v>
@@ -41810,7 +41810,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1429" t="n">
         <v>457</v>
@@ -41839,7 +41839,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1430" t="n">
         <v>4731</v>
@@ -41868,7 +41868,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752666473389</v>
+        <v>31.7752647399902</v>
       </c>
       <c r="H1431" t="n">
         <v>1418</v>
@@ -41984,7 +41984,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838470458984</v>
+        <v>31.5838508605957</v>
       </c>
       <c r="H1435" t="n">
         <v>1616</v>
@@ -42013,7 +42013,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1436" t="n">
         <v>3582</v>
@@ -42042,7 +42042,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623931884766</v>
+        <v>32.0623893737793</v>
       </c>
       <c r="H1437" t="n">
         <v>2662</v>
@@ -42100,7 +42100,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1439" t="n">
         <v>198</v>
@@ -42129,7 +42129,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709735870361</v>
+        <v>31.8709754943848</v>
       </c>
       <c r="H1440" t="n">
         <v>1144</v>
@@ -42245,7 +42245,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1444" t="n">
         <v>688</v>
@@ -42274,7 +42274,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.2967224121094</v>
+        <v>31.296724319458</v>
       </c>
       <c r="H1445" t="n">
         <v>1252</v>
@@ -42332,7 +42332,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1447" t="n">
         <v>4488</v>
@@ -42448,7 +42448,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1451" t="n">
         <v>2754</v>
@@ -42477,7 +42477,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1452" t="n">
         <v>793</v>
@@ -42535,7 +42535,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1454" t="n">
         <v>4612</v>
@@ -42622,7 +42622,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1457" t="n">
         <v>3819</v>
@@ -42709,7 +42709,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1460" t="n">
         <v>8292</v>
@@ -42796,7 +42796,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1463" t="n">
         <v>3283</v>
@@ -43028,7 +43028,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1471" t="n">
         <v>1571</v>
@@ -43260,7 +43260,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653865814209</v>
+        <v>29.7653846740723</v>
       </c>
       <c r="H1479" t="n">
         <v>13</v>
@@ -43347,7 +43347,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568023681641</v>
+        <v>29.9568004608154</v>
       </c>
       <c r="H1482" t="n">
         <v>5922</v>
@@ -43579,7 +43579,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1490" t="n">
         <v>3936</v>
@@ -43608,7 +43608,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1491" t="n">
         <v>9516</v>
@@ -43637,7 +43637,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1492" t="n">
         <v>12</v>
@@ -43695,7 +43695,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1494" t="n">
         <v>3670</v>
@@ -43782,7 +43782,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1497" t="n">
         <v>1307</v>
@@ -43811,7 +43811,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1498" t="n">
         <v>4115</v>
@@ -43956,7 +43956,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1503" t="n">
         <v>1545</v>
@@ -44043,7 +44043,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1506" t="n">
         <v>2072</v>
@@ -44072,7 +44072,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340469360352</v>
+        <v>28.2340488433838</v>
       </c>
       <c r="H1507" t="n">
         <v>211</v>
@@ -44101,7 +44101,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1508" t="n">
         <v>907</v>
@@ -44275,7 +44275,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1514" t="n">
         <v>1628</v>
@@ -44333,7 +44333,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1516" t="n">
         <v>5585</v>
@@ -44420,7 +44420,7 @@
         <v>27</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.841329574585</v>
+        <v>25.8413314819336</v>
       </c>
       <c r="H1519" t="n">
         <v>3989</v>
@@ -44623,7 +44623,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>26.5112915039062</v>
+        <v>26.5112934112549</v>
       </c>
       <c r="H1526" t="n">
         <v>4380</v>
@@ -44826,7 +44826,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.5211715698242</v>
+        <v>28.5211734771729</v>
       </c>
       <c r="H1533" t="n">
         <v>2355</v>
@@ -45029,7 +45029,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>26.6070003509521</v>
+        <v>26.6069984436035</v>
       </c>
       <c r="H1540" t="n">
         <v>2838</v>
@@ -45174,7 +45174,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.6499118804932</v>
+        <v>25.6499137878418</v>
       </c>
       <c r="H1545" t="n">
         <v>3951</v>
@@ -45232,7 +45232,7 @@
         <v>25.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.4057025909424</v>
+        <v>24.4057006835938</v>
       </c>
       <c r="H1547" t="n">
         <v>2784</v>
@@ -45319,7 +45319,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7456226348877</v>
+        <v>25.7456207275391</v>
       </c>
       <c r="H1550" t="n">
         <v>919</v>
@@ -45377,7 +45377,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1552" t="n">
         <v>4472</v>
@@ -45435,7 +45435,7 @@
         <v>29</v>
       </c>
       <c r="G1554" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1554" t="n">
         <v>252</v>
@@ -45464,7 +45464,7 @@
         <v>29</v>
       </c>
       <c r="G1555" t="n">
-        <v>27.7555046081543</v>
+        <v>27.7555027008057</v>
       </c>
       <c r="H1555" t="n">
         <v>2314</v>
@@ -45493,7 +45493,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1556" t="n">
         <v>3338</v>
@@ -45580,7 +45580,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1559" t="n">
         <v>612</v>
@@ -45725,7 +45725,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>27.6597938537598</v>
+        <v>27.6597957611084</v>
       </c>
       <c r="H1564" t="n">
         <v>1292</v>
@@ -45899,7 +45899,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1570" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1570" t="n">
         <v>2272</v>
@@ -45928,7 +45928,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>27.8512115478516</v>
+        <v>27.8512134552002</v>
       </c>
       <c r="H1571" t="n">
         <v>388</v>
@@ -56519,6 +56519,35 @@
         <v>2918</v>
       </c>
       <c r="I1936" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1937" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1937" t="n">
+        <v>43.9000015258789</v>
+      </c>
+      <c r="D1937" t="n">
+        <v>44.2999992370605</v>
+      </c>
+      <c r="E1937" t="n">
+        <v>43.7000007629395</v>
+      </c>
+      <c r="F1937" t="n">
+        <v>43.7000007629395</v>
+      </c>
+      <c r="G1937" t="n">
+        <v>43.7000007629395</v>
+      </c>
+      <c r="H1937" t="n">
+        <v>1145</v>
+      </c>
+      <c r="I1937" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/COM.MI.xlsx
+++ b/data/COM.MI.xlsx
@@ -456,7 +456,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>9.58128929138184</v>
+        <v>9.58128833770752</v>
       </c>
       <c r="H3" t="n">
         <v>62400</v>
@@ -485,7 +485,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>9.88293647766113</v>
+        <v>9.88293743133545</v>
       </c>
       <c r="H4" t="n">
         <v>14100</v>
@@ -514,7 +514,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>9.76386547088623</v>
+        <v>9.76386451721191</v>
       </c>
       <c r="H5" t="n">
         <v>9000</v>
@@ -543,7 +543,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G6" t="n">
-        <v>9.78768062591553</v>
+        <v>9.78767967224121</v>
       </c>
       <c r="H6" t="n">
         <v>5550</v>
@@ -572,7 +572,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G7" t="n">
-        <v>9.67654609680176</v>
+        <v>9.67654705047607</v>
       </c>
       <c r="H7" t="n">
         <v>9900</v>
@@ -601,7 +601,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>9.60510349273682</v>
+        <v>9.6051025390625</v>
       </c>
       <c r="H8" t="n">
         <v>3750</v>
@@ -659,7 +659,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G10" t="n">
-        <v>9.39871311187744</v>
+        <v>9.39871120452881</v>
       </c>
       <c r="H10" t="n">
         <v>1050</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>9.52572345733643</v>
+        <v>9.52572250366211</v>
       </c>
       <c r="H11" t="n">
         <v>1500</v>
@@ -775,7 +775,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.91468906402588</v>
+        <v>9.9146900177002</v>
       </c>
       <c r="H14" t="n">
         <v>3450</v>
@@ -804,7 +804,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3195333480835</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H15" t="n">
         <v>13050</v>
@@ -833,7 +833,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>10.1607704162598</v>
+        <v>10.1607694625854</v>
       </c>
       <c r="H16" t="n">
         <v>4350</v>
@@ -862,7 +862,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H17" t="n">
         <v>4650</v>
@@ -891,7 +891,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>10.3195333480835</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H18" t="n">
         <v>2700</v>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.3195333480835</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H20" t="n">
         <v>1500</v>
@@ -978,7 +978,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G21" t="n">
-        <v>10.208399772644</v>
+        <v>10.2084007263184</v>
       </c>
       <c r="H21" t="n">
         <v>4800</v>
@@ -1007,7 +1007,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2719049453735</v>
+        <v>10.2719030380249</v>
       </c>
       <c r="H22" t="n">
         <v>3150</v>
@@ -1036,7 +1036,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>10.208399772644</v>
+        <v>10.2084007263184</v>
       </c>
       <c r="H23" t="n">
         <v>1050</v>
@@ -1065,7 +1065,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>10.1607704162598</v>
+        <v>10.1607694625854</v>
       </c>
       <c r="H24" t="n">
         <v>2100</v>
@@ -1094,7 +1094,7 @@
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>10.3195333480835</v>
+        <v>10.3195323944092</v>
       </c>
       <c r="H25" t="n">
         <v>2550</v>
@@ -1152,7 +1152,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3989143371582</v>
+        <v>10.3989133834839</v>
       </c>
       <c r="H27" t="n">
         <v>750</v>
@@ -1181,7 +1181,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G28" t="n">
-        <v>10.2560291290283</v>
+        <v>10.256028175354</v>
       </c>
       <c r="H28" t="n">
         <v>1650</v>
@@ -1210,7 +1210,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>10.5576763153076</v>
+        <v>10.5576753616333</v>
       </c>
       <c r="H29" t="n">
         <v>2100</v>
@@ -1239,7 +1239,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>10.5576763153076</v>
+        <v>10.5576753616333</v>
       </c>
       <c r="H30" t="n">
         <v>1200</v>
@@ -1297,7 +1297,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>10.4147891998291</v>
+        <v>10.4147901535034</v>
       </c>
       <c r="H32" t="n">
         <v>6450</v>
@@ -1326,7 +1326,7 @@
         <v>13.5</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7164373397827</v>
+        <v>10.7164363861084</v>
       </c>
       <c r="H33" t="n">
         <v>6300</v>
@@ -1384,7 +1384,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G35" t="n">
-        <v>10.5100469589233</v>
+        <v>10.510046005249</v>
       </c>
       <c r="H35" t="n">
         <v>2550</v>
@@ -1413,7 +1413,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0588312149048</v>
+        <v>11.0588321685791</v>
       </c>
       <c r="H36" t="n">
         <v>3900</v>
@@ -1442,7 +1442,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1419792175293</v>
+        <v>11.1419820785522</v>
       </c>
       <c r="H37" t="n">
         <v>7050</v>
@@ -1471,7 +1471,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G38" t="n">
-        <v>11.1087198257446</v>
+        <v>11.1087207794189</v>
       </c>
       <c r="H38" t="n">
         <v>22800</v>
@@ -1500,7 +1500,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G39" t="n">
-        <v>10.8426427841187</v>
+        <v>10.8426446914673</v>
       </c>
       <c r="H39" t="n">
         <v>14250</v>
@@ -1529,7 +1529,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G40" t="n">
-        <v>10.7761240005493</v>
+        <v>10.776123046875</v>
       </c>
       <c r="H40" t="n">
         <v>3150</v>
@@ -1587,7 +1587,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H42" t="n">
         <v>3600</v>
@@ -1616,7 +1616,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G43" t="n">
-        <v>10.6763458251953</v>
+        <v>10.6763467788696</v>
       </c>
       <c r="H43" t="n">
         <v>13050</v>
@@ -1645,7 +1645,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>10.6763458251953</v>
+        <v>10.6763467788696</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="G45" t="n">
-        <v>10.8093852996826</v>
+        <v>10.8093843460083</v>
       </c>
       <c r="H45" t="n">
         <v>14250</v>
@@ -1703,7 +1703,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G46" t="n">
-        <v>10.6098260879517</v>
+        <v>10.609827041626</v>
       </c>
       <c r="H46" t="n">
         <v>750</v>
@@ -1993,7 +1993,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G56" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H56" t="n">
         <v>750</v>
@@ -2022,7 +2022,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>10.277229309082</v>
+        <v>10.2772283554077</v>
       </c>
       <c r="H58" t="n">
         <v>900</v>
@@ -2080,7 +2080,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G59" t="n">
-        <v>10.3271188735962</v>
+        <v>10.3271198272705</v>
       </c>
       <c r="H59" t="n">
         <v>300</v>
@@ -2138,7 +2138,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H61" t="n">
         <v>1650</v>
@@ -2167,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H62" t="n">
         <v>1950</v>
@@ -2225,7 +2225,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H64" t="n">
         <v>7950</v>
@@ -2283,7 +2283,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159591674805</v>
       </c>
       <c r="H66" t="n">
         <v>3900</v>
@@ -2341,7 +2341,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.4789981842041</v>
+        <v>9.47899627685547</v>
       </c>
       <c r="H68" t="n">
         <v>57450</v>
@@ -2370,7 +2370,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159591674805</v>
       </c>
       <c r="H69" t="n">
         <v>1200</v>
@@ -2399,7 +2399,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G70" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159591674805</v>
       </c>
       <c r="H70" t="n">
         <v>99900</v>
@@ -2428,7 +2428,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H71" t="n">
         <v>2400</v>
@@ -2457,7 +2457,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H72" t="n">
         <v>750</v>
@@ -2515,7 +2515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H74" t="n">
         <v>90600</v>
@@ -2544,7 +2544,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159591674805</v>
       </c>
       <c r="H76" t="n">
         <v>600</v>
@@ -2660,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2689,7 +2689,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G80" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159591674805</v>
       </c>
       <c r="H80" t="n">
         <v>49800</v>
@@ -2747,7 +2747,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H82" t="n">
         <v>3900</v>
@@ -2776,7 +2776,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833461761475</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>9.67855739593506</v>
+        <v>9.67855644226074</v>
       </c>
       <c r="H84" t="n">
         <v>1350</v>
@@ -2834,7 +2834,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G85" t="n">
-        <v>9.67855739593506</v>
+        <v>9.67855644226074</v>
       </c>
       <c r="H85" t="n">
         <v>44700</v>
@@ -2950,7 +2950,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>9.71181583404541</v>
+        <v>9.71181488037109</v>
       </c>
       <c r="H89" t="n">
         <v>900</v>
@@ -2979,7 +2979,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G90" t="n">
-        <v>9.6951847076416</v>
+        <v>9.69518566131592</v>
       </c>
       <c r="H90" t="n">
         <v>1350</v>
@@ -3037,7 +3037,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H92" t="n">
         <v>7050</v>
@@ -3066,7 +3066,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H93" t="n">
         <v>2550</v>
@@ -3095,7 +3095,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H94" t="n">
         <v>1050</v>
@@ -3124,7 +3124,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H95" t="n">
         <v>2550</v>
@@ -3240,7 +3240,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G99" t="n">
-        <v>10.1275625228882</v>
+        <v>10.1275615692139</v>
       </c>
       <c r="H99" t="n">
         <v>300</v>
@@ -3298,7 +3298,7 @@
         <v>12</v>
       </c>
       <c r="G101" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H101" t="n">
         <v>300</v>
@@ -3356,7 +3356,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G103" t="n">
-        <v>9.74507427215576</v>
+        <v>9.74507617950439</v>
       </c>
       <c r="H103" t="n">
         <v>150</v>
@@ -3385,7 +3385,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G104" t="n">
-        <v>9.74507427215576</v>
+        <v>9.74507617950439</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833461761475</v>
       </c>
       <c r="H105" t="n">
         <v>1200</v>
@@ -3443,7 +3443,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>9.77833652496338</v>
+        <v>9.77833461761475</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G112" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H112" t="n">
         <v>1800</v>
@@ -3646,7 +3646,7 @@
         <v>12</v>
       </c>
       <c r="G113" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H113" t="n">
         <v>750</v>
@@ -3675,7 +3675,7 @@
         <v>12</v>
       </c>
       <c r="G114" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H114" t="n">
         <v>1200</v>
@@ -3704,7 +3704,7 @@
         <v>12</v>
       </c>
       <c r="G115" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>12</v>
       </c>
       <c r="G117" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H117" t="n">
         <v>1200</v>
@@ -3820,7 +3820,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G119" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H119" t="n">
         <v>1500</v>
@@ -3936,7 +3936,7 @@
         <v>12</v>
       </c>
       <c r="G123" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H123" t="n">
         <v>900</v>
@@ -3994,7 +3994,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G125" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H125" t="n">
         <v>1500</v>
@@ -4052,7 +4052,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H127" t="n">
         <v>13050</v>
@@ -4081,7 +4081,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G128" t="n">
-        <v>10.277229309082</v>
+        <v>10.2772283554077</v>
       </c>
       <c r="H128" t="n">
         <v>4650</v>
@@ -4139,7 +4139,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G130" t="n">
-        <v>10.277229309082</v>
+        <v>10.2772283554077</v>
       </c>
       <c r="H130" t="n">
         <v>2700</v>
@@ -4226,7 +4226,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G133" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H133" t="n">
         <v>300</v>
@@ -4313,7 +4313,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G136" t="n">
-        <v>10.0444116592407</v>
+        <v>10.044412612915</v>
       </c>
       <c r="H136" t="n">
         <v>150</v>
@@ -4371,7 +4371,7 @@
         <v>12</v>
       </c>
       <c r="G138" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H138" t="n">
         <v>600</v>
@@ -4400,7 +4400,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>9.82822322845459</v>
+        <v>9.82822418212891</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4458,7 +4458,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G141" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H141" t="n">
         <v>300</v>
@@ -4487,7 +4487,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>9.86148357391357</v>
+        <v>9.86148452758789</v>
       </c>
       <c r="H142" t="n">
         <v>450</v>
@@ -4516,7 +4516,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H143" t="n">
         <v>1200</v>
@@ -4545,7 +4545,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G144" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.81159496307373</v>
+        <v>9.81159591674805</v>
       </c>
       <c r="H146" t="n">
         <v>3150</v>
@@ -4632,7 +4632,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G147" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H147" t="n">
         <v>1200</v>
@@ -4806,7 +4806,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G153" t="n">
-        <v>10.1275625228882</v>
+        <v>10.1275615692139</v>
       </c>
       <c r="H153" t="n">
         <v>150</v>
@@ -4835,7 +4835,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H154" t="n">
         <v>300</v>
@@ -4980,7 +4980,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H159" t="n">
         <v>15750</v>
@@ -5067,7 +5067,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H162" t="n">
         <v>150</v>
@@ -5212,7 +5212,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H167" t="n">
         <v>1500</v>
@@ -5328,7 +5328,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G171" t="n">
-        <v>10.2439708709717</v>
+        <v>10.2439699172974</v>
       </c>
       <c r="H171" t="n">
         <v>450</v>
@@ -5357,7 +5357,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G172" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H172" t="n">
         <v>150</v>
@@ -5444,7 +5444,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G175" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H175" t="n">
         <v>450</v>
@@ -5473,7 +5473,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G176" t="n">
-        <v>9.96126174926758</v>
+        <v>9.96126365661621</v>
       </c>
       <c r="H176" t="n">
         <v>150</v>
@@ -5502,7 +5502,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H177" t="n">
         <v>9000</v>
@@ -5531,7 +5531,7 @@
         <v>12</v>
       </c>
       <c r="G178" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H178" t="n">
         <v>9300</v>
@@ -5560,7 +5560,7 @@
         <v>12</v>
       </c>
       <c r="G179" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H179" t="n">
         <v>4500</v>
@@ -5618,7 +5618,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G181" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H181" t="n">
         <v>900</v>
@@ -5647,7 +5647,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>10.1109313964844</v>
+        <v>10.1109304428101</v>
       </c>
       <c r="H182" t="n">
         <v>1350</v>
@@ -5763,7 +5763,7 @@
         <v>12</v>
       </c>
       <c r="G186" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H186" t="n">
         <v>1350</v>
@@ -5792,7 +5792,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>9.89474296569824</v>
+        <v>9.89474391937256</v>
       </c>
       <c r="H187" t="n">
         <v>1050</v>
@@ -5879,7 +5879,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G190" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H190" t="n">
         <v>163050</v>
@@ -5937,7 +5937,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G192" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H192" t="n">
         <v>3300</v>
@@ -6053,7 +6053,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G196" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H196" t="n">
         <v>450</v>
@@ -6111,7 +6111,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G198" t="n">
-        <v>10.2938604354858</v>
+        <v>10.2938594818115</v>
       </c>
       <c r="H198" t="n">
         <v>150</v>
@@ -6140,7 +6140,7 @@
         <v>12</v>
       </c>
       <c r="G199" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H199" t="n">
         <v>16800</v>
@@ -6169,7 +6169,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G200" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H200" t="n">
         <v>15150</v>
@@ -6256,7 +6256,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G203" t="n">
-        <v>10.0444116592407</v>
+        <v>10.044412612915</v>
       </c>
       <c r="H203" t="n">
         <v>5250</v>
@@ -6285,7 +6285,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>10.0444116592407</v>
+        <v>10.044412612915</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H206" t="n">
         <v>450</v>
@@ -6401,7 +6401,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H208" t="n">
         <v>1200</v>
@@ -6430,7 +6430,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G209" t="n">
-        <v>10.2439708709717</v>
+        <v>10.2439699172974</v>
       </c>
       <c r="H209" t="n">
         <v>2850</v>
@@ -6488,7 +6488,7 @@
         <v>12</v>
       </c>
       <c r="G211" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H211" t="n">
         <v>1650</v>
@@ -6517,7 +6517,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>12</v>
       </c>
       <c r="G213" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H213" t="n">
         <v>1200</v>
@@ -6575,7 +6575,7 @@
         <v>12</v>
       </c>
       <c r="G214" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H214" t="n">
         <v>1350</v>
@@ -6749,7 +6749,7 @@
         <v>12</v>
       </c>
       <c r="G220" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H220" t="n">
         <v>16950</v>
@@ -6778,7 +6778,7 @@
         <v>12</v>
       </c>
       <c r="G221" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H221" t="n">
         <v>600</v>
@@ -6807,7 +6807,7 @@
         <v>12</v>
       </c>
       <c r="G222" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>12</v>
       </c>
       <c r="G226" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>10.1608209609985</v>
+        <v>10.1608200073242</v>
       </c>
       <c r="H227" t="n">
         <v>450</v>
@@ -7010,7 +7010,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G229" t="n">
-        <v>10.3603792190552</v>
+        <v>10.3603782653809</v>
       </c>
       <c r="H229" t="n">
         <v>2400</v>
@@ -7039,7 +7039,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="n">
-        <v>9.97789287567139</v>
+        <v>9.9778938293457</v>
       </c>
       <c r="H230" t="n">
         <v>1650</v>
@@ -7068,7 +7068,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G231" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H231" t="n">
         <v>600</v>
@@ -7213,7 +7213,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G236" t="n">
-        <v>10.0111513137817</v>
+        <v>10.0111522674561</v>
       </c>
       <c r="H236" t="n">
         <v>750</v>
@@ -7445,7 +7445,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>9.7284460067749</v>
+        <v>9.72844505310059</v>
       </c>
       <c r="H244" t="n">
         <v>300</v>
@@ -7503,7 +7503,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G246" t="n">
-        <v>9.17966079711914</v>
+        <v>9.17966175079346</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7619,7 +7619,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G250" t="n">
-        <v>9.11314392089844</v>
+        <v>9.11314296722412</v>
       </c>
       <c r="H250" t="n">
         <v>2250</v>
@@ -7648,7 +7648,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>8.66413688659668</v>
+        <v>8.664137840271</v>
       </c>
       <c r="H251" t="n">
         <v>4200</v>
@@ -7793,7 +7793,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G256" t="n">
-        <v>7.42521619796753</v>
+        <v>7.42521524429321</v>
       </c>
       <c r="H256" t="n">
         <v>2400</v>
@@ -7822,7 +7822,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.14861297607422</v>
+        <v>8.1486120223999</v>
       </c>
       <c r="H257" t="n">
         <v>450</v>
@@ -7851,7 +7851,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.14861297607422</v>
+        <v>8.1486120223999</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>7.96568536758423</v>
+        <v>7.96568441390991</v>
       </c>
       <c r="H259" t="n">
         <v>3600</v>
@@ -8083,7 +8083,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>8.27333545684814</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H266" t="n">
         <v>450</v>
@@ -8112,7 +8112,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.27333545684814</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>8.27333545684814</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>8.27333545684814</v>
+        <v>8.27333641052246</v>
       </c>
       <c r="H277" t="n">
         <v>1800</v>
@@ -8460,7 +8460,7 @@
         <v>11</v>
       </c>
       <c r="G279" t="n">
-        <v>9.14640331268311</v>
+        <v>9.14640235900879</v>
       </c>
       <c r="H279" t="n">
         <v>19950</v>
@@ -8489,7 +8489,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>9.14640331268311</v>
+        <v>9.14640235900879</v>
       </c>
       <c r="H280" t="n">
         <v>1350</v>
@@ -8518,7 +8518,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>8.98010444641113</v>
+        <v>8.9801025390625</v>
       </c>
       <c r="H281" t="n">
         <v>1050</v>
@@ -8547,7 +8547,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G282" t="n">
-        <v>8.98010444641113</v>
+        <v>8.9801025390625</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>9.06325340270996</v>
+        <v>9.06325149536133</v>
       </c>
       <c r="H283" t="n">
         <v>900</v>
@@ -8605,7 +8605,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>9.36392879486084</v>
+        <v>9.36392974853516</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211483001709</v>
       </c>
       <c r="H285" t="n">
         <v>2700</v>
@@ -8663,7 +8663,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H286" t="n">
         <v>3750</v>
@@ -8692,7 +8692,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H292" t="n">
         <v>2250</v>
@@ -8866,7 +8866,7 @@
         <v>10.5</v>
       </c>
       <c r="G293" t="n">
-        <v>9.02029800415039</v>
+        <v>9.02029991149902</v>
       </c>
       <c r="H293" t="n">
         <v>750</v>
@@ -8895,7 +8895,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>9.10620594024658</v>
+        <v>9.1062068939209</v>
       </c>
       <c r="H294" t="n">
         <v>1050</v>
@@ -8924,7 +8924,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H295" t="n">
         <v>1050</v>
@@ -9011,7 +9011,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G298" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H298" t="n">
         <v>300</v>
@@ -9040,7 +9040,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G299" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G300" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H300" t="n">
         <v>4350</v>
@@ -9098,7 +9098,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>10</v>
       </c>
       <c r="G303" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H303" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>10</v>
       </c>
       <c r="G304" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H304" t="n">
         <v>22950</v>
@@ -9214,7 +9214,7 @@
         <v>10</v>
       </c>
       <c r="G305" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>10</v>
       </c>
       <c r="G307" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>10</v>
       </c>
       <c r="G308" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>10</v>
       </c>
       <c r="G309" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>10</v>
       </c>
       <c r="G310" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H312" t="n">
         <v>750</v>
@@ -9446,7 +9446,7 @@
         <v>10.5</v>
       </c>
       <c r="G313" t="n">
-        <v>9.02029800415039</v>
+        <v>9.02029991149902</v>
       </c>
       <c r="H313" t="n">
         <v>2550</v>
@@ -9475,7 +9475,7 @@
         <v>10.5</v>
       </c>
       <c r="G314" t="n">
-        <v>9.02029800415039</v>
+        <v>9.02029991149902</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>10.5</v>
       </c>
       <c r="G315" t="n">
-        <v>9.02029800415039</v>
+        <v>9.02029991149902</v>
       </c>
       <c r="H315" t="n">
         <v>150</v>
@@ -9533,7 +9533,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G316" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9562,7 +9562,7 @@
         <v>10</v>
       </c>
       <c r="G317" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H317" t="n">
         <v>1050</v>
@@ -9591,7 +9591,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H318" t="n">
         <v>1050</v>
@@ -9620,7 +9620,7 @@
         <v>10</v>
       </c>
       <c r="G319" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H319" t="n">
         <v>150</v>
@@ -9649,7 +9649,7 @@
         <v>10</v>
       </c>
       <c r="G320" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>8.33303737640381</v>
+        <v>8.33303928375244</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.33303737640381</v>
+        <v>8.33303928375244</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G326" t="n">
-        <v>8.33303737640381</v>
+        <v>8.33303928375244</v>
       </c>
       <c r="H326" t="n">
         <v>2250</v>
@@ -9852,7 +9852,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.41894626617432</v>
+        <v>8.41894721984863</v>
       </c>
       <c r="H327" t="n">
         <v>8100</v>
@@ -9997,7 +9997,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H332" t="n">
         <v>300</v>
@@ -10026,7 +10026,7 @@
         <v>10</v>
       </c>
       <c r="G333" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10171,7 +10171,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H338" t="n">
         <v>1350</v>
@@ -10200,7 +10200,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H339" t="n">
         <v>450</v>
@@ -10229,7 +10229,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>10</v>
       </c>
       <c r="G345" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H345" t="n">
         <v>600</v>
@@ -10403,7 +10403,7 @@
         <v>10</v>
       </c>
       <c r="G346" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H346" t="n">
         <v>5550</v>
@@ -10432,7 +10432,7 @@
         <v>10</v>
       </c>
       <c r="G347" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H347" t="n">
         <v>600</v>
@@ -10461,7 +10461,7 @@
         <v>10</v>
       </c>
       <c r="G348" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>10</v>
       </c>
       <c r="G349" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>8.46189975738525</v>
+        <v>8.46190071105957</v>
       </c>
       <c r="H356" t="n">
         <v>1950</v>
@@ -10780,7 +10780,7 @@
         <v>10</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H359" t="n">
         <v>750</v>
@@ -10896,7 +10896,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G363" t="n">
-        <v>8.41894626617432</v>
+        <v>8.41894721984863</v>
       </c>
       <c r="H363" t="n">
         <v>150</v>
@@ -10925,7 +10925,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.41894626617432</v>
+        <v>8.41894721984863</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.41894626617432</v>
+        <v>8.41894721984863</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.41894626617432</v>
+        <v>8.41894721984863</v>
       </c>
       <c r="H366" t="n">
         <v>300</v>
@@ -11012,7 +11012,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.41894626617432</v>
+        <v>8.41894721984863</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>8.41894626617432</v>
+        <v>8.41894721984863</v>
       </c>
       <c r="H368" t="n">
         <v>150</v>
@@ -11099,7 +11099,7 @@
         <v>9.75</v>
       </c>
       <c r="G370" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H370" t="n">
         <v>3750</v>
@@ -11128,7 +11128,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H371" t="n">
         <v>3000</v>
@@ -11157,7 +11157,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>9.75</v>
       </c>
       <c r="G373" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>9.75</v>
       </c>
       <c r="G374" t="n">
-        <v>8.37599277496338</v>
+        <v>8.37599182128906</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>8.204176902771</v>
+        <v>8.20417594909668</v>
       </c>
       <c r="H375" t="n">
         <v>1950</v>
@@ -11331,7 +11331,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H378" t="n">
         <v>4200</v>
@@ -11360,7 +11360,7 @@
         <v>10</v>
       </c>
       <c r="G379" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H379" t="n">
         <v>1200</v>
@@ -11476,7 +11476,7 @@
         <v>10</v>
       </c>
       <c r="G383" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H383" t="n">
         <v>750</v>
@@ -11563,7 +11563,7 @@
         <v>10</v>
       </c>
       <c r="G386" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H386" t="n">
         <v>300</v>
@@ -11621,7 +11621,7 @@
         <v>10</v>
       </c>
       <c r="G388" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H388" t="n">
         <v>300</v>
@@ -11708,7 +11708,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H391" t="n">
         <v>150</v>
@@ -11737,7 +11737,7 @@
         <v>10</v>
       </c>
       <c r="G392" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H396" t="n">
         <v>300</v>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>10</v>
       </c>
       <c r="G398" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H398" t="n">
         <v>600</v>
@@ -11940,7 +11940,7 @@
         <v>10</v>
       </c>
       <c r="G399" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>10</v>
       </c>
       <c r="G400" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H401" t="n">
         <v>1800</v>
@@ -12027,7 +12027,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H406" t="n">
         <v>1050</v>
@@ -12172,7 +12172,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G407" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>10</v>
       </c>
       <c r="G408" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H408" t="n">
         <v>150</v>
@@ -12230,7 +12230,7 @@
         <v>10</v>
       </c>
       <c r="G409" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H409" t="n">
         <v>450</v>
@@ -12346,7 +12346,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H413" t="n">
         <v>5400</v>
@@ -12375,7 +12375,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H414" t="n">
         <v>150</v>
@@ -12404,7 +12404,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>8.41894626617432</v>
+        <v>8.41894721984863</v>
       </c>
       <c r="H415" t="n">
         <v>2400</v>
@@ -12433,7 +12433,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H416" t="n">
         <v>600</v>
@@ -12462,7 +12462,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H418" t="n">
         <v>450</v>
@@ -12520,7 +12520,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G420" t="n">
-        <v>8.84848308563232</v>
+        <v>8.84848403930664</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>10</v>
       </c>
       <c r="G422" t="n">
-        <v>8.59076023101807</v>
+        <v>8.59076118469238</v>
       </c>
       <c r="H422" t="n">
         <v>150</v>
@@ -12752,7 +12752,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>8.93439197540283</v>
+        <v>8.93439102172852</v>
       </c>
       <c r="H427" t="n">
         <v>450</v>
@@ -12781,7 +12781,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211483001709</v>
       </c>
       <c r="H428" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>9.10620594024658</v>
+        <v>9.1062068939209</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>9.36392879486084</v>
+        <v>9.36392974853516</v>
       </c>
       <c r="H430" t="n">
         <v>450</v>
@@ -12868,7 +12868,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211483001709</v>
       </c>
       <c r="H431" t="n">
         <v>300</v>
@@ -12897,7 +12897,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>9.19211387634277</v>
+        <v>9.19211483001709</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>9.27802276611328</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H433" t="n">
         <v>5700</v>
@@ -12955,7 +12955,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G434" t="n">
-        <v>9.27802276611328</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H434" t="n">
         <v>3750</v>
@@ -12984,7 +12984,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G435" t="n">
-        <v>9.27802276611328</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H435" t="n">
         <v>6750</v>
@@ -13013,7 +13013,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G436" t="n">
-        <v>9.27802276611328</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H436" t="n">
         <v>900</v>
@@ -13042,7 +13042,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G437" t="n">
-        <v>9.27802276611328</v>
+        <v>9.2780237197876</v>
       </c>
       <c r="H437" t="n">
         <v>1650</v>
@@ -13071,7 +13071,7 @@
         <v>11.5</v>
       </c>
       <c r="G438" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H438" t="n">
         <v>1350</v>
@@ -13129,7 +13129,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>9.96528244018555</v>
+        <v>9.96528434753418</v>
       </c>
       <c r="H440" t="n">
         <v>21900</v>
@@ -13187,7 +13187,7 @@
         <v>11.5</v>
       </c>
       <c r="G442" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H442" t="n">
         <v>300</v>
@@ -13216,7 +13216,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H443" t="n">
         <v>11400</v>
@@ -13245,7 +13245,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H444" t="n">
         <v>6150</v>
@@ -13419,7 +13419,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H450" t="n">
         <v>300</v>
@@ -13738,7 +13738,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>9.62165355682373</v>
+        <v>9.62165260314941</v>
       </c>
       <c r="H461" t="n">
         <v>2100</v>
@@ -13767,7 +13767,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.96528244018555</v>
+        <v>9.96528434753418</v>
       </c>
       <c r="H462" t="n">
         <v>2850</v>
@@ -13825,7 +13825,7 @@
         <v>11.5</v>
       </c>
       <c r="G464" t="n">
-        <v>9.87937545776367</v>
+        <v>9.87937450408936</v>
       </c>
       <c r="H464" t="n">
         <v>750</v>
@@ -13854,7 +13854,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.96528244018555</v>
+        <v>9.96528434753418</v>
       </c>
       <c r="H465" t="n">
         <v>1200</v>
@@ -14173,7 +14173,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>9.96528244018555</v>
+        <v>9.96528434753418</v>
       </c>
       <c r="H476" t="n">
         <v>750</v>
@@ -14231,7 +14231,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0511903762817</v>
+        <v>10.0511913299561</v>
       </c>
       <c r="H478" t="n">
         <v>1500</v>
@@ -14260,7 +14260,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0511903762817</v>
+        <v>10.0511913299561</v>
       </c>
       <c r="H479" t="n">
         <v>600</v>
@@ -14289,7 +14289,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H480" t="n">
         <v>1500</v>
@@ -14318,7 +14318,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>10.2230043411255</v>
+        <v>10.2230062484741</v>
       </c>
       <c r="H481" t="n">
         <v>150</v>
@@ -14405,7 +14405,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G484" t="n">
-        <v>10.6525430679321</v>
+        <v>10.6525421142578</v>
       </c>
       <c r="H484" t="n">
         <v>24150</v>
@@ -14434,7 +14434,7 @@
         <v>12.5</v>
       </c>
       <c r="G485" t="n">
-        <v>10.7384510040283</v>
+        <v>10.7384519577026</v>
       </c>
       <c r="H485" t="n">
         <v>15600</v>
@@ -14463,7 +14463,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="n">
-        <v>10.7384510040283</v>
+        <v>10.7384519577026</v>
       </c>
       <c r="H486" t="n">
         <v>5100</v>
@@ -14492,7 +14492,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>10.9102668762207</v>
+        <v>10.9102659225464</v>
       </c>
       <c r="H487" t="n">
         <v>4650</v>
@@ -14521,7 +14521,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.9102668762207</v>
+        <v>10.9102659225464</v>
       </c>
       <c r="H488" t="n">
         <v>4350</v>
@@ -14550,7 +14550,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>10.9102668762207</v>
+        <v>10.9102659225464</v>
       </c>
       <c r="H489" t="n">
         <v>14100</v>
@@ -14579,7 +14579,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H490" t="n">
         <v>6450</v>
@@ -14608,7 +14608,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H491" t="n">
         <v>6450</v>
@@ -14637,7 +14637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>10.8243589401245</v>
+        <v>10.8243598937988</v>
       </c>
       <c r="H492" t="n">
         <v>5100</v>
@@ -14666,7 +14666,7 @@
         <v>13</v>
       </c>
       <c r="G493" t="n">
-        <v>11.1679906845093</v>
+        <v>11.167989730835</v>
       </c>
       <c r="H493" t="n">
         <v>36300</v>
@@ -14695,7 +14695,7 @@
         <v>13</v>
       </c>
       <c r="G494" t="n">
-        <v>11.1679906845093</v>
+        <v>11.167989730835</v>
       </c>
       <c r="H494" t="n">
         <v>7050</v>
@@ -14724,7 +14724,7 @@
         <v>13</v>
       </c>
       <c r="G495" t="n">
-        <v>11.1679906845093</v>
+        <v>11.167989730835</v>
       </c>
       <c r="H495" t="n">
         <v>20850</v>
@@ -14782,7 +14782,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>11.5116195678711</v>
+        <v>11.5116186141968</v>
       </c>
       <c r="H497" t="n">
         <v>6600</v>
@@ -14840,7 +14840,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>11.4257125854492</v>
+        <v>11.4257116317749</v>
       </c>
       <c r="H499" t="n">
         <v>750</v>
@@ -14869,7 +14869,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>11.8552513122559</v>
+        <v>11.8552494049072</v>
       </c>
       <c r="H500" t="n">
         <v>5400</v>
@@ -14898,7 +14898,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>11.9411573410034</v>
+        <v>11.9411582946777</v>
       </c>
       <c r="H501" t="n">
         <v>9150</v>
@@ -14956,7 +14956,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>12.1129732131958</v>
+        <v>12.1129722595215</v>
       </c>
       <c r="H503" t="n">
         <v>4500</v>
@@ -14985,7 +14985,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>12.3706951141357</v>
+        <v>12.3706960678101</v>
       </c>
       <c r="H504" t="n">
         <v>6900</v>
@@ -15014,7 +15014,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>12.6284189224243</v>
+        <v>12.62841796875</v>
       </c>
       <c r="H505" t="n">
         <v>2400</v>
@@ -15043,7 +15043,7 @@
         <v>15</v>
       </c>
       <c r="G506" t="n">
-        <v>12.8861417770386</v>
+        <v>12.8861408233643</v>
       </c>
       <c r="H506" t="n">
         <v>29250</v>
@@ -15130,7 +15130,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>13.057957649231</v>
+        <v>13.0579557418823</v>
       </c>
       <c r="H509" t="n">
         <v>2550</v>
@@ -15159,7 +15159,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>13.057957649231</v>
+        <v>13.0579557418823</v>
       </c>
       <c r="H510" t="n">
         <v>12750</v>
@@ -15188,7 +15188,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720487594604</v>
       </c>
       <c r="H511" t="n">
         <v>86100</v>
@@ -15217,7 +15217,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720487594604</v>
       </c>
       <c r="H512" t="n">
         <v>750</v>
@@ -15246,7 +15246,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>12.9720497131348</v>
+        <v>12.9720487594604</v>
       </c>
       <c r="H513" t="n">
         <v>3750</v>
@@ -15275,7 +15275,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G514" t="n">
-        <v>13.057957649231</v>
+        <v>13.0579557418823</v>
       </c>
       <c r="H514" t="n">
         <v>10800</v>
@@ -15333,7 +15333,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>13.9170341491699</v>
+        <v>13.9170322418213</v>
       </c>
       <c r="H516" t="n">
         <v>13350</v>
@@ -15391,7 +15391,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>13.4874935150146</v>
+        <v>13.487494468689</v>
       </c>
       <c r="H518" t="n">
         <v>6600</v>
@@ -15449,7 +15449,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>14.2606649398804</v>
+        <v>14.2606639862061</v>
       </c>
       <c r="H520" t="n">
         <v>5700</v>
@@ -15478,7 +15478,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>14.4324779510498</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H521" t="n">
         <v>58800</v>
@@ -15565,7 +15565,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>14.2606649398804</v>
+        <v>14.2606639862061</v>
       </c>
       <c r="H524" t="n">
         <v>2250</v>
@@ -15594,7 +15594,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>14.0029392242432</v>
+        <v>14.0029401779175</v>
       </c>
       <c r="H525" t="n">
         <v>33900</v>
@@ -15652,7 +15652,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>14.4324779510498</v>
+        <v>14.4324769973755</v>
       </c>
       <c r="H527" t="n">
         <v>40350</v>
@@ -15681,7 +15681,7 @@
         <v>17</v>
       </c>
       <c r="G528" t="n">
-        <v>14.6042919158936</v>
+        <v>14.6042938232422</v>
       </c>
       <c r="H528" t="n">
         <v>25200</v>
@@ -15710,7 +15710,7 @@
         <v>18</v>
       </c>
       <c r="G529" t="n">
-        <v>15.4633703231812</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H529" t="n">
         <v>8700</v>
@@ -15739,7 +15739,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>15.2915544509888</v>
+        <v>15.2915554046631</v>
       </c>
       <c r="H530" t="n">
         <v>3450</v>
@@ -15768,7 +15768,7 @@
         <v>18</v>
       </c>
       <c r="G531" t="n">
-        <v>15.4633703231812</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H531" t="n">
         <v>3900</v>
@@ -15797,7 +15797,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>15.2056474685669</v>
+        <v>15.2056493759155</v>
       </c>
       <c r="H532" t="n">
         <v>8550</v>
@@ -15855,7 +15855,7 @@
         <v>18</v>
       </c>
       <c r="G534" t="n">
-        <v>15.4633703231812</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H534" t="n">
         <v>20100</v>
@@ -15884,7 +15884,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="n">
-        <v>15.4633703231812</v>
+        <v>15.4633693695068</v>
       </c>
       <c r="H535" t="n">
         <v>15300</v>
@@ -15913,7 +15913,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>15.5492763519287</v>
+        <v>15.5492782592773</v>
       </c>
       <c r="H536" t="n">
         <v>3000</v>
@@ -15971,7 +15971,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6376256942749</v>
+        <v>15.6376266479492</v>
       </c>
       <c r="H538" t="n">
         <v>2250</v>
@@ -16029,7 +16029,7 @@
         <v>17</v>
       </c>
       <c r="G540" t="n">
-        <v>15.0191898345947</v>
+        <v>15.0191888809204</v>
       </c>
       <c r="H540" t="n">
         <v>3150</v>
@@ -16058,7 +16058,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G541" t="n">
-        <v>15.1958875656128</v>
+        <v>15.1958866119385</v>
       </c>
       <c r="H541" t="n">
         <v>3300</v>
@@ -16116,7 +16116,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.5492763519287</v>
+        <v>15.5492782592773</v>
       </c>
       <c r="H543" t="n">
         <v>3600</v>
@@ -16232,7 +16232,7 @@
         <v>18.5</v>
       </c>
       <c r="G547" t="n">
-        <v>16.344409942627</v>
+        <v>16.3444118499756</v>
       </c>
       <c r="H547" t="n">
         <v>3750</v>
@@ -16319,7 +16319,7 @@
         <v>18.5</v>
       </c>
       <c r="G550" t="n">
-        <v>16.344409942627</v>
+        <v>16.3444118499756</v>
       </c>
       <c r="H550" t="n">
         <v>1050</v>
@@ -16348,7 +16348,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>16.2560634613037</v>
+        <v>16.2560615539551</v>
       </c>
       <c r="H551" t="n">
         <v>1800</v>
@@ -16377,7 +16377,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>16.2560634613037</v>
+        <v>16.2560615539551</v>
       </c>
       <c r="H552" t="n">
         <v>1800</v>
@@ -16406,7 +16406,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>16.2560634613037</v>
+        <v>16.2560615539551</v>
       </c>
       <c r="H553" t="n">
         <v>17850</v>
@@ -16435,7 +16435,7 @@
         <v>18.5</v>
       </c>
       <c r="G554" t="n">
-        <v>16.344409942627</v>
+        <v>16.3444118499756</v>
       </c>
       <c r="H554" t="n">
         <v>3000</v>
@@ -16464,7 +16464,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>16.2560634613037</v>
+        <v>16.2560615539551</v>
       </c>
       <c r="H555" t="n">
         <v>4950</v>
@@ -16522,7 +16522,7 @@
         <v>18.5</v>
       </c>
       <c r="G557" t="n">
-        <v>16.344409942627</v>
+        <v>16.3444118499756</v>
       </c>
       <c r="H557" t="n">
         <v>5550</v>
@@ -16551,7 +16551,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>16.9628486633301</v>
+        <v>16.9628467559814</v>
       </c>
       <c r="H558" t="n">
         <v>21300</v>
@@ -16580,7 +16580,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H559" t="n">
         <v>15150</v>
@@ -16609,7 +16609,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>18.1997222900391</v>
+        <v>18.1997241973877</v>
       </c>
       <c r="H560" t="n">
         <v>4650</v>
@@ -16638,7 +16638,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G561" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H561" t="n">
         <v>3450</v>
@@ -16667,7 +16667,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>19.0832042694092</v>
+        <v>19.0832061767578</v>
       </c>
       <c r="H562" t="n">
         <v>10050</v>
@@ -16696,7 +16696,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>19.9666843414307</v>
+        <v>19.9666881561279</v>
       </c>
       <c r="H563" t="n">
         <v>31500</v>
@@ -16725,7 +16725,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>19.9666843414307</v>
+        <v>19.9666881561279</v>
       </c>
       <c r="H564" t="n">
         <v>4200</v>
@@ -16783,7 +16783,7 @@
         <v>21</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5531177520752</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H566" t="n">
         <v>12300</v>
@@ -16841,7 +16841,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H568" t="n">
         <v>9600</v>
@@ -16899,7 +16899,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>17.4929351806641</v>
+        <v>17.4929370880127</v>
       </c>
       <c r="H570" t="n">
         <v>3150</v>
@@ -16928,7 +16928,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>18.3764171600342</v>
+        <v>18.3764190673828</v>
       </c>
       <c r="H571" t="n">
         <v>6150</v>
@@ -16957,7 +16957,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>18.3764171600342</v>
+        <v>18.3764190673828</v>
       </c>
       <c r="H572" t="n">
         <v>825</v>
@@ -16986,7 +16986,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>18.0230236053467</v>
+        <v>18.0230255126953</v>
       </c>
       <c r="H573" t="n">
         <v>8325</v>
@@ -17015,7 +17015,7 @@
         <v>20</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6696319580078</v>
+        <v>17.6696338653564</v>
       </c>
       <c r="H574" t="n">
         <v>5250</v>
@@ -17102,7 +17102,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.1395454406738</v>
+        <v>17.1395416259766</v>
       </c>
       <c r="H577" t="n">
         <v>5250</v>
@@ -17131,7 +17131,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>17.1395454406738</v>
+        <v>17.1395416259766</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17189,7 +17189,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>17.3162403106689</v>
+        <v>17.3162422180176</v>
       </c>
       <c r="H580" t="n">
         <v>3150</v>
@@ -17276,7 +17276,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>17.4929351806641</v>
+        <v>17.4929370880127</v>
       </c>
       <c r="H583" t="n">
         <v>3675</v>
@@ -17305,7 +17305,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>17.6696319580078</v>
+        <v>17.6696338653564</v>
       </c>
       <c r="H584" t="n">
         <v>1050</v>
@@ -17363,7 +17363,7 @@
         <v>21</v>
       </c>
       <c r="G586" t="n">
-        <v>18.5531177520752</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H586" t="n">
         <v>11325</v>
@@ -17421,7 +17421,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>18.3764171600342</v>
+        <v>18.3764190673828</v>
       </c>
       <c r="H588" t="n">
         <v>3000</v>
@@ -17450,7 +17450,7 @@
         <v>21</v>
       </c>
       <c r="G589" t="n">
-        <v>18.5531177520752</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H589" t="n">
         <v>900</v>
@@ -17479,7 +17479,7 @@
         <v>21</v>
       </c>
       <c r="G590" t="n">
-        <v>18.5531177520752</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H590" t="n">
         <v>20100</v>
@@ -17508,7 +17508,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>18.3764171600342</v>
+        <v>18.3764190673828</v>
       </c>
       <c r="H591" t="n">
         <v>28800</v>
@@ -17537,7 +17537,7 @@
         <v>21</v>
       </c>
       <c r="G592" t="n">
-        <v>18.5531177520752</v>
+        <v>18.5531158447266</v>
       </c>
       <c r="H592" t="n">
         <v>2325</v>
@@ -17624,7 +17624,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938251495361</v>
       </c>
       <c r="H595" t="n">
         <v>9525</v>
@@ -17653,7 +17653,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>20.673469543457</v>
+        <v>20.6734733581543</v>
       </c>
       <c r="H596" t="n">
         <v>39600</v>
@@ -17682,7 +17682,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H597" t="n">
         <v>13125</v>
@@ -17827,7 +17827,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>20.143383026123</v>
+        <v>20.1433811187744</v>
       </c>
       <c r="H602" t="n">
         <v>21825</v>
@@ -17856,7 +17856,7 @@
         <v>23</v>
       </c>
       <c r="G603" t="n">
-        <v>20.3200798034668</v>
+        <v>20.3200778961182</v>
       </c>
       <c r="H603" t="n">
         <v>11400</v>
@@ -17885,7 +17885,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H604" t="n">
         <v>19650</v>
@@ -17914,7 +17914,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H605" t="n">
         <v>10425</v>
@@ -17943,7 +17943,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G606" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H606" t="n">
         <v>10050</v>
@@ -17972,7 +17972,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>21.0268650054932</v>
+        <v>21.0268630981445</v>
       </c>
       <c r="H607" t="n">
         <v>5250</v>
@@ -18088,7 +18088,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938251495361</v>
       </c>
       <c r="H611" t="n">
         <v>7125</v>
@@ -18117,7 +18117,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>22.7938270568848</v>
+        <v>22.7938251495361</v>
       </c>
       <c r="H612" t="n">
         <v>7575</v>
@@ -18320,7 +18320,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>23.1472206115723</v>
+        <v>23.1472187042236</v>
       </c>
       <c r="H619" t="n">
         <v>8100</v>
@@ -18552,7 +18552,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>28.4481086730957</v>
+        <v>28.448112487793</v>
       </c>
       <c r="H627" t="n">
         <v>16800</v>
@@ -18639,7 +18639,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H630" t="n">
         <v>11250</v>
@@ -18668,7 +18668,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>29.8616790771484</v>
+        <v>29.8616771697998</v>
       </c>
       <c r="H631" t="n">
         <v>11700</v>
@@ -18697,7 +18697,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>30.7451629638672</v>
+        <v>30.7451572418213</v>
       </c>
       <c r="H632" t="n">
         <v>23025</v>
@@ -18755,7 +18755,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0985527038574</v>
+        <v>31.0985565185547</v>
       </c>
       <c r="H634" t="n">
         <v>8625</v>
@@ -18784,7 +18784,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.5684661865234</v>
+        <v>30.5684604644775</v>
       </c>
       <c r="H635" t="n">
         <v>3900</v>
@@ -18813,7 +18813,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>30.5684661865234</v>
+        <v>30.5684604644775</v>
       </c>
       <c r="H636" t="n">
         <v>21300</v>
@@ -18842,7 +18842,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>30.7451629638672</v>
+        <v>30.7451572418213</v>
       </c>
       <c r="H637" t="n">
         <v>1725</v>
@@ -18871,7 +18871,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G638" t="n">
-        <v>30.3917751312256</v>
+        <v>30.391773223877</v>
       </c>
       <c r="H638" t="n">
         <v>20325</v>
@@ -18929,7 +18929,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>29.5082855224609</v>
+        <v>29.5082874298096</v>
       </c>
       <c r="H640" t="n">
         <v>11100</v>
@@ -19016,7 +19016,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>28.4481086730957</v>
+        <v>28.448112487793</v>
       </c>
       <c r="H643" t="n">
         <v>2100</v>
@@ -19103,7 +19103,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H646" t="n">
         <v>10950</v>
@@ -19248,7 +19248,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H651" t="n">
         <v>10050</v>
@@ -19277,7 +19277,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H652" t="n">
         <v>5025</v>
@@ -19335,7 +19335,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H654" t="n">
         <v>6300</v>
@@ -19393,7 +19393,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H656" t="n">
         <v>5550</v>
@@ -19422,7 +19422,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H657" t="n">
         <v>2325</v>
@@ -19451,7 +19451,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H658" t="n">
         <v>975</v>
@@ -19480,7 +19480,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G659" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H659" t="n">
         <v>4200</v>
@@ -19509,7 +19509,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H660" t="n">
         <v>2700</v>
@@ -19538,7 +19538,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H661" t="n">
         <v>7575</v>
@@ -19596,7 +19596,7 @@
         <v>33</v>
       </c>
       <c r="G663" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548957824707</v>
       </c>
       <c r="H663" t="n">
         <v>5700</v>
@@ -19712,7 +19712,7 @@
         <v>34</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0383796691895</v>
+        <v>30.0383777618408</v>
       </c>
       <c r="H667" t="n">
         <v>6825</v>
@@ -19741,7 +19741,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>29.8616790771484</v>
+        <v>29.8616771697998</v>
       </c>
       <c r="H668" t="n">
         <v>5550</v>
@@ -19828,7 +19828,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>28.978199005127</v>
+        <v>28.9781970977783</v>
       </c>
       <c r="H671" t="n">
         <v>3900</v>
@@ -19886,7 +19886,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>28.978199005127</v>
+        <v>28.9781970977783</v>
       </c>
       <c r="H673" t="n">
         <v>4575</v>
@@ -19915,7 +19915,7 @@
         <v>33</v>
       </c>
       <c r="G674" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548957824707</v>
       </c>
       <c r="H674" t="n">
         <v>2400</v>
@@ -19944,7 +19944,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>29.8616790771484</v>
+        <v>29.8616771697998</v>
       </c>
       <c r="H675" t="n">
         <v>7800</v>
@@ -20002,7 +20002,7 @@
         <v>33</v>
       </c>
       <c r="G677" t="n">
-        <v>29.1548938751221</v>
+        <v>29.1548957824707</v>
       </c>
       <c r="H677" t="n">
         <v>6300</v>
@@ -20089,7 +20089,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H680" t="n">
         <v>4875</v>
@@ -20147,7 +20147,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>28.0947170257568</v>
+        <v>28.0947151184082</v>
       </c>
       <c r="H682" t="n">
         <v>5625</v>
@@ -20234,7 +20234,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G685" t="n">
-        <v>28.4481086730957</v>
+        <v>28.448112487793</v>
       </c>
       <c r="H685" t="n">
         <v>8100</v>
@@ -20263,7 +20263,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>28.8015022277832</v>
+        <v>28.8015003204346</v>
       </c>
       <c r="H686" t="n">
         <v>2250</v>
@@ -20321,7 +20321,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H688" t="n">
         <v>9075</v>
@@ -20350,7 +20350,7 @@
         <v>31</v>
       </c>
       <c r="G689" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H689" t="n">
         <v>1500</v>
@@ -20553,7 +20553,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H696" t="n">
         <v>5775</v>
@@ -20582,7 +20582,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H697" t="n">
         <v>1800</v>
@@ -20727,7 +20727,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>27.7413234710693</v>
+        <v>27.741325378418</v>
       </c>
       <c r="H702" t="n">
         <v>825</v>
@@ -20756,7 +20756,7 @@
         <v>31</v>
       </c>
       <c r="G703" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H703" t="n">
         <v>12375</v>
@@ -20785,7 +20785,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H704" t="n">
         <v>1350</v>
@@ -20814,7 +20814,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H705" t="n">
         <v>2550</v>
@@ -20843,7 +20843,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H706" t="n">
         <v>750</v>
@@ -20872,7 +20872,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G707" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H707" t="n">
         <v>4125</v>
@@ -21075,7 +21075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H714" t="n">
         <v>2100</v>
@@ -21104,7 +21104,7 @@
         <v>31</v>
       </c>
       <c r="G715" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H715" t="n">
         <v>2700</v>
@@ -21133,7 +21133,7 @@
         <v>31</v>
       </c>
       <c r="G716" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H716" t="n">
         <v>600</v>
@@ -21162,7 +21162,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G717" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H717" t="n">
         <v>150</v>
@@ -21191,7 +21191,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>26.8578414916992</v>
+        <v>26.8578433990479</v>
       </c>
       <c r="H718" t="n">
         <v>375</v>
@@ -21220,7 +21220,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H719" t="n">
         <v>600</v>
@@ -21916,7 +21916,7 @@
         <v>29</v>
       </c>
       <c r="G743" t="n">
-        <v>25.6209697723389</v>
+        <v>25.6209678649902</v>
       </c>
       <c r="H743" t="n">
         <v>1425</v>
@@ -21945,7 +21945,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H744" t="n">
         <v>6825</v>
@@ -22264,7 +22264,7 @@
         <v>25</v>
       </c>
       <c r="G755" t="n">
-        <v>22.087043762207</v>
+        <v>22.0870399475098</v>
       </c>
       <c r="H755" t="n">
         <v>2775</v>
@@ -22380,7 +22380,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>20.8501644134521</v>
+        <v>20.8501663208008</v>
       </c>
       <c r="H759" t="n">
         <v>2625</v>
@@ -22409,7 +22409,7 @@
         <v>25</v>
       </c>
       <c r="G760" t="n">
-        <v>22.087043762207</v>
+        <v>22.0870399475098</v>
       </c>
       <c r="H760" t="n">
         <v>9750</v>
@@ -22670,7 +22670,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H769" t="n">
         <v>2025</v>
@@ -22699,7 +22699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H770" t="n">
         <v>2925</v>
@@ -22757,7 +22757,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>27.0345401763916</v>
+        <v>27.034538269043</v>
       </c>
       <c r="H772" t="n">
         <v>1200</v>
@@ -22815,7 +22815,7 @@
         <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>27.3879337310791</v>
+        <v>27.3879318237305</v>
       </c>
       <c r="H774" t="n">
         <v>2850</v>
@@ -22844,7 +22844,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G775" t="n">
-        <v>27.2112369537354</v>
+        <v>27.2112350463867</v>
       </c>
       <c r="H775" t="n">
         <v>3675</v>
@@ -22873,7 +22873,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>26.6811466217041</v>
+        <v>26.6811485290527</v>
       </c>
       <c r="H776" t="n">
         <v>2550</v>
@@ -22960,7 +22960,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>25.797664642334</v>
+        <v>25.7976665496826</v>
       </c>
       <c r="H779" t="n">
         <v>2400</v>
@@ -22989,7 +22989,7 @@
         <v>29</v>
       </c>
       <c r="G780" t="n">
-        <v>25.6209697723389</v>
+        <v>25.6209678649902</v>
       </c>
       <c r="H780" t="n">
         <v>2100</v>
@@ -23018,7 +23018,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>25.532621383667</v>
+        <v>25.5326194763184</v>
       </c>
       <c r="H781" t="n">
         <v>300</v>
@@ -23134,7 +23134,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>24.6491374969482</v>
+        <v>24.6491394042969</v>
       </c>
       <c r="H785" t="n">
         <v>2100</v>
@@ -23192,7 +23192,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G787" t="n">
-        <v>23.1472206115723</v>
+        <v>23.1472187042236</v>
       </c>
       <c r="H787" t="n">
         <v>1650</v>
@@ -23453,7 +23453,7 @@
         <v>28.5</v>
       </c>
       <c r="G796" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H796" t="n">
         <v>4875</v>
@@ -23482,7 +23482,7 @@
         <v>28.5</v>
       </c>
       <c r="G797" t="n">
-        <v>25.1792259216309</v>
+        <v>25.1792278289795</v>
       </c>
       <c r="H797" t="n">
         <v>1950</v>
@@ -23569,7 +23569,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>25.4490032196045</v>
+        <v>25.4490051269531</v>
       </c>
       <c r="H800" t="n">
         <v>2925</v>
@@ -23656,7 +23656,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>23.9202651977539</v>
+        <v>23.9202671051025</v>
       </c>
       <c r="H803" t="n">
         <v>2625</v>
@@ -23743,7 +23743,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H806" t="n">
         <v>2175</v>
@@ -23772,7 +23772,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H807" t="n">
         <v>75</v>
@@ -23801,7 +23801,7 @@
         <v>27</v>
       </c>
       <c r="G808" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>27</v>
       </c>
       <c r="G810" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H810" t="n">
         <v>75</v>
@@ -23888,7 +23888,7 @@
         <v>27</v>
       </c>
       <c r="G811" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H811" t="n">
         <v>150</v>
@@ -24062,7 +24062,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H817" t="n">
         <v>450</v>
@@ -24091,7 +24091,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H818" t="n">
         <v>375</v>
@@ -24236,7 +24236,7 @@
         <v>26.5</v>
       </c>
       <c r="G823" t="n">
-        <v>23.8303394317627</v>
+        <v>23.8303413391113</v>
       </c>
       <c r="H823" t="n">
         <v>825</v>
@@ -24265,7 +24265,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>23.5605640411377</v>
+        <v>23.5605621337891</v>
       </c>
       <c r="H824" t="n">
         <v>825</v>
@@ -24294,7 +24294,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G825" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H825" t="n">
         <v>300</v>
@@ -24323,7 +24323,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H826" t="n">
         <v>1500</v>
@@ -24439,7 +24439,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>23.5605640411377</v>
+        <v>23.5605621337891</v>
       </c>
       <c r="H830" t="n">
         <v>5925</v>
@@ -24700,7 +24700,7 @@
         <v>25.5</v>
       </c>
       <c r="G839" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H839" t="n">
         <v>300</v>
@@ -24729,7 +24729,7 @@
         <v>25.5</v>
       </c>
       <c r="G840" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H840" t="n">
         <v>300</v>
@@ -24758,7 +24758,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>22.661304473877</v>
+        <v>22.6613063812256</v>
       </c>
       <c r="H841" t="n">
         <v>150</v>
@@ -24787,7 +24787,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>22.1217498779297</v>
+        <v>22.1217517852783</v>
       </c>
       <c r="H842" t="n">
         <v>825</v>
@@ -24874,7 +24874,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>21.3124160766602</v>
+        <v>21.3124179840088</v>
       </c>
       <c r="H845" t="n">
         <v>825</v>
@@ -24903,7 +24903,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>21.6721210479736</v>
+        <v>21.6721229553223</v>
       </c>
       <c r="H846" t="n">
         <v>2550</v>
@@ -24932,7 +24932,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H847" t="n">
         <v>300</v>
@@ -24961,7 +24961,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H848" t="n">
         <v>2100</v>
@@ -24990,7 +24990,7 @@
         <v>25</v>
       </c>
       <c r="G849" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H849" t="n">
         <v>1725</v>
@@ -25048,7 +25048,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>21.4023456573486</v>
+        <v>21.4023418426514</v>
       </c>
       <c r="H851" t="n">
         <v>300</v>
@@ -25193,7 +25193,7 @@
         <v>22</v>
       </c>
       <c r="G856" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H856" t="n">
         <v>5700</v>
@@ -25222,7 +25222,7 @@
         <v>22</v>
       </c>
       <c r="G857" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H857" t="n">
         <v>2925</v>
@@ -25251,7 +25251,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>19.5139026641846</v>
+        <v>19.5139007568359</v>
       </c>
       <c r="H858" t="n">
         <v>1275</v>
@@ -25367,7 +25367,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>19.693754196167</v>
+        <v>19.6937522888184</v>
       </c>
       <c r="H862" t="n">
         <v>1500</v>
@@ -25425,7 +25425,7 @@
         <v>21.5</v>
       </c>
       <c r="G864" t="n">
-        <v>19.3340492248535</v>
+        <v>19.3340511322021</v>
       </c>
       <c r="H864" t="n">
         <v>300</v>
@@ -25541,7 +25541,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G868" t="n">
-        <v>21.6721210479736</v>
+        <v>21.6721229553223</v>
       </c>
       <c r="H868" t="n">
         <v>6300</v>
@@ -25570,7 +25570,7 @@
         <v>25</v>
       </c>
       <c r="G869" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H869" t="n">
         <v>5550</v>
@@ -25599,7 +25599,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>22.391529083252</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H870" t="n">
         <v>4050</v>
@@ -25657,7 +25657,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H872" t="n">
         <v>2475</v>
@@ -25686,7 +25686,7 @@
         <v>25.5</v>
       </c>
       <c r="G873" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H873" t="n">
         <v>1650</v>
@@ -25715,7 +25715,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H874" t="n">
         <v>2400</v>
@@ -25744,7 +25744,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>21.4922695159912</v>
+        <v>21.4922676086426</v>
       </c>
       <c r="H876" t="n">
         <v>7725</v>
@@ -25802,7 +25802,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>20.5030860900879</v>
+        <v>20.5030841827393</v>
       </c>
       <c r="H877" t="n">
         <v>6075</v>
@@ -25831,7 +25831,7 @@
         <v>23</v>
       </c>
       <c r="G878" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H878" t="n">
         <v>10800</v>
@@ -25860,7 +25860,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>20.5030860900879</v>
+        <v>20.5030841827393</v>
       </c>
       <c r="H879" t="n">
         <v>1200</v>
@@ -25947,7 +25947,7 @@
         <v>22</v>
       </c>
       <c r="G882" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H882" t="n">
         <v>750</v>
@@ -26034,7 +26034,7 @@
         <v>22</v>
       </c>
       <c r="G885" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H885" t="n">
         <v>11025</v>
@@ -26063,7 +26063,7 @@
         <v>22</v>
       </c>
       <c r="G886" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H886" t="n">
         <v>4800</v>
@@ -26092,7 +26092,7 @@
         <v>22</v>
       </c>
       <c r="G887" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H887" t="n">
         <v>3975</v>
@@ -26121,7 +26121,7 @@
         <v>22</v>
       </c>
       <c r="G888" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H888" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>22</v>
       </c>
       <c r="G889" t="n">
-        <v>19.7836780548096</v>
+        <v>19.7836799621582</v>
       </c>
       <c r="H889" t="n">
         <v>1050</v>
@@ -26179,7 +26179,7 @@
         <v>23</v>
       </c>
       <c r="G890" t="n">
-        <v>20.6829376220703</v>
+        <v>20.6829357147217</v>
       </c>
       <c r="H890" t="n">
         <v>31200</v>
@@ -26266,7 +26266,7 @@
         <v>27</v>
       </c>
       <c r="G893" t="n">
-        <v>24.2799701690674</v>
+        <v>24.2799682617188</v>
       </c>
       <c r="H893" t="n">
         <v>14100</v>
@@ -26411,7 +26411,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>23.110933303833</v>
+        <v>23.1109352111816</v>
       </c>
       <c r="H898" t="n">
         <v>26925</v>
@@ -26440,7 +26440,7 @@
         <v>25.5</v>
       </c>
       <c r="G899" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H899" t="n">
         <v>16275</v>
@@ -26469,7 +26469,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H900" t="n">
         <v>1125</v>
@@ -26498,7 +26498,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>22.5713787078857</v>
+        <v>22.5713806152344</v>
       </c>
       <c r="H901" t="n">
         <v>1725</v>
@@ -26643,7 +26643,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>22.1217498779297</v>
+        <v>22.1217517852783</v>
       </c>
       <c r="H906" t="n">
         <v>1200</v>
@@ -26672,7 +26672,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>22.391529083252</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H907" t="n">
         <v>3225</v>
@@ -26730,7 +26730,7 @@
         <v>25.5</v>
       </c>
       <c r="G909" t="n">
-        <v>22.931079864502</v>
+        <v>22.9310817718506</v>
       </c>
       <c r="H909" t="n">
         <v>300</v>
@@ -26759,7 +26759,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>22.8411560058594</v>
+        <v>22.841157913208</v>
       </c>
       <c r="H910" t="n">
         <v>2250</v>
@@ -26788,7 +26788,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H911" t="n">
         <v>225</v>
@@ -26875,7 +26875,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>22.391529083252</v>
+        <v>22.3915271759033</v>
       </c>
       <c r="H914" t="n">
         <v>75</v>
@@ -26962,7 +26962,7 @@
         <v>25</v>
       </c>
       <c r="G917" t="n">
-        <v>22.4814548492432</v>
+        <v>22.4814529418945</v>
       </c>
       <c r="H917" t="n">
         <v>1200</v>
@@ -26991,7 +26991,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H918" t="n">
         <v>5175</v>
@@ -27107,7 +27107,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G922" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H922" t="n">
         <v>1050</v>
@@ -27136,7 +27136,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>22.7512302398682</v>
+        <v>22.7512283325195</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>23.110933303833</v>
+        <v>23.1109352111816</v>
       </c>
       <c r="H925" t="n">
         <v>375</v>
@@ -27223,7 +27223,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>23.110933303833</v>
+        <v>23.1109352111816</v>
       </c>
       <c r="H926" t="n">
         <v>825</v>
@@ -27281,7 +27281,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>22.5713787078857</v>
+        <v>22.5713806152344</v>
       </c>
       <c r="H928" t="n">
         <v>300</v>
@@ -27397,7 +27397,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G932" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H932" t="n">
         <v>2625</v>
@@ -27426,7 +27426,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H933" t="n">
         <v>4500</v>
@@ -27513,7 +27513,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H936" t="n">
         <v>1875</v>
@@ -27716,7 +27716,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H943" t="n">
         <v>21450</v>
@@ -27745,7 +27745,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G944" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H948" t="n">
         <v>4950</v>
@@ -27890,7 +27890,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G949" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H949" t="n">
         <v>1650</v>
@@ -27919,7 +27919,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H950" t="n">
         <v>6600</v>
@@ -27948,7 +27948,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H951" t="n">
         <v>3300</v>
@@ -27977,7 +27977,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H952" t="n">
         <v>2325</v>
@@ -28035,7 +28035,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>26.7978935241699</v>
+        <v>26.7978916168213</v>
       </c>
       <c r="H954" t="n">
         <v>69075</v>
@@ -28064,7 +28064,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H955" t="n">
         <v>1050</v>
@@ -28093,7 +28093,7 @@
         <v>30.5</v>
       </c>
       <c r="G956" t="n">
-        <v>27.4273738861084</v>
+        <v>27.4273719787598</v>
       </c>
       <c r="H956" t="n">
         <v>3300</v>
@@ -28122,7 +28122,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>27.6971492767334</v>
+        <v>27.697151184082</v>
       </c>
       <c r="H957" t="n">
         <v>10950</v>
@@ -28151,7 +28151,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>28.4165592193604</v>
+        <v>28.4165573120117</v>
       </c>
       <c r="H958" t="n">
         <v>6825</v>
@@ -28180,7 +28180,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G959" t="n">
-        <v>29.3158149719238</v>
+        <v>29.3158130645752</v>
       </c>
       <c r="H959" t="n">
         <v>6600</v>
@@ -28238,7 +28238,7 @@
         <v>30.5</v>
       </c>
       <c r="G961" t="n">
-        <v>27.4273738861084</v>
+        <v>27.4273719787598</v>
       </c>
       <c r="H961" t="n">
         <v>5175</v>
@@ -28267,7 +28267,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G962" t="n">
-        <v>27.2475185394287</v>
+        <v>27.247522354126</v>
       </c>
       <c r="H962" t="n">
         <v>1950</v>
@@ -28441,7 +28441,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H968" t="n">
         <v>450</v>
@@ -28615,7 +28615,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H974" t="n">
         <v>75</v>
@@ -28644,7 +28644,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G976" t="n">
-        <v>25.9885597229004</v>
+        <v>25.9885578155518</v>
       </c>
       <c r="H976" t="n">
         <v>375</v>
@@ -28702,7 +28702,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H977" t="n">
         <v>750</v>
@@ -28731,7 +28731,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>26.1684112548828</v>
+        <v>26.1684131622314</v>
       </c>
       <c r="H978" t="n">
         <v>450</v>
@@ -28760,7 +28760,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>26.3482627868652</v>
+        <v>26.3482608795166</v>
       </c>
       <c r="H979" t="n">
         <v>4275</v>
@@ -28789,7 +28789,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H980" t="n">
         <v>6150</v>
@@ -28876,7 +28876,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>24.819522857666</v>
+        <v>24.8195247650146</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -29021,7 +29021,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>24.4598217010498</v>
+        <v>24.4598236083984</v>
       </c>
       <c r="H988" t="n">
         <v>675</v>
@@ -29224,7 +29224,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H995" t="n">
         <v>525</v>
@@ -29485,7 +29485,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>25.5389308929443</v>
+        <v>25.5389289855957</v>
       </c>
       <c r="H1004" t="n">
         <v>1050</v>
@@ -29601,7 +29601,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>24.6396732330322</v>
+        <v>24.6396713256836</v>
       </c>
       <c r="H1008" t="n">
         <v>17250</v>
@@ -29630,7 +29630,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>24.819522857666</v>
+        <v>24.8195247650146</v>
       </c>
       <c r="H1009" t="n">
         <v>750</v>
@@ -29775,7 +29775,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>26.6180419921875</v>
+        <v>26.6180400848389</v>
       </c>
       <c r="H1014" t="n">
         <v>2175</v>
@@ -29804,7 +29804,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1015" t="n">
-        <v>27.2475185394287</v>
+        <v>27.247522354126</v>
       </c>
       <c r="H1015" t="n">
         <v>2625</v>
@@ -29978,7 +29978,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>27.5172996520996</v>
+        <v>27.517297744751</v>
       </c>
       <c r="H1021" t="n">
         <v>5400</v>
@@ -30036,7 +30036,7 @@
         <v>31</v>
       </c>
       <c r="G1023" t="n">
-        <v>27.8770027160645</v>
+        <v>27.8770008087158</v>
       </c>
       <c r="H1023" t="n">
         <v>9450</v>
@@ -30065,7 +30065,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>28.1467781066895</v>
+        <v>28.1467800140381</v>
       </c>
       <c r="H1024" t="n">
         <v>1200</v>
@@ -30094,7 +30094,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>28.2367038726807</v>
+        <v>28.2367057800293</v>
       </c>
       <c r="H1025" t="n">
         <v>2475</v>
@@ -30123,7 +30123,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>29.4057426452637</v>
+        <v>29.405740737915</v>
       </c>
       <c r="H1026" t="n">
         <v>2025</v>
@@ -30181,7 +30181,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>29.0460357666016</v>
+        <v>29.0460376739502</v>
       </c>
       <c r="H1028" t="n">
         <v>4350</v>
@@ -30210,7 +30210,7 @@
         <v>33</v>
       </c>
       <c r="G1029" t="n">
-        <v>29.6755180358887</v>
+        <v>29.6755199432373</v>
       </c>
       <c r="H1029" t="n">
         <v>2700</v>
@@ -30268,7 +30268,7 @@
         <v>33.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1031" t="n">
         <v>1050</v>
@@ -30326,7 +30326,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>28.9561100006104</v>
+        <v>28.9561138153076</v>
       </c>
       <c r="H1033" t="n">
         <v>1575</v>
@@ -30355,7 +30355,7 @@
         <v>32.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>29.2258892059326</v>
+        <v>29.225887298584</v>
       </c>
       <c r="H1034" t="n">
         <v>1500</v>
@@ -30413,7 +30413,7 @@
         <v>32</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.7762603759766</v>
+        <v>28.7762584686279</v>
       </c>
       <c r="H1036" t="n">
         <v>3075</v>
@@ -30529,7 +30529,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1040" t="n">
-        <v>31.5639610290527</v>
+        <v>31.5639591217041</v>
       </c>
       <c r="H1040" t="n">
         <v>4425</v>
@@ -30558,7 +30558,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>31.8337364196777</v>
+        <v>31.8337383270264</v>
       </c>
       <c r="H1041" t="n">
         <v>7800</v>
@@ -30587,7 +30587,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2941837310791</v>
+        <v>31.2941818237305</v>
       </c>
       <c r="H1042" t="n">
         <v>4200</v>
@@ -30616,7 +30616,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>31.2941837310791</v>
+        <v>31.2941818237305</v>
       </c>
       <c r="H1043" t="n">
         <v>3750</v>
@@ -30645,7 +30645,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.2042579650879</v>
+        <v>31.2042541503906</v>
       </c>
       <c r="H1044" t="n">
         <v>1425</v>
@@ -30674,7 +30674,7 @@
         <v>33.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1045" t="n">
         <v>10575</v>
@@ -30732,7 +30732,7 @@
         <v>32</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7762603759766</v>
+        <v>28.7762584686279</v>
       </c>
       <c r="H1047" t="n">
         <v>14700</v>
@@ -30790,7 +30790,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1049" t="n">
         <v>2100</v>
@@ -30877,7 +30877,7 @@
         <v>33.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>30.1251449584961</v>
+        <v>30.1251468658447</v>
       </c>
       <c r="H1052" t="n">
         <v>675</v>
@@ -30906,7 +30906,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.2150688171387</v>
+        <v>30.2150707244873</v>
       </c>
       <c r="H1053" t="n">
         <v>525</v>
@@ -30935,7 +30935,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>30.3050003051758</v>
+        <v>30.3049983978271</v>
       </c>
       <c r="H1054" t="n">
         <v>1050</v>
@@ -31051,7 +31051,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1058" t="n">
-        <v>29.4057426452637</v>
+        <v>29.405740737915</v>
       </c>
       <c r="H1058" t="n">
         <v>1575</v>
@@ -31109,7 +31109,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1060" t="n">
-        <v>28.5064849853516</v>
+        <v>28.5064830780029</v>
       </c>
       <c r="H1060" t="n">
         <v>2175</v>
@@ -31138,7 +31138,7 @@
         <v>32</v>
       </c>
       <c r="G1061" t="n">
-        <v>28.7762603759766</v>
+        <v>28.7762584686279</v>
       </c>
       <c r="H1061" t="n">
         <v>95700</v>
@@ -31167,7 +31167,7 @@
         <v>32.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>29.2258892059326</v>
+        <v>29.225887298584</v>
       </c>
       <c r="H1062" t="n">
         <v>1050</v>
@@ -31196,7 +31196,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1063" t="n">
         <v>1650</v>
@@ -31312,7 +31312,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1067" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1067" t="n">
         <v>5775</v>
@@ -31341,7 +31341,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1068" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1068" t="n">
         <v>525</v>
@@ -31515,7 +31515,7 @@
         <v>32.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1074" t="n">
         <v>975</v>
@@ -31573,7 +31573,7 @@
         <v>31</v>
       </c>
       <c r="G1076" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1076" t="n">
         <v>3600</v>
@@ -31602,7 +31602,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1077" t="n">
         <v>450</v>
@@ -31631,7 +31631,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1078" t="n">
         <v>300</v>
@@ -31660,7 +31660,7 @@
         <v>31.5</v>
       </c>
       <c r="G1079" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1079" t="n">
         <v>1350</v>
@@ -31689,7 +31689,7 @@
         <v>31</v>
       </c>
       <c r="G1080" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1080" t="n">
         <v>14100</v>
@@ -31718,7 +31718,7 @@
         <v>31.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1081" t="n">
         <v>7125</v>
@@ -31776,7 +31776,7 @@
         <v>31.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1083" t="n">
         <v>6450</v>
@@ -31863,7 +31863,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1086" t="n">
         <v>2100</v>
@@ -31979,7 +31979,7 @@
         <v>31.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1090" t="n">
         <v>150</v>
@@ -32008,7 +32008,7 @@
         <v>31.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1091" t="n">
         <v>75</v>
@@ -32037,7 +32037,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1092" t="n">
         <v>450</v>
@@ -32124,7 +32124,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1095" t="n">
         <v>600</v>
@@ -32153,7 +32153,7 @@
         <v>32.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1096" t="n">
         <v>2550</v>
@@ -32182,7 +32182,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1097" t="n">
         <v>2400</v>
@@ -32704,7 +32704,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1115" t="n">
         <v>1069</v>
@@ -32762,7 +32762,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1117" t="n">
         <v>874</v>
@@ -32791,7 +32791,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1118" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1118" t="n">
         <v>404</v>
@@ -32820,7 +32820,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1119" t="n">
         <v>1426</v>
@@ -32849,7 +32849,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1120" t="n">
         <v>683</v>
@@ -32907,7 +32907,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1122" t="n">
         <v>791</v>
@@ -33139,7 +33139,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1130" t="n">
         <v>147</v>
@@ -33197,7 +33197,7 @@
         <v>32.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1132" t="n">
         <v>235</v>
@@ -33226,7 +33226,7 @@
         <v>32.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1133" t="n">
         <v>397</v>
@@ -33255,7 +33255,7 @@
         <v>32.5</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1134" t="n">
         <v>300</v>
@@ -33458,7 +33458,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1141" t="n">
         <v>1405</v>
@@ -33487,7 +33487,7 @@
         <v>31</v>
       </c>
       <c r="G1142" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1142" t="n">
         <v>1568</v>
@@ -33574,7 +33574,7 @@
         <v>31</v>
       </c>
       <c r="G1145" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1145" t="n">
         <v>240</v>
@@ -33690,7 +33690,7 @@
         <v>31</v>
       </c>
       <c r="G1149" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1149" t="n">
         <v>1616</v>
@@ -33748,7 +33748,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1151" t="n">
         <v>773</v>
@@ -33777,7 +33777,7 @@
         <v>31</v>
       </c>
       <c r="G1152" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1152" t="n">
         <v>442</v>
@@ -33806,7 +33806,7 @@
         <v>31</v>
       </c>
       <c r="G1153" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1153" t="n">
         <v>365</v>
@@ -34009,7 +34009,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.8786144256592</v>
+        <v>26.8786125183105</v>
       </c>
       <c r="H1160" t="n">
         <v>1105</v>
@@ -34096,7 +34096,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1163" t="n">
         <v>1128</v>
@@ -34125,7 +34125,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1164" t="n">
         <v>5262</v>
@@ -34212,7 +34212,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1167" t="n">
         <v>1240</v>
@@ -34241,7 +34241,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1168" t="n">
         <v>7918</v>
@@ -34270,7 +34270,7 @@
         <v>27.5</v>
       </c>
       <c r="G1169" t="n">
-        <v>25.3137626647949</v>
+        <v>25.3137607574463</v>
       </c>
       <c r="H1169" t="n">
         <v>3413</v>
@@ -34299,7 +34299,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1170" t="n">
         <v>1331</v>
@@ -34328,7 +34328,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1171" t="n">
         <v>1864</v>
@@ -34357,7 +34357,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1172" t="n">
         <v>10192</v>
@@ -34386,7 +34386,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1173" t="n">
         <v>27679</v>
@@ -34415,7 +34415,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1174" t="n">
         <v>300</v>
@@ -34444,7 +34444,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1175" t="n">
         <v>596</v>
@@ -34473,7 +34473,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1176" t="n">
         <v>119</v>
@@ -34502,7 +34502,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1177" t="n">
         <v>572</v>
@@ -34531,7 +34531,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1178" t="n">
         <v>572</v>
@@ -34647,7 +34647,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.1966133117676</v>
+        <v>23.1966114044189</v>
       </c>
       <c r="H1182" t="n">
         <v>16419</v>
@@ -34676,7 +34676,7 @@
         <v>25</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0125102996826</v>
+        <v>23.0125122070312</v>
       </c>
       <c r="H1183" t="n">
         <v>6634</v>
@@ -34734,7 +34734,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1185" t="n">
         <v>3901</v>
@@ -34763,7 +34763,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1186" t="n">
         <v>4535</v>
@@ -34792,7 +34792,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1187" t="n">
         <v>1957</v>
@@ -34821,7 +34821,7 @@
         <v>26.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1188" t="n">
         <v>550</v>
@@ -34879,7 +34879,7 @@
         <v>26</v>
       </c>
       <c r="G1190" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1190" t="n">
         <v>3364</v>
@@ -34966,7 +34966,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.1171112060547</v>
+        <v>24.1171131134033</v>
       </c>
       <c r="H1193" t="n">
         <v>5553</v>
@@ -34995,7 +34995,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1194" t="n">
         <v>6387</v>
@@ -35024,7 +35024,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1195" t="n">
         <v>15303</v>
@@ -35169,7 +35169,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.9455642700195</v>
+        <v>24.9455623626709</v>
       </c>
       <c r="H1200" t="n">
         <v>2435</v>
@@ -35198,7 +35198,7 @@
         <v>27</v>
       </c>
       <c r="G1201" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1201" t="n">
         <v>345</v>
@@ -35256,7 +35256,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1203" t="n">
         <v>250</v>
@@ -35285,7 +35285,7 @@
         <v>26.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3932609558105</v>
+        <v>24.3932628631592</v>
       </c>
       <c r="H1204" t="n">
         <v>2078</v>
@@ -35401,7 +35401,7 @@
         <v>27</v>
       </c>
       <c r="G1208" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1208" t="n">
         <v>6977</v>
@@ -35575,7 +35575,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1214" t="n">
         <v>1681</v>
@@ -35604,7 +35604,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>26.8786144256592</v>
+        <v>26.8786125183105</v>
       </c>
       <c r="H1215" t="n">
         <v>2568</v>
@@ -35836,7 +35836,7 @@
         <v>29</v>
       </c>
       <c r="G1223" t="n">
-        <v>26.6945133209229</v>
+        <v>26.6945152282715</v>
       </c>
       <c r="H1223" t="n">
         <v>4183</v>
@@ -36010,7 +36010,7 @@
         <v>28</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.7740135192871</v>
+        <v>25.7740116119385</v>
       </c>
       <c r="H1229" t="n">
         <v>4634</v>
@@ -36097,7 +36097,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1232" t="n">
         <v>4851</v>
@@ -36155,7 +36155,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1234" t="n">
         <v>2409</v>
@@ -36184,7 +36184,7 @@
         <v>28</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.7740135192871</v>
+        <v>25.7740116119385</v>
       </c>
       <c r="H1235" t="n">
         <v>2267</v>
@@ -36213,7 +36213,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1236" t="n">
         <v>5154</v>
@@ -36329,7 +36329,7 @@
         <v>27.5</v>
       </c>
       <c r="G1240" t="n">
-        <v>25.3137626647949</v>
+        <v>25.3137607574463</v>
       </c>
       <c r="H1240" t="n">
         <v>499</v>
@@ -36387,7 +36387,7 @@
         <v>27</v>
       </c>
       <c r="G1242" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1242" t="n">
         <v>4303</v>
@@ -36416,7 +36416,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1243" t="n">
         <v>11050</v>
@@ -36445,7 +36445,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1244" t="n">
-        <v>25.0376148223877</v>
+        <v>25.0376129150391</v>
       </c>
       <c r="H1244" t="n">
         <v>11217</v>
@@ -36474,7 +36474,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1245" t="n">
         <v>11733</v>
@@ -36503,7 +36503,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1246" t="n">
         <v>16021</v>
@@ -36532,7 +36532,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1247" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1247" t="n">
         <v>8843</v>
@@ -36561,7 +36561,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1248" t="n">
         <v>10327</v>
@@ -36590,7 +36590,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1249" t="n">
-        <v>24.669412612915</v>
+        <v>24.6694107055664</v>
       </c>
       <c r="H1249" t="n">
         <v>7712</v>
@@ -36619,7 +36619,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>24.7614631652832</v>
+        <v>24.7614612579346</v>
       </c>
       <c r="H1250" t="n">
         <v>7483</v>
@@ -36648,7 +36648,7 @@
         <v>27</v>
       </c>
       <c r="G1251" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1251" t="n">
         <v>2164</v>
@@ -36677,7 +36677,7 @@
         <v>27</v>
       </c>
       <c r="G1252" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1252" t="n">
         <v>1117</v>
@@ -36764,7 +36764,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1255" t="n">
         <v>3149</v>
@@ -36793,7 +36793,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1256" t="n">
         <v>3291</v>
@@ -36822,7 +36822,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>24.5773620605469</v>
+        <v>24.5773639678955</v>
       </c>
       <c r="H1257" t="n">
         <v>2319</v>
@@ -36880,7 +36880,7 @@
         <v>26</v>
       </c>
       <c r="G1259" t="n">
-        <v>23.9330139160156</v>
+        <v>23.933012008667</v>
       </c>
       <c r="H1259" t="n">
         <v>15177</v>
@@ -36938,7 +36938,7 @@
         <v>27</v>
       </c>
       <c r="G1261" t="n">
-        <v>24.8535118103027</v>
+        <v>24.8535137176514</v>
       </c>
       <c r="H1261" t="n">
         <v>4013</v>
@@ -36967,7 +36967,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>25.4978656768799</v>
+        <v>25.4978637695312</v>
       </c>
       <c r="H1262" t="n">
         <v>10735</v>
@@ -36996,7 +36996,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>25.9581127166748</v>
+        <v>25.9581146240234</v>
       </c>
       <c r="H1263" t="n">
         <v>5803</v>
@@ -37112,7 +37112,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>27.0627117156982</v>
+        <v>27.0627136230469</v>
       </c>
       <c r="H1267" t="n">
         <v>12740</v>
@@ -37199,7 +37199,7 @@
         <v>31</v>
       </c>
       <c r="G1270" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1270" t="n">
         <v>1818</v>
@@ -37257,7 +37257,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1272" t="n">
         <v>50004</v>
@@ -37286,7 +37286,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1273" t="n">
-        <v>28.7196140289307</v>
+        <v>28.7196159362793</v>
       </c>
       <c r="H1273" t="n">
         <v>8005</v>
@@ -37315,7 +37315,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1274" t="n">
-        <v>28.903715133667</v>
+        <v>28.9037132263184</v>
       </c>
       <c r="H1274" t="n">
         <v>4136</v>
@@ -37373,7 +37373,7 @@
         <v>31.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>28.9957637786865</v>
+        <v>28.9957656860352</v>
       </c>
       <c r="H1276" t="n">
         <v>13340</v>
@@ -37489,7 +37489,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1280" t="n">
-        <v>29.6401176452637</v>
+        <v>29.640115737915</v>
       </c>
       <c r="H1280" t="n">
         <v>2808</v>
@@ -37518,7 +37518,7 @@
         <v>32.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1281" t="n">
         <v>5505</v>
@@ -37547,7 +37547,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1282" t="n">
         <v>10071</v>
@@ -37576,7 +37576,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1283" t="n">
         <v>7498</v>
@@ -37721,7 +37721,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.020866394043</v>
+        <v>31.0208644866943</v>
       </c>
       <c r="H1288" t="n">
         <v>4493</v>
@@ -37808,7 +37808,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.7447166442871</v>
+        <v>30.7447147369385</v>
       </c>
       <c r="H1291" t="n">
         <v>10264</v>
@@ -38040,7 +38040,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1299" t="n">
-        <v>30.9288120269775</v>
+        <v>30.9288139343262</v>
       </c>
       <c r="H1299" t="n">
         <v>10536</v>
@@ -38098,7 +38098,7 @@
         <v>33.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>30.836763381958</v>
+        <v>30.8367652893066</v>
       </c>
       <c r="H1301" t="n">
         <v>18694</v>
@@ -38185,7 +38185,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1304" t="n">
         <v>2779</v>
@@ -38243,7 +38243,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>30.5606155395508</v>
+        <v>30.5606174468994</v>
       </c>
       <c r="H1306" t="n">
         <v>1787</v>
@@ -38330,7 +38330,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>29.8242149353027</v>
+        <v>29.8242168426514</v>
       </c>
       <c r="H1309" t="n">
         <v>8681</v>
@@ -38388,7 +38388,7 @@
         <v>31</v>
       </c>
       <c r="G1311" t="n">
-        <v>28.5355167388916</v>
+        <v>28.535514831543</v>
       </c>
       <c r="H1311" t="n">
         <v>14200</v>
@@ -38475,7 +38475,7 @@
         <v>32.5</v>
       </c>
       <c r="G1314" t="n">
-        <v>29.9162654876709</v>
+        <v>29.9162635803223</v>
       </c>
       <c r="H1314" t="n">
         <v>4455</v>
@@ -38504,7 +38504,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>30.1003646850586</v>
+        <v>30.1003665924072</v>
       </c>
       <c r="H1315" t="n">
         <v>12589</v>
@@ -38562,7 +38562,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.095422744751</v>
+        <v>29.0954246520996</v>
       </c>
       <c r="H1317" t="n">
         <v>6125</v>
@@ -38765,7 +38765,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1324" t="n">
         <v>12844</v>
@@ -38823,7 +38823,7 @@
         <v>29</v>
       </c>
       <c r="G1326" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1326" t="n">
         <v>9621</v>
@@ -38852,7 +38852,7 @@
         <v>29.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1327" t="n">
         <v>46167</v>
@@ -38881,7 +38881,7 @@
         <v>29.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1328" t="n">
         <v>3959</v>
@@ -38997,7 +38997,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1332" t="n">
         <v>24982</v>
@@ -39026,7 +39026,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1333" t="n">
         <v>8601</v>
@@ -39055,7 +39055,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1334" t="n">
         <v>5309</v>
@@ -39084,7 +39084,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1335" t="n">
         <v>21621</v>
@@ -39113,7 +39113,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1336" t="n">
         <v>16181</v>
@@ -39142,7 +39142,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1337" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1337" t="n">
         <v>6822</v>
@@ -39171,7 +39171,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1338" t="n">
         <v>3455</v>
@@ -39200,7 +39200,7 @@
         <v>33</v>
       </c>
       <c r="G1339" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1339" t="n">
         <v>5494</v>
@@ -39229,7 +39229,7 @@
         <v>33</v>
       </c>
       <c r="G1340" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1340" t="n">
         <v>13157</v>
@@ -39258,7 +39258,7 @@
         <v>33</v>
       </c>
       <c r="G1341" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1341" t="n">
         <v>2965</v>
@@ -39287,7 +39287,7 @@
         <v>33</v>
       </c>
       <c r="G1342" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1342" t="n">
         <v>1570</v>
@@ -39345,7 +39345,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1344" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1344" t="n">
         <v>2849</v>
@@ -39374,7 +39374,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1345" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1345" t="n">
         <v>4077</v>
@@ -39461,7 +39461,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1348" t="n">
         <v>3503</v>
@@ -39548,7 +39548,7 @@
         <v>33.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1351" t="n">
         <v>3621</v>
@@ -39693,7 +39693,7 @@
         <v>33.5</v>
       </c>
       <c r="G1356" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1356" t="n">
         <v>1074</v>
@@ -39722,7 +39722,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1357" t="n">
         <v>1555</v>
@@ -39896,7 +39896,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>33.7851448059082</v>
+        <v>33.7851486206055</v>
       </c>
       <c r="H1363" t="n">
         <v>12779</v>
@@ -39925,7 +39925,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1364" t="n">
         <v>7910</v>
@@ -40012,7 +40012,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1367" t="n">
         <v>2625</v>
@@ -40157,7 +40157,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1372" t="n">
         <v>2528</v>
@@ -40186,7 +40186,7 @@
         <v>33.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1373" t="n">
         <v>5370</v>
@@ -40273,7 +40273,7 @@
         <v>32.5</v>
       </c>
       <c r="G1376" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1376" t="n">
         <v>9183</v>
@@ -40302,7 +40302,7 @@
         <v>32.5</v>
       </c>
       <c r="G1377" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1377" t="n">
         <v>4352</v>
@@ -40331,7 +40331,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>31.0095996856689</v>
+        <v>31.0095977783203</v>
       </c>
       <c r="H1378" t="n">
         <v>1704</v>
@@ -40360,7 +40360,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1379" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1379" t="n">
         <v>553</v>
@@ -40389,7 +40389,7 @@
         <v>32.5</v>
       </c>
       <c r="G1380" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1380" t="n">
         <v>732</v>
@@ -40476,7 +40476,7 @@
         <v>32.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1383" t="n">
         <v>1248</v>
@@ -40505,7 +40505,7 @@
         <v>32.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>31.1053047180176</v>
+        <v>31.1053066253662</v>
       </c>
       <c r="H1384" t="n">
         <v>1301</v>
@@ -40563,7 +40563,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1386" t="n">
         <v>1483</v>
@@ -40592,7 +40592,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1387" t="n">
         <v>3214</v>
@@ -40708,7 +40708,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1391" t="n">
         <v>3859</v>
@@ -40737,7 +40737,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1392" t="n">
         <v>1387</v>
@@ -40766,7 +40766,7 @@
         <v>33</v>
       </c>
       <c r="G1393" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1393" t="n">
         <v>569</v>
@@ -40795,7 +40795,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>31.2010135650635</v>
+        <v>31.2010116577148</v>
       </c>
       <c r="H1394" t="n">
         <v>1704</v>
@@ -40940,7 +40940,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1399" t="n">
         <v>2679</v>
@@ -40998,7 +40998,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1401" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1401" t="n">
         <v>4340</v>
@@ -41027,7 +41027,7 @@
         <v>33</v>
       </c>
       <c r="G1402" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1402" t="n">
         <v>3944</v>
@@ -41056,7 +41056,7 @@
         <v>33</v>
       </c>
       <c r="G1403" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1403" t="n">
         <v>1728</v>
@@ -41085,7 +41085,7 @@
         <v>33</v>
       </c>
       <c r="G1404" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1404" t="n">
         <v>1317</v>
@@ -41114,7 +41114,7 @@
         <v>33</v>
       </c>
       <c r="G1405" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1405" t="n">
         <v>2062</v>
@@ -41143,7 +41143,7 @@
         <v>33</v>
       </c>
       <c r="G1406" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1406" t="n">
         <v>1291</v>
@@ -41230,7 +41230,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1409" t="n">
-        <v>32.6366424560547</v>
+        <v>32.636646270752</v>
       </c>
       <c r="H1409" t="n">
         <v>4625</v>
@@ -41346,7 +41346,7 @@
         <v>33.5</v>
       </c>
       <c r="G1413" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1413" t="n">
         <v>2410</v>
@@ -41375,7 +41375,7 @@
         <v>33.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1414" t="n">
         <v>31931</v>
@@ -41404,7 +41404,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1415" t="n">
         <v>13442</v>
@@ -41549,7 +41549,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1420" t="n">
         <v>2989</v>
@@ -41607,7 +41607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1422" t="n">
         <v>2861</v>
@@ -41636,7 +41636,7 @@
         <v>33.5</v>
       </c>
       <c r="G1423" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1423" t="n">
         <v>3892</v>
@@ -41752,7 +41752,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1427" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1427" t="n">
         <v>2872</v>
@@ -41781,7 +41781,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>31.6795558929443</v>
+        <v>31.679557800293</v>
       </c>
       <c r="H1428" t="n">
         <v>3471</v>
@@ -41810,7 +41810,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1429" t="n">
         <v>457</v>
@@ -41839,7 +41839,7 @@
         <v>33.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1430" t="n">
         <v>4731</v>
@@ -41868,7 +41868,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1431" t="n">
-        <v>31.7752647399902</v>
+        <v>31.7752666473389</v>
       </c>
       <c r="H1431" t="n">
         <v>1418</v>
@@ -41984,7 +41984,7 @@
         <v>33</v>
       </c>
       <c r="G1435" t="n">
-        <v>31.5838508605957</v>
+        <v>31.5838470458984</v>
       </c>
       <c r="H1435" t="n">
         <v>1616</v>
@@ -42013,7 +42013,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1436" t="n">
         <v>3582</v>
@@ -42042,7 +42042,7 @@
         <v>33.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>32.0623893737793</v>
+        <v>32.0623931884766</v>
       </c>
       <c r="H1437" t="n">
         <v>2662</v>
@@ -42100,7 +42100,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1439" t="n">
         <v>198</v>
@@ -42129,7 +42129,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>31.8709754943848</v>
+        <v>31.8709735870361</v>
       </c>
       <c r="H1440" t="n">
         <v>1144</v>
@@ -42245,7 +42245,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1444" t="n">
         <v>688</v>
@@ -42274,7 +42274,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>31.296724319458</v>
+        <v>31.2967224121094</v>
       </c>
       <c r="H1445" t="n">
         <v>1252</v>
@@ -42332,7 +42332,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1447" t="n">
         <v>4488</v>
@@ -42448,7 +42448,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1451" t="n">
         <v>2754</v>
@@ -42477,7 +42477,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1452" t="n">
         <v>793</v>
@@ -42535,7 +42535,7 @@
         <v>29.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1454" t="n">
         <v>4612</v>
@@ -42622,7 +42622,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1457" t="n">
         <v>3819</v>
@@ -42709,7 +42709,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1460" t="n">
         <v>8292</v>
@@ -42796,7 +42796,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1463" t="n">
         <v>3283</v>
@@ -43028,7 +43028,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1471" t="n">
         <v>1571</v>
@@ -43260,7 +43260,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1479" t="n">
-        <v>29.7653846740723</v>
+        <v>29.7653865814209</v>
       </c>
       <c r="H1479" t="n">
         <v>13</v>
@@ -43347,7 +43347,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>29.9568004608154</v>
+        <v>29.9568023681641</v>
       </c>
       <c r="H1482" t="n">
         <v>5922</v>
@@ -43579,7 +43579,7 @@
         <v>29</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1490" t="n">
         <v>3936</v>
@@ -43608,7 +43608,7 @@
         <v>29</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1491" t="n">
         <v>9516</v>
@@ -43637,7 +43637,7 @@
         <v>29</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1492" t="n">
         <v>12</v>
@@ -43695,7 +43695,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1494" t="n">
         <v>3670</v>
@@ -43782,7 +43782,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>27.8512134552002</v>
+        <v>27.8512115478516</v>
       </c>
       <c r="H1497" t="n">
         <v>1307</v>
@@ -43811,7 +43811,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1498" t="n">
         <v>4115</v>
@@ -43956,7 +43956,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1503" t="n">
-        <v>27.6597957611084</v>
+        <v>27.6597938537598</v>
       </c>
       <c r="H1503" t="n">
         <v>1545</v>
@@ -44043,7 +44043,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>28.5211734771729</v>
+        <v>28.5211715698242</v>
       </c>
       <c r="H1506" t="n">
         <v>2072</v>
@@ -44072,7 +44072,7 @@
         <v>29.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>28.2340488433838</v>
+        <v>28.2340469360352</v>
       </c>
       <c r="H1507" t="n">
         <v>211</v>
@@ -44101,7 +44101,7 @@
         <v>29</v>
       </c>
       <c r="G1508" t="n">
-        <v>27.7555027008057</v>
+        <v>27.7555046081543</v>
       </c>
       <c r="H1508" t="n">
         <v>907</v>
@@ -44275,7 +44275,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>26.6069984436035</v>
+        <v>26.6070003509521</v>
       </c>
       <c r="H1514" t="n">
         <v>1628</v>
@@ -44333,7 +44333,7 @@
         <v>27</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.8413314819336</v>
+ 